--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/035c350e73bda838/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="8_{B8CB855E-6BA8-449C-BA84-C63F4CECB145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D056D7E-2EE9-425B-86E7-3EEBFC2E2A3A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2727545E-6906-4B8A-B5DC-3E94DC1C2B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="630">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -1870,10 +1870,6 @@
     <t>深堀町</t>
   </si>
   <si>
-    <t xml:space="preserve">	柏木町</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>杉並町</t>
   </si>
   <si>
@@ -1930,13 +1926,631 @@
   </si>
   <si>
     <t>函館どつく前</t>
+  </si>
+  <si>
+    <t>柏木町</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北海道</t>
+    <rPh sb="0" eb="3">
+      <t>ホッカイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青森</t>
+  </si>
+  <si>
+    <t>青森</t>
+    <rPh sb="0" eb="2">
+      <t>アオモリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>津軽湯の沢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>碇ヶ関</t>
+  </si>
+  <si>
+    <t>長峰</t>
+  </si>
+  <si>
+    <t>大鰐温泉</t>
+  </si>
+  <si>
+    <t>石川（ＪＲ）</t>
+  </si>
+  <si>
+    <t>弘前</t>
+  </si>
+  <si>
+    <t>撫牛子</t>
+  </si>
+  <si>
+    <t>川部</t>
+  </si>
+  <si>
+    <t>北常盤</t>
+  </si>
+  <si>
+    <t>浪岡</t>
+  </si>
+  <si>
+    <t>大釈迦</t>
+  </si>
+  <si>
+    <t>鶴ヶ坂</t>
+  </si>
+  <si>
+    <t>津軽新城</t>
+  </si>
+  <si>
+    <t>新青森</t>
+  </si>
+  <si>
+    <t>奥羽本線、五能線、弘南鉄道弘南線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゴノウセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウナンテツドウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>コウナンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、五能線</t>
+    <rPh sb="0" eb="2">
+      <t>オウウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、津軽線、青い森鉄道</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ツガルセン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モリテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大間越</t>
+  </si>
+  <si>
+    <t>五能線</t>
+    <rPh sb="0" eb="3">
+      <t>ゴノウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白神岳登山口</t>
+  </si>
+  <si>
+    <t>松神</t>
+  </si>
+  <si>
+    <t>十二湖</t>
+  </si>
+  <si>
+    <t>陸奥岩崎</t>
+  </si>
+  <si>
+    <t>陸奥沢辺</t>
+  </si>
+  <si>
+    <t>ウェスパ椿山</t>
+  </si>
+  <si>
+    <t>艫作</t>
+  </si>
+  <si>
+    <t>横磯</t>
+  </si>
+  <si>
+    <t>深浦</t>
+  </si>
+  <si>
+    <t>広戸</t>
+  </si>
+  <si>
+    <t>追良瀬</t>
+  </si>
+  <si>
+    <t>驫木</t>
+  </si>
+  <si>
+    <t>風合瀬</t>
+  </si>
+  <si>
+    <t>大戸瀬</t>
+  </si>
+  <si>
+    <t>千畳敷（青森）</t>
+  </si>
+  <si>
+    <t>北金ヶ沢</t>
+  </si>
+  <si>
+    <t>陸奥柳田</t>
+  </si>
+  <si>
+    <t>陸奥赤石</t>
+  </si>
+  <si>
+    <t>鰺ヶ沢</t>
+  </si>
+  <si>
+    <t>鳴沢</t>
+  </si>
+  <si>
+    <t>越水</t>
+  </si>
+  <si>
+    <t>陸奥森田</t>
+  </si>
+  <si>
+    <t>中田（青森）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木造</t>
+  </si>
+  <si>
+    <t>五所川原</t>
+  </si>
+  <si>
+    <t>陸奥鶴田</t>
+  </si>
+  <si>
+    <t>鶴泊</t>
+  </si>
+  <si>
+    <t>板柳</t>
+  </si>
+  <si>
+    <t>林崎</t>
+  </si>
+  <si>
+    <t>藤崎（青森）</t>
+  </si>
+  <si>
+    <t>野辺地</t>
+  </si>
+  <si>
+    <t>北野辺地</t>
+  </si>
+  <si>
+    <t>有戸</t>
+  </si>
+  <si>
+    <t>吹越</t>
+  </si>
+  <si>
+    <t>陸奥横浜</t>
+    <rPh sb="0" eb="2">
+      <t>ムツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有畑</t>
+  </si>
+  <si>
+    <t>近川</t>
+  </si>
+  <si>
+    <t>金谷沢</t>
+  </si>
+  <si>
+    <t>赤川</t>
+  </si>
+  <si>
+    <t>下北</t>
+  </si>
+  <si>
+    <t>大湊</t>
+  </si>
+  <si>
+    <t>大湊線</t>
+    <rPh sb="0" eb="3">
+      <t>オオミナトセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大湊線、青い森鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>オオミナトセン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>モリテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>油川</t>
+  </si>
+  <si>
+    <t>奥内</t>
+  </si>
+  <si>
+    <t>左堰</t>
+  </si>
+  <si>
+    <t>後潟</t>
+  </si>
+  <si>
+    <t>中沢</t>
+  </si>
+  <si>
+    <t>蓬田</t>
+  </si>
+  <si>
+    <t>郷沢</t>
+  </si>
+  <si>
+    <t>瀬辺地</t>
+  </si>
+  <si>
+    <t>蟹田</t>
+  </si>
+  <si>
+    <t>中小国</t>
+  </si>
+  <si>
+    <t>津軽二股</t>
+  </si>
+  <si>
+    <t>大川平</t>
+  </si>
+  <si>
+    <t>今別</t>
+  </si>
+  <si>
+    <t>津軽浜名</t>
+  </si>
+  <si>
+    <t>三厩</t>
+  </si>
+  <si>
+    <t>津軽線</t>
+  </si>
+  <si>
+    <t>八戸</t>
+  </si>
+  <si>
+    <t>七戸十和田</t>
+  </si>
+  <si>
+    <t>奥津軽いまべつ</t>
+  </si>
+  <si>
+    <t>東北新幹線</t>
+  </si>
+  <si>
+    <t>北海道新幹線</t>
+  </si>
+  <si>
+    <t>奥羽本線、東北新幹線、北海道新幹線</t>
+  </si>
+  <si>
+    <t>東北新幹線、八戸線、青い森鉄道線</t>
+  </si>
+  <si>
+    <t>長苗代</t>
+  </si>
+  <si>
+    <t>本八戸</t>
+  </si>
+  <si>
+    <t>小中野</t>
+  </si>
+  <si>
+    <t>陸奥湊</t>
+  </si>
+  <si>
+    <t>白銀</t>
+  </si>
+  <si>
+    <t>鮫</t>
+  </si>
+  <si>
+    <t>陸奥白浜</t>
+  </si>
+  <si>
+    <t>種差海岸</t>
+  </si>
+  <si>
+    <t>大久喜</t>
+  </si>
+  <si>
+    <t>金浜</t>
+  </si>
+  <si>
+    <t>大蛇</t>
+  </si>
+  <si>
+    <t>階上</t>
+  </si>
+  <si>
+    <t>八戸線</t>
+  </si>
+  <si>
+    <t>津軽宮田</t>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大平</t>
+    <rPh sb="0" eb="2">
+      <t>オオダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弘南鉄道弘南線</t>
+  </si>
+  <si>
+    <t>弘前東高前</t>
+  </si>
+  <si>
+    <t>運動公園前（青森）</t>
+  </si>
+  <si>
+    <t>新里（青森）</t>
+  </si>
+  <si>
+    <t>館田</t>
+  </si>
+  <si>
+    <t>平賀</t>
+  </si>
+  <si>
+    <t>柏農高校前</t>
+  </si>
+  <si>
+    <t>津軽尾上</t>
+  </si>
+  <si>
+    <t>尾上高校前</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>田んぼアート</t>
+  </si>
+  <si>
+    <t>田舎館</t>
+  </si>
+  <si>
+    <t>境松</t>
+  </si>
+  <si>
+    <t>黒石（青森）</t>
+  </si>
+  <si>
+    <t>弘南鉄道大鰐線</t>
+  </si>
+  <si>
+    <t>大鰐</t>
+  </si>
+  <si>
+    <t>宿川原</t>
+  </si>
+  <si>
+    <t>鯖石</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石川プール前</t>
+  </si>
+  <si>
+    <t>石川（弘南鉄道）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>義塾高校前</t>
+  </si>
+  <si>
+    <t>津軽大沢</t>
+  </si>
+  <si>
+    <t>松木平</t>
+  </si>
+  <si>
+    <t>小栗山</t>
+  </si>
+  <si>
+    <t>千年</t>
+  </si>
+  <si>
+    <t>聖愛中高前</t>
+  </si>
+  <si>
+    <t>弘前学院大前</t>
+  </si>
+  <si>
+    <t>弘高下</t>
+  </si>
+  <si>
+    <t>中央弘前</t>
+  </si>
+  <si>
+    <t>津軽五所川原</t>
+  </si>
+  <si>
+    <t>津軽鉄道</t>
+    <rPh sb="0" eb="4">
+      <t>ツガルテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>十川（青森）</t>
+  </si>
+  <si>
+    <t>五農校前</t>
+  </si>
+  <si>
+    <t>津軽飯詰</t>
+  </si>
+  <si>
+    <t>毘沙門</t>
+  </si>
+  <si>
+    <t>嘉瀬</t>
+  </si>
+  <si>
+    <t>金木</t>
+  </si>
+  <si>
+    <t>芦野公園</t>
+  </si>
+  <si>
+    <t>川倉</t>
+  </si>
+  <si>
+    <t>大沢内</t>
+  </si>
+  <si>
+    <t>深郷田</t>
+  </si>
+  <si>
+    <t>津軽中里</t>
+  </si>
+  <si>
+    <t>目時</t>
+  </si>
+  <si>
+    <t>ＩＧＲいわて銀河鉄道、青い森鉄道</t>
+    <rPh sb="11" eb="12">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モリテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三戸</t>
+  </si>
+  <si>
+    <t>諏訪ノ平</t>
+  </si>
+  <si>
+    <t>剣吉</t>
+  </si>
+  <si>
+    <t>苫米地</t>
+  </si>
+  <si>
+    <t>北高岩</t>
+  </si>
+  <si>
+    <t>陸奥市川</t>
+  </si>
+  <si>
+    <t>下田（青森）</t>
+  </si>
+  <si>
+    <t>向山</t>
+  </si>
+  <si>
+    <t>三沢（青森）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小川原</t>
+  </si>
+  <si>
+    <t>上北町</t>
+  </si>
+  <si>
+    <t>乙供</t>
+  </si>
+  <si>
+    <t>千曳</t>
+  </si>
+  <si>
+    <t>狩場沢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>清水川</t>
+  </si>
+  <si>
+    <t>小湊</t>
+  </si>
+  <si>
+    <t>西平内</t>
+  </si>
+  <si>
+    <t>浅虫温泉</t>
+  </si>
+  <si>
+    <t>野内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢田前</t>
+  </si>
+  <si>
+    <t>小柳（青森）</t>
+  </si>
+  <si>
+    <t>東青森</t>
+  </si>
+  <si>
+    <t>筒井（青森）</t>
+  </si>
+  <si>
+    <t>青い森鉄道</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>モリテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1951,12 +2565,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -1964,26 +2572,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF555555"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F2F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1999,32 +2594,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2361,7 +2947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:C424"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -2370,47 +2956,44 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>345</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -2418,7 +3001,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -2426,7 +3009,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -2434,7 +3017,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -2442,7 +3025,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -2450,7 +3033,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -2458,7 +3041,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -2466,7 +3049,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -2474,7 +3057,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -2482,7 +3065,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -2490,7 +3073,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -2498,7 +3081,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -2506,7 +3089,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -2514,7 +3097,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -2522,7 +3105,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -2530,7 +3113,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -2538,7 +3121,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -2546,7 +3129,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -2554,7 +3137,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -2562,7 +3145,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -2570,7 +3153,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -2578,23 +3161,23 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -2602,7 +3185,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -2610,7 +3193,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -2618,7 +3201,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -2626,7 +3209,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -2634,7 +3217,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -2642,7 +3225,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -2650,7 +3233,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -2658,7 +3241,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -2666,7 +3249,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2674,7 +3257,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -2682,7 +3265,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2690,7 +3273,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -2698,7 +3281,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2706,15 +3289,15 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
         <v>210</v>
@@ -2722,7 +3305,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>210</v>
@@ -2730,7 +3313,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>210</v>
@@ -2738,7 +3321,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
         <v>210</v>
@@ -2746,7 +3329,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s">
         <v>210</v>
@@ -2754,7 +3337,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
         <v>210</v>
@@ -2762,7 +3345,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
         <v>210</v>
@@ -2770,7 +3353,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
         <v>210</v>
@@ -2778,7 +3361,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
         <v>210</v>
@@ -2786,7 +3369,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
         <v>210</v>
@@ -2794,7 +3377,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="s">
         <v>210</v>
@@ -2802,7 +3385,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="s">
         <v>210</v>
@@ -2810,31 +3393,31 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
         <v>71</v>
@@ -2842,15 +3425,15 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -2858,7 +3441,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -2866,7 +3449,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -2874,7 +3457,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
@@ -2882,7 +3465,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
@@ -2890,7 +3473,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -2898,7 +3481,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
@@ -2906,7 +3489,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
@@ -2914,23 +3497,23 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -2938,7 +3521,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -2946,7 +3529,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -2954,7 +3537,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
@@ -2962,7 +3545,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
@@ -2970,7 +3553,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
@@ -2978,23 +3561,23 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
@@ -3002,23 +3585,23 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -3026,23 +3609,23 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B85" t="s">
         <v>0</v>
@@ -3050,7 +3633,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B86" t="s">
         <v>0</v>
@@ -3058,7 +3641,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B87" t="s">
         <v>0</v>
@@ -3066,7 +3649,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B88" t="s">
         <v>0</v>
@@ -3074,7 +3657,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B89" t="s">
         <v>0</v>
@@ -3082,7 +3665,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
         <v>0</v>
@@ -3090,7 +3673,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" t="s">
         <v>0</v>
@@ -3098,7 +3681,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92" t="s">
         <v>0</v>
@@ -3106,7 +3689,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B93" t="s">
         <v>0</v>
@@ -3114,7 +3697,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94" t="s">
         <v>0</v>
@@ -3122,7 +3705,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95" t="s">
         <v>0</v>
@@ -3130,7 +3713,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s">
         <v>0</v>
@@ -3138,7 +3721,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97" t="s">
         <v>0</v>
@@ -3146,7 +3729,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B98" t="s">
         <v>0</v>
@@ -3154,7 +3737,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" t="s">
         <v>0</v>
@@ -3162,7 +3745,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100" t="s">
         <v>0</v>
@@ -3170,7 +3753,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B101" t="s">
         <v>0</v>
@@ -3178,7 +3761,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B102" t="s">
         <v>0</v>
@@ -3186,7 +3769,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" t="s">
         <v>0</v>
@@ -3194,7 +3777,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" t="s">
         <v>0</v>
@@ -3202,7 +3785,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B105" t="s">
         <v>0</v>
@@ -3210,7 +3793,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B106" t="s">
         <v>0</v>
@@ -3218,7 +3801,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B107" t="s">
         <v>0</v>
@@ -3226,7 +3809,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B108" t="s">
         <v>0</v>
@@ -3234,7 +3817,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B109" t="s">
         <v>0</v>
@@ -3242,7 +3825,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110" t="s">
         <v>0</v>
@@ -3250,7 +3833,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B111" t="s">
         <v>0</v>
@@ -3258,7 +3841,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B112" t="s">
         <v>0</v>
@@ -3266,7 +3849,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B113" t="s">
         <v>0</v>
@@ -3274,7 +3857,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B114" t="s">
         <v>0</v>
@@ -3282,7 +3865,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" t="s">
         <v>0</v>
@@ -3290,31 +3873,31 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B119" t="s">
         <v>0</v>
@@ -3322,7 +3905,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120" t="s">
         <v>0</v>
@@ -3330,23 +3913,23 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B123" t="s">
         <v>0</v>
@@ -3354,7 +3937,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B124" t="s">
         <v>0</v>
@@ -3362,7 +3945,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B125" t="s">
         <v>0</v>
@@ -3370,7 +3953,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B126" t="s">
         <v>0</v>
@@ -3378,7 +3961,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127" t="s">
         <v>0</v>
@@ -3386,7 +3969,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128" t="s">
         <v>0</v>
@@ -3394,15 +3977,15 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B130" t="s">
         <v>188</v>
@@ -3410,7 +3993,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B131" t="s">
         <v>188</v>
@@ -3418,7 +4001,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B132" t="s">
         <v>188</v>
@@ -3426,7 +4009,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B133" t="s">
         <v>188</v>
@@ -3434,7 +4017,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B134" t="s">
         <v>188</v>
@@ -3442,23 +4025,23 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B135" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B137" t="s">
         <v>188</v>
@@ -3466,7 +4049,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B138" t="s">
         <v>188</v>
@@ -3474,7 +4057,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B139" t="s">
         <v>188</v>
@@ -3482,7 +4065,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B140" t="s">
         <v>188</v>
@@ -3490,7 +4073,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B141" t="s">
         <v>188</v>
@@ -3498,7 +4081,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B142" t="s">
         <v>188</v>
@@ -3506,7 +4089,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
         <v>188</v>
@@ -3514,7 +4097,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B144" t="s">
         <v>188</v>
@@ -3522,7 +4105,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B145" t="s">
         <v>188</v>
@@ -3530,7 +4113,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
         <v>188</v>
@@ -3538,7 +4121,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B147" t="s">
         <v>188</v>
@@ -3546,7 +4129,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B148" t="s">
         <v>188</v>
@@ -3554,7 +4137,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B149" t="s">
         <v>188</v>
@@ -3562,7 +4145,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B150" t="s">
         <v>188</v>
@@ -3570,7 +4153,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B151" t="s">
         <v>188</v>
@@ -3578,7 +4161,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B152" t="s">
         <v>188</v>
@@ -3586,7 +4169,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B153" t="s">
         <v>188</v>
@@ -3594,7 +4177,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B154" t="s">
         <v>188</v>
@@ -3602,7 +4185,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B155" t="s">
         <v>188</v>
@@ -3610,7 +4193,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B156" t="s">
         <v>188</v>
@@ -3618,7 +4201,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B157" t="s">
         <v>188</v>
@@ -3626,7 +4209,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B158" t="s">
         <v>188</v>
@@ -3634,7 +4217,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B159" t="s">
         <v>188</v>
@@ -3642,15 +4225,15 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B161" t="s">
         <v>190</v>
@@ -3658,15 +4241,15 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B163" t="s">
         <v>191</v>
@@ -3674,7 +4257,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B164" t="s">
         <v>191</v>
@@ -3682,7 +4265,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B165" t="s">
         <v>191</v>
@@ -3690,7 +4273,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B166" t="s">
         <v>191</v>
@@ -3698,7 +4281,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B167" t="s">
         <v>191</v>
@@ -3706,7 +4289,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B168" t="s">
         <v>191</v>
@@ -3714,7 +4297,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B169" t="s">
         <v>191</v>
@@ -3722,7 +4305,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B170" t="s">
         <v>191</v>
@@ -3730,7 +4313,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B171" t="s">
         <v>191</v>
@@ -3738,7 +4321,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B172" t="s">
         <v>191</v>
@@ -3746,7 +4329,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B173" t="s">
         <v>191</v>
@@ -3754,7 +4337,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B174" t="s">
         <v>191</v>
@@ -3762,7 +4345,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B175" t="s">
         <v>191</v>
@@ -3770,7 +4353,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B176" t="s">
         <v>191</v>
@@ -3778,39 +4361,39 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B177" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B178" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B179" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B180" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B181" t="s">
         <v>207</v>
@@ -3818,7 +4401,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B182" t="s">
         <v>207</v>
@@ -3826,7 +4409,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B183" t="s">
         <v>207</v>
@@ -3834,7 +4417,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B184" t="s">
         <v>207</v>
@@ -3842,7 +4425,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B185" t="s">
         <v>207</v>
@@ -3850,7 +4433,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B186" t="s">
         <v>207</v>
@@ -3858,39 +4441,39 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B187" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B188" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B189" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B190" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B191" t="s">
         <v>214</v>
@@ -3898,7 +4481,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B192" t="s">
         <v>214</v>
@@ -3906,7 +4489,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B193" t="s">
         <v>214</v>
@@ -3914,15 +4497,15 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B194" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B195" t="s">
         <v>219</v>
@@ -3930,7 +4513,7 @@
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B196" t="s">
         <v>219</v>
@@ -3938,7 +4521,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B197" t="s">
         <v>219</v>
@@ -3946,7 +4529,7 @@
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B198" t="s">
         <v>219</v>
@@ -3954,7 +4537,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B199" t="s">
         <v>219</v>
@@ -3962,7 +4545,7 @@
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B200" t="s">
         <v>219</v>
@@ -3970,7 +4553,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B201" t="s">
         <v>219</v>
@@ -3978,7 +4561,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B202" t="s">
         <v>219</v>
@@ -3986,7 +4569,7 @@
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B203" t="s">
         <v>219</v>
@@ -3994,7 +4577,7 @@
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B204" t="s">
         <v>219</v>
@@ -4002,7 +4585,7 @@
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B205" t="s">
         <v>219</v>
@@ -4010,7 +4593,7 @@
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B206" t="s">
         <v>219</v>
@@ -4018,7 +4601,7 @@
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B207" t="s">
         <v>219</v>
@@ -4026,7 +4609,7 @@
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B208" t="s">
         <v>219</v>
@@ -4034,7 +4617,7 @@
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B209" t="s">
         <v>219</v>
@@ -4042,15 +4625,15 @@
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B210" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B211" t="s">
         <v>236</v>
@@ -4058,15 +4641,15 @@
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B212" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B213" t="s">
         <v>270</v>
@@ -4074,7 +4657,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B214" t="s">
         <v>270</v>
@@ -4082,7 +4665,7 @@
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B215" t="s">
         <v>270</v>
@@ -4090,7 +4673,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B216" t="s">
         <v>270</v>
@@ -4098,7 +4681,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B217" t="s">
         <v>270</v>
@@ -4106,7 +4689,7 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B218" t="s">
         <v>270</v>
@@ -4114,7 +4697,7 @@
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B219" t="s">
         <v>270</v>
@@ -4122,7 +4705,7 @@
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B220" t="s">
         <v>270</v>
@@ -4130,7 +4713,7 @@
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B221" t="s">
         <v>270</v>
@@ -4138,7 +4721,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B222" t="s">
         <v>270</v>
@@ -4146,7 +4729,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B223" t="s">
         <v>270</v>
@@ -4154,7 +4737,7 @@
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B224" t="s">
         <v>270</v>
@@ -4162,7 +4745,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B225" t="s">
         <v>270</v>
@@ -4170,7 +4753,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B226" t="s">
         <v>270</v>
@@ -4178,7 +4761,7 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B227" t="s">
         <v>270</v>
@@ -4186,7 +4769,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B228" t="s">
         <v>270</v>
@@ -4194,7 +4777,7 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B229" t="s">
         <v>270</v>
@@ -4202,7 +4785,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B230" t="s">
         <v>270</v>
@@ -4210,7 +4793,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B231" t="s">
         <v>270</v>
@@ -4218,7 +4801,7 @@
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B232" t="s">
         <v>270</v>
@@ -4226,7 +4809,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B233" t="s">
         <v>270</v>
@@ -4234,7 +4817,7 @@
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B234" t="s">
         <v>270</v>
@@ -4242,7 +4825,7 @@
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B235" t="s">
         <v>270</v>
@@ -4250,7 +4833,7 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B236" t="s">
         <v>270</v>
@@ -4258,7 +4841,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B237" t="s">
         <v>270</v>
@@ -4266,7 +4849,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B238" t="s">
         <v>270</v>
@@ -4274,7 +4857,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B239" t="s">
         <v>270</v>
@@ -4282,7 +4865,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B240" t="s">
         <v>270</v>
@@ -4290,7 +4873,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B241" t="s">
         <v>270</v>
@@ -4298,7 +4881,7 @@
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B242" t="s">
         <v>270</v>
@@ -4306,7 +4889,7 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B243" t="s">
         <v>270</v>
@@ -4314,15 +4897,15 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B244" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B245" t="s">
         <v>272</v>
@@ -4330,7 +4913,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B246" t="s">
         <v>272</v>
@@ -4338,7 +4921,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B247" t="s">
         <v>272</v>
@@ -4346,7 +4929,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B248" t="s">
         <v>272</v>
@@ -4354,7 +4937,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B249" t="s">
         <v>272</v>
@@ -4362,7 +4945,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B250" t="s">
         <v>272</v>
@@ -4370,7 +4953,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B251" t="s">
         <v>272</v>
@@ -4378,7 +4961,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B252" t="s">
         <v>272</v>
@@ -4386,7 +4969,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B253" t="s">
         <v>272</v>
@@ -4394,7 +4977,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B254" t="s">
         <v>272</v>
@@ -4402,7 +4985,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B255" t="s">
         <v>272</v>
@@ -4410,7 +4993,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B256" t="s">
         <v>272</v>
@@ -4418,7 +5001,7 @@
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B257" t="s">
         <v>272</v>
@@ -4426,7 +5009,7 @@
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B258" t="s">
         <v>272</v>
@@ -4434,7 +5017,7 @@
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B259" t="s">
         <v>272</v>
@@ -4442,7 +5025,7 @@
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B260" t="s">
         <v>272</v>
@@ -4450,7 +5033,7 @@
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B261" t="s">
         <v>272</v>
@@ -4458,7 +5041,7 @@
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B262" t="s">
         <v>272</v>
@@ -4466,7 +5049,7 @@
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B263" t="s">
         <v>272</v>
@@ -4474,7 +5057,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B264" t="s">
         <v>272</v>
@@ -4482,7 +5065,7 @@
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B265" t="s">
         <v>272</v>
@@ -4490,7 +5073,7 @@
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B266" t="s">
         <v>272</v>
@@ -4498,7 +5081,7 @@
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B267" t="s">
         <v>272</v>
@@ -4506,7 +5089,7 @@
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B268" t="s">
         <v>272</v>
@@ -4514,7 +5097,7 @@
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B269" t="s">
         <v>272</v>
@@ -4522,7 +5105,7 @@
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B270" t="s">
         <v>272</v>
@@ -4530,7 +5113,7 @@
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B271" t="s">
         <v>272</v>
@@ -4538,7 +5121,7 @@
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B272" t="s">
         <v>272</v>
@@ -4546,23 +5129,23 @@
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B273" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B274" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B275" t="s">
         <v>325</v>
@@ -4570,7 +5153,7 @@
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B276" t="s">
         <v>325</v>
@@ -4578,7 +5161,7 @@
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B277" t="s">
         <v>325</v>
@@ -4586,7 +5169,7 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B278" t="s">
         <v>325</v>
@@ -4594,7 +5177,7 @@
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B279" t="s">
         <v>325</v>
@@ -4602,7 +5185,7 @@
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B280" t="s">
         <v>325</v>
@@ -4610,7 +5193,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B281" t="s">
         <v>325</v>
@@ -4618,7 +5201,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B282" t="s">
         <v>325</v>
@@ -4626,7 +5209,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B283" t="s">
         <v>325</v>
@@ -4634,7 +5217,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B284" t="s">
         <v>325</v>
@@ -4642,7 +5225,7 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B285" t="s">
         <v>325</v>
@@ -4650,7 +5233,7 @@
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B286" t="s">
         <v>325</v>
@@ -4658,7 +5241,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B287" t="s">
         <v>325</v>
@@ -4666,7 +5249,7 @@
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B288" t="s">
         <v>325</v>
@@ -4674,7 +5257,7 @@
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B289" t="s">
         <v>325</v>
@@ -4682,7 +5265,7 @@
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B290" t="s">
         <v>325</v>
@@ -4690,7 +5273,7 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B291" t="s">
         <v>325</v>
@@ -4698,7 +5281,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B292" t="s">
         <v>325</v>
@@ -4706,7 +5289,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B293" t="s">
         <v>325</v>
@@ -4714,7 +5297,7 @@
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B294" t="s">
         <v>325</v>
@@ -4722,7 +5305,7 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B295" t="s">
         <v>325</v>
@@ -4730,15 +5313,15 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B296" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B297" t="s">
         <v>339</v>
@@ -4746,7 +5329,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B298" t="s">
         <v>339</v>
@@ -4754,7 +5337,7 @@
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B299" t="s">
         <v>339</v>
@@ -4762,7 +5345,7 @@
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B300" t="s">
         <v>339</v>
@@ -4770,7 +5353,7 @@
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B301" t="s">
         <v>339</v>
@@ -4778,7 +5361,7 @@
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B302" t="s">
         <v>339</v>
@@ -4786,7 +5369,7 @@
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B303" t="s">
         <v>339</v>
@@ -4794,7 +5377,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B304" t="s">
         <v>339</v>
@@ -4802,7 +5385,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B305" t="s">
         <v>339</v>
@@ -4810,7 +5393,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B306" t="s">
         <v>339</v>
@@ -4818,7 +5401,7 @@
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B307" t="s">
         <v>339</v>
@@ -4826,7 +5409,7 @@
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B308" t="s">
         <v>339</v>
@@ -4834,15 +5417,15 @@
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B309" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B310" t="s">
         <v>340</v>
@@ -4850,7 +5433,7 @@
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B311" t="s">
         <v>340</v>
@@ -4858,15 +5441,15 @@
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B312" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B313" t="s">
         <v>344</v>
@@ -4874,7 +5457,7 @@
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B314" t="s">
         <v>344</v>
@@ -4882,7 +5465,7 @@
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B315" t="s">
         <v>344</v>
@@ -4890,7 +5473,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B316" t="s">
         <v>344</v>
@@ -4898,7 +5481,7 @@
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B317" t="s">
         <v>344</v>
@@ -4906,7 +5489,7 @@
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B318" t="s">
         <v>344</v>
@@ -4914,7 +5497,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B319" t="s">
         <v>344</v>
@@ -4922,7 +5505,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B320" t="s">
         <v>344</v>
@@ -4930,7 +5513,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B321" t="s">
         <v>344</v>
@@ -4938,15 +5521,15 @@
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B322" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B323" t="s">
         <v>372</v>
@@ -4954,7 +5537,7 @@
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B324" t="s">
         <v>372</v>
@@ -4962,7 +5545,7 @@
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B325" t="s">
         <v>372</v>
@@ -4970,7 +5553,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B326" t="s">
         <v>372</v>
@@ -4978,39 +5561,39 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B327" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B328" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>363</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>374</v>
+        <v>362</v>
+      </c>
+      <c r="B329" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>364</v>
-      </c>
-      <c r="B330" t="s">
-        <v>372</v>
+        <v>363</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B331" t="s">
         <v>372</v>
@@ -5018,7 +5601,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B332" t="s">
         <v>372</v>
@@ -5026,7 +5609,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B333" t="s">
         <v>372</v>
@@ -5034,7 +5617,7 @@
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B334" t="s">
         <v>372</v>
@@ -5042,7 +5625,7 @@
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B335" t="s">
         <v>372</v>
@@ -5050,136 +5633,135 @@
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B336" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B337" t="s">
         <v>372</v>
       </c>
-      <c r="C337" s="1"/>
-    </row>
-    <row r="338" spans="1:3">
+    </row>
+    <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>371</v>
+      </c>
+      <c r="B338" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" t="s">
         <v>375</v>
-      </c>
-      <c r="B338" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3">
-      <c r="A339" t="s">
-        <v>376</v>
       </c>
       <c r="B339" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B340" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B341" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B342" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B343" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B344" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B345" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B346" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B347" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B348" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B349" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B350" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B351" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B352" t="s">
         <v>393</v>
@@ -5187,7 +5769,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B353" t="s">
         <v>393</v>
@@ -5195,7 +5777,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B354" t="s">
         <v>393</v>
@@ -5203,7 +5785,7 @@
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B355" t="s">
         <v>393</v>
@@ -5211,15 +5793,15 @@
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B356" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B357" t="s">
         <v>407</v>
@@ -5227,7 +5809,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B358" t="s">
         <v>407</v>
@@ -5235,7 +5817,7 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B359" t="s">
         <v>407</v>
@@ -5243,7 +5825,7 @@
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B360" t="s">
         <v>407</v>
@@ -5251,7 +5833,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B361" t="s">
         <v>407</v>
@@ -5259,7 +5841,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B362" t="s">
         <v>407</v>
@@ -5267,7 +5849,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B363" t="s">
         <v>407</v>
@@ -5275,7 +5857,7 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B364" t="s">
         <v>407</v>
@@ -5283,7 +5865,7 @@
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B365" t="s">
         <v>407</v>
@@ -5291,7 +5873,7 @@
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B366" t="s">
         <v>407</v>
@@ -5299,7 +5881,7 @@
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B367" t="s">
         <v>407</v>
@@ -5307,15 +5889,15 @@
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B368" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B369" t="s">
         <v>431</v>
@@ -5323,7 +5905,7 @@
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B370" t="s">
         <v>431</v>
@@ -5331,7 +5913,7 @@
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B371" t="s">
         <v>431</v>
@@ -5339,7 +5921,7 @@
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B372" t="s">
         <v>431</v>
@@ -5347,7 +5929,7 @@
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B373" t="s">
         <v>431</v>
@@ -5355,7 +5937,7 @@
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B374" t="s">
         <v>431</v>
@@ -5363,7 +5945,7 @@
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B375" t="s">
         <v>431</v>
@@ -5371,7 +5953,7 @@
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B376" t="s">
         <v>431</v>
@@ -5379,7 +5961,7 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B377" t="s">
         <v>431</v>
@@ -5387,7 +5969,7 @@
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B378" t="s">
         <v>431</v>
@@ -5395,7 +5977,7 @@
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B379" t="s">
         <v>431</v>
@@ -5403,7 +5985,7 @@
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B380" t="s">
         <v>431</v>
@@ -5411,7 +5993,7 @@
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B381" t="s">
         <v>431</v>
@@ -5419,7 +6001,7 @@
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B382" t="s">
         <v>431</v>
@@ -5427,7 +6009,7 @@
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B383" t="s">
         <v>431</v>
@@ -5435,7 +6017,7 @@
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B384" t="s">
         <v>431</v>
@@ -5443,7 +6025,7 @@
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B385" t="s">
         <v>431</v>
@@ -5451,7 +6033,7 @@
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B386" t="s">
         <v>431</v>
@@ -5459,7 +6041,7 @@
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B387" t="s">
         <v>431</v>
@@ -5467,7 +6049,7 @@
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B388" t="s">
         <v>431</v>
@@ -5475,7 +6057,7 @@
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B389" t="s">
         <v>431</v>
@@ -5483,7 +6065,7 @@
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B390" t="s">
         <v>431</v>
@@ -5491,15 +6073,15 @@
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B391" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B392" t="s">
         <v>432</v>
@@ -5507,7 +6089,7 @@
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B393" t="s">
         <v>432</v>
@@ -5515,7 +6097,7 @@
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B394" t="s">
         <v>432</v>
@@ -5523,7 +6105,7 @@
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B395" t="s">
         <v>432</v>
@@ -5531,7 +6113,7 @@
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B396" t="s">
         <v>432</v>
@@ -5539,7 +6121,7 @@
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B397" t="s">
         <v>432</v>
@@ -5547,7 +6129,7 @@
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="B398" t="s">
         <v>432</v>
@@ -5555,7 +6137,7 @@
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B399" t="s">
         <v>432</v>
@@ -5563,7 +6145,7 @@
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B400" t="s">
         <v>432</v>
@@ -5571,7 +6153,7 @@
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B401" t="s">
         <v>432</v>
@@ -5579,7 +6161,7 @@
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B402" t="s">
         <v>432</v>
@@ -5587,7 +6169,7 @@
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B403" t="s">
         <v>432</v>
@@ -5595,7 +6177,7 @@
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B404" t="s">
         <v>432</v>
@@ -5603,7 +6185,7 @@
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B405" t="s">
         <v>432</v>
@@ -5611,7 +6193,7 @@
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B406" t="s">
         <v>432</v>
@@ -5619,7 +6201,7 @@
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B407" t="s">
         <v>432</v>
@@ -5627,7 +6209,7 @@
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B408" t="s">
         <v>432</v>
@@ -5635,7 +6217,7 @@
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B409" t="s">
         <v>432</v>
@@ -5643,7 +6225,7 @@
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B410" t="s">
         <v>432</v>
@@ -5651,7 +6233,7 @@
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B411" t="s">
         <v>432</v>
@@ -5659,7 +6241,7 @@
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B412" t="s">
         <v>432</v>
@@ -5667,7 +6249,7 @@
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B413" t="s">
         <v>432</v>
@@ -5675,7 +6257,7 @@
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B414" t="s">
         <v>432</v>
@@ -5683,7 +6265,7 @@
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B415" t="s">
         <v>432</v>
@@ -5691,20 +6273,1232 @@
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B416" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="422" spans="1:1">
-      <c r="A422" s="3"/>
-    </row>
-    <row r="423" spans="1:1">
-      <c r="A423" s="4"/>
-    </row>
-    <row r="424" spans="1:1">
-      <c r="A424" s="5"/>
+    <row r="417" spans="1:2">
+      <c r="A417" t="s">
+        <v>457</v>
+      </c>
+      <c r="B417" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" t="s">
+        <v>462</v>
+      </c>
+      <c r="B421" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" t="s">
+        <v>464</v>
+      </c>
+      <c r="B422" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" t="s">
+        <v>465</v>
+      </c>
+      <c r="B423" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" t="s">
+        <v>466</v>
+      </c>
+      <c r="B424" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" t="s">
+        <v>467</v>
+      </c>
+      <c r="B425" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" t="s">
+        <v>468</v>
+      </c>
+      <c r="B426" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" t="s">
+        <v>469</v>
+      </c>
+      <c r="B427" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" t="s">
+        <v>470</v>
+      </c>
+      <c r="B428" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" t="s">
+        <v>471</v>
+      </c>
+      <c r="B429" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" t="s">
+        <v>472</v>
+      </c>
+      <c r="B430" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" t="s">
+        <v>473</v>
+      </c>
+      <c r="B431" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" t="s">
+        <v>474</v>
+      </c>
+      <c r="B432" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" t="s">
+        <v>475</v>
+      </c>
+      <c r="B433" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" t="s">
+        <v>476</v>
+      </c>
+      <c r="B434" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" t="s">
+        <v>460</v>
+      </c>
+      <c r="B435" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" t="s">
+        <v>480</v>
+      </c>
+      <c r="B436" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" t="s">
+        <v>482</v>
+      </c>
+      <c r="B437" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" t="s">
+        <v>483</v>
+      </c>
+      <c r="B438" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" t="s">
+        <v>484</v>
+      </c>
+      <c r="B439" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" t="s">
+        <v>485</v>
+      </c>
+      <c r="B440" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" t="s">
+        <v>486</v>
+      </c>
+      <c r="B441" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" t="s">
+        <v>487</v>
+      </c>
+      <c r="B442" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" t="s">
+        <v>488</v>
+      </c>
+      <c r="B443" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" t="s">
+        <v>489</v>
+      </c>
+      <c r="B444" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" t="s">
+        <v>490</v>
+      </c>
+      <c r="B445" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" t="s">
+        <v>491</v>
+      </c>
+      <c r="B446" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" t="s">
+        <v>492</v>
+      </c>
+      <c r="B447" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" t="s">
+        <v>493</v>
+      </c>
+      <c r="B448" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" t="s">
+        <v>494</v>
+      </c>
+      <c r="B449" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" t="s">
+        <v>495</v>
+      </c>
+      <c r="B450" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" t="s">
+        <v>496</v>
+      </c>
+      <c r="B451" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" t="s">
+        <v>497</v>
+      </c>
+      <c r="B452" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" t="s">
+        <v>498</v>
+      </c>
+      <c r="B453" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" t="s">
+        <v>499</v>
+      </c>
+      <c r="B454" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" t="s">
+        <v>500</v>
+      </c>
+      <c r="B455" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" t="s">
+        <v>501</v>
+      </c>
+      <c r="B456" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" t="s">
+        <v>502</v>
+      </c>
+      <c r="B457" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" t="s">
+        <v>503</v>
+      </c>
+      <c r="B458" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" t="s">
+        <v>504</v>
+      </c>
+      <c r="B459" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" t="s">
+        <v>505</v>
+      </c>
+      <c r="B460" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" t="s">
+        <v>506</v>
+      </c>
+      <c r="B461" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" t="s">
+        <v>507</v>
+      </c>
+      <c r="B462" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" t="s">
+        <v>508</v>
+      </c>
+      <c r="B463" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" t="s">
+        <v>509</v>
+      </c>
+      <c r="B464" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" t="s">
+        <v>510</v>
+      </c>
+      <c r="B465" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" t="s">
+        <v>511</v>
+      </c>
+      <c r="B466" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" t="s">
+        <v>512</v>
+      </c>
+      <c r="B467" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" t="s">
+        <v>513</v>
+      </c>
+      <c r="B468" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" t="s">
+        <v>514</v>
+      </c>
+      <c r="B469" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" t="s">
+        <v>515</v>
+      </c>
+      <c r="B470" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" t="s">
+        <v>516</v>
+      </c>
+      <c r="B471" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" t="s">
+        <v>517</v>
+      </c>
+      <c r="B472" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" t="s">
+        <v>518</v>
+      </c>
+      <c r="B473" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" t="s">
+        <v>519</v>
+      </c>
+      <c r="B474" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" t="s">
+        <v>520</v>
+      </c>
+      <c r="B475" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" t="s">
+        <v>521</v>
+      </c>
+      <c r="B476" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" t="s">
+        <v>522</v>
+      </c>
+      <c r="B477" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" t="s">
+        <v>525</v>
+      </c>
+      <c r="B478" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" t="s">
+        <v>561</v>
+      </c>
+      <c r="B479" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" t="s">
+        <v>526</v>
+      </c>
+      <c r="B480" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" t="s">
+        <v>527</v>
+      </c>
+      <c r="B481" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" t="s">
+        <v>528</v>
+      </c>
+      <c r="B482" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" t="s">
+        <v>529</v>
+      </c>
+      <c r="B483" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" t="s">
+        <v>530</v>
+      </c>
+      <c r="B484" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" t="s">
+        <v>531</v>
+      </c>
+      <c r="B485" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" t="s">
+        <v>532</v>
+      </c>
+      <c r="B486" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" t="s">
+        <v>533</v>
+      </c>
+      <c r="B487" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" t="s">
+        <v>534</v>
+      </c>
+      <c r="B488" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" t="s">
+        <v>562</v>
+      </c>
+      <c r="B489" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" t="s">
+        <v>535</v>
+      </c>
+      <c r="B490" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" t="s">
+        <v>536</v>
+      </c>
+      <c r="B491" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" t="s">
+        <v>537</v>
+      </c>
+      <c r="B492" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" t="s">
+        <v>538</v>
+      </c>
+      <c r="B493" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" t="s">
+        <v>539</v>
+      </c>
+      <c r="B494" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" t="s">
+        <v>541</v>
+      </c>
+      <c r="B495" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" t="s">
+        <v>542</v>
+      </c>
+      <c r="B496" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" t="s">
+        <v>543</v>
+      </c>
+      <c r="B497" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" t="s">
+        <v>548</v>
+      </c>
+      <c r="B498" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" t="s">
+        <v>549</v>
+      </c>
+      <c r="B499" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" t="s">
+        <v>550</v>
+      </c>
+      <c r="B500" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" t="s">
+        <v>551</v>
+      </c>
+      <c r="B501" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" t="s">
+        <v>552</v>
+      </c>
+      <c r="B502" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" t="s">
+        <v>553</v>
+      </c>
+      <c r="B503" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" t="s">
+        <v>554</v>
+      </c>
+      <c r="B504" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" t="s">
+        <v>555</v>
+      </c>
+      <c r="B505" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" t="s">
+        <v>556</v>
+      </c>
+      <c r="B506" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" t="s">
+        <v>557</v>
+      </c>
+      <c r="B507" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" t="s">
+        <v>558</v>
+      </c>
+      <c r="B508" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" t="s">
+        <v>559</v>
+      </c>
+      <c r="B509" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B510" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B511" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B512" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B513" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B514" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B515" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B516" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" t="s">
+        <v>571</v>
+      </c>
+      <c r="B517" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B518" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B519" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B520" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B521" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B522" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B523" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B524" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B525" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" t="s">
+        <v>581</v>
+      </c>
+      <c r="B526" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B527" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B528" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B529" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B530" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B531" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B532" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B533" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B534" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B535" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B536" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B537" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B538" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B539" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B540" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B541" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B542" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B543" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B544" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B545" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B546" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B547" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B548" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B549" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B550" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B551" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B552" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B553" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B554" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B555" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B556" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B557" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B558" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B559" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B560" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B561" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B562" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B563" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B564" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B565" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B566" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B567" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B568" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B569" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B570" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B571" t="s">
+        <v>629</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2727545E-6906-4B8A-B5DC-3E94DC1C2B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D13521A6-71DB-4D82-A805-E0C1101BF7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="841">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -2543,6 +2543,791 @@
     <rPh sb="2" eb="5">
       <t>モリテツドウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩手県</t>
+    <rPh sb="0" eb="3">
+      <t>イワテケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花輪線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>好摩</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東大更</t>
+  </si>
+  <si>
+    <t>大更</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平館</t>
+  </si>
+  <si>
+    <t>北森</t>
+  </si>
+  <si>
+    <t>松尾八幡平</t>
+  </si>
+  <si>
+    <t>安比高原</t>
+  </si>
+  <si>
+    <t>赤坂田</t>
+  </si>
+  <si>
+    <t>小屋の畑</t>
+  </si>
+  <si>
+    <t>荒屋新町</t>
+  </si>
+  <si>
+    <t>横間</t>
+  </si>
+  <si>
+    <t>田山</t>
+  </si>
+  <si>
+    <t>兄畑</t>
+  </si>
+  <si>
+    <t>花輪線、ＩＧＲいわて銀河鉄道</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花巻</t>
+  </si>
+  <si>
+    <t>似内</t>
+  </si>
+  <si>
+    <t>新花巻</t>
+  </si>
+  <si>
+    <t>小山田</t>
+  </si>
+  <si>
+    <t>土沢</t>
+  </si>
+  <si>
+    <t>晴山</t>
+  </si>
+  <si>
+    <t>岩根橋</t>
+  </si>
+  <si>
+    <t>宮守</t>
+  </si>
+  <si>
+    <t>柏木平</t>
+  </si>
+  <si>
+    <t>鱒沢</t>
+  </si>
+  <si>
+    <t>荒谷前</t>
+  </si>
+  <si>
+    <t>岩手二日町</t>
+  </si>
+  <si>
+    <t>綾織</t>
+  </si>
+  <si>
+    <t>遠野</t>
+  </si>
+  <si>
+    <t>青笹</t>
+  </si>
+  <si>
+    <t>岩手上郷</t>
+  </si>
+  <si>
+    <t>平倉</t>
+  </si>
+  <si>
+    <t>足ヶ瀬</t>
+  </si>
+  <si>
+    <t>上有住</t>
+  </si>
+  <si>
+    <t>陸中大橋</t>
+  </si>
+  <si>
+    <t>洞泉</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松倉</t>
+  </si>
+  <si>
+    <t>小佐野</t>
+  </si>
+  <si>
+    <t>釜石</t>
+  </si>
+  <si>
+    <t>釜石線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釜石線、東北本線</t>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釜石線、東北新幹線、秋田新幹線</t>
+    <rPh sb="4" eb="9">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釜石線、三陸鉄道リアス線</t>
+    <rPh sb="4" eb="6">
+      <t>サンリク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テツドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宮古</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千徳</t>
+  </si>
+  <si>
+    <t>花原市</t>
+  </si>
+  <si>
+    <t>蟇目</t>
+  </si>
+  <si>
+    <t>茂市</t>
+  </si>
+  <si>
+    <t>腹帯</t>
+  </si>
+  <si>
+    <t>陸中川井</t>
+  </si>
+  <si>
+    <t>箱石</t>
+  </si>
+  <si>
+    <t>川内（岩手）</t>
+  </si>
+  <si>
+    <t>松草</t>
+  </si>
+  <si>
+    <t>区界</t>
+  </si>
+  <si>
+    <t>上米内</t>
+  </si>
+  <si>
+    <t>山岸</t>
+  </si>
+  <si>
+    <t>上盛岡</t>
+  </si>
+  <si>
+    <t>盛岡</t>
+  </si>
+  <si>
+    <t>山田線</t>
+  </si>
+  <si>
+    <t>山田線、三陸鉄道リアス線</t>
+    <rPh sb="4" eb="8">
+      <t>サンリクテツドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山田線、東北本線、田沢湖線、ＩＧＲいわて銀河鉄道、秋田新幹線、東北新幹線</t>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タザワコ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="25" eb="30">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <rPh sb="31" eb="36">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一ノ関</t>
+  </si>
+  <si>
+    <t>真滝</t>
+  </si>
+  <si>
+    <t>陸中門崎</t>
+  </si>
+  <si>
+    <t>岩ノ下</t>
+  </si>
+  <si>
+    <t>陸中松川</t>
+  </si>
+  <si>
+    <t>猊鼻渓</t>
+  </si>
+  <si>
+    <t>柴宿</t>
+  </si>
+  <si>
+    <t>摺沢</t>
+  </si>
+  <si>
+    <t>千厩</t>
+  </si>
+  <si>
+    <t>小梨</t>
+  </si>
+  <si>
+    <t>矢越</t>
+  </si>
+  <si>
+    <t>折壁</t>
+  </si>
+  <si>
+    <t>新月</t>
+  </si>
+  <si>
+    <t>長部</t>
+  </si>
+  <si>
+    <t>山田線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大船渡線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大船渡線（ＢＲＴ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陸前矢作</t>
+  </si>
+  <si>
+    <t>陸前今泉</t>
+  </si>
+  <si>
+    <t>奇跡の一本松</t>
+  </si>
+  <si>
+    <t>竹駒</t>
+  </si>
+  <si>
+    <t>栃ヶ沢公園</t>
+  </si>
+  <si>
+    <t>陸前高田</t>
+  </si>
+  <si>
+    <t>高田高校前</t>
+  </si>
+  <si>
+    <t>高田病院</t>
+  </si>
+  <si>
+    <t>脇ノ沢</t>
+  </si>
+  <si>
+    <t>西下</t>
+  </si>
+  <si>
+    <t>小友</t>
+  </si>
+  <si>
+    <t>碁石海岸口</t>
+  </si>
+  <si>
+    <t>細浦</t>
+  </si>
+  <si>
+    <t>大船渡丸森</t>
+  </si>
+  <si>
+    <t>下船渡</t>
+  </si>
+  <si>
+    <t>大船渡魚市場前</t>
+  </si>
+  <si>
+    <t>大船渡</t>
+  </si>
+  <si>
+    <t>地ノ森</t>
+  </si>
+  <si>
+    <t>田茂山</t>
+  </si>
+  <si>
+    <t>盛</t>
+  </si>
+  <si>
+    <t>大船渡線（ＢＲＴ)、三陸鉄道リアス線</t>
+    <rPh sb="10" eb="14">
+      <t>サンリクテツドウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大船渡線、東北本線、東北新幹線、秋田新幹線</t>
+    <rPh sb="5" eb="9">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="16" eb="21">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前潟</t>
+  </si>
+  <si>
+    <t>大釜</t>
+  </si>
+  <si>
+    <t>小岩井</t>
+  </si>
+  <si>
+    <t>雫石</t>
+  </si>
+  <si>
+    <t>春木場</t>
+  </si>
+  <si>
+    <t>赤渕</t>
+  </si>
+  <si>
+    <t>田沢湖線</t>
+    <rPh sb="0" eb="4">
+      <t>タザワコセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>田沢湖線、秋田新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>タザワコセン</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水沢江刺</t>
+  </si>
+  <si>
+    <t>北上</t>
+  </si>
+  <si>
+    <t>いわて沼宮内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二戸</t>
+  </si>
+  <si>
+    <t>東北新幹線、秋田新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北新幹線、北上線、東北本線、秋田新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>キタカミセン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウホク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホンセン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>アキタ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>シンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北新幹線、ＩＧＲいわて銀河鉄道</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ギンガテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仙北町</t>
+  </si>
+  <si>
+    <t>岩手飯岡</t>
+  </si>
+  <si>
+    <t>矢幅</t>
+  </si>
+  <si>
+    <t>古館</t>
+  </si>
+  <si>
+    <t>紫波中央</t>
+  </si>
+  <si>
+    <t>日詰</t>
+  </si>
+  <si>
+    <t>石鳥谷</t>
+  </si>
+  <si>
+    <t>花巻空港（ＪＲ）</t>
+  </si>
+  <si>
+    <t>村崎野</t>
+  </si>
+  <si>
+    <t>六原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金ヶ崎</t>
+  </si>
+  <si>
+    <t>水沢</t>
+  </si>
+  <si>
+    <t>陸中折居</t>
+  </si>
+  <si>
+    <t>平泉</t>
+  </si>
+  <si>
+    <t>山ノ目</t>
+  </si>
+  <si>
+    <t>清水原</t>
+  </si>
+  <si>
+    <t>花泉</t>
+  </si>
+  <si>
+    <t>油島</t>
+  </si>
+  <si>
+    <t>東北本線</t>
+    <rPh sb="0" eb="4">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>角の浜</t>
+  </si>
+  <si>
+    <t>平内</t>
+  </si>
+  <si>
+    <t>種市</t>
+  </si>
+  <si>
+    <t>玉川（岩手）</t>
+  </si>
+  <si>
+    <t>宿戸</t>
+  </si>
+  <si>
+    <t>陸中八木</t>
+  </si>
+  <si>
+    <t>有家（岩手）</t>
+  </si>
+  <si>
+    <t>陸中中野</t>
+  </si>
+  <si>
+    <t>侍浜</t>
+  </si>
+  <si>
+    <t>陸中夏井</t>
+  </si>
+  <si>
+    <t>久慈</t>
+  </si>
+  <si>
+    <t>八戸線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチノヘセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柳原（岩手）</t>
+  </si>
+  <si>
+    <t>江釣子</t>
+  </si>
+  <si>
+    <t>藤根</t>
+  </si>
+  <si>
+    <t>立川目</t>
+  </si>
+  <si>
+    <t>横川目</t>
+  </si>
+  <si>
+    <t>岩沢</t>
+  </si>
+  <si>
+    <t>和賀仙人</t>
+  </si>
+  <si>
+    <t>ゆだ錦秋湖</t>
+  </si>
+  <si>
+    <t>ほっとゆだ</t>
+  </si>
+  <si>
+    <t>ゆだ高原</t>
+  </si>
+  <si>
+    <t>北上線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陸前赤崎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綾里</t>
+  </si>
+  <si>
+    <t>恋し浜</t>
+  </si>
+  <si>
+    <t>甫嶺</t>
+  </si>
+  <si>
+    <t>三陸</t>
+  </si>
+  <si>
+    <t>吉浜（岩手）</t>
+  </si>
+  <si>
+    <t>唐丹</t>
+  </si>
+  <si>
+    <t>平田（岩手）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両石</t>
+  </si>
+  <si>
+    <t>鵜住居</t>
+  </si>
+  <si>
+    <t>大槌</t>
+  </si>
+  <si>
+    <t>吉里吉里</t>
+  </si>
+  <si>
+    <t>浪板海岸</t>
+  </si>
+  <si>
+    <t>岩手船越</t>
+  </si>
+  <si>
+    <t>織笠</t>
+  </si>
+  <si>
+    <t>陸中山田</t>
+  </si>
+  <si>
+    <t>豊間根</t>
+  </si>
+  <si>
+    <t>払川</t>
+  </si>
+  <si>
+    <t>津軽石</t>
+  </si>
+  <si>
+    <t>八木沢・宮古短大</t>
+  </si>
+  <si>
+    <t>磯鶏</t>
+  </si>
+  <si>
+    <t>山口団地</t>
+  </si>
+  <si>
+    <t>一の渡</t>
+  </si>
+  <si>
+    <t>佐羽根</t>
+  </si>
+  <si>
+    <t>田老</t>
+  </si>
+  <si>
+    <t>新田老</t>
+  </si>
+  <si>
+    <t>摂待</t>
+  </si>
+  <si>
+    <t>岩泉小本</t>
+  </si>
+  <si>
+    <t>島越</t>
+  </si>
+  <si>
+    <t>田野畑</t>
+  </si>
+  <si>
+    <t>普代</t>
+  </si>
+  <si>
+    <t>白井海岸</t>
+  </si>
+  <si>
+    <t>堀内</t>
+  </si>
+  <si>
+    <t>野田玉川</t>
+  </si>
+  <si>
+    <t>十府ヶ浦海岸</t>
+  </si>
+  <si>
+    <t>陸中野田</t>
+  </si>
+  <si>
+    <t>陸中宇部</t>
+  </si>
+  <si>
+    <t>八戸線、三陸鉄道リアス線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチノヘセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>サンリクテツドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三陸鉄道リアス線</t>
+    <rPh sb="0" eb="4">
+      <t>サンリクテツドウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青山（岩手）</t>
+  </si>
+  <si>
+    <t>厨川</t>
+  </si>
+  <si>
+    <t>巣子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>滝沢</t>
+  </si>
+  <si>
+    <t>渋民</t>
+  </si>
+  <si>
+    <t>岩手川口</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>御堂</t>
+  </si>
+  <si>
+    <t>奥中山高原</t>
+  </si>
+  <si>
+    <t>小繋</t>
+  </si>
+  <si>
+    <t>小鳥谷</t>
+  </si>
+  <si>
+    <t>一戸</t>
+  </si>
+  <si>
+    <t>斗米</t>
+  </si>
+  <si>
+    <t>金田一温泉</t>
+  </si>
+  <si>
+    <t>ＩＧＲいわて銀河鉄道</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2947,11 +3732,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B761"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="48.88671875" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7005,7 +7790,7 @@
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="2" t="s">
+      <c r="A510" t="s">
         <v>564</v>
       </c>
       <c r="B510" t="s">
@@ -7013,7 +7798,7 @@
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="2" t="s">
+      <c r="A511" t="s">
         <v>565</v>
       </c>
       <c r="B511" t="s">
@@ -7021,7 +7806,7 @@
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="2" t="s">
+      <c r="A512" t="s">
         <v>566</v>
       </c>
       <c r="B512" t="s">
@@ -7029,7 +7814,7 @@
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="2" t="s">
+      <c r="A513" t="s">
         <v>567</v>
       </c>
       <c r="B513" t="s">
@@ -7037,7 +7822,7 @@
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="2" t="s">
+      <c r="A514" t="s">
         <v>568</v>
       </c>
       <c r="B514" t="s">
@@ -7045,7 +7830,7 @@
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="2" t="s">
+      <c r="A515" t="s">
         <v>569</v>
       </c>
       <c r="B515" t="s">
@@ -7053,7 +7838,7 @@
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="2" t="s">
+      <c r="A516" t="s">
         <v>570</v>
       </c>
       <c r="B516" t="s">
@@ -7069,7 +7854,7 @@
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="2" t="s">
+      <c r="A518" t="s">
         <v>572</v>
       </c>
       <c r="B518" t="s">
@@ -7077,7 +7862,7 @@
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="2" t="s">
+      <c r="A519" t="s">
         <v>573</v>
       </c>
       <c r="B519" t="s">
@@ -7085,7 +7870,7 @@
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="2" t="s">
+      <c r="A520" t="s">
         <v>574</v>
       </c>
       <c r="B520" t="s">
@@ -7093,7 +7878,7 @@
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="2" t="s">
+      <c r="A521" t="s">
         <v>575</v>
       </c>
       <c r="B521" t="s">
@@ -7101,7 +7886,7 @@
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="2" t="s">
+      <c r="A522" t="s">
         <v>577</v>
       </c>
       <c r="B522" t="s">
@@ -7109,7 +7894,7 @@
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="2" t="s">
+      <c r="A523" t="s">
         <v>578</v>
       </c>
       <c r="B523" t="s">
@@ -7117,7 +7902,7 @@
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="2" t="s">
+      <c r="A524" t="s">
         <v>579</v>
       </c>
       <c r="B524" t="s">
@@ -7125,7 +7910,7 @@
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="2" t="s">
+      <c r="A525" t="s">
         <v>580</v>
       </c>
       <c r="B525" t="s">
@@ -7141,7 +7926,7 @@
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="2" t="s">
+      <c r="A527" t="s">
         <v>582</v>
       </c>
       <c r="B527" t="s">
@@ -7149,7 +7934,7 @@
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="2" t="s">
+      <c r="A528" t="s">
         <v>583</v>
       </c>
       <c r="B528" t="s">
@@ -7157,7 +7942,7 @@
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="2" t="s">
+      <c r="A529" t="s">
         <v>584</v>
       </c>
       <c r="B529" t="s">
@@ -7165,7 +7950,7 @@
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="2" t="s">
+      <c r="A530" t="s">
         <v>585</v>
       </c>
       <c r="B530" t="s">
@@ -7173,7 +7958,7 @@
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="2" t="s">
+      <c r="A531" t="s">
         <v>586</v>
       </c>
       <c r="B531" t="s">
@@ -7181,7 +7966,7 @@
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="2" t="s">
+      <c r="A532" t="s">
         <v>587</v>
       </c>
       <c r="B532" t="s">
@@ -7189,7 +7974,7 @@
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="2" t="s">
+      <c r="A533" t="s">
         <v>588</v>
       </c>
       <c r="B533" t="s">
@@ -7197,7 +7982,7 @@
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="2" t="s">
+      <c r="A534" t="s">
         <v>589</v>
       </c>
       <c r="B534" t="s">
@@ -7205,7 +7990,7 @@
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="2" t="s">
+      <c r="A535" t="s">
         <v>590</v>
       </c>
       <c r="B535" t="s">
@@ -7213,7 +7998,7 @@
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="2" t="s">
+      <c r="A536" t="s">
         <v>591</v>
       </c>
       <c r="B536" t="s">
@@ -7221,7 +8006,7 @@
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="2" t="s">
+      <c r="A537" t="s">
         <v>593</v>
       </c>
       <c r="B537" t="s">
@@ -7229,7 +8014,7 @@
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="2" t="s">
+      <c r="A538" t="s">
         <v>594</v>
       </c>
       <c r="B538" t="s">
@@ -7237,7 +8022,7 @@
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="2" t="s">
+      <c r="A539" t="s">
         <v>595</v>
       </c>
       <c r="B539" t="s">
@@ -7245,7 +8030,7 @@
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="2" t="s">
+      <c r="A540" t="s">
         <v>596</v>
       </c>
       <c r="B540" t="s">
@@ -7253,7 +8038,7 @@
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="2" t="s">
+      <c r="A541" t="s">
         <v>597</v>
       </c>
       <c r="B541" t="s">
@@ -7261,7 +8046,7 @@
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="2" t="s">
+      <c r="A542" t="s">
         <v>598</v>
       </c>
       <c r="B542" t="s">
@@ -7269,7 +8054,7 @@
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="2" t="s">
+      <c r="A543" t="s">
         <v>599</v>
       </c>
       <c r="B543" t="s">
@@ -7277,7 +8062,7 @@
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="2" t="s">
+      <c r="A544" t="s">
         <v>600</v>
       </c>
       <c r="B544" t="s">
@@ -7285,7 +8070,7 @@
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="2" t="s">
+      <c r="A545" t="s">
         <v>601</v>
       </c>
       <c r="B545" t="s">
@@ -7293,7 +8078,7 @@
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="A546" s="2" t="s">
+      <c r="A546" t="s">
         <v>602</v>
       </c>
       <c r="B546" t="s">
@@ -7301,7 +8086,7 @@
       </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="A547" s="2" t="s">
+      <c r="A547" t="s">
         <v>603</v>
       </c>
       <c r="B547" t="s">
@@ -7309,7 +8094,7 @@
       </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="A548" s="2" t="s">
+      <c r="A548" t="s">
         <v>604</v>
       </c>
       <c r="B548" t="s">
@@ -7317,7 +8102,7 @@
       </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="A549" s="2" t="s">
+      <c r="A549" t="s">
         <v>606</v>
       </c>
       <c r="B549" t="s">
@@ -7325,7 +8110,7 @@
       </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="A550" s="2" t="s">
+      <c r="A550" t="s">
         <v>607</v>
       </c>
       <c r="B550" t="s">
@@ -7333,7 +8118,7 @@
       </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="A551" s="2" t="s">
+      <c r="A551" t="s">
         <v>608</v>
       </c>
       <c r="B551" t="s">
@@ -7341,7 +8126,7 @@
       </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="A552" s="2" t="s">
+      <c r="A552" t="s">
         <v>609</v>
       </c>
       <c r="B552" t="s">
@@ -7349,7 +8134,7 @@
       </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="A553" s="2" t="s">
+      <c r="A553" t="s">
         <v>610</v>
       </c>
       <c r="B553" t="s">
@@ -7357,7 +8142,7 @@
       </c>
     </row>
     <row r="554" spans="1:2">
-      <c r="A554" s="2" t="s">
+      <c r="A554" t="s">
         <v>611</v>
       </c>
       <c r="B554" t="s">
@@ -7365,7 +8150,7 @@
       </c>
     </row>
     <row r="555" spans="1:2">
-      <c r="A555" s="2" t="s">
+      <c r="A555" t="s">
         <v>612</v>
       </c>
       <c r="B555" t="s">
@@ -7373,7 +8158,7 @@
       </c>
     </row>
     <row r="556" spans="1:2">
-      <c r="A556" s="2" t="s">
+      <c r="A556" t="s">
         <v>613</v>
       </c>
       <c r="B556" t="s">
@@ -7381,7 +8166,7 @@
       </c>
     </row>
     <row r="557" spans="1:2">
-      <c r="A557" s="2" t="s">
+      <c r="A557" t="s">
         <v>614</v>
       </c>
       <c r="B557" t="s">
@@ -7389,7 +8174,7 @@
       </c>
     </row>
     <row r="558" spans="1:2">
-      <c r="A558" s="2" t="s">
+      <c r="A558" t="s">
         <v>615</v>
       </c>
       <c r="B558" t="s">
@@ -7397,7 +8182,7 @@
       </c>
     </row>
     <row r="559" spans="1:2">
-      <c r="A559" s="2" t="s">
+      <c r="A559" t="s">
         <v>616</v>
       </c>
       <c r="B559" t="s">
@@ -7405,7 +8190,7 @@
       </c>
     </row>
     <row r="560" spans="1:2">
-      <c r="A560" s="2" t="s">
+      <c r="A560" t="s">
         <v>617</v>
       </c>
       <c r="B560" t="s">
@@ -7413,7 +8198,7 @@
       </c>
     </row>
     <row r="561" spans="1:2">
-      <c r="A561" s="2" t="s">
+      <c r="A561" t="s">
         <v>618</v>
       </c>
       <c r="B561" t="s">
@@ -7421,7 +8206,7 @@
       </c>
     </row>
     <row r="562" spans="1:2">
-      <c r="A562" s="2" t="s">
+      <c r="A562" t="s">
         <v>619</v>
       </c>
       <c r="B562" t="s">
@@ -7429,7 +8214,7 @@
       </c>
     </row>
     <row r="563" spans="1:2">
-      <c r="A563" s="2" t="s">
+      <c r="A563" t="s">
         <v>620</v>
       </c>
       <c r="B563" t="s">
@@ -7437,7 +8222,7 @@
       </c>
     </row>
     <row r="564" spans="1:2">
-      <c r="A564" s="2" t="s">
+      <c r="A564" t="s">
         <v>621</v>
       </c>
       <c r="B564" t="s">
@@ -7445,7 +8230,7 @@
       </c>
     </row>
     <row r="565" spans="1:2">
-      <c r="A565" s="2" t="s">
+      <c r="A565" t="s">
         <v>622</v>
       </c>
       <c r="B565" t="s">
@@ -7453,7 +8238,7 @@
       </c>
     </row>
     <row r="566" spans="1:2">
-      <c r="A566" s="2" t="s">
+      <c r="A566" t="s">
         <v>623</v>
       </c>
       <c r="B566" t="s">
@@ -7461,7 +8246,7 @@
       </c>
     </row>
     <row r="567" spans="1:2">
-      <c r="A567" s="2" t="s">
+      <c r="A567" t="s">
         <v>624</v>
       </c>
       <c r="B567" t="s">
@@ -7469,7 +8254,7 @@
       </c>
     </row>
     <row r="568" spans="1:2">
-      <c r="A568" s="2" t="s">
+      <c r="A568" t="s">
         <v>625</v>
       </c>
       <c r="B568" t="s">
@@ -7477,7 +8262,7 @@
       </c>
     </row>
     <row r="569" spans="1:2">
-      <c r="A569" s="2" t="s">
+      <c r="A569" t="s">
         <v>626</v>
       </c>
       <c r="B569" t="s">
@@ -7485,7 +8270,7 @@
       </c>
     </row>
     <row r="570" spans="1:2">
-      <c r="A570" s="2" t="s">
+      <c r="A570" t="s">
         <v>627</v>
       </c>
       <c r="B570" t="s">
@@ -7493,11 +8278,1512 @@
       </c>
     </row>
     <row r="571" spans="1:2">
-      <c r="A571" s="2" t="s">
+      <c r="A571" t="s">
         <v>628</v>
       </c>
       <c r="B571" t="s">
         <v>629</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>632</v>
+      </c>
+      <c r="B575" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>633</v>
+      </c>
+      <c r="B576" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>634</v>
+      </c>
+      <c r="B577" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>635</v>
+      </c>
+      <c r="B578" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>636</v>
+      </c>
+      <c r="B579" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>637</v>
+      </c>
+      <c r="B580" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>638</v>
+      </c>
+      <c r="B581" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>639</v>
+      </c>
+      <c r="B582" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>640</v>
+      </c>
+      <c r="B583" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>641</v>
+      </c>
+      <c r="B584" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>642</v>
+      </c>
+      <c r="B585" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>643</v>
+      </c>
+      <c r="B586" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>644</v>
+      </c>
+      <c r="B587" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" t="s">
+        <v>646</v>
+      </c>
+      <c r="B588" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" t="s">
+        <v>647</v>
+      </c>
+      <c r="B589" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" t="s">
+        <v>648</v>
+      </c>
+      <c r="B590" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" t="s">
+        <v>649</v>
+      </c>
+      <c r="B591" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" t="s">
+        <v>650</v>
+      </c>
+      <c r="B592" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>651</v>
+      </c>
+      <c r="B593" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>652</v>
+      </c>
+      <c r="B594" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>653</v>
+      </c>
+      <c r="B595" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>654</v>
+      </c>
+      <c r="B596" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>655</v>
+      </c>
+      <c r="B597" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>656</v>
+      </c>
+      <c r="B598" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>657</v>
+      </c>
+      <c r="B599" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>658</v>
+      </c>
+      <c r="B600" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>659</v>
+      </c>
+      <c r="B601" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>660</v>
+      </c>
+      <c r="B602" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>661</v>
+      </c>
+      <c r="B603" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>662</v>
+      </c>
+      <c r="B604" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>663</v>
+      </c>
+      <c r="B605" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>664</v>
+      </c>
+      <c r="B606" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>665</v>
+      </c>
+      <c r="B607" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>666</v>
+      </c>
+      <c r="B608" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>667</v>
+      </c>
+      <c r="B609" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>668</v>
+      </c>
+      <c r="B610" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>669</v>
+      </c>
+      <c r="B611" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>674</v>
+      </c>
+      <c r="B612" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>675</v>
+      </c>
+      <c r="B613" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>676</v>
+      </c>
+      <c r="B614" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>677</v>
+      </c>
+      <c r="B615" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>678</v>
+      </c>
+      <c r="B616" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>679</v>
+      </c>
+      <c r="B617" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
+        <v>680</v>
+      </c>
+      <c r="B618" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" t="s">
+        <v>681</v>
+      </c>
+      <c r="B619" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" t="s">
+        <v>682</v>
+      </c>
+      <c r="B620" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" t="s">
+        <v>683</v>
+      </c>
+      <c r="B621" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" t="s">
+        <v>684</v>
+      </c>
+      <c r="B622" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" t="s">
+        <v>685</v>
+      </c>
+      <c r="B623" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" t="s">
+        <v>686</v>
+      </c>
+      <c r="B624" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" t="s">
+        <v>687</v>
+      </c>
+      <c r="B625" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" t="s">
+        <v>688</v>
+      </c>
+      <c r="B626" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" t="s">
+        <v>692</v>
+      </c>
+      <c r="B627" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" t="s">
+        <v>693</v>
+      </c>
+      <c r="B628" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" t="s">
+        <v>694</v>
+      </c>
+      <c r="B629" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" t="s">
+        <v>695</v>
+      </c>
+      <c r="B630" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" t="s">
+        <v>696</v>
+      </c>
+      <c r="B631" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" t="s">
+        <v>697</v>
+      </c>
+      <c r="B632" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" t="s">
+        <v>698</v>
+      </c>
+      <c r="B633" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" t="s">
+        <v>699</v>
+      </c>
+      <c r="B634" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" t="s">
+        <v>700</v>
+      </c>
+      <c r="B635" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" t="s">
+        <v>701</v>
+      </c>
+      <c r="B636" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" t="s">
+        <v>702</v>
+      </c>
+      <c r="B637" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" t="s">
+        <v>703</v>
+      </c>
+      <c r="B638" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" t="s">
+        <v>704</v>
+      </c>
+      <c r="B639" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" t="s">
+        <v>705</v>
+      </c>
+      <c r="B640" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" t="s">
+        <v>709</v>
+      </c>
+      <c r="B641" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" t="s">
+        <v>710</v>
+      </c>
+      <c r="B642" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" t="s">
+        <v>711</v>
+      </c>
+      <c r="B643" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" t="s">
+        <v>712</v>
+      </c>
+      <c r="B644" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" t="s">
+        <v>713</v>
+      </c>
+      <c r="B645" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" t="s">
+        <v>714</v>
+      </c>
+      <c r="B646" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" t="s">
+        <v>715</v>
+      </c>
+      <c r="B647" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" t="s">
+        <v>716</v>
+      </c>
+      <c r="B648" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" t="s">
+        <v>717</v>
+      </c>
+      <c r="B649" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" t="s">
+        <v>718</v>
+      </c>
+      <c r="B650" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" t="s">
+        <v>719</v>
+      </c>
+      <c r="B651" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" t="s">
+        <v>720</v>
+      </c>
+      <c r="B652" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" t="s">
+        <v>721</v>
+      </c>
+      <c r="B653" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" t="s">
+        <v>722</v>
+      </c>
+      <c r="B654" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" t="s">
+        <v>723</v>
+      </c>
+      <c r="B655" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" t="s">
+        <v>724</v>
+      </c>
+      <c r="B656" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" t="s">
+        <v>725</v>
+      </c>
+      <c r="B657" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" t="s">
+        <v>726</v>
+      </c>
+      <c r="B658" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" t="s">
+        <v>727</v>
+      </c>
+      <c r="B659" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" t="s">
+        <v>728</v>
+      </c>
+      <c r="B660" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" t="s">
+        <v>731</v>
+      </c>
+      <c r="B661" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" t="s">
+        <v>732</v>
+      </c>
+      <c r="B662" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" t="s">
+        <v>733</v>
+      </c>
+      <c r="B663" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" t="s">
+        <v>734</v>
+      </c>
+      <c r="B664" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" t="s">
+        <v>735</v>
+      </c>
+      <c r="B665" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" t="s">
+        <v>736</v>
+      </c>
+      <c r="B666" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" t="s">
+        <v>739</v>
+      </c>
+      <c r="B667" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" t="s">
+        <v>740</v>
+      </c>
+      <c r="B668" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" t="s">
+        <v>741</v>
+      </c>
+      <c r="B669" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" t="s">
+        <v>742</v>
+      </c>
+      <c r="B670" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" t="s">
+        <v>746</v>
+      </c>
+      <c r="B671" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" t="s">
+        <v>747</v>
+      </c>
+      <c r="B672" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" t="s">
+        <v>748</v>
+      </c>
+      <c r="B673" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" t="s">
+        <v>749</v>
+      </c>
+      <c r="B674" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" t="s">
+        <v>750</v>
+      </c>
+      <c r="B675" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" t="s">
+        <v>751</v>
+      </c>
+      <c r="B676" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" t="s">
+        <v>752</v>
+      </c>
+      <c r="B677" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" t="s">
+        <v>753</v>
+      </c>
+      <c r="B678" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" t="s">
+        <v>646</v>
+      </c>
+      <c r="B679" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" t="s">
+        <v>754</v>
+      </c>
+      <c r="B680" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" t="s">
+        <v>755</v>
+      </c>
+      <c r="B681" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" t="s">
+        <v>756</v>
+      </c>
+      <c r="B682" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" t="s">
+        <v>757</v>
+      </c>
+      <c r="B683" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" t="s">
+        <v>758</v>
+      </c>
+      <c r="B684" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" t="s">
+        <v>759</v>
+      </c>
+      <c r="B685" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" t="s">
+        <v>760</v>
+      </c>
+      <c r="B686" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" t="s">
+        <v>761</v>
+      </c>
+      <c r="B687" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" t="s">
+        <v>762</v>
+      </c>
+      <c r="B688" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" t="s">
+        <v>763</v>
+      </c>
+      <c r="B689" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" t="s">
+        <v>765</v>
+      </c>
+      <c r="B690" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" t="s">
+        <v>766</v>
+      </c>
+      <c r="B691" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" t="s">
+        <v>767</v>
+      </c>
+      <c r="B692" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" t="s">
+        <v>768</v>
+      </c>
+      <c r="B693" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" t="s">
+        <v>769</v>
+      </c>
+      <c r="B694" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" t="s">
+        <v>770</v>
+      </c>
+      <c r="B695" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" t="s">
+        <v>771</v>
+      </c>
+      <c r="B696" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" t="s">
+        <v>772</v>
+      </c>
+      <c r="B697" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" t="s">
+        <v>773</v>
+      </c>
+      <c r="B698" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" t="s">
+        <v>774</v>
+      </c>
+      <c r="B699" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" t="s">
+        <v>775</v>
+      </c>
+      <c r="B700" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" t="s">
+        <v>777</v>
+      </c>
+      <c r="B701" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" t="s">
+        <v>778</v>
+      </c>
+      <c r="B702" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" t="s">
+        <v>779</v>
+      </c>
+      <c r="B703" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" t="s">
+        <v>780</v>
+      </c>
+      <c r="B704" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" t="s">
+        <v>781</v>
+      </c>
+      <c r="B705" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" t="s">
+        <v>782</v>
+      </c>
+      <c r="B706" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" t="s">
+        <v>783</v>
+      </c>
+      <c r="B707" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" t="s">
+        <v>784</v>
+      </c>
+      <c r="B708" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" t="s">
+        <v>785</v>
+      </c>
+      <c r="B709" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" t="s">
+        <v>786</v>
+      </c>
+      <c r="B710" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" t="s">
+        <v>788</v>
+      </c>
+      <c r="B711" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" t="s">
+        <v>789</v>
+      </c>
+      <c r="B712" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" t="s">
+        <v>790</v>
+      </c>
+      <c r="B713" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" t="s">
+        <v>791</v>
+      </c>
+      <c r="B714" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" t="s">
+        <v>792</v>
+      </c>
+      <c r="B715" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" t="s">
+        <v>793</v>
+      </c>
+      <c r="B716" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" t="s">
+        <v>794</v>
+      </c>
+      <c r="B717" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" t="s">
+        <v>795</v>
+      </c>
+      <c r="B718" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" t="s">
+        <v>796</v>
+      </c>
+      <c r="B719" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" t="s">
+        <v>797</v>
+      </c>
+      <c r="B720" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" t="s">
+        <v>798</v>
+      </c>
+      <c r="B721" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722" t="s">
+        <v>799</v>
+      </c>
+      <c r="B722" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723" t="s">
+        <v>800</v>
+      </c>
+      <c r="B723" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" t="s">
+        <v>801</v>
+      </c>
+      <c r="B724" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725" t="s">
+        <v>802</v>
+      </c>
+      <c r="B725" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" t="s">
+        <v>803</v>
+      </c>
+      <c r="B726" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" t="s">
+        <v>804</v>
+      </c>
+      <c r="B727" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" t="s">
+        <v>805</v>
+      </c>
+      <c r="B728" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" t="s">
+        <v>806</v>
+      </c>
+      <c r="B729" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" t="s">
+        <v>807</v>
+      </c>
+      <c r="B730" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" t="s">
+        <v>808</v>
+      </c>
+      <c r="B731" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" t="s">
+        <v>809</v>
+      </c>
+      <c r="B732" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" t="s">
+        <v>810</v>
+      </c>
+      <c r="B733" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" t="s">
+        <v>811</v>
+      </c>
+      <c r="B734" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" t="s">
+        <v>812</v>
+      </c>
+      <c r="B735" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" t="s">
+        <v>813</v>
+      </c>
+      <c r="B736" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" t="s">
+        <v>814</v>
+      </c>
+      <c r="B737" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" t="s">
+        <v>815</v>
+      </c>
+      <c r="B738" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" t="s">
+        <v>816</v>
+      </c>
+      <c r="B739" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" t="s">
+        <v>817</v>
+      </c>
+      <c r="B740" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" t="s">
+        <v>818</v>
+      </c>
+      <c r="B741" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" t="s">
+        <v>819</v>
+      </c>
+      <c r="B742" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" t="s">
+        <v>820</v>
+      </c>
+      <c r="B743" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" t="s">
+        <v>821</v>
+      </c>
+      <c r="B744" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" t="s">
+        <v>822</v>
+      </c>
+      <c r="B745" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" t="s">
+        <v>823</v>
+      </c>
+      <c r="B746" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" t="s">
+        <v>824</v>
+      </c>
+      <c r="B747" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D13521A6-71DB-4D82-A805-E0C1101BF7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC21E81E-D21B-487C-9A39-52416A3AA7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1051">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -3328,6 +3328,793 @@
   </si>
   <si>
     <t>ＩＧＲいわて銀河鉄道</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宮城県</t>
+    <rPh sb="0" eb="3">
+      <t>ミヤギケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小牛田</t>
+  </si>
+  <si>
+    <t>上涌谷</t>
+  </si>
+  <si>
+    <t>涌谷</t>
+  </si>
+  <si>
+    <t>前谷地</t>
+  </si>
+  <si>
+    <t>和渕</t>
+  </si>
+  <si>
+    <t>のの岳</t>
+  </si>
+  <si>
+    <t>陸前豊里</t>
+  </si>
+  <si>
+    <t>御岳堂</t>
+  </si>
+  <si>
+    <t>柳津（宮城）</t>
+  </si>
+  <si>
+    <t>陸前横山</t>
+  </si>
+  <si>
+    <t>気仙沼線</t>
+    <rPh sb="0" eb="4">
+      <t>ケセンヌマセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気仙沼線（ＢＲＴ)</t>
+    <rPh sb="0" eb="3">
+      <t>ケセンヌマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陸前戸倉</t>
+  </si>
+  <si>
+    <t>志津川</t>
+  </si>
+  <si>
+    <t>南三陸町役場・病院前</t>
+  </si>
+  <si>
+    <t>志津川中央団地</t>
+  </si>
+  <si>
+    <t>清水浜</t>
+  </si>
+  <si>
+    <t>歌津</t>
+  </si>
+  <si>
+    <t>陸前港</t>
+  </si>
+  <si>
+    <t>蔵内</t>
+  </si>
+  <si>
+    <t>陸前小泉</t>
+  </si>
+  <si>
+    <t>本吉</t>
+  </si>
+  <si>
+    <t>小金沢</t>
+  </si>
+  <si>
+    <t>大谷海岸</t>
+  </si>
+  <si>
+    <t>大谷まち</t>
+  </si>
+  <si>
+    <t>陸前階上</t>
+  </si>
+  <si>
+    <t>最知</t>
+  </si>
+  <si>
+    <t>岩月</t>
+  </si>
+  <si>
+    <t>松岩</t>
+  </si>
+  <si>
+    <t>赤岩港</t>
+  </si>
+  <si>
+    <t>南気仙沼</t>
+  </si>
+  <si>
+    <t>気仙沼市立病院</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不動の沢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東新城</t>
+  </si>
+  <si>
+    <t>気仙沼</t>
+  </si>
+  <si>
+    <t>仙台</t>
+  </si>
+  <si>
+    <t>長町</t>
+  </si>
+  <si>
+    <t>太子堂</t>
+  </si>
+  <si>
+    <t>南仙台</t>
+  </si>
+  <si>
+    <t>名取</t>
+  </si>
+  <si>
+    <t>館腰</t>
+  </si>
+  <si>
+    <t>岩沼</t>
+  </si>
+  <si>
+    <t>逢隈</t>
+  </si>
+  <si>
+    <t>亘理</t>
+  </si>
+  <si>
+    <t>浜吉田</t>
+  </si>
+  <si>
+    <t>山下（宮城）</t>
+  </si>
+  <si>
+    <t>坂元</t>
+  </si>
+  <si>
+    <t>常磐線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、東北本線、仙台空港アクセス線、仙台地下鉄南北線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、東北本線、仙台空港アクセス線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、東北本線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気仙沼線、石巻線</t>
+    <rPh sb="0" eb="4">
+      <t>ケセンヌマセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イシノマキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気仙沼線、石巻線、東北本線、陸羽東線</t>
+    <rPh sb="0" eb="4">
+      <t>ケセンヌマセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イシノマキセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>リクウトウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佳景山</t>
+  </si>
+  <si>
+    <t>鹿又</t>
+  </si>
+  <si>
+    <t>曽波神</t>
+  </si>
+  <si>
+    <t>陸前稲井</t>
+  </si>
+  <si>
+    <t>渡波</t>
+  </si>
+  <si>
+    <t>万石浦</t>
+  </si>
+  <si>
+    <t>沢田</t>
+  </si>
+  <si>
+    <t>浦宿</t>
+  </si>
+  <si>
+    <t>女川</t>
+  </si>
+  <si>
+    <t>石巻線</t>
+    <rPh sb="0" eb="3">
+      <t>イシノマキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石巻線、仙石線、仙石東北ライン</t>
+    <rPh sb="0" eb="3">
+      <t>イシノマキセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>センセキセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>センセキトウホク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東照宮</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北仙台</t>
+  </si>
+  <si>
+    <t>北山（宮城）</t>
+  </si>
+  <si>
+    <t>東北福祉大前</t>
+  </si>
+  <si>
+    <t>国見（宮城）</t>
+  </si>
+  <si>
+    <t>葛岡</t>
+  </si>
+  <si>
+    <t>陸前落合</t>
+  </si>
+  <si>
+    <t>愛子</t>
+  </si>
+  <si>
+    <t>陸前白沢</t>
+  </si>
+  <si>
+    <t>熊ヶ根</t>
+  </si>
+  <si>
+    <t>作並</t>
+  </si>
+  <si>
+    <t>奥新川</t>
+  </si>
+  <si>
+    <t>仙山線</t>
+    <rPh sb="0" eb="3">
+      <t>センザンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仙山線、仙台地下鉄南北線</t>
+    <rPh sb="0" eb="3">
+      <t>センザンセン</t>
+    </rPh>
+    <rPh sb="4" eb="12">
+      <t>センダイチカテツナンボクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仙石線</t>
+  </si>
+  <si>
+    <t>あおば通</t>
+  </si>
+  <si>
+    <t>榴ヶ岡</t>
+  </si>
+  <si>
+    <t>宮城野原</t>
+  </si>
+  <si>
+    <t>陸前原ノ町</t>
+  </si>
+  <si>
+    <t>苦竹</t>
+  </si>
+  <si>
+    <t>小鶴新田</t>
+  </si>
+  <si>
+    <t>福田町</t>
+  </si>
+  <si>
+    <t>陸前高砂</t>
+  </si>
+  <si>
+    <t>中野栄</t>
+  </si>
+  <si>
+    <t>多賀城</t>
+  </si>
+  <si>
+    <t>下馬</t>
+  </si>
+  <si>
+    <t>西塩釜</t>
+  </si>
+  <si>
+    <t>本塩釜</t>
+  </si>
+  <si>
+    <t>東塩釜</t>
+  </si>
+  <si>
+    <t>陸前浜田</t>
+  </si>
+  <si>
+    <t>松島海岸</t>
+  </si>
+  <si>
+    <t>高城町</t>
+  </si>
+  <si>
+    <t>手樽</t>
+  </si>
+  <si>
+    <t>陸前富山</t>
+  </si>
+  <si>
+    <t>陸前大塚</t>
+  </si>
+  <si>
+    <t>東名</t>
+  </si>
+  <si>
+    <t>野蒜</t>
+  </si>
+  <si>
+    <t>陸前小野</t>
+  </si>
+  <si>
+    <t>鹿妻</t>
+  </si>
+  <si>
+    <t>矢本</t>
+  </si>
+  <si>
+    <t>東矢本</t>
+  </si>
+  <si>
+    <t>陸前赤井</t>
+  </si>
+  <si>
+    <t>石巻あゆみ野</t>
+  </si>
+  <si>
+    <t>蛇田</t>
+  </si>
+  <si>
+    <t>陸前山下</t>
+  </si>
+  <si>
+    <t>仙石線、仙石東北ライン</t>
+    <rPh sb="4" eb="8">
+      <t>センセキトウホク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唐桑大沢</t>
+  </si>
+  <si>
+    <t>上鹿折</t>
+  </si>
+  <si>
+    <t>八幡大橋</t>
+  </si>
+  <si>
+    <t>鹿折唐桑</t>
+  </si>
+  <si>
+    <t>内湾入口</t>
+  </si>
+  <si>
+    <t>気仙沼線（ＢＲＴ)、大船渡線</t>
+    <rPh sb="0" eb="3">
+      <t>ケセンヌマ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>オオフナトセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くりこま高原</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古川</t>
+    <rPh sb="0" eb="2">
+      <t>フルカワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白石蔵王</t>
+    <rPh sb="0" eb="4">
+      <t>シロイシザオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北新幹線、陸羽東線、秋田新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北新幹線、秋田新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有壁</t>
+    <rPh sb="0" eb="2">
+      <t>アリカベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石越</t>
+  </si>
+  <si>
+    <t>新田（宮城）</t>
+  </si>
+  <si>
+    <t>梅ヶ沢</t>
+  </si>
+  <si>
+    <t>瀬峰</t>
+  </si>
+  <si>
+    <t>田尻（宮城）</t>
+  </si>
+  <si>
+    <t>松山町（宮城）</t>
+  </si>
+  <si>
+    <t>鹿島台</t>
+  </si>
+  <si>
+    <t>品井沼</t>
+  </si>
+  <si>
+    <t>愛宕（宮城）</t>
+  </si>
+  <si>
+    <t>松島</t>
+  </si>
+  <si>
+    <t>塩釜</t>
+  </si>
+  <si>
+    <t>国府多賀城</t>
+  </si>
+  <si>
+    <t>陸前山王</t>
+  </si>
+  <si>
+    <t>岩切</t>
+  </si>
+  <si>
+    <t>東仙台</t>
+  </si>
+  <si>
+    <t>槻木</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>船岡（宮城）</t>
+  </si>
+  <si>
+    <t>大河原（宮城）</t>
+  </si>
+  <si>
+    <t>北白川</t>
+  </si>
+  <si>
+    <t>東白石</t>
+  </si>
+  <si>
+    <t>白石（宮城）</t>
+  </si>
+  <si>
+    <t>越河</t>
+  </si>
+  <si>
+    <t>東北本線、仙石東北ライン</t>
+    <rPh sb="0" eb="4">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>センセキトウホク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新利府</t>
+  </si>
+  <si>
+    <t>利府</t>
+  </si>
+  <si>
+    <t>東北本線（利府支線）</t>
+    <rPh sb="0" eb="4">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>リフシセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北本線、仙石東北ライン、東北本線（利府支線）</t>
+    <rPh sb="0" eb="4">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>センセキトウホク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、東北本線、東北本線（利府支線）、仙石東北ライン、仙山線、仙石線、仙台地下鉄南北線、仙台地下鉄東西線、仙台空港アクセス線、東北新幹線、秋田新幹線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北本線、阿武隈急行</t>
+    <rPh sb="0" eb="4">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北浦（宮城）</t>
+  </si>
+  <si>
+    <t>陸前谷地</t>
+  </si>
+  <si>
+    <t>塚目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西古川</t>
+  </si>
+  <si>
+    <t>東大崎</t>
+  </si>
+  <si>
+    <t>西大崎</t>
+  </si>
+  <si>
+    <t>岩出山</t>
+  </si>
+  <si>
+    <t>有備館</t>
+  </si>
+  <si>
+    <t>上野目</t>
+  </si>
+  <si>
+    <t>池月</t>
+  </si>
+  <si>
+    <t>川渡温泉</t>
+  </si>
+  <si>
+    <t>鳴子御殿湯</t>
+  </si>
+  <si>
+    <t>鳴子温泉</t>
+  </si>
+  <si>
+    <t>中山平温泉</t>
+  </si>
+  <si>
+    <t>陸羽東線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東船岡</t>
+  </si>
+  <si>
+    <t>岡</t>
+  </si>
+  <si>
+    <t>横倉（宮城）</t>
+  </si>
+  <si>
+    <t>角田</t>
+  </si>
+  <si>
+    <t>南角田</t>
+  </si>
+  <si>
+    <t>北丸森</t>
+  </si>
+  <si>
+    <t>丸森</t>
+  </si>
+  <si>
+    <t>あぶくま</t>
+  </si>
+  <si>
+    <t>阿武隈急行</t>
+    <rPh sb="0" eb="5">
+      <t>アブクマキュウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富沢</t>
+  </si>
+  <si>
+    <t>長町南</t>
+  </si>
+  <si>
+    <t>長町一丁目</t>
+  </si>
+  <si>
+    <t>河原町（宮城）</t>
+  </si>
+  <si>
+    <t>愛宕橋</t>
+  </si>
+  <si>
+    <t>五橋</t>
+  </si>
+  <si>
+    <t>広瀬通</t>
+  </si>
+  <si>
+    <t>勾当台公園</t>
+  </si>
+  <si>
+    <t>北四番丁</t>
+  </si>
+  <si>
+    <t>台原</t>
+  </si>
+  <si>
+    <t>旭ヶ丘（宮城）</t>
+  </si>
+  <si>
+    <t>黒松（宮城）</t>
+  </si>
+  <si>
+    <t>八乙女</t>
+  </si>
+  <si>
+    <t>泉中央</t>
+  </si>
+  <si>
+    <t>仙台地下鉄南北線</t>
+  </si>
+  <si>
+    <t>仙台空港アクセス線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杜せきのした</t>
+  </si>
+  <si>
+    <t>美田園</t>
+  </si>
+  <si>
+    <t>仙台空港</t>
+  </si>
+  <si>
+    <t>石巻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八木山動物公園</t>
+  </si>
+  <si>
+    <t>青葉山</t>
+  </si>
+  <si>
+    <t>川内（宮城）</t>
+  </si>
+  <si>
+    <t>国際センター（宮城）</t>
+  </si>
+  <si>
+    <t>大町西公園</t>
+  </si>
+  <si>
+    <t>青葉通一番町</t>
+  </si>
+  <si>
+    <t>宮城野通</t>
+  </si>
+  <si>
+    <t>連坊</t>
+  </si>
+  <si>
+    <t>薬師堂（宮城）</t>
+  </si>
+  <si>
+    <t>卸町（宮城）</t>
+  </si>
+  <si>
+    <t>六丁の目</t>
+  </si>
+  <si>
+    <t>荒井（宮城）</t>
+  </si>
+  <si>
+    <t>仙台地下鉄東西線</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3383,7 +4170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3391,6 +4178,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3732,7 +4522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B761"/>
+  <dimension ref="A1:B945"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -9675,115 +10465,1568 @@
       </c>
     </row>
     <row r="748" spans="1:2">
-      <c r="A748" s="2" t="s">
+      <c r="A748" t="s">
         <v>827</v>
       </c>
-      <c r="B748" s="2" t="s">
+      <c r="B748" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="749" spans="1:2">
-      <c r="A749" s="2" t="s">
+      <c r="A749" t="s">
         <v>828</v>
       </c>
-      <c r="B749" s="2" t="s">
+      <c r="B749" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="750" spans="1:2">
-      <c r="A750" s="2" t="s">
+      <c r="A750" t="s">
         <v>829</v>
       </c>
-      <c r="B750" s="2" t="s">
+      <c r="B750" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="751" spans="1:2">
-      <c r="A751" s="2" t="s">
+      <c r="A751" t="s">
         <v>830</v>
       </c>
-      <c r="B751" s="2" t="s">
+      <c r="B751" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="752" spans="1:2">
-      <c r="A752" s="2" t="s">
+      <c r="A752" t="s">
         <v>831</v>
       </c>
-      <c r="B752" s="2" t="s">
+      <c r="B752" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="753" spans="1:2">
-      <c r="A753" s="2" t="s">
+      <c r="A753" t="s">
         <v>832</v>
       </c>
-      <c r="B753" s="2" t="s">
+      <c r="B753" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="754" spans="1:2">
-      <c r="A754" s="2" t="s">
+      <c r="A754" t="s">
         <v>833</v>
       </c>
-      <c r="B754" s="2" t="s">
+      <c r="B754" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="755" spans="1:2">
-      <c r="A755" s="2" t="s">
+      <c r="A755" t="s">
         <v>834</v>
       </c>
-      <c r="B755" s="2" t="s">
+      <c r="B755" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="756" spans="1:2">
-      <c r="A756" s="2" t="s">
+      <c r="A756" t="s">
         <v>835</v>
       </c>
-      <c r="B756" s="2" t="s">
+      <c r="B756" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="757" spans="1:2">
-      <c r="A757" s="2" t="s">
+      <c r="A757" t="s">
         <v>836</v>
       </c>
-      <c r="B757" s="2" t="s">
+      <c r="B757" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="758" spans="1:2">
-      <c r="A758" s="2" t="s">
+      <c r="A758" t="s">
         <v>837</v>
       </c>
-      <c r="B758" s="2" t="s">
+      <c r="B758" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="759" spans="1:2">
-      <c r="A759" s="2" t="s">
+      <c r="A759" t="s">
         <v>838</v>
       </c>
-      <c r="B759" s="2" t="s">
+      <c r="B759" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="760" spans="1:2">
-      <c r="A760" s="2" t="s">
+      <c r="A760" t="s">
         <v>839</v>
       </c>
-      <c r="B760" s="2" t="s">
+      <c r="B760" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="761" spans="1:2">
-      <c r="A761" s="2" t="s">
+      <c r="A761" t="s">
         <v>604</v>
       </c>
-      <c r="B761" s="2" t="s">
+      <c r="B761" t="s">
         <v>605</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B765" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B766" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B767" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B768" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B769" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B770" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B771" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B772" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B773" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B774" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="B775" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B776" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B777" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B778" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B779" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B780" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B781" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B782" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B783" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B784" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B785" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B786" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B787" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B788" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B789" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B790" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B791" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B792" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B793" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B794" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B795" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B796" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B797" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B798" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B799" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B800" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B801" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B802" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B803" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B804" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B805" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B806" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B807" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B808" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B809" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B810" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B811" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B812" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B813" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B814" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B815" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B816" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B817" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B818" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B819" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2">
+      <c r="A820" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B820" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B821" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2">
+      <c r="A822" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="B822" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2">
+      <c r="A823" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B823" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2">
+      <c r="A824" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B824" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2">
+      <c r="A825" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B825" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2">
+      <c r="A826" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B826" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2">
+      <c r="A827" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B827" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2">
+      <c r="A828" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="B828" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2">
+      <c r="A829" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B829" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2">
+      <c r="A830" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B830" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2">
+      <c r="A831" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B831" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2">
+      <c r="A832" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B832" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B833" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B834" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B835" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B836" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B837" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B838" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B839" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B840" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B841" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B842" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B843" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B844" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B845" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B846" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B847" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B848" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B849" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B850" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B851" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B852" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B853" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B854" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B855" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B856" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B857" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B858" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B859" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B860" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="B861" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="B862" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B863" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="B864" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B865" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2">
+      <c r="A866" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="B866" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2">
+      <c r="A867" t="s">
+        <v>958</v>
+      </c>
+      <c r="B867" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2">
+      <c r="A868" t="s">
+        <v>959</v>
+      </c>
+      <c r="B868" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2">
+      <c r="A869" t="s">
+        <v>960</v>
+      </c>
+      <c r="B869" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2">
+      <c r="A870" t="s">
+        <v>964</v>
+      </c>
+      <c r="B870" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2">
+      <c r="A871" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="B871" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2">
+      <c r="A872" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="B872" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2">
+      <c r="A873" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B873" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2">
+      <c r="A874" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B874" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2">
+      <c r="A875" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B875" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2">
+      <c r="A876" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B876" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2">
+      <c r="A877" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B877" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2">
+      <c r="A878" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B878" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2">
+      <c r="A879" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B879" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2">
+      <c r="A880" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B880" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2">
+      <c r="A881" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B881" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B882" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2">
+      <c r="A883" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B883" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2">
+      <c r="A884" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B884" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2">
+      <c r="A885" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B885" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2">
+      <c r="A886" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B886" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2">
+      <c r="A887" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B887" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B888" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B889" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2">
+      <c r="A890" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B890" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2">
+      <c r="A891" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B891" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2">
+      <c r="A892" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B892" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2">
+      <c r="A893" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B893" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2">
+      <c r="A894" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B894" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2">
+      <c r="A895" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2">
+      <c r="A896" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2">
+      <c r="A897" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2">
+      <c r="A898" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2">
+      <c r="A899" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2">
+      <c r="A900" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B900" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2">
+      <c r="A901" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B901" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2">
+      <c r="A902" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B902" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2">
+      <c r="A903" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B903" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2">
+      <c r="A904" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2">
+      <c r="A905" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2">
+      <c r="A906" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2">
+      <c r="A907" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2">
+      <c r="A908" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2">
+      <c r="A909" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2">
+      <c r="A910" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2">
+      <c r="A911" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2">
+      <c r="A912" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2">
+      <c r="A913" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B913" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2">
+      <c r="A914" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2">
+      <c r="A915" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2">
+      <c r="A916" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2">
+      <c r="A917" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2">
+      <c r="A923" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B930" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2">
+      <c r="A931" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B931" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2">
+      <c r="A932" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B932" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B933" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2">
+      <c r="A934" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2">
+      <c r="A939" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2">
+      <c r="A940" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2">
+      <c r="A942" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1050</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC21E81E-D21B-487C-9A39-52416A3AA7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC3172C-EB8D-47EA-A27F-E897D950475C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1342">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -3447,6 +3447,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>陸羽東線</t>
+  </si>
+  <si>
     <t>東新城</t>
   </si>
   <si>
@@ -4116,6 +4119,1065 @@
   <si>
     <t>仙台地下鉄東西線</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋田</t>
+  </si>
+  <si>
+    <t>秋田県</t>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羽後牛島</t>
+  </si>
+  <si>
+    <t>新屋（秋田）</t>
+  </si>
+  <si>
+    <t>桂根</t>
+  </si>
+  <si>
+    <t>下浜</t>
+  </si>
+  <si>
+    <t>道川</t>
+  </si>
+  <si>
+    <t>岩城みなと</t>
+  </si>
+  <si>
+    <t>羽後亀田</t>
+  </si>
+  <si>
+    <t>折渡</t>
+  </si>
+  <si>
+    <t>羽後岩谷</t>
+  </si>
+  <si>
+    <t>羽後本荘</t>
+  </si>
+  <si>
+    <t>西目</t>
+  </si>
+  <si>
+    <t>仁賀保</t>
+  </si>
+  <si>
+    <t>金浦</t>
+  </si>
+  <si>
+    <t>象潟</t>
+  </si>
+  <si>
+    <t>上浜</t>
+  </si>
+  <si>
+    <t>小砂川</t>
+  </si>
+  <si>
+    <t>羽越本線</t>
+    <rPh sb="0" eb="4">
+      <t>ウエツホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羽越本線、奥羽本線、男鹿線、秋田新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>ウエツホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>オガセン</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羽越本線、由利高原鉄道鳥海山ろく線</t>
+    <rPh sb="0" eb="4">
+      <t>ウエツホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陣場</t>
+  </si>
+  <si>
+    <t>白沢（秋田）</t>
+  </si>
+  <si>
+    <t>大館</t>
+  </si>
+  <si>
+    <t>下川沿</t>
+  </si>
+  <si>
+    <t>早口</t>
+  </si>
+  <si>
+    <t>糠沢</t>
+  </si>
+  <si>
+    <t>鷹ノ巣</t>
+  </si>
+  <si>
+    <t>前山</t>
+  </si>
+  <si>
+    <t>二ッ井</t>
+  </si>
+  <si>
+    <t>富根</t>
+  </si>
+  <si>
+    <t>鶴形</t>
+  </si>
+  <si>
+    <t>東能代</t>
+  </si>
+  <si>
+    <t>北金岡</t>
+  </si>
+  <si>
+    <t>森岳</t>
+  </si>
+  <si>
+    <t>鹿渡</t>
+  </si>
+  <si>
+    <t>鯉川</t>
+  </si>
+  <si>
+    <t>八郎潟</t>
+  </si>
+  <si>
+    <t>井川さくら</t>
+  </si>
+  <si>
+    <t>羽後飯塚</t>
+  </si>
+  <si>
+    <t>大久保（秋田）</t>
+  </si>
+  <si>
+    <t>追分（秋田）</t>
+  </si>
+  <si>
+    <t>上飯島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土崎</t>
+  </si>
+  <si>
+    <t>泉外旭川</t>
+  </si>
+  <si>
+    <t>四ッ小屋</t>
+  </si>
+  <si>
+    <t>和田</t>
+  </si>
+  <si>
+    <t>大張野</t>
+  </si>
+  <si>
+    <t>羽後境</t>
+  </si>
+  <si>
+    <t>峰吉川</t>
+  </si>
+  <si>
+    <t>刈和野</t>
+  </si>
+  <si>
+    <t>神宮寺</t>
+  </si>
+  <si>
+    <t>大曲（秋田）</t>
+  </si>
+  <si>
+    <t>飯詰</t>
+  </si>
+  <si>
+    <t>後三年</t>
+  </si>
+  <si>
+    <t>横手</t>
+  </si>
+  <si>
+    <t>柳田</t>
+  </si>
+  <si>
+    <t>醍醐（秋田）</t>
+  </si>
+  <si>
+    <t>十文字</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下湯沢</t>
+  </si>
+  <si>
+    <t>湯沢</t>
+  </si>
+  <si>
+    <t>上湯沢</t>
+  </si>
+  <si>
+    <t>三関</t>
+  </si>
+  <si>
+    <t>横堀</t>
+  </si>
+  <si>
+    <t>院内</t>
+  </si>
+  <si>
+    <t>奥羽本線、花輪線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ハナワセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、五能線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゴノウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、男鹿線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>オガセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、田沢湖線、秋田新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>タザワコセン</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、北上線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>キタカミセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>湯瀬温泉</t>
+  </si>
+  <si>
+    <t>八幡平</t>
+  </si>
+  <si>
+    <t>陸中大里</t>
+  </si>
+  <si>
+    <t>鹿角花輪</t>
+  </si>
+  <si>
+    <t>柴平</t>
+  </si>
+  <si>
+    <t>十和田南</t>
+  </si>
+  <si>
+    <t>末広</t>
+  </si>
+  <si>
+    <t>土深井</t>
+  </si>
+  <si>
+    <t>沢尻</t>
+  </si>
+  <si>
+    <t>十二所</t>
+  </si>
+  <si>
+    <t>大滝温泉</t>
+  </si>
+  <si>
+    <t>扇田</t>
+  </si>
+  <si>
+    <t>東大館</t>
+  </si>
+  <si>
+    <t>五能線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩館</t>
+  </si>
+  <si>
+    <t>あきた白神</t>
+  </si>
+  <si>
+    <t>滝ノ間</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八森</t>
+  </si>
+  <si>
+    <t>東八森</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沢目</t>
+  </si>
+  <si>
+    <t>鳥形</t>
+  </si>
+  <si>
+    <t>北能代</t>
+  </si>
+  <si>
+    <t>向能代</t>
+  </si>
+  <si>
+    <t>能代</t>
+  </si>
+  <si>
+    <t>出戸浜</t>
+  </si>
+  <si>
+    <t>男鹿線</t>
+    <rPh sb="0" eb="3">
+      <t>オガセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上二田</t>
+  </si>
+  <si>
+    <t>二田</t>
+  </si>
+  <si>
+    <t>天王</t>
+  </si>
+  <si>
+    <t>船越</t>
+  </si>
+  <si>
+    <t>脇本</t>
+  </si>
+  <si>
+    <t>羽立</t>
+  </si>
+  <si>
+    <t>男鹿</t>
+  </si>
+  <si>
+    <t>田沢湖</t>
+  </si>
+  <si>
+    <t>刺巻</t>
+  </si>
+  <si>
+    <t>神代（秋田）</t>
+  </si>
+  <si>
+    <t>生田（秋田）</t>
+  </si>
+  <si>
+    <t>角館</t>
+  </si>
+  <si>
+    <t>鶯野</t>
+  </si>
+  <si>
+    <t>羽後長野</t>
+  </si>
+  <si>
+    <t>鑓見内</t>
+  </si>
+  <si>
+    <t>羽後四ッ屋</t>
+  </si>
+  <si>
+    <t>北大曲</t>
+  </si>
+  <si>
+    <t>田沢湖線、秋田内陸縦貫鉄道、秋田新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>タザワコセン</t>
+    </rPh>
+    <rPh sb="5" eb="13">
+      <t>アキタナイリクジュウカンテツドウ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>アキタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒沢（ＪＲ）</t>
+  </si>
+  <si>
+    <t>小松川</t>
+  </si>
+  <si>
+    <t>相野々</t>
+  </si>
+  <si>
+    <t>北上線</t>
+    <rPh sb="0" eb="3">
+      <t>キタカミセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋田内陸縦貫鉄道</t>
+  </si>
+  <si>
+    <t>羽後太田</t>
+  </si>
+  <si>
+    <t>西明寺</t>
+  </si>
+  <si>
+    <t>八津</t>
+  </si>
+  <si>
+    <t>羽後長戸呂</t>
+  </si>
+  <si>
+    <t>松葉</t>
+  </si>
+  <si>
+    <t>羽後中里</t>
+  </si>
+  <si>
+    <t>左通</t>
+  </si>
+  <si>
+    <t>上桧木内</t>
+  </si>
+  <si>
+    <t>戸沢</t>
+  </si>
+  <si>
+    <t>阿仁マタギ</t>
+  </si>
+  <si>
+    <t>奥阿仁</t>
+  </si>
+  <si>
+    <t>比立内</t>
+  </si>
+  <si>
+    <t>岩野目</t>
+  </si>
+  <si>
+    <t>笑内</t>
+  </si>
+  <si>
+    <t>萱草</t>
+  </si>
+  <si>
+    <t>荒瀬</t>
+  </si>
+  <si>
+    <t>阿仁合</t>
+  </si>
+  <si>
+    <t>小渕</t>
+  </si>
+  <si>
+    <t>前田南</t>
+  </si>
+  <si>
+    <t>阿仁前田温泉</t>
+  </si>
+  <si>
+    <t>桂瀬</t>
+  </si>
+  <si>
+    <t>米内沢</t>
+  </si>
+  <si>
+    <t>上杉</t>
+  </si>
+  <si>
+    <t>合川</t>
+  </si>
+  <si>
+    <t>大野台</t>
+  </si>
+  <si>
+    <t>縄文小ヶ田</t>
+  </si>
+  <si>
+    <t>西鷹巣</t>
+  </si>
+  <si>
+    <t>鷹巣</t>
+  </si>
+  <si>
+    <t>由利高原鉄道鳥海山ろく線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬師堂（秋田）</t>
+  </si>
+  <si>
+    <t>子吉</t>
+  </si>
+  <si>
+    <t>鮎川（秋田）</t>
+  </si>
+  <si>
+    <t>黒沢（由利高原鉄道）</t>
+  </si>
+  <si>
+    <t>曲沢</t>
+  </si>
+  <si>
+    <t>前郷</t>
+  </si>
+  <si>
+    <t>久保田（秋田）</t>
+  </si>
+  <si>
+    <t>西滝沢</t>
+  </si>
+  <si>
+    <t>吉沢</t>
+  </si>
+  <si>
+    <t>川辺</t>
+  </si>
+  <si>
+    <t>矢島</t>
+  </si>
+  <si>
+    <t>山形県</t>
+    <rPh sb="0" eb="3">
+      <t>ヤマガタケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>女鹿</t>
+  </si>
+  <si>
+    <t>吹浦</t>
+  </si>
+  <si>
+    <t>遊佐</t>
+  </si>
+  <si>
+    <t>南鳥海</t>
+  </si>
+  <si>
+    <t>本楯</t>
+  </si>
+  <si>
+    <t>酒田</t>
+  </si>
+  <si>
+    <t>東酒田</t>
+  </si>
+  <si>
+    <t>砂越</t>
+  </si>
+  <si>
+    <t>北余目</t>
+  </si>
+  <si>
+    <t>余目</t>
+  </si>
+  <si>
+    <t>西袋</t>
+  </si>
+  <si>
+    <t>鶴岡</t>
+  </si>
+  <si>
+    <t>藤島</t>
+    <rPh sb="0" eb="2">
+      <t>フジシマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羽前大山</t>
+  </si>
+  <si>
+    <t>羽前水沢</t>
+  </si>
+  <si>
+    <t>三瀬</t>
+  </si>
+  <si>
+    <t>小波渡</t>
+  </si>
+  <si>
+    <t>五十川</t>
+  </si>
+  <si>
+    <t>あつみ温泉</t>
+  </si>
+  <si>
+    <t>小岩川</t>
+  </si>
+  <si>
+    <t>鼠ヶ関</t>
+  </si>
+  <si>
+    <t>板谷</t>
+  </si>
+  <si>
+    <t>峠</t>
+  </si>
+  <si>
+    <t>関根</t>
+  </si>
+  <si>
+    <t>米沢</t>
+  </si>
+  <si>
+    <t>置賜</t>
+  </si>
+  <si>
+    <t>高畠</t>
+  </si>
+  <si>
+    <t>赤湯</t>
+  </si>
+  <si>
+    <t>中川（山形）</t>
+  </si>
+  <si>
+    <t>羽前中山</t>
+  </si>
+  <si>
+    <t>かみのやま温泉</t>
+  </si>
+  <si>
+    <t>茂吉記念館前</t>
+  </si>
+  <si>
+    <t>蔵王</t>
+  </si>
+  <si>
+    <t>山形</t>
+  </si>
+  <si>
+    <t>北山形</t>
+  </si>
+  <si>
+    <t>羽前千歳</t>
+  </si>
+  <si>
+    <t>南出羽</t>
+  </si>
+  <si>
+    <t>漆山（山形）</t>
+  </si>
+  <si>
+    <t>高擶</t>
+  </si>
+  <si>
+    <t>天童南</t>
+  </si>
+  <si>
+    <t>天童</t>
+  </si>
+  <si>
+    <t>乱川</t>
+  </si>
+  <si>
+    <t>神町</t>
+  </si>
+  <si>
+    <t>さくらんぼ東根</t>
+  </si>
+  <si>
+    <t>東根</t>
+  </si>
+  <si>
+    <t>村山（山形）</t>
+  </si>
+  <si>
+    <t>袖崎</t>
+  </si>
+  <si>
+    <t>大石田</t>
+  </si>
+  <si>
+    <t>北大石田</t>
+  </si>
+  <si>
+    <t>芦沢</t>
+  </si>
+  <si>
+    <t>舟形</t>
+  </si>
+  <si>
+    <t>新庄</t>
+  </si>
+  <si>
+    <t>泉田</t>
+  </si>
+  <si>
+    <t>羽前豊里</t>
+  </si>
+  <si>
+    <t>真室川</t>
+  </si>
+  <si>
+    <t>釜淵</t>
+  </si>
+  <si>
+    <t>大滝</t>
+  </si>
+  <si>
+    <t>及位</t>
+  </si>
+  <si>
+    <t>奥羽本線、米坂線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨネサカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="9" eb="14">
+      <t>ヤマガタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ヤマガタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、山形鉄道フラワー長井線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="17" eb="22">
+      <t>ヤマガタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、仙山線、左沢線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>センザンセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>アテラザワセン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヤマガタ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>シンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、仙山線、左沢線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>センザンセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>アテラザワセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、仙山線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>センザンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥羽本線、陸羽東線、陸羽西線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>リクウヒガシセン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>リクウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="15" eb="20">
+      <t>ヤマガタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左沢線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東金井</t>
+  </si>
+  <si>
+    <t>羽前山辺</t>
+  </si>
+  <si>
+    <t>羽前金沢</t>
+  </si>
+  <si>
+    <t>羽前長崎</t>
+  </si>
+  <si>
+    <t>南寒河江</t>
+  </si>
+  <si>
+    <t>寒河江</t>
+  </si>
+  <si>
+    <t>西寒河江</t>
+  </si>
+  <si>
+    <t>羽前高松</t>
+  </si>
+  <si>
+    <t>柴橋</t>
+  </si>
+  <si>
+    <t>左沢</t>
+  </si>
+  <si>
+    <t>面白山高原</t>
+  </si>
+  <si>
+    <t>山寺</t>
+  </si>
+  <si>
+    <t>高瀬（山形）</t>
+  </si>
+  <si>
+    <t>楯山</t>
+  </si>
+  <si>
+    <t>米坂線</t>
+  </si>
+  <si>
+    <t>南米沢</t>
+  </si>
+  <si>
+    <t>西米沢</t>
+  </si>
+  <si>
+    <t>成島（山形）</t>
+  </si>
+  <si>
+    <t>中郡（山形）</t>
+  </si>
+  <si>
+    <t>羽前小松</t>
+  </si>
+  <si>
+    <t>犬川</t>
+  </si>
+  <si>
+    <t>今泉（山形）</t>
+  </si>
+  <si>
+    <t>萩生</t>
+  </si>
+  <si>
+    <t>羽前椿</t>
+  </si>
+  <si>
+    <t>手ノ子</t>
+  </si>
+  <si>
+    <t>羽前沼沢</t>
+  </si>
+  <si>
+    <t>伊佐領</t>
+  </si>
+  <si>
+    <t>羽前松岡</t>
+  </si>
+  <si>
+    <t>小国</t>
+  </si>
+  <si>
+    <t>米坂線、山形鉄道フラワー長井線</t>
+    <rPh sb="4" eb="8">
+      <t>ヤマガタテツドウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ナガイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陸羽西線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>升形</t>
+  </si>
+  <si>
+    <t>津谷</t>
+  </si>
+  <si>
+    <t>古口</t>
+  </si>
+  <si>
+    <t>清川</t>
+  </si>
+  <si>
+    <t>狩川</t>
+  </si>
+  <si>
+    <t>南野</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羽越本線、陸羽西線</t>
+    <rPh sb="0" eb="4">
+      <t>ウエツホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堺田</t>
+  </si>
+  <si>
+    <t>赤倉温泉</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立小路</t>
+  </si>
+  <si>
+    <t>最上</t>
+  </si>
+  <si>
+    <t>大堀</t>
+  </si>
+  <si>
+    <t>鵜杉</t>
+  </si>
+  <si>
+    <t>瀬見温泉</t>
+  </si>
+  <si>
+    <t>東長沢</t>
+  </si>
+  <si>
+    <t>長沢</t>
+  </si>
+  <si>
+    <t>南新庄</t>
+  </si>
+  <si>
+    <t>南陽市役所</t>
+  </si>
+  <si>
+    <t>宮内（山形）</t>
+  </si>
+  <si>
+    <t>おりはた</t>
+  </si>
+  <si>
+    <t>梨郷</t>
+  </si>
+  <si>
+    <t>西大塚</t>
+  </si>
+  <si>
+    <t>時庭</t>
+  </si>
+  <si>
+    <t>南長井</t>
+  </si>
+  <si>
+    <t>長井</t>
+  </si>
+  <si>
+    <t>あやめ公園</t>
+  </si>
+  <si>
+    <t>羽前成田</t>
+  </si>
+  <si>
+    <t>白兎</t>
+  </si>
+  <si>
+    <t>蚕桑</t>
+  </si>
+  <si>
+    <t>鮎貝</t>
+  </si>
+  <si>
+    <t>四季の郷</t>
+  </si>
+  <si>
+    <t>荒砥</t>
+  </si>
+  <si>
+    <t>山形鉄道フラワー長井線</t>
   </si>
 </sst>
 </file>
@@ -4522,7 +5584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B945"/>
+  <dimension ref="A1:B1212"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -10586,7 +11648,7 @@
         <v>842</v>
       </c>
       <c r="B765" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -10594,7 +11656,7 @@
         <v>843</v>
       </c>
       <c r="B766" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -10602,7 +11664,7 @@
         <v>844</v>
       </c>
       <c r="B767" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -10610,7 +11672,7 @@
         <v>845</v>
       </c>
       <c r="B768" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -10831,7 +11893,7 @@
     </row>
     <row r="796" spans="1:2">
       <c r="A796" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B796" t="s">
         <v>853</v>
@@ -10839,527 +11901,527 @@
     </row>
     <row r="797" spans="1:2">
       <c r="A797" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B797" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B798" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B799" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B800" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B801" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B802" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B803" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B804" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B805" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B806" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B807" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B808" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B809" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B810" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B811" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B812" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B813" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B814" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B815" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B816" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B817" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B818" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B819" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B820" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B821" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B822" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B823" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B824" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B825" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B826" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B827" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B828" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B829" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B830" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B831" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B832" t="s">
         <v>921</v>
-      </c>
-      <c r="B832" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B833" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B834" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B835" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B836" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B837" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B838" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B839" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B840" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B841" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B842" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B843" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B844" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B845" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B846" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B847" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B848" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B849" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B850" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B851" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B852" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B853" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B854" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B855" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B856" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B857" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B858" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B859" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B860" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B861" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B862" t="s">
         <v>708</v>
@@ -11367,7 +12429,7 @@
     </row>
     <row r="863" spans="1:2">
       <c r="A863" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B863" t="s">
         <v>708</v>
@@ -11375,7 +12437,7 @@
     </row>
     <row r="864" spans="1:2">
       <c r="A864" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B864" t="s">
         <v>708</v>
@@ -11383,7 +12445,7 @@
     </row>
     <row r="865" spans="1:2">
       <c r="A865" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B865" t="s">
         <v>708</v>
@@ -11391,7 +12453,7 @@
     </row>
     <row r="866" spans="1:2">
       <c r="A866" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B866" t="s">
         <v>708</v>
@@ -11399,31 +12461,31 @@
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B867" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B868" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B869" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B870" t="s">
         <v>764</v>
@@ -11431,7 +12493,7 @@
     </row>
     <row r="871" spans="1:2">
       <c r="A871" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B871" t="s">
         <v>764</v>
@@ -11439,7 +12501,7 @@
     </row>
     <row r="872" spans="1:2">
       <c r="A872" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B872" t="s">
         <v>764</v>
@@ -11447,7 +12509,7 @@
     </row>
     <row r="873" spans="1:2">
       <c r="A873" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B873" t="s">
         <v>764</v>
@@ -11455,7 +12517,7 @@
     </row>
     <row r="874" spans="1:2">
       <c r="A874" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B874" t="s">
         <v>764</v>
@@ -11463,7 +12525,7 @@
     </row>
     <row r="875" spans="1:2">
       <c r="A875" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B875" t="s">
         <v>764</v>
@@ -11471,7 +12533,7 @@
     </row>
     <row r="876" spans="1:2">
       <c r="A876" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B876" t="s">
         <v>764</v>
@@ -11479,7 +12541,7 @@
     </row>
     <row r="877" spans="1:2">
       <c r="A877" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B877" t="s">
         <v>764</v>
@@ -11487,7 +12549,7 @@
     </row>
     <row r="878" spans="1:2">
       <c r="A878" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B878" t="s">
         <v>764</v>
@@ -11495,7 +12557,7 @@
     </row>
     <row r="879" spans="1:2">
       <c r="A879" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B879" t="s">
         <v>764</v>
@@ -11503,7 +12565,7 @@
     </row>
     <row r="880" spans="1:2">
       <c r="A880" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B880" t="s">
         <v>764</v>
@@ -11511,55 +12573,55 @@
     </row>
     <row r="881" spans="1:2">
       <c r="A881" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B881" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B882" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B883" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B884" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B885" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B886" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B887" t="s">
         <v>764</v>
@@ -11567,7 +12629,7 @@
     </row>
     <row r="888" spans="1:2">
       <c r="A888" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B888" t="s">
         <v>764</v>
@@ -11575,7 +12637,7 @@
     </row>
     <row r="889" spans="1:2">
       <c r="A889" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B889" t="s">
         <v>764</v>
@@ -11583,7 +12645,7 @@
     </row>
     <row r="890" spans="1:2">
       <c r="A890" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B890" t="s">
         <v>764</v>
@@ -11591,7 +12653,7 @@
     </row>
     <row r="891" spans="1:2">
       <c r="A891" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B891" t="s">
         <v>764</v>
@@ -11599,7 +12661,7 @@
     </row>
     <row r="892" spans="1:2">
       <c r="A892" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B892" t="s">
         <v>764</v>
@@ -11607,426 +12669,2524 @@
     </row>
     <row r="893" spans="1:2">
       <c r="A893" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B893" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B894" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B895" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B896" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B897" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B898" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B899" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B900" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B901" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B902" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B903" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B904" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B905" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B906" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B907" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B908" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B909" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B910" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B911" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B912" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B913" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B914" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B915" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B916" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B917" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B918" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B919" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B920" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B921" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B922" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B923" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B924" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B925" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B926" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B927" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B928" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B929" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B930" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B931" t="s">
         <v>1034</v>
-      </c>
-      <c r="B931" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B932" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B933" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B934" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B935" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B936" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B937" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B938" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B939" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B940" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B941" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B942" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B943" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B944" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B945" t="s">
-        <v>1050</v>
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2">
+      <c r="A948" s="2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2">
+      <c r="A949" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B949" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2">
+      <c r="A950" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B950" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2">
+      <c r="A951" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2">
+      <c r="A952" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2">
+      <c r="A953" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2">
+      <c r="A954" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2">
+      <c r="A955" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2">
+      <c r="A956" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2">
+      <c r="A957" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2">
+      <c r="A958" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2">
+      <c r="A959" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2">
+      <c r="A960" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2">
+      <c r="A961" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2">
+      <c r="A962" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2">
+      <c r="A963" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2">
+      <c r="A964" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2">
+      <c r="A965" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2">
+      <c r="A966" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B966" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2">
+      <c r="A967" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B967" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2">
+      <c r="A968" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2">
+      <c r="A969" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B969" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2">
+      <c r="A970" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B970" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2">
+      <c r="A971" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B971" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2">
+      <c r="A972" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B972" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2">
+      <c r="A973" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B973" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2">
+      <c r="A974" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B974" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2">
+      <c r="A975" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B975" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2">
+      <c r="A976" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B976" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2">
+      <c r="A977" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B977" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2">
+      <c r="A978" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B978" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2">
+      <c r="A979" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B979" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2">
+      <c r="A980" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B980" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2">
+      <c r="A981" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B981" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2">
+      <c r="A982" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B982" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2">
+      <c r="A983" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B983" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2">
+      <c r="A984" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B984" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2">
+      <c r="A985" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B985" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2">
+      <c r="A986" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B986" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2">
+      <c r="A987" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B987" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2">
+      <c r="A988" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2">
+      <c r="A989" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B989" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2">
+      <c r="A990" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B990" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2">
+      <c r="A991" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B991" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2">
+      <c r="A992" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B992" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2">
+      <c r="A993" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B993" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2">
+      <c r="A994" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B994" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2">
+      <c r="A995" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B995" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2">
+      <c r="A996" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B996" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2">
+      <c r="A997" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B997" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2">
+      <c r="A998" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B998" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2">
+      <c r="A999" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B999" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2">
+      <c r="A1000" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2">
+      <c r="A1001" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:2">
+      <c r="A1002" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:2">
+      <c r="A1003" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:2">
+      <c r="A1004" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:2">
+      <c r="A1005" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:2">
+      <c r="A1006" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:2">
+      <c r="A1007" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:2">
+      <c r="A1008" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:2">
+      <c r="A1009" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:2">
+      <c r="A1010" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:2">
+      <c r="A1011" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:2">
+      <c r="A1012" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:2">
+      <c r="A1013" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:2">
+      <c r="A1014" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:2">
+      <c r="A1015" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:2">
+      <c r="A1016" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:2">
+      <c r="A1017" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:2">
+      <c r="A1018" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:2">
+      <c r="A1019" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:2">
+      <c r="A1020" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:2">
+      <c r="A1021" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:2">
+      <c r="A1022" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:2">
+      <c r="A1023" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:2">
+      <c r="A1024" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:2">
+      <c r="A1025" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:2">
+      <c r="A1026" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:2">
+      <c r="A1027" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:2">
+      <c r="A1028" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:2">
+      <c r="A1029" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:2">
+      <c r="A1030" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:2">
+      <c r="A1031" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:2">
+      <c r="A1032" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:2">
+      <c r="A1033" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:2">
+      <c r="A1034" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:2">
+      <c r="A1035" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:2">
+      <c r="A1036" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:2">
+      <c r="A1037" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:2">
+      <c r="A1038" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:2">
+      <c r="A1039" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:2">
+      <c r="A1040" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:2">
+      <c r="A1041" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:2">
+      <c r="A1042" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:2">
+      <c r="A1043" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:2">
+      <c r="A1044" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:2">
+      <c r="A1045" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:2">
+      <c r="A1046" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:2">
+      <c r="A1047" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:2">
+      <c r="A1048" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:2">
+      <c r="A1049" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:2">
+      <c r="A1050" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:2">
+      <c r="A1051" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:2">
+      <c r="A1052" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:2">
+      <c r="A1053" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:2">
+      <c r="A1054" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:2">
+      <c r="A1055" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:2">
+      <c r="A1056" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:2">
+      <c r="A1057" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:2">
+      <c r="A1058" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:2">
+      <c r="A1059" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:2">
+      <c r="A1060" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:2">
+      <c r="A1061" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:2">
+      <c r="A1062" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:2">
+      <c r="A1063" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:2">
+      <c r="A1064" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:2">
+      <c r="A1065" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:2">
+      <c r="A1066" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:2">
+      <c r="A1067" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:2">
+      <c r="A1068" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:2">
+      <c r="A1069" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:2">
+      <c r="A1070" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:2">
+      <c r="A1071" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:2">
+      <c r="A1072" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:2">
+      <c r="A1073" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:2">
+      <c r="A1074" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:2">
+      <c r="A1075" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:2">
+      <c r="A1076" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:2">
+      <c r="A1077" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:2">
+      <c r="A1078" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:2">
+      <c r="A1079" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:2">
+      <c r="A1080" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:2">
+      <c r="A1081" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:2">
+      <c r="A1082" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:2">
+      <c r="A1083" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:2">
+      <c r="A1084" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:2">
+      <c r="A1085" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:2">
+      <c r="A1086" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:2">
+      <c r="A1087" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:2">
+      <c r="A1088" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:2">
+      <c r="A1089" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:2">
+      <c r="A1090" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:2">
+      <c r="A1091" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:2">
+      <c r="A1092" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:2">
+      <c r="A1095" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:2">
+      <c r="A1096" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:2">
+      <c r="A1097" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:2">
+      <c r="A1098" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:2">
+      <c r="A1099" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:2">
+      <c r="A1100" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:2">
+      <c r="A1101" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:2">
+      <c r="A1102" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:2">
+      <c r="A1103" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:2">
+      <c r="A1104" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:2">
+      <c r="A1105" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:2">
+      <c r="A1106" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:2">
+      <c r="A1107" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:2">
+      <c r="A1108" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:2">
+      <c r="A1109" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:2">
+      <c r="A1110" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:2">
+      <c r="A1111" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:2">
+      <c r="A1112" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:2">
+      <c r="A1113" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:2">
+      <c r="A1114" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:2">
+      <c r="A1115" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:2">
+      <c r="A1116" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:2">
+      <c r="A1117" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:2">
+      <c r="A1118" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:2">
+      <c r="A1119" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:2">
+      <c r="A1120" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:2">
+      <c r="A1121" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:2">
+      <c r="A1122" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:2">
+      <c r="A1123" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:2">
+      <c r="A1124" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:2">
+      <c r="A1125" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:2">
+      <c r="A1126" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:2">
+      <c r="A1127" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:2">
+      <c r="A1128" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:2">
+      <c r="A1129" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:2">
+      <c r="A1130" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:2">
+      <c r="A1131" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:2">
+      <c r="A1132" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:2">
+      <c r="A1133" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:2">
+      <c r="A1134" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:2">
+      <c r="A1135" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:2">
+      <c r="A1136" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:2">
+      <c r="A1137" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:2">
+      <c r="A1138" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:2">
+      <c r="A1139" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:2">
+      <c r="A1140" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:2">
+      <c r="A1141" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:2">
+      <c r="A1142" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:2">
+      <c r="A1143" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:2">
+      <c r="A1144" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:2">
+      <c r="A1145" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:2">
+      <c r="A1146" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:2">
+      <c r="A1147" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:2">
+      <c r="A1148" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:2">
+      <c r="A1149" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:2">
+      <c r="A1150" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:2">
+      <c r="A1151" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:2">
+      <c r="A1152" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:2">
+      <c r="A1153" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:2">
+      <c r="A1154" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:2">
+      <c r="A1155" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:2">
+      <c r="A1156" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:2">
+      <c r="A1157" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:2">
+      <c r="A1158" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:2">
+      <c r="A1159" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:2">
+      <c r="A1160" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:2">
+      <c r="A1161" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:2">
+      <c r="A1162" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:2">
+      <c r="A1163" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:2">
+      <c r="A1164" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:2">
+      <c r="A1165" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:2">
+      <c r="A1166" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:2">
+      <c r="A1167" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:2">
+      <c r="A1168" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:2">
+      <c r="A1169" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:2">
+      <c r="A1170" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:2">
+      <c r="A1171" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:2">
+      <c r="A1172" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:2">
+      <c r="A1173" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:2">
+      <c r="A1174" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2">
+      <c r="A1175" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2">
+      <c r="A1176" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2">
+      <c r="A1177" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:2">
+      <c r="A1194" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:2">
+      <c r="A1200" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:2">
+      <c r="A1201" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:2">
+      <c r="A1202" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:2">
+      <c r="A1203" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:2">
+      <c r="A1204" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:2">
+      <c r="A1205" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2">
+      <c r="A1210" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2">
+      <c r="A1211" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2">
+      <c r="A1212" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>1341</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC3172C-EB8D-47EA-A27F-E897D950475C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9B8633F-E209-4212-8629-31E0ADDD5D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11688" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1552">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -4013,6 +4013,9 @@
   </si>
   <si>
     <t>阿武隈急行</t>
+  </si>
+  <si>
+    <t>阿武隈急行</t>
     <rPh sb="0" eb="5">
       <t>アブクマキュウコウ</t>
     </rPh>
@@ -5178,6 +5181,733 @@
   </si>
   <si>
     <t>山形鉄道フラワー長井線</t>
+  </si>
+  <si>
+    <t>福島県</t>
+    <rPh sb="0" eb="3">
+      <t>フクシマケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福島（福島）</t>
+  </si>
+  <si>
+    <t>笹木野</t>
+  </si>
+  <si>
+    <t>庭坂</t>
+  </si>
+  <si>
+    <t>新地</t>
+  </si>
+  <si>
+    <t>駒ヶ嶺</t>
+  </si>
+  <si>
+    <t>相馬</t>
+  </si>
+  <si>
+    <t>日立木</t>
+  </si>
+  <si>
+    <t>鹿島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原ノ町</t>
+  </si>
+  <si>
+    <t>磐城太田</t>
+  </si>
+  <si>
+    <t>小高</t>
+  </si>
+  <si>
+    <t>桃内</t>
+  </si>
+  <si>
+    <t>浪江</t>
+  </si>
+  <si>
+    <t>双葉</t>
+  </si>
+  <si>
+    <t>大野</t>
+  </si>
+  <si>
+    <t>夜ノ森</t>
+  </si>
+  <si>
+    <t>富岡</t>
+  </si>
+  <si>
+    <t>竜田</t>
+  </si>
+  <si>
+    <t>木戸</t>
+  </si>
+  <si>
+    <t>Ｊヴィレッジ</t>
+  </si>
+  <si>
+    <t>広野（福島）</t>
+  </si>
+  <si>
+    <t>末続</t>
+  </si>
+  <si>
+    <t>久ノ浜</t>
+  </si>
+  <si>
+    <t>四ッ倉</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>草野（福島）</t>
+  </si>
+  <si>
+    <t>いわき</t>
+  </si>
+  <si>
+    <t>内郷</t>
+  </si>
+  <si>
+    <t>湯本</t>
+  </si>
+  <si>
+    <t>泉（ＪＲ）</t>
+  </si>
+  <si>
+    <t>植田（福島）</t>
+  </si>
+  <si>
+    <t>勿来</t>
+  </si>
+  <si>
+    <t>奥羽本線、東北本線、阿武隈急行、福島交通飯坂線、東北新幹線、山形新幹線</t>
+    <rPh sb="0" eb="4">
+      <t>オウウホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>アブクマキュウコウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>フクシマコウツウ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イイサカセン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウホク</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>シンカンセン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヤマガタ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>シンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、磐越東線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>バンエツトウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水郡線</t>
+    <rPh sb="0" eb="3">
+      <t>スイグンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢祭山</t>
+  </si>
+  <si>
+    <t>東館</t>
+  </si>
+  <si>
+    <t>南石井</t>
+  </si>
+  <si>
+    <t>磐城石井</t>
+  </si>
+  <si>
+    <t>磐城塙</t>
+  </si>
+  <si>
+    <t>近津</t>
+  </si>
+  <si>
+    <t>中豊</t>
+  </si>
+  <si>
+    <t>磐城棚倉</t>
+  </si>
+  <si>
+    <t>磐城浅川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>里白石</t>
+  </si>
+  <si>
+    <t>磐城石川</t>
+  </si>
+  <si>
+    <t>野木沢</t>
+  </si>
+  <si>
+    <t>川辺沖</t>
+  </si>
+  <si>
+    <t>泉郷</t>
+  </si>
+  <si>
+    <t>川東（福島）</t>
+  </si>
+  <si>
+    <t>小塩江</t>
+  </si>
+  <si>
+    <t>谷田川</t>
+  </si>
+  <si>
+    <t>磐城守山</t>
+  </si>
+  <si>
+    <t>安積永盛</t>
+  </si>
+  <si>
+    <t>郡山（福島）</t>
+  </si>
+  <si>
+    <t>水郡線、東北本線</t>
+    <rPh sb="0" eb="3">
+      <t>スイグンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水郡線、東北本線、磐越東線、磐越西線、東北新幹線、山形新幹線</t>
+    <rPh sb="0" eb="3">
+      <t>スイグンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>バンエツトウセン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>バンエツサイセン</t>
+    </rPh>
+    <rPh sb="19" eb="24">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="25" eb="30">
+      <t>ヤマガタシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>只見線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会津若松</t>
+  </si>
+  <si>
+    <t>七日町</t>
+  </si>
+  <si>
+    <t>西若松</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会津本郷</t>
+  </si>
+  <si>
+    <t>会津高田</t>
+  </si>
+  <si>
+    <t>根岸（福島）</t>
+  </si>
+  <si>
+    <t>新鶴</t>
+  </si>
+  <si>
+    <t>若宮</t>
+  </si>
+  <si>
+    <t>会津坂下</t>
+  </si>
+  <si>
+    <t>塔寺</t>
+  </si>
+  <si>
+    <t>会津坂本</t>
+  </si>
+  <si>
+    <t>会津柳津</t>
+  </si>
+  <si>
+    <t>郷戸</t>
+  </si>
+  <si>
+    <t>滝谷（福島）</t>
+  </si>
+  <si>
+    <t>会津桧原</t>
+  </si>
+  <si>
+    <t>会津西方</t>
+  </si>
+  <si>
+    <t>会津宮下</t>
+  </si>
+  <si>
+    <t>早戸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会津水沼</t>
+  </si>
+  <si>
+    <t>会津中川</t>
+  </si>
+  <si>
+    <t>会津川口</t>
+  </si>
+  <si>
+    <t>本名</t>
+  </si>
+  <si>
+    <t>会津越川</t>
+  </si>
+  <si>
+    <t>会津横田</t>
+  </si>
+  <si>
+    <t>会津大塩</t>
+  </si>
+  <si>
+    <t>会津塩沢</t>
+  </si>
+  <si>
+    <t>会津蒲生</t>
+  </si>
+  <si>
+    <t>只見</t>
+  </si>
+  <si>
+    <t>大白川</t>
+  </si>
+  <si>
+    <t>入広瀬</t>
+  </si>
+  <si>
+    <t>上条（新潟）</t>
+  </si>
+  <si>
+    <t>越後須原</t>
+  </si>
+  <si>
+    <t>魚沼田中</t>
+  </si>
+  <si>
+    <t>越後広瀬</t>
+  </si>
+  <si>
+    <t>藪神</t>
+  </si>
+  <si>
+    <t>小出</t>
+  </si>
+  <si>
+    <t>只見線、磐越西線</t>
+    <rPh sb="4" eb="8">
+      <t>バンエツサイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>只見線、上越線</t>
+    <rPh sb="4" eb="7">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新白河</t>
+  </si>
+  <si>
+    <t>東北新幹線、東北本線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白坂</t>
+  </si>
+  <si>
+    <t>白河</t>
+  </si>
+  <si>
+    <t>久田野</t>
+  </si>
+  <si>
+    <t>泉崎</t>
+  </si>
+  <si>
+    <t>矢吹</t>
+  </si>
+  <si>
+    <t>鏡石</t>
+  </si>
+  <si>
+    <t>須賀川</t>
+  </si>
+  <si>
+    <t>日和田</t>
+  </si>
+  <si>
+    <t>五百川</t>
+  </si>
+  <si>
+    <t>本宮（福島）</t>
+  </si>
+  <si>
+    <t>杉田（福島）</t>
+  </si>
+  <si>
+    <t>二本松</t>
+  </si>
+  <si>
+    <t>安達</t>
+  </si>
+  <si>
+    <t>松川</t>
+  </si>
+  <si>
+    <t>金谷川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南福島</t>
+  </si>
+  <si>
+    <t>東福島</t>
+  </si>
+  <si>
+    <t>伊達</t>
+  </si>
+  <si>
+    <t>桑折</t>
+  </si>
+  <si>
+    <t>藤田</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>貝田</t>
+  </si>
+  <si>
+    <t>磐越西線</t>
+  </si>
+  <si>
+    <t>郡山富田</t>
+  </si>
+  <si>
+    <t>喜久田</t>
+  </si>
+  <si>
+    <t>安子ヶ島</t>
+  </si>
+  <si>
+    <t>磐梯熱海</t>
+  </si>
+  <si>
+    <t>中山宿</t>
+  </si>
+  <si>
+    <t>上戸（福島）</t>
+  </si>
+  <si>
+    <t>関都</t>
+  </si>
+  <si>
+    <t>川桁</t>
+  </si>
+  <si>
+    <t>猪苗代</t>
+  </si>
+  <si>
+    <t>翁島</t>
+  </si>
+  <si>
+    <t>磐梯町</t>
+  </si>
+  <si>
+    <t>東長原</t>
+  </si>
+  <si>
+    <t>広田</t>
+  </si>
+  <si>
+    <t>堂島</t>
+  </si>
+  <si>
+    <t>笈川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>塩川</t>
+  </si>
+  <si>
+    <t>姥堂</t>
+  </si>
+  <si>
+    <t>会津豊川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喜多方</t>
+  </si>
+  <si>
+    <t>山都</t>
+  </si>
+  <si>
+    <t>荻野</t>
+  </si>
+  <si>
+    <t>尾登</t>
+  </si>
+  <si>
+    <t>野沢</t>
+  </si>
+  <si>
+    <t>上野尻</t>
+  </si>
+  <si>
+    <t>徳沢</t>
+  </si>
+  <si>
+    <t>磐越東線</t>
+  </si>
+  <si>
+    <t>赤井</t>
+  </si>
+  <si>
+    <t>小川郷</t>
+  </si>
+  <si>
+    <t>江田（福島）</t>
+  </si>
+  <si>
+    <t>川前</t>
+  </si>
+  <si>
+    <t>夏井</t>
+  </si>
+  <si>
+    <t>小野新町</t>
+  </si>
+  <si>
+    <t>神俣</t>
+  </si>
+  <si>
+    <t>菅谷</t>
+  </si>
+  <si>
+    <t>大越</t>
+  </si>
+  <si>
+    <t>磐城常葉</t>
+  </si>
+  <si>
+    <t>船引</t>
+  </si>
+  <si>
+    <t>要田</t>
+  </si>
+  <si>
+    <t>三春</t>
+  </si>
+  <si>
+    <t>舞木</t>
+  </si>
+  <si>
+    <t>兜</t>
+    <rPh sb="0" eb="1">
+      <t>カブト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富野</t>
+  </si>
+  <si>
+    <t>やながわ希望の森公園前</t>
+  </si>
+  <si>
+    <t>梁川（福島）</t>
+  </si>
+  <si>
+    <t>新田（福島）</t>
+  </si>
+  <si>
+    <t>二井田</t>
+  </si>
+  <si>
+    <t>大泉（福島）</t>
+  </si>
+  <si>
+    <t>保原</t>
+  </si>
+  <si>
+    <t>上保原</t>
+  </si>
+  <si>
+    <t>高子</t>
+  </si>
+  <si>
+    <t>向瀬上</t>
+  </si>
+  <si>
+    <t>瀬上</t>
+  </si>
+  <si>
+    <t>福島学院前</t>
+  </si>
+  <si>
+    <t>卸町（福島）</t>
+  </si>
+  <si>
+    <t>只見線、会津鉄道会津線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会津鉄道会津線</t>
+  </si>
+  <si>
+    <t>会津高原尾瀬口</t>
+  </si>
+  <si>
+    <t>七ヶ岳登山口</t>
+  </si>
+  <si>
+    <t>会津山村道場</t>
+  </si>
+  <si>
+    <t>会津荒海</t>
+  </si>
+  <si>
+    <t>中荒井</t>
+  </si>
+  <si>
+    <t>会津田島</t>
+  </si>
+  <si>
+    <t>田島高校前</t>
+  </si>
+  <si>
+    <t>会津長野</t>
+  </si>
+  <si>
+    <t>養鱒公園</t>
+  </si>
+  <si>
+    <t>ふるさと公園</t>
+  </si>
+  <si>
+    <t>会津下郷</t>
+  </si>
+  <si>
+    <t>弥五島</t>
+  </si>
+  <si>
+    <t>塔のへつり</t>
+  </si>
+  <si>
+    <t>湯野上温泉</t>
+  </si>
+  <si>
+    <t>芦ノ牧温泉南</t>
+  </si>
+  <si>
+    <t>大川ダム公園</t>
+  </si>
+  <si>
+    <t>芦ノ牧温泉</t>
+  </si>
+  <si>
+    <t>あまや</t>
+  </si>
+  <si>
+    <t>門田</t>
+  </si>
+  <si>
+    <t>南若松</t>
+  </si>
+  <si>
+    <t>福島交通飯坂線</t>
+  </si>
+  <si>
+    <t>曽根田</t>
+  </si>
+  <si>
+    <t>会津鉄道会津線、野岩鉄道会津鬼怒川線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美術館図書館前</t>
+  </si>
+  <si>
+    <t>岩代清水</t>
+  </si>
+  <si>
+    <t>泉（福島交通）</t>
+  </si>
+  <si>
+    <t>上松川</t>
+  </si>
+  <si>
+    <t>笹谷</t>
+  </si>
+  <si>
+    <t>桜水</t>
+  </si>
+  <si>
+    <t>平野（福島）</t>
+  </si>
+  <si>
+    <t>医王寺前</t>
+  </si>
+  <si>
+    <t>花水坂</t>
+  </si>
+  <si>
+    <t>飯坂温泉</t>
   </si>
 </sst>
 </file>
@@ -5207,12 +5937,24 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F2F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -5224,20 +5966,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -5246,8 +6000,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5584,7 +6339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B1212"/>
+  <dimension ref="A1:B1408"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -11644,7 +12399,7 @@
       </c>
     </row>
     <row r="765" spans="1:2">
-      <c r="A765" s="2" t="s">
+      <c r="A765" s="5" t="s">
         <v>842</v>
       </c>
       <c r="B765" t="s">
@@ -11652,7 +12407,7 @@
       </c>
     </row>
     <row r="766" spans="1:2">
-      <c r="A766" s="2" t="s">
+      <c r="A766" s="5" t="s">
         <v>843</v>
       </c>
       <c r="B766" t="s">
@@ -11660,7 +12415,7 @@
       </c>
     </row>
     <row r="767" spans="1:2">
-      <c r="A767" s="2" t="s">
+      <c r="A767" s="5" t="s">
         <v>844</v>
       </c>
       <c r="B767" t="s">
@@ -11668,7 +12423,7 @@
       </c>
     </row>
     <row r="768" spans="1:2">
-      <c r="A768" s="2" t="s">
+      <c r="A768" s="5" t="s">
         <v>845</v>
       </c>
       <c r="B768" t="s">
@@ -11676,7 +12431,7 @@
       </c>
     </row>
     <row r="769" spans="1:2">
-      <c r="A769" s="2" t="s">
+      <c r="A769" s="5" t="s">
         <v>846</v>
       </c>
       <c r="B769" t="s">
@@ -11684,7 +12439,7 @@
       </c>
     </row>
     <row r="770" spans="1:2">
-      <c r="A770" s="2" t="s">
+      <c r="A770" s="5" t="s">
         <v>847</v>
       </c>
       <c r="B770" t="s">
@@ -11692,7 +12447,7 @@
       </c>
     </row>
     <row r="771" spans="1:2">
-      <c r="A771" s="2" t="s">
+      <c r="A771" s="5" t="s">
         <v>848</v>
       </c>
       <c r="B771" t="s">
@@ -11700,7 +12455,7 @@
       </c>
     </row>
     <row r="772" spans="1:2">
-      <c r="A772" s="2" t="s">
+      <c r="A772" s="5" t="s">
         <v>849</v>
       </c>
       <c r="B772" t="s">
@@ -11708,7 +12463,7 @@
       </c>
     </row>
     <row r="773" spans="1:2">
-      <c r="A773" s="2" t="s">
+      <c r="A773" s="5" t="s">
         <v>850</v>
       </c>
       <c r="B773" t="s">
@@ -11716,7 +12471,7 @@
       </c>
     </row>
     <row r="774" spans="1:2">
-      <c r="A774" s="2" t="s">
+      <c r="A774" s="5" t="s">
         <v>851</v>
       </c>
       <c r="B774" t="s">
@@ -11724,7 +12479,7 @@
       </c>
     </row>
     <row r="775" spans="1:2">
-      <c r="A775" s="2" t="s">
+      <c r="A775" s="5" t="s">
         <v>854</v>
       </c>
       <c r="B775" t="s">
@@ -11732,7 +12487,7 @@
       </c>
     </row>
     <row r="776" spans="1:2">
-      <c r="A776" s="2" t="s">
+      <c r="A776" s="5" t="s">
         <v>855</v>
       </c>
       <c r="B776" t="s">
@@ -11740,7 +12495,7 @@
       </c>
     </row>
     <row r="777" spans="1:2">
-      <c r="A777" s="2" t="s">
+      <c r="A777" s="5" t="s">
         <v>856</v>
       </c>
       <c r="B777" t="s">
@@ -11748,7 +12503,7 @@
       </c>
     </row>
     <row r="778" spans="1:2">
-      <c r="A778" s="2" t="s">
+      <c r="A778" s="5" t="s">
         <v>857</v>
       </c>
       <c r="B778" t="s">
@@ -11756,7 +12511,7 @@
       </c>
     </row>
     <row r="779" spans="1:2">
-      <c r="A779" s="2" t="s">
+      <c r="A779" s="5" t="s">
         <v>858</v>
       </c>
       <c r="B779" t="s">
@@ -11764,7 +12519,7 @@
       </c>
     </row>
     <row r="780" spans="1:2">
-      <c r="A780" s="2" t="s">
+      <c r="A780" s="5" t="s">
         <v>859</v>
       </c>
       <c r="B780" t="s">
@@ -11772,7 +12527,7 @@
       </c>
     </row>
     <row r="781" spans="1:2">
-      <c r="A781" s="2" t="s">
+      <c r="A781" s="5" t="s">
         <v>860</v>
       </c>
       <c r="B781" t="s">
@@ -11780,7 +12535,7 @@
       </c>
     </row>
     <row r="782" spans="1:2">
-      <c r="A782" s="2" t="s">
+      <c r="A782" s="5" t="s">
         <v>861</v>
       </c>
       <c r="B782" t="s">
@@ -11788,7 +12543,7 @@
       </c>
     </row>
     <row r="783" spans="1:2">
-      <c r="A783" s="2" t="s">
+      <c r="A783" s="5" t="s">
         <v>862</v>
       </c>
       <c r="B783" t="s">
@@ -11796,7 +12551,7 @@
       </c>
     </row>
     <row r="784" spans="1:2">
-      <c r="A784" s="2" t="s">
+      <c r="A784" s="5" t="s">
         <v>863</v>
       </c>
       <c r="B784" t="s">
@@ -11804,7 +12559,7 @@
       </c>
     </row>
     <row r="785" spans="1:2">
-      <c r="A785" s="2" t="s">
+      <c r="A785" s="5" t="s">
         <v>864</v>
       </c>
       <c r="B785" t="s">
@@ -11812,7 +12567,7 @@
       </c>
     </row>
     <row r="786" spans="1:2">
-      <c r="A786" s="2" t="s">
+      <c r="A786" s="5" t="s">
         <v>865</v>
       </c>
       <c r="B786" t="s">
@@ -11820,7 +12575,7 @@
       </c>
     </row>
     <row r="787" spans="1:2">
-      <c r="A787" s="2" t="s">
+      <c r="A787" s="5" t="s">
         <v>866</v>
       </c>
       <c r="B787" t="s">
@@ -11828,7 +12583,7 @@
       </c>
     </row>
     <row r="788" spans="1:2">
-      <c r="A788" s="2" t="s">
+      <c r="A788" s="5" t="s">
         <v>867</v>
       </c>
       <c r="B788" t="s">
@@ -11836,7 +12591,7 @@
       </c>
     </row>
     <row r="789" spans="1:2">
-      <c r="A789" s="2" t="s">
+      <c r="A789" s="5" t="s">
         <v>868</v>
       </c>
       <c r="B789" t="s">
@@ -11844,7 +12599,7 @@
       </c>
     </row>
     <row r="790" spans="1:2">
-      <c r="A790" s="2" t="s">
+      <c r="A790" s="5" t="s">
         <v>869</v>
       </c>
       <c r="B790" t="s">
@@ -11852,7 +12607,7 @@
       </c>
     </row>
     <row r="791" spans="1:2">
-      <c r="A791" s="2" t="s">
+      <c r="A791" s="5" t="s">
         <v>870</v>
       </c>
       <c r="B791" t="s">
@@ -11860,7 +12615,7 @@
       </c>
     </row>
     <row r="792" spans="1:2">
-      <c r="A792" s="2" t="s">
+      <c r="A792" s="5" t="s">
         <v>871</v>
       </c>
       <c r="B792" t="s">
@@ -11868,7 +12623,7 @@
       </c>
     </row>
     <row r="793" spans="1:2">
-      <c r="A793" s="2" t="s">
+      <c r="A793" s="5" t="s">
         <v>873</v>
       </c>
       <c r="B793" t="s">
@@ -11876,7 +12631,7 @@
       </c>
     </row>
     <row r="794" spans="1:2">
-      <c r="A794" s="2" t="s">
+      <c r="A794" s="5" t="s">
         <v>872</v>
       </c>
       <c r="B794" t="s">
@@ -11884,7 +12639,7 @@
       </c>
     </row>
     <row r="795" spans="1:2">
-      <c r="A795" s="2" t="s">
+      <c r="A795" s="5" t="s">
         <v>874</v>
       </c>
       <c r="B795" t="s">
@@ -11892,7 +12647,7 @@
       </c>
     </row>
     <row r="796" spans="1:2">
-      <c r="A796" s="2" t="s">
+      <c r="A796" s="5" t="s">
         <v>876</v>
       </c>
       <c r="B796" t="s">
@@ -11900,7 +12655,7 @@
       </c>
     </row>
     <row r="797" spans="1:2">
-      <c r="A797" s="2" t="s">
+      <c r="A797" s="5" t="s">
         <v>877</v>
       </c>
       <c r="B797" t="s">
@@ -11908,7 +12663,7 @@
       </c>
     </row>
     <row r="798" spans="1:2">
-      <c r="A798" s="2" t="s">
+      <c r="A798" s="5" t="s">
         <v>878</v>
       </c>
       <c r="B798" t="s">
@@ -11916,7 +12671,7 @@
       </c>
     </row>
     <row r="799" spans="1:2">
-      <c r="A799" s="2" t="s">
+      <c r="A799" s="5" t="s">
         <v>879</v>
       </c>
       <c r="B799" t="s">
@@ -11924,7 +12679,7 @@
       </c>
     </row>
     <row r="800" spans="1:2">
-      <c r="A800" s="2" t="s">
+      <c r="A800" s="5" t="s">
         <v>880</v>
       </c>
       <c r="B800" t="s">
@@ -11932,7 +12687,7 @@
       </c>
     </row>
     <row r="801" spans="1:2">
-      <c r="A801" s="2" t="s">
+      <c r="A801" s="5" t="s">
         <v>881</v>
       </c>
       <c r="B801" t="s">
@@ -11940,7 +12695,7 @@
       </c>
     </row>
     <row r="802" spans="1:2">
-      <c r="A802" s="2" t="s">
+      <c r="A802" s="5" t="s">
         <v>882</v>
       </c>
       <c r="B802" t="s">
@@ -11948,7 +12703,7 @@
       </c>
     </row>
     <row r="803" spans="1:2">
-      <c r="A803" s="2" t="s">
+      <c r="A803" s="5" t="s">
         <v>883</v>
       </c>
       <c r="B803" t="s">
@@ -11956,7 +12711,7 @@
       </c>
     </row>
     <row r="804" spans="1:2">
-      <c r="A804" s="2" t="s">
+      <c r="A804" s="5" t="s">
         <v>884</v>
       </c>
       <c r="B804" t="s">
@@ -11964,7 +12719,7 @@
       </c>
     </row>
     <row r="805" spans="1:2">
-      <c r="A805" s="2" t="s">
+      <c r="A805" s="5" t="s">
         <v>885</v>
       </c>
       <c r="B805" t="s">
@@ -11972,7 +12727,7 @@
       </c>
     </row>
     <row r="806" spans="1:2">
-      <c r="A806" s="2" t="s">
+      <c r="A806" s="5" t="s">
         <v>886</v>
       </c>
       <c r="B806" t="s">
@@ -11980,7 +12735,7 @@
       </c>
     </row>
     <row r="807" spans="1:2">
-      <c r="A807" s="2" t="s">
+      <c r="A807" s="5" t="s">
         <v>887</v>
       </c>
       <c r="B807" t="s">
@@ -11988,7 +12743,7 @@
       </c>
     </row>
     <row r="808" spans="1:2">
-      <c r="A808" s="2" t="s">
+      <c r="A808" s="5" t="s">
         <v>888</v>
       </c>
       <c r="B808" t="s">
@@ -11996,7 +12751,7 @@
       </c>
     </row>
     <row r="809" spans="1:2">
-      <c r="A809" s="2" t="s">
+      <c r="A809" s="5" t="s">
         <v>889</v>
       </c>
       <c r="B809" t="s">
@@ -12004,7 +12759,7 @@
       </c>
     </row>
     <row r="810" spans="1:2">
-      <c r="A810" s="2" t="s">
+      <c r="A810" s="5" t="s">
         <v>896</v>
       </c>
       <c r="B810" t="s">
@@ -12012,7 +12767,7 @@
       </c>
     </row>
     <row r="811" spans="1:2">
-      <c r="A811" s="2" t="s">
+      <c r="A811" s="5" t="s">
         <v>897</v>
       </c>
       <c r="B811" t="s">
@@ -12020,7 +12775,7 @@
       </c>
     </row>
     <row r="812" spans="1:2">
-      <c r="A812" s="2" t="s">
+      <c r="A812" s="5" t="s">
         <v>898</v>
       </c>
       <c r="B812" t="s">
@@ -12028,15 +12783,15 @@
       </c>
     </row>
     <row r="813" spans="1:2">
-      <c r="A813" s="2" t="s">
-        <v>1038</v>
+      <c r="A813" s="5" t="s">
+        <v>1039</v>
       </c>
       <c r="B813" t="s">
         <v>906</v>
       </c>
     </row>
     <row r="814" spans="1:2">
-      <c r="A814" s="2" t="s">
+      <c r="A814" s="5" t="s">
         <v>899</v>
       </c>
       <c r="B814" t="s">
@@ -12044,7 +12799,7 @@
       </c>
     </row>
     <row r="815" spans="1:2">
-      <c r="A815" s="2" t="s">
+      <c r="A815" s="5" t="s">
         <v>900</v>
       </c>
       <c r="B815" t="s">
@@ -12052,7 +12807,7 @@
       </c>
     </row>
     <row r="816" spans="1:2">
-      <c r="A816" s="2" t="s">
+      <c r="A816" s="5" t="s">
         <v>901</v>
       </c>
       <c r="B816" t="s">
@@ -12060,7 +12815,7 @@
       </c>
     </row>
     <row r="817" spans="1:2">
-      <c r="A817" s="2" t="s">
+      <c r="A817" s="5" t="s">
         <v>902</v>
       </c>
       <c r="B817" t="s">
@@ -12068,7 +12823,7 @@
       </c>
     </row>
     <row r="818" spans="1:2">
-      <c r="A818" s="2" t="s">
+      <c r="A818" s="5" t="s">
         <v>903</v>
       </c>
       <c r="B818" t="s">
@@ -12076,7 +12831,7 @@
       </c>
     </row>
     <row r="819" spans="1:2">
-      <c r="A819" s="2" t="s">
+      <c r="A819" s="5" t="s">
         <v>904</v>
       </c>
       <c r="B819" t="s">
@@ -12084,7 +12839,7 @@
       </c>
     </row>
     <row r="820" spans="1:2">
-      <c r="A820" s="2" t="s">
+      <c r="A820" s="5" t="s">
         <v>907</v>
       </c>
       <c r="B820" t="s">
@@ -12092,7 +12847,7 @@
       </c>
     </row>
     <row r="821" spans="1:2">
-      <c r="A821" s="2" t="s">
+      <c r="A821" s="5" t="s">
         <v>908</v>
       </c>
       <c r="B821" t="s">
@@ -12100,7 +12855,7 @@
       </c>
     </row>
     <row r="822" spans="1:2">
-      <c r="A822" s="2" t="s">
+      <c r="A822" s="5" t="s">
         <v>909</v>
       </c>
       <c r="B822" t="s">
@@ -12108,7 +12863,7 @@
       </c>
     </row>
     <row r="823" spans="1:2">
-      <c r="A823" s="2" t="s">
+      <c r="A823" s="5" t="s">
         <v>910</v>
       </c>
       <c r="B823" t="s">
@@ -12116,7 +12871,7 @@
       </c>
     </row>
     <row r="824" spans="1:2">
-      <c r="A824" s="2" t="s">
+      <c r="A824" s="5" t="s">
         <v>911</v>
       </c>
       <c r="B824" t="s">
@@ -12124,7 +12879,7 @@
       </c>
     </row>
     <row r="825" spans="1:2">
-      <c r="A825" s="2" t="s">
+      <c r="A825" s="5" t="s">
         <v>912</v>
       </c>
       <c r="B825" t="s">
@@ -12132,7 +12887,7 @@
       </c>
     </row>
     <row r="826" spans="1:2">
-      <c r="A826" s="2" t="s">
+      <c r="A826" s="5" t="s">
         <v>913</v>
       </c>
       <c r="B826" t="s">
@@ -12140,7 +12895,7 @@
       </c>
     </row>
     <row r="827" spans="1:2">
-      <c r="A827" s="2" t="s">
+      <c r="A827" s="5" t="s">
         <v>914</v>
       </c>
       <c r="B827" t="s">
@@ -12148,7 +12903,7 @@
       </c>
     </row>
     <row r="828" spans="1:2">
-      <c r="A828" s="2" t="s">
+      <c r="A828" s="5" t="s">
         <v>915</v>
       </c>
       <c r="B828" t="s">
@@ -12156,7 +12911,7 @@
       </c>
     </row>
     <row r="829" spans="1:2">
-      <c r="A829" s="2" t="s">
+      <c r="A829" s="5" t="s">
         <v>916</v>
       </c>
       <c r="B829" t="s">
@@ -12164,7 +12919,7 @@
       </c>
     </row>
     <row r="830" spans="1:2">
-      <c r="A830" s="2" t="s">
+      <c r="A830" s="5" t="s">
         <v>917</v>
       </c>
       <c r="B830" t="s">
@@ -12172,7 +12927,7 @@
       </c>
     </row>
     <row r="831" spans="1:2">
-      <c r="A831" s="2" t="s">
+      <c r="A831" s="5" t="s">
         <v>918</v>
       </c>
       <c r="B831" t="s">
@@ -12180,7 +12935,7 @@
       </c>
     </row>
     <row r="832" spans="1:2">
-      <c r="A832" s="2" t="s">
+      <c r="A832" s="5" t="s">
         <v>922</v>
       </c>
       <c r="B832" t="s">
@@ -12188,7 +12943,7 @@
       </c>
     </row>
     <row r="833" spans="1:2">
-      <c r="A833" s="2" t="s">
+      <c r="A833" s="5" t="s">
         <v>923</v>
       </c>
       <c r="B833" t="s">
@@ -12196,7 +12951,7 @@
       </c>
     </row>
     <row r="834" spans="1:2">
-      <c r="A834" s="2" t="s">
+      <c r="A834" s="5" t="s">
         <v>924</v>
       </c>
       <c r="B834" t="s">
@@ -12204,7 +12959,7 @@
       </c>
     </row>
     <row r="835" spans="1:2">
-      <c r="A835" s="2" t="s">
+      <c r="A835" s="5" t="s">
         <v>925</v>
       </c>
       <c r="B835" t="s">
@@ -12212,7 +12967,7 @@
       </c>
     </row>
     <row r="836" spans="1:2">
-      <c r="A836" s="2" t="s">
+      <c r="A836" s="5" t="s">
         <v>926</v>
       </c>
       <c r="B836" t="s">
@@ -12220,7 +12975,7 @@
       </c>
     </row>
     <row r="837" spans="1:2">
-      <c r="A837" s="2" t="s">
+      <c r="A837" s="5" t="s">
         <v>927</v>
       </c>
       <c r="B837" t="s">
@@ -12228,7 +12983,7 @@
       </c>
     </row>
     <row r="838" spans="1:2">
-      <c r="A838" s="2" t="s">
+      <c r="A838" s="5" t="s">
         <v>928</v>
       </c>
       <c r="B838" t="s">
@@ -12236,7 +12991,7 @@
       </c>
     </row>
     <row r="839" spans="1:2">
-      <c r="A839" s="2" t="s">
+      <c r="A839" s="5" t="s">
         <v>929</v>
       </c>
       <c r="B839" t="s">
@@ -12244,7 +12999,7 @@
       </c>
     </row>
     <row r="840" spans="1:2">
-      <c r="A840" s="2" t="s">
+      <c r="A840" s="5" t="s">
         <v>930</v>
       </c>
       <c r="B840" t="s">
@@ -12252,7 +13007,7 @@
       </c>
     </row>
     <row r="841" spans="1:2">
-      <c r="A841" s="2" t="s">
+      <c r="A841" s="5" t="s">
         <v>931</v>
       </c>
       <c r="B841" t="s">
@@ -12260,7 +13015,7 @@
       </c>
     </row>
     <row r="842" spans="1:2">
-      <c r="A842" s="2" t="s">
+      <c r="A842" s="5" t="s">
         <v>932</v>
       </c>
       <c r="B842" t="s">
@@ -12268,7 +13023,7 @@
       </c>
     </row>
     <row r="843" spans="1:2">
-      <c r="A843" s="2" t="s">
+      <c r="A843" s="5" t="s">
         <v>933</v>
       </c>
       <c r="B843" t="s">
@@ -12276,7 +13031,7 @@
       </c>
     </row>
     <row r="844" spans="1:2">
-      <c r="A844" s="2" t="s">
+      <c r="A844" s="5" t="s">
         <v>934</v>
       </c>
       <c r="B844" t="s">
@@ -12284,7 +13039,7 @@
       </c>
     </row>
     <row r="845" spans="1:2">
-      <c r="A845" s="2" t="s">
+      <c r="A845" s="5" t="s">
         <v>935</v>
       </c>
       <c r="B845" t="s">
@@ -12292,7 +13047,7 @@
       </c>
     </row>
     <row r="846" spans="1:2">
-      <c r="A846" s="2" t="s">
+      <c r="A846" s="5" t="s">
         <v>936</v>
       </c>
       <c r="B846" t="s">
@@ -12300,7 +13055,7 @@
       </c>
     </row>
     <row r="847" spans="1:2">
-      <c r="A847" s="2" t="s">
+      <c r="A847" s="5" t="s">
         <v>937</v>
       </c>
       <c r="B847" t="s">
@@ -12308,7 +13063,7 @@
       </c>
     </row>
     <row r="848" spans="1:2">
-      <c r="A848" s="2" t="s">
+      <c r="A848" s="5" t="s">
         <v>938</v>
       </c>
       <c r="B848" t="s">
@@ -12316,7 +13071,7 @@
       </c>
     </row>
     <row r="849" spans="1:2">
-      <c r="A849" s="2" t="s">
+      <c r="A849" s="5" t="s">
         <v>939</v>
       </c>
       <c r="B849" t="s">
@@ -12324,7 +13079,7 @@
       </c>
     </row>
     <row r="850" spans="1:2">
-      <c r="A850" s="2" t="s">
+      <c r="A850" s="5" t="s">
         <v>940</v>
       </c>
       <c r="B850" t="s">
@@ -12332,7 +13087,7 @@
       </c>
     </row>
     <row r="851" spans="1:2">
-      <c r="A851" s="2" t="s">
+      <c r="A851" s="5" t="s">
         <v>941</v>
       </c>
       <c r="B851" t="s">
@@ -12340,7 +13095,7 @@
       </c>
     </row>
     <row r="852" spans="1:2">
-      <c r="A852" s="2" t="s">
+      <c r="A852" s="5" t="s">
         <v>942</v>
       </c>
       <c r="B852" t="s">
@@ -12348,7 +13103,7 @@
       </c>
     </row>
     <row r="853" spans="1:2">
-      <c r="A853" s="2" t="s">
+      <c r="A853" s="5" t="s">
         <v>943</v>
       </c>
       <c r="B853" t="s">
@@ -12356,7 +13111,7 @@
       </c>
     </row>
     <row r="854" spans="1:2">
-      <c r="A854" s="2" t="s">
+      <c r="A854" s="5" t="s">
         <v>944</v>
       </c>
       <c r="B854" t="s">
@@ -12364,7 +13119,7 @@
       </c>
     </row>
     <row r="855" spans="1:2">
-      <c r="A855" s="2" t="s">
+      <c r="A855" s="5" t="s">
         <v>945</v>
       </c>
       <c r="B855" t="s">
@@ -12372,7 +13127,7 @@
       </c>
     </row>
     <row r="856" spans="1:2">
-      <c r="A856" s="2" t="s">
+      <c r="A856" s="5" t="s">
         <v>946</v>
       </c>
       <c r="B856" t="s">
@@ -12380,7 +13135,7 @@
       </c>
     </row>
     <row r="857" spans="1:2">
-      <c r="A857" s="2" t="s">
+      <c r="A857" s="5" t="s">
         <v>947</v>
       </c>
       <c r="B857" t="s">
@@ -12388,7 +13143,7 @@
       </c>
     </row>
     <row r="858" spans="1:2">
-      <c r="A858" s="2" t="s">
+      <c r="A858" s="5" t="s">
         <v>948</v>
       </c>
       <c r="B858" t="s">
@@ -12396,7 +13151,7 @@
       </c>
     </row>
     <row r="859" spans="1:2">
-      <c r="A859" s="2" t="s">
+      <c r="A859" s="5" t="s">
         <v>949</v>
       </c>
       <c r="B859" t="s">
@@ -12404,7 +13159,7 @@
       </c>
     </row>
     <row r="860" spans="1:2">
-      <c r="A860" s="2" t="s">
+      <c r="A860" s="5" t="s">
         <v>950</v>
       </c>
       <c r="B860" t="s">
@@ -12412,7 +13167,7 @@
       </c>
     </row>
     <row r="861" spans="1:2">
-      <c r="A861" s="2" t="s">
+      <c r="A861" s="5" t="s">
         <v>951</v>
       </c>
       <c r="B861" t="s">
@@ -12420,7 +13175,7 @@
       </c>
     </row>
     <row r="862" spans="1:2">
-      <c r="A862" s="2" t="s">
+      <c r="A862" s="5" t="s">
         <v>953</v>
       </c>
       <c r="B862" t="s">
@@ -12428,7 +13183,7 @@
       </c>
     </row>
     <row r="863" spans="1:2">
-      <c r="A863" s="2" t="s">
+      <c r="A863" s="5" t="s">
         <v>954</v>
       </c>
       <c r="B863" t="s">
@@ -12436,7 +13191,7 @@
       </c>
     </row>
     <row r="864" spans="1:2">
-      <c r="A864" s="2" t="s">
+      <c r="A864" s="5" t="s">
         <v>955</v>
       </c>
       <c r="B864" t="s">
@@ -12444,7 +13199,7 @@
       </c>
     </row>
     <row r="865" spans="1:2">
-      <c r="A865" s="2" t="s">
+      <c r="A865" s="5" t="s">
         <v>956</v>
       </c>
       <c r="B865" t="s">
@@ -12452,7 +13207,7 @@
       </c>
     </row>
     <row r="866" spans="1:2">
-      <c r="A866" s="2" t="s">
+      <c r="A866" s="5" t="s">
         <v>957</v>
       </c>
       <c r="B866" t="s">
@@ -12492,7 +13247,7 @@
       </c>
     </row>
     <row r="871" spans="1:2">
-      <c r="A871" s="2" t="s">
+      <c r="A871" s="5" t="s">
         <v>966</v>
       </c>
       <c r="B871" t="s">
@@ -12500,7 +13255,7 @@
       </c>
     </row>
     <row r="872" spans="1:2">
-      <c r="A872" s="2" t="s">
+      <c r="A872" s="5" t="s">
         <v>967</v>
       </c>
       <c r="B872" t="s">
@@ -12508,7 +13263,7 @@
       </c>
     </row>
     <row r="873" spans="1:2">
-      <c r="A873" s="2" t="s">
+      <c r="A873" s="5" t="s">
         <v>968</v>
       </c>
       <c r="B873" t="s">
@@ -12516,7 +13271,7 @@
       </c>
     </row>
     <row r="874" spans="1:2">
-      <c r="A874" s="2" t="s">
+      <c r="A874" s="5" t="s">
         <v>969</v>
       </c>
       <c r="B874" t="s">
@@ -12524,7 +13279,7 @@
       </c>
     </row>
     <row r="875" spans="1:2">
-      <c r="A875" s="2" t="s">
+      <c r="A875" s="5" t="s">
         <v>970</v>
       </c>
       <c r="B875" t="s">
@@ -12532,7 +13287,7 @@
       </c>
     </row>
     <row r="876" spans="1:2">
-      <c r="A876" s="2" t="s">
+      <c r="A876" s="5" t="s">
         <v>971</v>
       </c>
       <c r="B876" t="s">
@@ -12540,7 +13295,7 @@
       </c>
     </row>
     <row r="877" spans="1:2">
-      <c r="A877" s="2" t="s">
+      <c r="A877" s="5" t="s">
         <v>972</v>
       </c>
       <c r="B877" t="s">
@@ -12548,7 +13303,7 @@
       </c>
     </row>
     <row r="878" spans="1:2">
-      <c r="A878" s="2" t="s">
+      <c r="A878" s="5" t="s">
         <v>973</v>
       </c>
       <c r="B878" t="s">
@@ -12556,7 +13311,7 @@
       </c>
     </row>
     <row r="879" spans="1:2">
-      <c r="A879" s="2" t="s">
+      <c r="A879" s="5" t="s">
         <v>974</v>
       </c>
       <c r="B879" t="s">
@@ -12564,7 +13319,7 @@
       </c>
     </row>
     <row r="880" spans="1:2">
-      <c r="A880" s="2" t="s">
+      <c r="A880" s="5" t="s">
         <v>975</v>
       </c>
       <c r="B880" t="s">
@@ -12572,7 +13327,7 @@
       </c>
     </row>
     <row r="881" spans="1:2">
-      <c r="A881" s="2" t="s">
+      <c r="A881" s="5" t="s">
         <v>976</v>
       </c>
       <c r="B881" t="s">
@@ -12580,7 +13335,7 @@
       </c>
     </row>
     <row r="882" spans="1:2">
-      <c r="A882" s="2" t="s">
+      <c r="A882" s="5" t="s">
         <v>977</v>
       </c>
       <c r="B882" t="s">
@@ -12588,7 +13343,7 @@
       </c>
     </row>
     <row r="883" spans="1:2">
-      <c r="A883" s="2" t="s">
+      <c r="A883" s="5" t="s">
         <v>978</v>
       </c>
       <c r="B883" t="s">
@@ -12596,7 +13351,7 @@
       </c>
     </row>
     <row r="884" spans="1:2">
-      <c r="A884" s="2" t="s">
+      <c r="A884" s="5" t="s">
         <v>979</v>
       </c>
       <c r="B884" t="s">
@@ -12604,7 +13359,7 @@
       </c>
     </row>
     <row r="885" spans="1:2">
-      <c r="A885" s="2" t="s">
+      <c r="A885" s="5" t="s">
         <v>980</v>
       </c>
       <c r="B885" t="s">
@@ -12612,7 +13367,7 @@
       </c>
     </row>
     <row r="886" spans="1:2">
-      <c r="A886" s="2" t="s">
+      <c r="A886" s="5" t="s">
         <v>981</v>
       </c>
       <c r="B886" t="s">
@@ -12620,7 +13375,7 @@
       </c>
     </row>
     <row r="887" spans="1:2">
-      <c r="A887" s="2" t="s">
+      <c r="A887" s="5" t="s">
         <v>982</v>
       </c>
       <c r="B887" t="s">
@@ -12628,7 +13383,7 @@
       </c>
     </row>
     <row r="888" spans="1:2">
-      <c r="A888" s="2" t="s">
+      <c r="A888" s="5" t="s">
         <v>983</v>
       </c>
       <c r="B888" t="s">
@@ -12636,7 +13391,7 @@
       </c>
     </row>
     <row r="889" spans="1:2">
-      <c r="A889" s="2" t="s">
+      <c r="A889" s="5" t="s">
         <v>984</v>
       </c>
       <c r="B889" t="s">
@@ -12644,7 +13399,7 @@
       </c>
     </row>
     <row r="890" spans="1:2">
-      <c r="A890" s="2" t="s">
+      <c r="A890" s="5" t="s">
         <v>985</v>
       </c>
       <c r="B890" t="s">
@@ -12652,7 +13407,7 @@
       </c>
     </row>
     <row r="891" spans="1:2">
-      <c r="A891" s="2" t="s">
+      <c r="A891" s="5" t="s">
         <v>986</v>
       </c>
       <c r="B891" t="s">
@@ -12660,7 +13415,7 @@
       </c>
     </row>
     <row r="892" spans="1:2">
-      <c r="A892" s="2" t="s">
+      <c r="A892" s="5" t="s">
         <v>987</v>
       </c>
       <c r="B892" t="s">
@@ -12668,7 +13423,7 @@
       </c>
     </row>
     <row r="893" spans="1:2">
-      <c r="A893" s="2" t="s">
+      <c r="A893" s="5" t="s">
         <v>989</v>
       </c>
       <c r="B893" t="s">
@@ -12676,7 +13431,7 @@
       </c>
     </row>
     <row r="894" spans="1:2">
-      <c r="A894" s="2" t="s">
+      <c r="A894" s="5" t="s">
         <v>990</v>
       </c>
       <c r="B894" t="s">
@@ -12684,7 +13439,7 @@
       </c>
     </row>
     <row r="895" spans="1:2">
-      <c r="A895" s="2" t="s">
+      <c r="A895" s="5" t="s">
         <v>995</v>
       </c>
       <c r="B895" t="s">
@@ -12692,7 +13447,7 @@
       </c>
     </row>
     <row r="896" spans="1:2">
-      <c r="A896" s="2" t="s">
+      <c r="A896" s="5" t="s">
         <v>996</v>
       </c>
       <c r="B896" t="s">
@@ -12700,7 +13455,7 @@
       </c>
     </row>
     <row r="897" spans="1:2">
-      <c r="A897" s="3" t="s">
+      <c r="A897" s="6" t="s">
         <v>997</v>
       </c>
       <c r="B897" t="s">
@@ -12708,7 +13463,7 @@
       </c>
     </row>
     <row r="898" spans="1:2">
-      <c r="A898" s="2" t="s">
+      <c r="A898" s="5" t="s">
         <v>998</v>
       </c>
       <c r="B898" t="s">
@@ -12716,7 +13471,7 @@
       </c>
     </row>
     <row r="899" spans="1:2">
-      <c r="A899" s="2" t="s">
+      <c r="A899" s="5" t="s">
         <v>999</v>
       </c>
       <c r="B899" t="s">
@@ -12724,7 +13479,7 @@
       </c>
     </row>
     <row r="900" spans="1:2">
-      <c r="A900" s="2" t="s">
+      <c r="A900" s="5" t="s">
         <v>1000</v>
       </c>
       <c r="B900" t="s">
@@ -12732,7 +13487,7 @@
       </c>
     </row>
     <row r="901" spans="1:2">
-      <c r="A901" s="2" t="s">
+      <c r="A901" s="5" t="s">
         <v>1001</v>
       </c>
       <c r="B901" t="s">
@@ -12740,7 +13495,7 @@
       </c>
     </row>
     <row r="902" spans="1:2">
-      <c r="A902" s="2" t="s">
+      <c r="A902" s="5" t="s">
         <v>1002</v>
       </c>
       <c r="B902" t="s">
@@ -12748,7 +13503,7 @@
       </c>
     </row>
     <row r="903" spans="1:2">
-      <c r="A903" s="2" t="s">
+      <c r="A903" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="B903" t="s">
@@ -12756,7 +13511,7 @@
       </c>
     </row>
     <row r="904" spans="1:2">
-      <c r="A904" s="2" t="s">
+      <c r="A904" s="5" t="s">
         <v>1004</v>
       </c>
       <c r="B904" t="s">
@@ -12764,7 +13519,7 @@
       </c>
     </row>
     <row r="905" spans="1:2">
-      <c r="A905" s="2" t="s">
+      <c r="A905" s="5" t="s">
         <v>1005</v>
       </c>
       <c r="B905" t="s">
@@ -12772,7 +13527,7 @@
       </c>
     </row>
     <row r="906" spans="1:2">
-      <c r="A906" s="2" t="s">
+      <c r="A906" s="5" t="s">
         <v>1006</v>
       </c>
       <c r="B906" t="s">
@@ -12780,7 +13535,7 @@
       </c>
     </row>
     <row r="907" spans="1:2">
-      <c r="A907" s="2" t="s">
+      <c r="A907" s="5" t="s">
         <v>1007</v>
       </c>
       <c r="B907" t="s">
@@ -12788,7 +13543,7 @@
       </c>
     </row>
     <row r="908" spans="1:2">
-      <c r="A908" s="2" t="s">
+      <c r="A908" s="5" t="s">
         <v>1008</v>
       </c>
       <c r="B908" t="s">
@@ -12796,1650 +13551,1650 @@
       </c>
     </row>
     <row r="909" spans="1:2">
-      <c r="A909" s="2" t="s">
+      <c r="A909" s="5" t="s">
         <v>1010</v>
       </c>
       <c r="B909" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="910" spans="1:2">
-      <c r="A910" s="2" t="s">
+      <c r="A910" s="5" t="s">
         <v>1011</v>
       </c>
       <c r="B910" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="911" spans="1:2">
-      <c r="A911" s="2" t="s">
+      <c r="A911" s="5" t="s">
         <v>1012</v>
       </c>
       <c r="B911" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="912" spans="1:2">
-      <c r="A912" s="2" t="s">
+      <c r="A912" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="B912" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="913" spans="1:2">
-      <c r="A913" s="2" t="s">
+      <c r="A913" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="B913" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="914" spans="1:2">
-      <c r="A914" s="2" t="s">
+      <c r="A914" s="5" t="s">
         <v>1015</v>
       </c>
       <c r="B914" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="915" spans="1:2">
-      <c r="A915" s="2" t="s">
+      <c r="A915" s="5" t="s">
         <v>1016</v>
       </c>
       <c r="B915" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="916" spans="1:2">
-      <c r="A916" s="2" t="s">
+      <c r="A916" s="5" t="s">
         <v>1017</v>
       </c>
       <c r="B916" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="917" spans="1:2">
-      <c r="A917" s="2" t="s">
-        <v>1019</v>
+      <c r="A917" s="5" t="s">
+        <v>1020</v>
       </c>
       <c r="B917" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2">
+      <c r="A923" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="5" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="918" spans="1:2">
-      <c r="A918" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="919" spans="1:2">
-      <c r="A919" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="920" spans="1:2">
-      <c r="A920" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="921" spans="1:2">
-      <c r="A921" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="922" spans="1:2">
-      <c r="A922" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="923" spans="1:2">
-      <c r="A923" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B923" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="924" spans="1:2">
-      <c r="A924" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="925" spans="1:2">
-      <c r="A925" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="926" spans="1:2">
-      <c r="A926" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="927" spans="1:2">
-      <c r="A927" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="928" spans="1:2">
-      <c r="A928" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="929" spans="1:2">
-      <c r="A929" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="930" spans="1:2">
-      <c r="A930" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="B930" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="931" spans="1:2">
-      <c r="A931" s="2" t="s">
+      <c r="A931" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B931" t="s">
         <v>1035</v>
       </c>
-      <c r="B931" t="s">
-        <v>1034</v>
-      </c>
     </row>
     <row r="932" spans="1:2">
-      <c r="A932" s="2" t="s">
-        <v>1036</v>
+      <c r="A932" s="5" t="s">
+        <v>1037</v>
       </c>
       <c r="B932" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="933" spans="1:2">
-      <c r="A933" s="2" t="s">
-        <v>1037</v>
+      <c r="A933" s="5" t="s">
+        <v>1038</v>
       </c>
       <c r="B933" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="934" spans="1:2">
-      <c r="A934" s="2" t="s">
-        <v>1039</v>
+      <c r="A934" s="5" t="s">
+        <v>1040</v>
       </c>
       <c r="B934" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2">
+      <c r="A939" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2">
+      <c r="A940" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2">
+      <c r="A942" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" s="5" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="935" spans="1:2">
-      <c r="A935" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="936" spans="1:2">
-      <c r="A936" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="937" spans="1:2">
-      <c r="A937" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="938" spans="1:2">
-      <c r="A938" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="939" spans="1:2">
-      <c r="A939" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="940" spans="1:2">
-      <c r="A940" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="941" spans="1:2">
-      <c r="A941" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="942" spans="1:2">
-      <c r="A942" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="943" spans="1:2">
-      <c r="A943" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="944" spans="1:2">
-      <c r="A944" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="945" spans="1:2">
-      <c r="A945" s="2" t="s">
-        <v>1050</v>
-      </c>
       <c r="B945" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="948" spans="1:2">
-      <c r="A948" s="2" t="s">
+      <c r="A948" s="5" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2">
+      <c r="A949" s="5" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="949" spans="1:2">
-      <c r="A949" s="2" t="s">
-        <v>1052</v>
-      </c>
       <c r="B949" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2">
+      <c r="A950" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B950" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="950" spans="1:2">
-      <c r="A950" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B950" t="s">
+    <row r="951" spans="1:2">
+      <c r="A951" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2">
+      <c r="A952" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2">
+      <c r="A953" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2">
+      <c r="A954" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2">
+      <c r="A955" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2">
+      <c r="A956" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2">
+      <c r="A957" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2">
+      <c r="A958" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2">
+      <c r="A959" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2">
+      <c r="A960" s="5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2">
+      <c r="A961" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2">
+      <c r="A962" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2">
+      <c r="A963" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2">
+      <c r="A964" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2">
+      <c r="A965" s="5" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="951" spans="1:2">
-      <c r="A951" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B951" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="952" spans="1:2">
-      <c r="A952" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="953" spans="1:2">
-      <c r="A953" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="954" spans="1:2">
-      <c r="A954" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="955" spans="1:2">
-      <c r="A955" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="956" spans="1:2">
-      <c r="A956" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="957" spans="1:2">
-      <c r="A957" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B957" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="958" spans="1:2">
-      <c r="A958" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="959" spans="1:2">
-      <c r="A959" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="960" spans="1:2">
-      <c r="A960" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="961" spans="1:2">
-      <c r="A961" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="962" spans="1:2">
-      <c r="A962" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="963" spans="1:2">
-      <c r="A963" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="964" spans="1:2">
-      <c r="A964" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="965" spans="1:2">
-      <c r="A965" s="2" t="s">
-        <v>1069</v>
-      </c>
       <c r="B965" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="966" spans="1:2">
-      <c r="A966" s="2" t="s">
-        <v>1073</v>
+      <c r="A966" s="5" t="s">
+        <v>1074</v>
       </c>
       <c r="B966" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="967" spans="1:2">
-      <c r="A967" s="2" t="s">
-        <v>1074</v>
+      <c r="A967" s="5" t="s">
+        <v>1075</v>
       </c>
       <c r="B967" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="968" spans="1:2">
-      <c r="A968" s="2" t="s">
-        <v>1075</v>
+      <c r="A968" s="5" t="s">
+        <v>1076</v>
       </c>
       <c r="B968" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="969" spans="1:2">
-      <c r="A969" s="2" t="s">
-        <v>1076</v>
+      <c r="A969" s="5" t="s">
+        <v>1077</v>
       </c>
       <c r="B969" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="970" spans="1:2">
-      <c r="A970" s="2" t="s">
-        <v>1077</v>
+      <c r="A970" s="5" t="s">
+        <v>1078</v>
       </c>
       <c r="B970" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="971" spans="1:2">
-      <c r="A971" s="2" t="s">
-        <v>1078</v>
+      <c r="A971" s="5" t="s">
+        <v>1079</v>
       </c>
       <c r="B971" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="972" spans="1:2">
-      <c r="A972" s="2" t="s">
-        <v>1079</v>
+      <c r="A972" s="5" t="s">
+        <v>1080</v>
       </c>
       <c r="B972" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="973" spans="1:2">
-      <c r="A973" s="2" t="s">
-        <v>1080</v>
+      <c r="A973" s="5" t="s">
+        <v>1081</v>
       </c>
       <c r="B973" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="974" spans="1:2">
-      <c r="A974" s="2" t="s">
-        <v>1081</v>
+      <c r="A974" s="5" t="s">
+        <v>1082</v>
       </c>
       <c r="B974" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="975" spans="1:2">
-      <c r="A975" s="2" t="s">
-        <v>1082</v>
+      <c r="A975" s="5" t="s">
+        <v>1083</v>
       </c>
       <c r="B975" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="976" spans="1:2">
-      <c r="A976" s="2" t="s">
-        <v>1083</v>
+      <c r="A976" s="5" t="s">
+        <v>1084</v>
       </c>
       <c r="B976" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="977" spans="1:2">
-      <c r="A977" s="2" t="s">
-        <v>1084</v>
+      <c r="A977" s="5" t="s">
+        <v>1085</v>
       </c>
       <c r="B977" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="978" spans="1:2">
-      <c r="A978" s="2" t="s">
-        <v>1085</v>
+      <c r="A978" s="5" t="s">
+        <v>1086</v>
       </c>
       <c r="B978" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="979" spans="1:2">
-      <c r="A979" s="2" t="s">
-        <v>1086</v>
+      <c r="A979" s="5" t="s">
+        <v>1087</v>
       </c>
       <c r="B979" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="980" spans="1:2">
-      <c r="A980" s="2" t="s">
-        <v>1087</v>
+      <c r="A980" s="5" t="s">
+        <v>1088</v>
       </c>
       <c r="B980" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="981" spans="1:2">
-      <c r="A981" s="2" t="s">
-        <v>1088</v>
+      <c r="A981" s="5" t="s">
+        <v>1089</v>
       </c>
       <c r="B981" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="982" spans="1:2">
-      <c r="A982" s="2" t="s">
-        <v>1089</v>
+      <c r="A982" s="5" t="s">
+        <v>1090</v>
       </c>
       <c r="B982" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="983" spans="1:2">
-      <c r="A983" s="2" t="s">
-        <v>1090</v>
+      <c r="A983" s="5" t="s">
+        <v>1091</v>
       </c>
       <c r="B983" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="984" spans="1:2">
-      <c r="A984" s="2" t="s">
-        <v>1091</v>
+      <c r="A984" s="5" t="s">
+        <v>1092</v>
       </c>
       <c r="B984" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="985" spans="1:2">
-      <c r="A985" s="2" t="s">
-        <v>1092</v>
+      <c r="A985" s="5" t="s">
+        <v>1093</v>
       </c>
       <c r="B985" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="986" spans="1:2">
-      <c r="A986" s="2" t="s">
-        <v>1093</v>
+      <c r="A986" s="5" t="s">
+        <v>1094</v>
       </c>
       <c r="B986" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B987" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="988" spans="1:2">
-      <c r="A988" s="2" t="s">
-        <v>1095</v>
+      <c r="A988" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B988" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="989" spans="1:2">
-      <c r="A989" s="2" t="s">
-        <v>1096</v>
+      <c r="A989" s="5" t="s">
+        <v>1097</v>
       </c>
       <c r="B989" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="990" spans="1:2">
-      <c r="A990" s="2" t="s">
-        <v>1097</v>
+      <c r="A990" s="5" t="s">
+        <v>1098</v>
       </c>
       <c r="B990" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="991" spans="1:2">
-      <c r="A991" s="2" t="s">
-        <v>1098</v>
+      <c r="A991" s="5" t="s">
+        <v>1099</v>
       </c>
       <c r="B991" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="992" spans="1:2">
-      <c r="A992" s="2" t="s">
-        <v>1099</v>
+      <c r="A992" s="5" t="s">
+        <v>1100</v>
       </c>
       <c r="B992" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="993" spans="1:2">
-      <c r="A993" s="2" t="s">
-        <v>1100</v>
+      <c r="A993" s="5" t="s">
+        <v>1101</v>
       </c>
       <c r="B993" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="994" spans="1:2">
-      <c r="A994" s="2" t="s">
-        <v>1101</v>
+      <c r="A994" s="5" t="s">
+        <v>1102</v>
       </c>
       <c r="B994" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="995" spans="1:2">
-      <c r="A995" s="2" t="s">
-        <v>1102</v>
+      <c r="A995" s="5" t="s">
+        <v>1103</v>
       </c>
       <c r="B995" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="996" spans="1:2">
-      <c r="A996" s="2" t="s">
-        <v>1103</v>
+      <c r="A996" s="5" t="s">
+        <v>1104</v>
       </c>
       <c r="B996" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="997" spans="1:2">
-      <c r="A997" s="2" t="s">
-        <v>1104</v>
+      <c r="A997" s="5" t="s">
+        <v>1105</v>
       </c>
       <c r="B997" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="998" spans="1:2">
-      <c r="A998" s="2" t="s">
-        <v>1105</v>
+      <c r="A998" s="5" t="s">
+        <v>1106</v>
       </c>
       <c r="B998" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="999" spans="1:2">
-      <c r="A999" s="2" t="s">
-        <v>1106</v>
+      <c r="A999" s="5" t="s">
+        <v>1107</v>
       </c>
       <c r="B999" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
-      <c r="A1000" s="2" t="s">
-        <v>1107</v>
+      <c r="A1000" s="5" t="s">
+        <v>1108</v>
       </c>
       <c r="B1000" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
-      <c r="A1001" s="2" t="s">
-        <v>1108</v>
+      <c r="A1001" s="5" t="s">
+        <v>1109</v>
       </c>
       <c r="B1001" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
-      <c r="A1002" s="2" t="s">
-        <v>1109</v>
+      <c r="A1002" s="5" t="s">
+        <v>1110</v>
       </c>
       <c r="B1002" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
-      <c r="A1003" s="2" t="s">
-        <v>1110</v>
+      <c r="A1003" s="5" t="s">
+        <v>1111</v>
       </c>
       <c r="B1003" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
-      <c r="A1004" s="2" t="s">
-        <v>1111</v>
+      <c r="A1004" s="5" t="s">
+        <v>1112</v>
       </c>
       <c r="B1004" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
-      <c r="A1005" s="2" t="s">
-        <v>1112</v>
+      <c r="A1005" s="5" t="s">
+        <v>1113</v>
       </c>
       <c r="B1005" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
-      <c r="A1006" s="2" t="s">
-        <v>1113</v>
+      <c r="A1006" s="5" t="s">
+        <v>1114</v>
       </c>
       <c r="B1006" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
-      <c r="A1007" s="2" t="s">
-        <v>1114</v>
+      <c r="A1007" s="5" t="s">
+        <v>1115</v>
       </c>
       <c r="B1007" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
-      <c r="A1008" s="2" t="s">
-        <v>1115</v>
+      <c r="A1008" s="5" t="s">
+        <v>1116</v>
       </c>
       <c r="B1008" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
-      <c r="A1009" s="2" t="s">
-        <v>1116</v>
+      <c r="A1009" s="5" t="s">
+        <v>1117</v>
       </c>
       <c r="B1009" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
-      <c r="A1010" s="2" t="s">
-        <v>1122</v>
+      <c r="A1010" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="B1010" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
-      <c r="A1011" s="2" t="s">
-        <v>1123</v>
+      <c r="A1011" s="5" t="s">
+        <v>1124</v>
       </c>
       <c r="B1011" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
-      <c r="A1012" s="2" t="s">
-        <v>1124</v>
+      <c r="A1012" s="5" t="s">
+        <v>1125</v>
       </c>
       <c r="B1012" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
-      <c r="A1013" s="2" t="s">
-        <v>1125</v>
+      <c r="A1013" s="5" t="s">
+        <v>1126</v>
       </c>
       <c r="B1013" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
-      <c r="A1014" s="2" t="s">
-        <v>1126</v>
+      <c r="A1014" s="5" t="s">
+        <v>1127</v>
       </c>
       <c r="B1014" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
-      <c r="A1015" s="2" t="s">
-        <v>1127</v>
+      <c r="A1015" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="B1015" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
-      <c r="A1016" s="2" t="s">
-        <v>1128</v>
+      <c r="A1016" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="B1016" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
-      <c r="A1017" s="2" t="s">
-        <v>1129</v>
+      <c r="A1017" s="5" t="s">
+        <v>1130</v>
       </c>
       <c r="B1017" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
-      <c r="A1018" s="2" t="s">
-        <v>1130</v>
+      <c r="A1018" s="5" t="s">
+        <v>1131</v>
       </c>
       <c r="B1018" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
-      <c r="A1019" s="2" t="s">
-        <v>1131</v>
+      <c r="A1019" s="5" t="s">
+        <v>1132</v>
       </c>
       <c r="B1019" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
-      <c r="A1020" s="2" t="s">
-        <v>1132</v>
+      <c r="A1020" s="5" t="s">
+        <v>1133</v>
       </c>
       <c r="B1020" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
-      <c r="A1021" s="2" t="s">
-        <v>1133</v>
+      <c r="A1021" s="5" t="s">
+        <v>1134</v>
       </c>
       <c r="B1021" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
-      <c r="A1022" s="2" t="s">
-        <v>1134</v>
+      <c r="A1022" s="5" t="s">
+        <v>1135</v>
       </c>
       <c r="B1022" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
-      <c r="A1023" s="2" t="s">
+      <c r="A1023" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1136</v>
       </c>
-      <c r="B1023" t="s">
-        <v>1135</v>
-      </c>
     </row>
     <row r="1024" spans="1:2">
-      <c r="A1024" s="2" t="s">
-        <v>1137</v>
+      <c r="A1024" s="5" t="s">
+        <v>1138</v>
       </c>
       <c r="B1024" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
-      <c r="A1025" s="2" t="s">
-        <v>1138</v>
+      <c r="A1025" s="5" t="s">
+        <v>1139</v>
       </c>
       <c r="B1025" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
-      <c r="A1026" s="2" t="s">
-        <v>1139</v>
+      <c r="A1026" s="5" t="s">
+        <v>1140</v>
       </c>
       <c r="B1026" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
-      <c r="A1027" s="2" t="s">
-        <v>1140</v>
+      <c r="A1027" s="5" t="s">
+        <v>1141</v>
       </c>
       <c r="B1027" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
-      <c r="A1028" s="2" t="s">
-        <v>1141</v>
+      <c r="A1028" s="5" t="s">
+        <v>1142</v>
       </c>
       <c r="B1028" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
-      <c r="A1029" s="2" t="s">
-        <v>1142</v>
+      <c r="A1029" s="5" t="s">
+        <v>1143</v>
       </c>
       <c r="B1029" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
-      <c r="A1030" s="2" t="s">
-        <v>1143</v>
+      <c r="A1030" s="5" t="s">
+        <v>1144</v>
       </c>
       <c r="B1030" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
-      <c r="A1031" s="2" t="s">
-        <v>1144</v>
+      <c r="A1031" s="5" t="s">
+        <v>1145</v>
       </c>
       <c r="B1031" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
-      <c r="A1032" s="2" t="s">
-        <v>1145</v>
+      <c r="A1032" s="5" t="s">
+        <v>1146</v>
       </c>
       <c r="B1032" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
-      <c r="A1033" s="2" t="s">
-        <v>1146</v>
+      <c r="A1033" s="5" t="s">
+        <v>1147</v>
       </c>
       <c r="B1033" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
-      <c r="A1034" s="2" t="s">
+      <c r="A1034" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B1034" t="s">
         <v>1148</v>
       </c>
-      <c r="B1034" t="s">
-        <v>1147</v>
-      </c>
     </row>
     <row r="1035" spans="1:2">
-      <c r="A1035" s="2" t="s">
-        <v>1149</v>
+      <c r="A1035" s="5" t="s">
+        <v>1150</v>
       </c>
       <c r="B1035" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
-      <c r="A1036" s="2" t="s">
-        <v>1150</v>
+      <c r="A1036" s="5" t="s">
+        <v>1151</v>
       </c>
       <c r="B1036" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
-      <c r="A1037" s="2" t="s">
-        <v>1151</v>
+      <c r="A1037" s="5" t="s">
+        <v>1152</v>
       </c>
       <c r="B1037" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
-      <c r="A1038" s="2" t="s">
-        <v>1152</v>
+      <c r="A1038" s="5" t="s">
+        <v>1153</v>
       </c>
       <c r="B1038" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
-      <c r="A1039" s="2" t="s">
-        <v>1153</v>
+      <c r="A1039" s="5" t="s">
+        <v>1154</v>
       </c>
       <c r="B1039" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
-      <c r="A1040" s="2" t="s">
-        <v>1154</v>
+      <c r="A1040" s="5" t="s">
+        <v>1155</v>
       </c>
       <c r="B1040" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
-      <c r="A1041" s="2" t="s">
-        <v>1155</v>
+      <c r="A1041" s="5" t="s">
+        <v>1156</v>
       </c>
       <c r="B1041" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
-      <c r="A1042" s="2" t="s">
-        <v>1156</v>
+      <c r="A1042" s="5" t="s">
+        <v>1157</v>
       </c>
       <c r="B1042" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
-      <c r="A1043" s="2" t="s">
-        <v>1157</v>
+      <c r="A1043" s="5" t="s">
+        <v>1158</v>
       </c>
       <c r="B1043" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
-      <c r="A1044" s="2" t="s">
-        <v>1158</v>
+      <c r="A1044" s="5" t="s">
+        <v>1159</v>
       </c>
       <c r="B1044" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
-      <c r="A1045" s="2" t="s">
-        <v>1159</v>
+      <c r="A1045" s="5" t="s">
+        <v>1160</v>
       </c>
       <c r="B1045" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
-      <c r="A1046" s="2" t="s">
-        <v>1160</v>
+      <c r="A1046" s="5" t="s">
+        <v>1161</v>
       </c>
       <c r="B1046" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
-      <c r="A1047" s="2" t="s">
-        <v>1161</v>
+      <c r="A1047" s="5" t="s">
+        <v>1162</v>
       </c>
       <c r="B1047" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
-      <c r="A1048" s="2" t="s">
-        <v>1162</v>
+      <c r="A1048" s="5" t="s">
+        <v>1163</v>
       </c>
       <c r="B1048" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
-      <c r="A1049" s="2" t="s">
-        <v>1163</v>
+      <c r="A1049" s="5" t="s">
+        <v>1164</v>
       </c>
       <c r="B1049" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
-      <c r="A1050" s="2" t="s">
-        <v>1164</v>
+      <c r="A1050" s="5" t="s">
+        <v>1165</v>
       </c>
       <c r="B1050" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
-      <c r="A1051" s="2" t="s">
-        <v>1166</v>
+      <c r="A1051" s="5" t="s">
+        <v>1167</v>
       </c>
       <c r="B1051" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:2">
+      <c r="A1052" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:2">
+      <c r="A1053" s="5" t="s">
         <v>1169</v>
       </c>
-    </row>
-    <row r="1052" spans="1:2">
-      <c r="A1052" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="1053" spans="1:2">
-      <c r="A1053" s="2" t="s">
-        <v>1168</v>
-      </c>
       <c r="B1053" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
-      <c r="A1054" s="2" t="s">
+      <c r="A1054" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1171</v>
       </c>
-      <c r="B1054" t="s">
-        <v>1170</v>
-      </c>
     </row>
     <row r="1055" spans="1:2">
-      <c r="A1055" s="2" t="s">
-        <v>1172</v>
+      <c r="A1055" s="5" t="s">
+        <v>1173</v>
       </c>
       <c r="B1055" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
-      <c r="A1056" s="2" t="s">
-        <v>1173</v>
+      <c r="A1056" s="5" t="s">
+        <v>1174</v>
       </c>
       <c r="B1056" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
-      <c r="A1057" s="2" t="s">
-        <v>1174</v>
+      <c r="A1057" s="5" t="s">
+        <v>1175</v>
       </c>
       <c r="B1057" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
-      <c r="A1058" s="2" t="s">
-        <v>1175</v>
+      <c r="A1058" s="5" t="s">
+        <v>1176</v>
       </c>
       <c r="B1058" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
-      <c r="A1059" s="2" t="s">
-        <v>1176</v>
+      <c r="A1059" s="5" t="s">
+        <v>1177</v>
       </c>
       <c r="B1059" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
-      <c r="A1060" s="2" t="s">
-        <v>1177</v>
+      <c r="A1060" s="5" t="s">
+        <v>1178</v>
       </c>
       <c r="B1060" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
-      <c r="A1061" s="2" t="s">
-        <v>1178</v>
+      <c r="A1061" s="5" t="s">
+        <v>1179</v>
       </c>
       <c r="B1061" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
-      <c r="A1062" s="2" t="s">
-        <v>1179</v>
+      <c r="A1062" s="5" t="s">
+        <v>1180</v>
       </c>
       <c r="B1062" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
-      <c r="A1063" s="2" t="s">
-        <v>1180</v>
+      <c r="A1063" s="5" t="s">
+        <v>1181</v>
       </c>
       <c r="B1063" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
-      <c r="A1064" s="2" t="s">
-        <v>1181</v>
+      <c r="A1064" s="5" t="s">
+        <v>1182</v>
       </c>
       <c r="B1064" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
-      <c r="A1065" s="2" t="s">
-        <v>1182</v>
+      <c r="A1065" s="5" t="s">
+        <v>1183</v>
       </c>
       <c r="B1065" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
-      <c r="A1066" s="2" t="s">
-        <v>1183</v>
+      <c r="A1066" s="5" t="s">
+        <v>1184</v>
       </c>
       <c r="B1066" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
-      <c r="A1067" s="2" t="s">
-        <v>1184</v>
+      <c r="A1067" s="5" t="s">
+        <v>1185</v>
       </c>
       <c r="B1067" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
-      <c r="A1068" s="2" t="s">
-        <v>1185</v>
+      <c r="A1068" s="5" t="s">
+        <v>1186</v>
       </c>
       <c r="B1068" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
-      <c r="A1069" s="2" t="s">
-        <v>1186</v>
+      <c r="A1069" s="5" t="s">
+        <v>1187</v>
       </c>
       <c r="B1069" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
-      <c r="A1070" s="2" t="s">
-        <v>1187</v>
+      <c r="A1070" s="5" t="s">
+        <v>1188</v>
       </c>
       <c r="B1070" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
-      <c r="A1071" s="2" t="s">
-        <v>1188</v>
+      <c r="A1071" s="5" t="s">
+        <v>1189</v>
       </c>
       <c r="B1071" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
-      <c r="A1072" s="2" t="s">
-        <v>1189</v>
+      <c r="A1072" s="5" t="s">
+        <v>1190</v>
       </c>
       <c r="B1072" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
-      <c r="A1073" s="2" t="s">
-        <v>1190</v>
+      <c r="A1073" s="5" t="s">
+        <v>1191</v>
       </c>
       <c r="B1073" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
-      <c r="A1074" s="2" t="s">
-        <v>1191</v>
+      <c r="A1074" s="5" t="s">
+        <v>1192</v>
       </c>
       <c r="B1074" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
-      <c r="A1075" s="2" t="s">
-        <v>1192</v>
+      <c r="A1075" s="5" t="s">
+        <v>1193</v>
       </c>
       <c r="B1075" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
-      <c r="A1076" s="2" t="s">
-        <v>1193</v>
+      <c r="A1076" s="5" t="s">
+        <v>1194</v>
       </c>
       <c r="B1076" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
-      <c r="A1077" s="2" t="s">
-        <v>1194</v>
+      <c r="A1077" s="5" t="s">
+        <v>1195</v>
       </c>
       <c r="B1077" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
-      <c r="A1078" s="2" t="s">
-        <v>1195</v>
+      <c r="A1078" s="5" t="s">
+        <v>1196</v>
       </c>
       <c r="B1078" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
-      <c r="A1079" s="2" t="s">
-        <v>1196</v>
+      <c r="A1079" s="5" t="s">
+        <v>1197</v>
       </c>
       <c r="B1079" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
-      <c r="A1080" s="2" t="s">
-        <v>1197</v>
+      <c r="A1080" s="5" t="s">
+        <v>1198</v>
       </c>
       <c r="B1080" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
-      <c r="A1081" s="2" t="s">
-        <v>1198</v>
+      <c r="A1081" s="5" t="s">
+        <v>1199</v>
       </c>
       <c r="B1081" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
-      <c r="A1082" s="2" t="s">
+      <c r="A1082" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B1082" t="s">
         <v>1200</v>
       </c>
-      <c r="B1082" t="s">
-        <v>1199</v>
-      </c>
     </row>
     <row r="1083" spans="1:2">
-      <c r="A1083" s="2" t="s">
-        <v>1201</v>
+      <c r="A1083" s="5" t="s">
+        <v>1202</v>
       </c>
       <c r="B1083" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
-      <c r="A1084" s="2" t="s">
-        <v>1202</v>
+      <c r="A1084" s="5" t="s">
+        <v>1203</v>
       </c>
       <c r="B1084" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
-      <c r="A1085" s="2" t="s">
-        <v>1203</v>
+      <c r="A1085" s="5" t="s">
+        <v>1204</v>
       </c>
       <c r="B1085" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
-      <c r="A1086" s="2" t="s">
-        <v>1204</v>
+      <c r="A1086" s="5" t="s">
+        <v>1205</v>
       </c>
       <c r="B1086" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
-      <c r="A1087" s="2" t="s">
-        <v>1205</v>
+      <c r="A1087" s="5" t="s">
+        <v>1206</v>
       </c>
       <c r="B1087" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
-      <c r="A1088" s="2" t="s">
-        <v>1206</v>
+      <c r="A1088" s="5" t="s">
+        <v>1207</v>
       </c>
       <c r="B1088" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
-      <c r="A1089" s="2" t="s">
-        <v>1207</v>
+      <c r="A1089" s="5" t="s">
+        <v>1208</v>
       </c>
       <c r="B1089" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
-      <c r="A1090" s="2" t="s">
-        <v>1208</v>
+      <c r="A1090" s="5" t="s">
+        <v>1209</v>
       </c>
       <c r="B1090" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
-      <c r="A1091" s="2" t="s">
-        <v>1209</v>
+      <c r="A1091" s="5" t="s">
+        <v>1210</v>
       </c>
       <c r="B1091" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
-      <c r="A1092" s="2" t="s">
-        <v>1210</v>
+      <c r="A1092" s="5" t="s">
+        <v>1211</v>
       </c>
       <c r="B1092" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
-      <c r="A1096" s="2" t="s">
-        <v>1212</v>
+      <c r="A1096" s="5" t="s">
+        <v>1213</v>
       </c>
       <c r="B1096" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
-      <c r="A1097" s="2" t="s">
-        <v>1213</v>
+      <c r="A1097" s="5" t="s">
+        <v>1214</v>
       </c>
       <c r="B1097" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
-      <c r="A1098" s="2" t="s">
-        <v>1214</v>
+      <c r="A1098" s="5" t="s">
+        <v>1215</v>
       </c>
       <c r="B1098" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
-      <c r="A1099" s="2" t="s">
-        <v>1215</v>
+      <c r="A1099" s="5" t="s">
+        <v>1216</v>
       </c>
       <c r="B1099" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
-      <c r="A1100" s="2" t="s">
-        <v>1216</v>
+      <c r="A1100" s="5" t="s">
+        <v>1217</v>
       </c>
       <c r="B1100" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
-      <c r="A1101" s="2" t="s">
-        <v>1217</v>
+      <c r="A1101" s="5" t="s">
+        <v>1218</v>
       </c>
       <c r="B1101" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
-      <c r="A1102" s="2" t="s">
-        <v>1218</v>
+      <c r="A1102" s="5" t="s">
+        <v>1219</v>
       </c>
       <c r="B1102" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
-      <c r="A1103" s="2" t="s">
-        <v>1219</v>
+      <c r="A1103" s="5" t="s">
+        <v>1220</v>
       </c>
       <c r="B1103" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
-      <c r="A1104" s="2" t="s">
-        <v>1220</v>
+      <c r="A1104" s="5" t="s">
+        <v>1221</v>
       </c>
       <c r="B1104" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
-      <c r="A1105" s="2" t="s">
-        <v>1221</v>
+      <c r="A1105" s="5" t="s">
+        <v>1222</v>
       </c>
       <c r="B1105" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
-      <c r="A1106" s="2" t="s">
-        <v>1222</v>
+      <c r="A1106" s="5" t="s">
+        <v>1223</v>
       </c>
       <c r="B1106" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
-      <c r="A1107" s="2" t="s">
+      <c r="A1107" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:2">
+      <c r="A1108" s="5" t="s">
         <v>1224</v>
       </c>
-      <c r="B1107" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:2">
-      <c r="A1108" s="2" t="s">
-        <v>1223</v>
-      </c>
       <c r="B1108" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
-      <c r="A1109" s="2" t="s">
-        <v>1225</v>
+      <c r="A1109" s="5" t="s">
+        <v>1226</v>
       </c>
       <c r="B1109" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
-      <c r="A1110" s="2" t="s">
-        <v>1226</v>
+      <c r="A1110" s="5" t="s">
+        <v>1227</v>
       </c>
       <c r="B1110" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
-      <c r="A1111" s="2" t="s">
-        <v>1227</v>
+      <c r="A1111" s="5" t="s">
+        <v>1228</v>
       </c>
       <c r="B1111" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
-      <c r="A1112" s="2" t="s">
-        <v>1228</v>
+      <c r="A1112" s="5" t="s">
+        <v>1229</v>
       </c>
       <c r="B1112" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
-      <c r="A1113" s="2" t="s">
-        <v>1229</v>
+      <c r="A1113" s="5" t="s">
+        <v>1230</v>
       </c>
       <c r="B1113" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
-      <c r="A1114" s="2" t="s">
-        <v>1230</v>
+      <c r="A1114" s="5" t="s">
+        <v>1231</v>
       </c>
       <c r="B1114" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
-      <c r="A1115" s="2" t="s">
-        <v>1231</v>
+      <c r="A1115" s="5" t="s">
+        <v>1232</v>
       </c>
       <c r="B1115" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
-      <c r="A1116" s="2" t="s">
-        <v>1232</v>
+      <c r="A1116" s="5" t="s">
+        <v>1233</v>
       </c>
       <c r="B1116" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
-      <c r="A1117" s="2" t="s">
-        <v>1233</v>
+      <c r="A1117" s="5" t="s">
+        <v>1234</v>
       </c>
       <c r="B1117" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
-      <c r="A1118" s="2" t="s">
-        <v>1234</v>
+      <c r="A1118" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="B1118" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
-      <c r="A1119" s="2" t="s">
-        <v>1235</v>
+      <c r="A1119" s="5" t="s">
+        <v>1236</v>
       </c>
       <c r="B1119" t="s">
         <v>463</v>
@@ -14447,551 +15202,551 @@
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B1120" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
-      <c r="A1121" s="2" t="s">
-        <v>1237</v>
+      <c r="A1121" s="5" t="s">
+        <v>1238</v>
       </c>
       <c r="B1121" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
-      <c r="A1122" s="2" t="s">
-        <v>1238</v>
+      <c r="A1122" s="5" t="s">
+        <v>1239</v>
       </c>
       <c r="B1122" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
-      <c r="A1123" s="2" t="s">
-        <v>1239</v>
+      <c r="A1123" s="5" t="s">
+        <v>1240</v>
       </c>
       <c r="B1123" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
-      <c r="A1124" s="2" t="s">
-        <v>1240</v>
+      <c r="A1124" s="5" t="s">
+        <v>1241</v>
       </c>
       <c r="B1124" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
-      <c r="A1125" s="2" t="s">
-        <v>1241</v>
+      <c r="A1125" s="5" t="s">
+        <v>1242</v>
       </c>
       <c r="B1125" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
-      <c r="A1126" s="2" t="s">
-        <v>1242</v>
+      <c r="A1126" s="5" t="s">
+        <v>1243</v>
       </c>
       <c r="B1126" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
-      <c r="A1127" s="2" t="s">
-        <v>1243</v>
+      <c r="A1127" s="5" t="s">
+        <v>1244</v>
       </c>
       <c r="B1127" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
-      <c r="A1128" s="2" t="s">
-        <v>1244</v>
+      <c r="A1128" s="5" t="s">
+        <v>1245</v>
       </c>
       <c r="B1128" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
-      <c r="A1129" s="2" t="s">
-        <v>1245</v>
+      <c r="A1129" s="5" t="s">
+        <v>1246</v>
       </c>
       <c r="B1129" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
-      <c r="A1130" s="2" t="s">
-        <v>1246</v>
+      <c r="A1130" s="5" t="s">
+        <v>1247</v>
       </c>
       <c r="B1130" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
-      <c r="A1131" s="2" t="s">
-        <v>1247</v>
+      <c r="A1131" s="5" t="s">
+        <v>1248</v>
       </c>
       <c r="B1131" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
-      <c r="A1132" s="2" t="s">
-        <v>1248</v>
+      <c r="A1132" s="5" t="s">
+        <v>1249</v>
       </c>
       <c r="B1132" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
-      <c r="A1133" s="2" t="s">
-        <v>1249</v>
+      <c r="A1133" s="5" t="s">
+        <v>1250</v>
       </c>
       <c r="B1133" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
-      <c r="A1134" s="2" t="s">
-        <v>1250</v>
+      <c r="A1134" s="5" t="s">
+        <v>1251</v>
       </c>
       <c r="B1134" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
-      <c r="A1135" s="2" t="s">
-        <v>1251</v>
+      <c r="A1135" s="5" t="s">
+        <v>1252</v>
       </c>
       <c r="B1135" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
-      <c r="A1136" s="2" t="s">
-        <v>1252</v>
+      <c r="A1136" s="5" t="s">
+        <v>1253</v>
       </c>
       <c r="B1136" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
-      <c r="A1137" s="2" t="s">
-        <v>1253</v>
+      <c r="A1137" s="5" t="s">
+        <v>1254</v>
       </c>
       <c r="B1137" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
-      <c r="A1138" s="2" t="s">
-        <v>1254</v>
+      <c r="A1138" s="5" t="s">
+        <v>1255</v>
       </c>
       <c r="B1138" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
-      <c r="A1139" s="2" t="s">
-        <v>1255</v>
+      <c r="A1139" s="5" t="s">
+        <v>1256</v>
       </c>
       <c r="B1139" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
-      <c r="A1140" s="2" t="s">
-        <v>1256</v>
+      <c r="A1140" s="5" t="s">
+        <v>1257</v>
       </c>
       <c r="B1140" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
-      <c r="A1141" s="2" t="s">
-        <v>1257</v>
+      <c r="A1141" s="5" t="s">
+        <v>1258</v>
       </c>
       <c r="B1141" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
-      <c r="A1142" s="2" t="s">
-        <v>1258</v>
+      <c r="A1142" s="5" t="s">
+        <v>1259</v>
       </c>
       <c r="B1142" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
-      <c r="A1143" s="2" t="s">
-        <v>1259</v>
+      <c r="A1143" s="5" t="s">
+        <v>1260</v>
       </c>
       <c r="B1143" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
-      <c r="A1144" s="2" t="s">
-        <v>1260</v>
+      <c r="A1144" s="5" t="s">
+        <v>1261</v>
       </c>
       <c r="B1144" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
-      <c r="A1145" s="2" t="s">
-        <v>1261</v>
+      <c r="A1145" s="5" t="s">
+        <v>1262</v>
       </c>
       <c r="B1145" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
-      <c r="A1146" s="2" t="s">
-        <v>1262</v>
+      <c r="A1146" s="5" t="s">
+        <v>1263</v>
       </c>
       <c r="B1146" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
-      <c r="A1147" s="2" t="s">
-        <v>1263</v>
+      <c r="A1147" s="5" t="s">
+        <v>1264</v>
       </c>
       <c r="B1147" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
-      <c r="A1148" s="2" t="s">
-        <v>1264</v>
+      <c r="A1148" s="5" t="s">
+        <v>1265</v>
       </c>
       <c r="B1148" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
-      <c r="A1149" s="2" t="s">
-        <v>1265</v>
+      <c r="A1149" s="5" t="s">
+        <v>1266</v>
       </c>
       <c r="B1149" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
-      <c r="A1150" s="2" t="s">
-        <v>1266</v>
+      <c r="A1150" s="5" t="s">
+        <v>1267</v>
       </c>
       <c r="B1150" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
-      <c r="A1151" s="2" t="s">
-        <v>1267</v>
+      <c r="A1151" s="5" t="s">
+        <v>1268</v>
       </c>
       <c r="B1151" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
-      <c r="A1152" s="2" t="s">
-        <v>1268</v>
+      <c r="A1152" s="5" t="s">
+        <v>1269</v>
       </c>
       <c r="B1152" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
-      <c r="A1153" s="2" t="s">
-        <v>1269</v>
+      <c r="A1153" s="5" t="s">
+        <v>1270</v>
       </c>
       <c r="B1153" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
-      <c r="A1154" s="2" t="s">
+      <c r="A1154" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1278</v>
       </c>
-      <c r="B1154" t="s">
-        <v>1277</v>
-      </c>
     </row>
     <row r="1155" spans="1:2">
-      <c r="A1155" s="2" t="s">
-        <v>1279</v>
+      <c r="A1155" s="5" t="s">
+        <v>1280</v>
       </c>
       <c r="B1155" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
-      <c r="A1156" s="2" t="s">
-        <v>1280</v>
+      <c r="A1156" s="5" t="s">
+        <v>1281</v>
       </c>
       <c r="B1156" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
-      <c r="A1157" s="2" t="s">
-        <v>1281</v>
+      <c r="A1157" s="5" t="s">
+        <v>1282</v>
       </c>
       <c r="B1157" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
-      <c r="A1158" s="2" t="s">
-        <v>1282</v>
+      <c r="A1158" s="5" t="s">
+        <v>1283</v>
       </c>
       <c r="B1158" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
-      <c r="A1159" s="2" t="s">
-        <v>1283</v>
+      <c r="A1159" s="5" t="s">
+        <v>1284</v>
       </c>
       <c r="B1159" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
-      <c r="A1160" s="2" t="s">
-        <v>1284</v>
+      <c r="A1160" s="5" t="s">
+        <v>1285</v>
       </c>
       <c r="B1160" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
-      <c r="A1161" s="2" t="s">
-        <v>1285</v>
+      <c r="A1161" s="5" t="s">
+        <v>1286</v>
       </c>
       <c r="B1161" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
-      <c r="A1162" s="2" t="s">
-        <v>1286</v>
+      <c r="A1162" s="5" t="s">
+        <v>1287</v>
       </c>
       <c r="B1162" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
-      <c r="A1163" s="2" t="s">
-        <v>1287</v>
+      <c r="A1163" s="5" t="s">
+        <v>1288</v>
       </c>
       <c r="B1163" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
-      <c r="A1164" s="2" t="s">
-        <v>1288</v>
+      <c r="A1164" s="5" t="s">
+        <v>1289</v>
       </c>
       <c r="B1164" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
-      <c r="A1165" s="2" t="s">
-        <v>1289</v>
+      <c r="A1165" s="5" t="s">
+        <v>1290</v>
       </c>
       <c r="B1165" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
-      <c r="A1166" s="2" t="s">
-        <v>1290</v>
+      <c r="A1166" s="5" t="s">
+        <v>1291</v>
       </c>
       <c r="B1166" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
-      <c r="A1167" s="2" t="s">
-        <v>1291</v>
+      <c r="A1167" s="5" t="s">
+        <v>1292</v>
       </c>
       <c r="B1167" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
-      <c r="A1168" s="2" t="s">
+      <c r="A1168" s="5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1168" t="s">
         <v>1293</v>
       </c>
-      <c r="B1168" t="s">
-        <v>1292</v>
-      </c>
     </row>
     <row r="1169" spans="1:2">
-      <c r="A1169" s="2" t="s">
-        <v>1294</v>
+      <c r="A1169" s="5" t="s">
+        <v>1295</v>
       </c>
       <c r="B1169" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
-      <c r="A1170" s="2" t="s">
-        <v>1295</v>
+      <c r="A1170" s="5" t="s">
+        <v>1296</v>
       </c>
       <c r="B1170" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
-      <c r="A1171" s="2" t="s">
-        <v>1296</v>
+      <c r="A1171" s="5" t="s">
+        <v>1297</v>
       </c>
       <c r="B1171" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
-      <c r="A1172" s="2" t="s">
-        <v>1297</v>
+      <c r="A1172" s="5" t="s">
+        <v>1298</v>
       </c>
       <c r="B1172" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
-      <c r="A1173" s="2" t="s">
-        <v>1298</v>
+      <c r="A1173" s="5" t="s">
+        <v>1299</v>
       </c>
       <c r="B1173" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
-      <c r="A1174" s="2" t="s">
-        <v>1299</v>
+      <c r="A1174" s="5" t="s">
+        <v>1300</v>
       </c>
       <c r="B1174" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2">
+      <c r="A1175" s="5" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2">
+      <c r="A1176" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2">
+      <c r="A1177" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" s="5" t="s">
         <v>1307</v>
       </c>
-    </row>
-    <row r="1175" spans="1:2">
-      <c r="A1175" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:2">
-      <c r="A1176" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:2">
-      <c r="A1177" s="2" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1178" spans="1:2">
-      <c r="A1178" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:2">
-      <c r="A1179" s="2" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:2">
-      <c r="A1180" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:2">
-      <c r="A1181" s="2" t="s">
-        <v>1306</v>
-      </c>
       <c r="B1181" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
-      <c r="A1182" s="2" t="s">
+      <c r="A1182" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1182" t="s">
         <v>1309</v>
       </c>
-      <c r="B1182" t="s">
-        <v>1308</v>
-      </c>
     </row>
     <row r="1183" spans="1:2">
-      <c r="A1183" s="2" t="s">
-        <v>1310</v>
+      <c r="A1183" s="5" t="s">
+        <v>1311</v>
       </c>
       <c r="B1183" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
-      <c r="A1184" s="2" t="s">
-        <v>1311</v>
+      <c r="A1184" s="5" t="s">
+        <v>1312</v>
       </c>
       <c r="B1184" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
-      <c r="A1185" s="2" t="s">
-        <v>1312</v>
+      <c r="A1185" s="5" t="s">
+        <v>1313</v>
       </c>
       <c r="B1185" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
-      <c r="A1186" s="2" t="s">
-        <v>1313</v>
+      <c r="A1186" s="5" t="s">
+        <v>1314</v>
       </c>
       <c r="B1186" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B1187" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
-      <c r="A1188" s="2" t="s">
-        <v>1316</v>
+      <c r="A1188" s="5" t="s">
+        <v>1317</v>
       </c>
       <c r="B1188" t="s">
         <v>875</v>
@@ -14999,198 +15754,1760 @@
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B1189" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
-      <c r="A1190" s="2" t="s">
-        <v>1318</v>
+      <c r="A1190" s="5" t="s">
+        <v>1319</v>
       </c>
       <c r="B1190" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
-      <c r="A1191" s="2" t="s">
-        <v>1319</v>
+      <c r="A1191" s="5" t="s">
+        <v>1320</v>
       </c>
       <c r="B1191" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
-      <c r="A1192" s="2" t="s">
-        <v>1320</v>
+      <c r="A1192" s="5" t="s">
+        <v>1321</v>
       </c>
       <c r="B1192" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
-      <c r="A1193" s="2" t="s">
-        <v>1321</v>
+      <c r="A1193" s="5" t="s">
+        <v>1322</v>
       </c>
       <c r="B1193" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
-      <c r="A1194" s="2" t="s">
-        <v>1322</v>
+      <c r="A1194" s="5" t="s">
+        <v>1323</v>
       </c>
       <c r="B1194" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
-      <c r="A1195" s="2" t="s">
-        <v>1323</v>
+      <c r="A1195" s="5" t="s">
+        <v>1324</v>
       </c>
       <c r="B1195" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
-      <c r="A1196" s="2" t="s">
-        <v>1324</v>
+      <c r="A1196" s="5" t="s">
+        <v>1325</v>
       </c>
       <c r="B1196" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
-      <c r="A1197" s="2" t="s">
-        <v>1325</v>
+      <c r="A1197" s="5" t="s">
+        <v>1326</v>
       </c>
       <c r="B1197" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
-      <c r="A1198" s="2" t="s">
-        <v>1326</v>
+      <c r="A1198" s="5" t="s">
+        <v>1327</v>
       </c>
       <c r="B1198" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" s="5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:2">
+      <c r="A1200" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:2">
+      <c r="A1201" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:2">
+      <c r="A1202" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:2">
+      <c r="A1203" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:2">
+      <c r="A1204" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:2">
+      <c r="A1205" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2">
+      <c r="A1210" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2">
+      <c r="A1211" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2">
+      <c r="A1212" s="5" t="s">
         <v>1341</v>
       </c>
-    </row>
-    <row r="1199" spans="1:2">
-      <c r="A1199" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="B1199" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:2">
-      <c r="A1200" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B1200" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:2">
-      <c r="A1201" s="2" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B1201" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:2">
-      <c r="A1202" s="2" t="s">
-        <v>1330</v>
-      </c>
-      <c r="B1202" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:2">
-      <c r="A1203" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B1203" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:2">
-      <c r="A1204" s="2" t="s">
-        <v>1332</v>
-      </c>
-      <c r="B1204" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:2">
-      <c r="A1205" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B1205" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:2">
-      <c r="A1206" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B1206" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:2">
-      <c r="A1207" s="2" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B1207" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1208" spans="1:2">
-      <c r="A1208" s="2" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B1208" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:2">
-      <c r="A1209" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B1209" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1210" spans="1:2">
-      <c r="A1210" s="2" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B1210" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:2">
-      <c r="A1211" s="2" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B1211" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:2">
-      <c r="A1212" s="2" t="s">
-        <v>1340</v>
-      </c>
       <c r="B1212" t="s">
-        <v>1341</v>
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:2">
+      <c r="A1215" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:2">
+      <c r="A1216" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:2">
+      <c r="A1217" s="5" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:2">
+      <c r="A1218" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:2">
+      <c r="A1219" s="5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:2">
+      <c r="A1220" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:2">
+      <c r="A1221" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:2">
+      <c r="A1222" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:2">
+      <c r="A1223" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:2">
+      <c r="A1224" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:2">
+      <c r="A1225" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:2">
+      <c r="A1226" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:2">
+      <c r="A1227" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:2">
+      <c r="A1228" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:2">
+      <c r="A1229" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:2">
+      <c r="A1230" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:2">
+      <c r="A1231" s="5" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:2">
+      <c r="A1232" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:2">
+      <c r="A1233" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:2">
+      <c r="A1234" s="5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:2">
+      <c r="A1235" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:2">
+      <c r="A1236" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:2">
+      <c r="A1237" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:2">
+      <c r="A1238" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:2">
+      <c r="A1239" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:2">
+      <c r="A1240" s="5" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:2">
+      <c r="A1241" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:2">
+      <c r="A1242" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:2">
+      <c r="A1243" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:2">
+      <c r="A1244" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:2">
+      <c r="A1245" s="5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:2">
+      <c r="A1246" s="5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:2">
+      <c r="A1247" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:2">
+      <c r="A1248" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:2">
+      <c r="A1249" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:2">
+      <c r="A1250" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:2">
+      <c r="A1251" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:2">
+      <c r="A1252" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:2">
+      <c r="A1253" s="5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:2">
+      <c r="A1254" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:2">
+      <c r="A1255" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:2">
+      <c r="A1256" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2">
+      <c r="A1257" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:2">
+      <c r="A1258" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:2">
+      <c r="A1259" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:2">
+      <c r="A1260" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:2">
+      <c r="A1261" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:2">
+      <c r="A1262" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:2">
+      <c r="A1263" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:2">
+      <c r="A1264" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:2">
+      <c r="A1265" s="5" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:2">
+      <c r="A1266" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:2">
+      <c r="A1267" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:2">
+      <c r="A1268" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:2">
+      <c r="A1269" s="6" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:2">
+      <c r="A1270" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:2">
+      <c r="A1271" s="5" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:2">
+      <c r="A1272" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:2">
+      <c r="A1273" s="5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:2">
+      <c r="A1274" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:2">
+      <c r="A1275" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:2">
+      <c r="A1276" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:2">
+      <c r="A1277" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:2">
+      <c r="A1278" s="5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:2">
+      <c r="A1279" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:2">
+      <c r="A1280" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:2">
+      <c r="A1281" s="5" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:2">
+      <c r="A1282" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:2">
+      <c r="A1283" s="5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:2">
+      <c r="A1284" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:2">
+      <c r="A1285" s="5" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:2">
+      <c r="A1286" s="5" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:2">
+      <c r="A1287" s="5" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:2">
+      <c r="A1288" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:2">
+      <c r="A1289" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:2">
+      <c r="A1290" s="5" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:2">
+      <c r="A1291" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:2">
+      <c r="A1292" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:2">
+      <c r="A1293" s="5" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:2">
+      <c r="A1294" s="5" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:2">
+      <c r="A1295" s="5" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:2">
+      <c r="A1296" s="5" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:2">
+      <c r="A1297" s="5" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2">
+      <c r="A1298" s="5" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2">
+      <c r="A1299" s="5" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:2">
+      <c r="A1300" s="5" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2">
+      <c r="A1301" s="5" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2">
+      <c r="A1302" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:2">
+      <c r="A1303" s="5" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:2">
+      <c r="A1304" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:2">
+      <c r="A1305" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:2">
+      <c r="A1306" s="5" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2">
+      <c r="A1307" s="5" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2">
+      <c r="A1308" s="5" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:2">
+      <c r="A1309" s="5" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:2">
+      <c r="A1310" s="5" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:2">
+      <c r="A1311" s="5" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:2">
+      <c r="A1312" s="5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:2">
+      <c r="A1313" s="5" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:2">
+      <c r="A1314" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:2">
+      <c r="A1315" s="5" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2">
+      <c r="A1316" s="5" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2">
+      <c r="A1317" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:2">
+      <c r="A1318" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2">
+      <c r="A1319" s="5" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2">
+      <c r="A1320" s="5" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2">
+      <c r="A1321" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2">
+      <c r="A1322" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:2">
+      <c r="A1323" s="5" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:2">
+      <c r="A1324" s="5" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2">
+      <c r="A1325" s="5" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2">
+      <c r="A1326" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:2">
+      <c r="A1327" s="5" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:2">
+      <c r="A1328" s="5" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:2">
+      <c r="A1329" s="5" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:2">
+      <c r="A1330" s="5" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:2">
+      <c r="A1331" s="5" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:2">
+      <c r="A1332" s="5" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:2">
+      <c r="A1333" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:2">
+      <c r="A1334" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:2">
+      <c r="A1335" s="5" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:2">
+      <c r="A1336" s="5" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:2">
+      <c r="A1337" s="5" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:2">
+      <c r="A1338" s="5" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:2">
+      <c r="A1339" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:2">
+      <c r="A1340" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:2">
+      <c r="A1341" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:2">
+      <c r="A1342" s="5" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:2">
+      <c r="A1343" s="5" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:2">
+      <c r="A1344" s="5" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:2">
+      <c r="A1345" s="5" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:2">
+      <c r="A1346" s="5" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:2">
+      <c r="A1347" s="5" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:2">
+      <c r="A1348" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:2">
+      <c r="A1349" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:2">
+      <c r="A1350" s="5" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:2">
+      <c r="A1351" s="5" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:2">
+      <c r="A1352" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:2">
+      <c r="A1353" s="5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:2">
+      <c r="A1354" s="5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:2">
+      <c r="A1355" s="5" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:2">
+      <c r="A1356" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:2">
+      <c r="A1357" s="5" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:2">
+      <c r="A1358" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:2">
+      <c r="A1359" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:2">
+      <c r="A1360" s="5" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:2">
+      <c r="A1361" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:2">
+      <c r="A1362" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:2">
+      <c r="A1363" s="5" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:2">
+      <c r="A1364" s="5" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:2">
+      <c r="A1365" s="5" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:2">
+      <c r="A1366" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:2">
+      <c r="A1367" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:2">
+      <c r="A1368" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:2">
+      <c r="A1369" s="5" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:2">
+      <c r="A1370" s="5" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:2">
+      <c r="A1371" s="5" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:2">
+      <c r="A1372" s="5" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:2">
+      <c r="A1373" s="5" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:2">
+      <c r="A1374" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:2">
+      <c r="A1375" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:2">
+      <c r="A1376" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:2">
+      <c r="A1377" s="5" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:2">
+      <c r="A1378" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:2">
+      <c r="A1379" s="5" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:2">
+      <c r="A1380" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:2">
+      <c r="A1381" s="5" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:2">
+      <c r="A1382" s="5" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:2">
+      <c r="A1383" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:2">
+      <c r="A1384" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:2">
+      <c r="A1385" s="5" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:2">
+      <c r="A1386" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:2">
+      <c r="A1387" s="5" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:2">
+      <c r="A1388" s="5" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:2">
+      <c r="A1389" s="5" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:2">
+      <c r="A1390" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:2">
+      <c r="A1391" s="5" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:2">
+      <c r="A1392" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:2">
+      <c r="A1393" s="5" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:2">
+      <c r="A1394" s="5" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:2">
+      <c r="A1395" s="5" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:2">
+      <c r="A1396" s="5" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:2">
+      <c r="A1397" s="5" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:2">
+      <c r="A1398" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:2">
+      <c r="A1399" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:2">
+      <c r="A1400" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:2">
+      <c r="A1401" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:2">
+      <c r="A1402" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:2">
+      <c r="A1403" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:2">
+      <c r="A1404" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:2">
+      <c r="A1405" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:2">
+      <c r="A1406" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:2">
+      <c r="A1407" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:2">
+      <c r="A1408" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>1539</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A1398" r:id="rId1" display="https://www.jorudan.co.jp/time/eki_%E6%9B%BD%E6%A0%B9%E7%94%B0_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{68ACE546-A750-4F60-AED4-E07901AC3288}"/>
+    <hyperlink ref="A1399" r:id="rId2" display="https://www.jorudan.co.jp/time/eki_%E7%BE%8E%E8%A1%93%E9%A4%A8%E5%9B%B3%E6%9B%B8%E9%A4%A8%E5%89%8D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{28EE59C4-EA83-4E89-B034-6FD4AAD99E24}"/>
+    <hyperlink ref="A1400" r:id="rId3" display="https://www.jorudan.co.jp/time/eki_%E5%B2%A9%E4%BB%A3%E6%B8%85%E6%B0%B4_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{E1829E4B-BE00-4B4B-9C93-EBACFAC95BF7}"/>
+    <hyperlink ref="A1401" r:id="rId4" display="https://www.jorudan.co.jp/time/eki_%E6%B3%89%EF%BC%88%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%EF%BC%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{99D58D68-BA64-4C3F-B934-A4D08A1C303D}"/>
+    <hyperlink ref="A1402" r:id="rId5" display="https://www.jorudan.co.jp/time/eki_%E4%B8%8A%E6%9D%BE%E5%B7%9D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{E886F647-D1CC-4E57-88DB-E2CF61B5B64D}"/>
+    <hyperlink ref="A1403" r:id="rId6" display="https://www.jorudan.co.jp/time/eki_%E7%AC%B9%E8%B0%B7_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{F142FFF2-AD53-477A-8681-688EC66C51D3}"/>
+    <hyperlink ref="A1404" r:id="rId7" display="https://www.jorudan.co.jp/time/eki_%E6%A1%9C%E6%B0%B4_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{ACF6A996-D26F-475F-8321-2FCF98842525}"/>
+    <hyperlink ref="A1405" r:id="rId8" display="https://www.jorudan.co.jp/time/eki_%E5%B9%B3%E9%87%8E%EF%BC%88%E7%A6%8F%E5%B3%B6%EF%BC%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{55ED7298-022F-4823-BAF4-7F4FC1E5ACD6}"/>
+    <hyperlink ref="A1406" r:id="rId9" display="https://www.jorudan.co.jp/time/eki_%E5%8C%BB%E7%8E%8B%E5%AF%BA%E5%89%8D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{3F5B7580-48A7-4529-B87F-13D558B2B700}"/>
+    <hyperlink ref="A1407" r:id="rId10" display="https://www.jorudan.co.jp/time/eki_%E8%8A%B1%E6%B0%B4%E5%9D%82_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{62680C19-8AA2-4379-A265-56EF70ABA63F}"/>
+    <hyperlink ref="A1408" r:id="rId11" display="https://www.jorudan.co.jp/time/eki_%E9%A3%AF%E5%9D%82%E6%B8%A9%E6%B3%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{B472157B-450F-4DB5-96FD-6C63E26D7034}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9B8633F-E209-4212-8629-31E0ADDD5D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BB3AD8-2F56-4035-9827-1A789E0D7667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11688" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17292" windowHeight="8880" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5937,24 +5937,12 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F2F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -5966,43 +5954,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
-    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6016,10 +5988,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12399,7 +12367,7 @@
       </c>
     </row>
     <row r="765" spans="1:2">
-      <c r="A765" s="5" t="s">
+      <c r="A765" t="s">
         <v>842</v>
       </c>
       <c r="B765" t="s">
@@ -12407,7 +12375,7 @@
       </c>
     </row>
     <row r="766" spans="1:2">
-      <c r="A766" s="5" t="s">
+      <c r="A766" t="s">
         <v>843</v>
       </c>
       <c r="B766" t="s">
@@ -12415,7 +12383,7 @@
       </c>
     </row>
     <row r="767" spans="1:2">
-      <c r="A767" s="5" t="s">
+      <c r="A767" t="s">
         <v>844</v>
       </c>
       <c r="B767" t="s">
@@ -12423,7 +12391,7 @@
       </c>
     </row>
     <row r="768" spans="1:2">
-      <c r="A768" s="5" t="s">
+      <c r="A768" t="s">
         <v>845</v>
       </c>
       <c r="B768" t="s">
@@ -12431,7 +12399,7 @@
       </c>
     </row>
     <row r="769" spans="1:2">
-      <c r="A769" s="5" t="s">
+      <c r="A769" t="s">
         <v>846</v>
       </c>
       <c r="B769" t="s">
@@ -12439,7 +12407,7 @@
       </c>
     </row>
     <row r="770" spans="1:2">
-      <c r="A770" s="5" t="s">
+      <c r="A770" t="s">
         <v>847</v>
       </c>
       <c r="B770" t="s">
@@ -12447,7 +12415,7 @@
       </c>
     </row>
     <row r="771" spans="1:2">
-      <c r="A771" s="5" t="s">
+      <c r="A771" t="s">
         <v>848</v>
       </c>
       <c r="B771" t="s">
@@ -12455,7 +12423,7 @@
       </c>
     </row>
     <row r="772" spans="1:2">
-      <c r="A772" s="5" t="s">
+      <c r="A772" t="s">
         <v>849</v>
       </c>
       <c r="B772" t="s">
@@ -12463,7 +12431,7 @@
       </c>
     </row>
     <row r="773" spans="1:2">
-      <c r="A773" s="5" t="s">
+      <c r="A773" t="s">
         <v>850</v>
       </c>
       <c r="B773" t="s">
@@ -12471,7 +12439,7 @@
       </c>
     </row>
     <row r="774" spans="1:2">
-      <c r="A774" s="5" t="s">
+      <c r="A774" t="s">
         <v>851</v>
       </c>
       <c r="B774" t="s">
@@ -12479,7 +12447,7 @@
       </c>
     </row>
     <row r="775" spans="1:2">
-      <c r="A775" s="5" t="s">
+      <c r="A775" t="s">
         <v>854</v>
       </c>
       <c r="B775" t="s">
@@ -12487,7 +12455,7 @@
       </c>
     </row>
     <row r="776" spans="1:2">
-      <c r="A776" s="5" t="s">
+      <c r="A776" t="s">
         <v>855</v>
       </c>
       <c r="B776" t="s">
@@ -12495,7 +12463,7 @@
       </c>
     </row>
     <row r="777" spans="1:2">
-      <c r="A777" s="5" t="s">
+      <c r="A777" t="s">
         <v>856</v>
       </c>
       <c r="B777" t="s">
@@ -12503,7 +12471,7 @@
       </c>
     </row>
     <row r="778" spans="1:2">
-      <c r="A778" s="5" t="s">
+      <c r="A778" t="s">
         <v>857</v>
       </c>
       <c r="B778" t="s">
@@ -12511,7 +12479,7 @@
       </c>
     </row>
     <row r="779" spans="1:2">
-      <c r="A779" s="5" t="s">
+      <c r="A779" t="s">
         <v>858</v>
       </c>
       <c r="B779" t="s">
@@ -12519,7 +12487,7 @@
       </c>
     </row>
     <row r="780" spans="1:2">
-      <c r="A780" s="5" t="s">
+      <c r="A780" t="s">
         <v>859</v>
       </c>
       <c r="B780" t="s">
@@ -12527,7 +12495,7 @@
       </c>
     </row>
     <row r="781" spans="1:2">
-      <c r="A781" s="5" t="s">
+      <c r="A781" t="s">
         <v>860</v>
       </c>
       <c r="B781" t="s">
@@ -12535,7 +12503,7 @@
       </c>
     </row>
     <row r="782" spans="1:2">
-      <c r="A782" s="5" t="s">
+      <c r="A782" t="s">
         <v>861</v>
       </c>
       <c r="B782" t="s">
@@ -12543,7 +12511,7 @@
       </c>
     </row>
     <row r="783" spans="1:2">
-      <c r="A783" s="5" t="s">
+      <c r="A783" t="s">
         <v>862</v>
       </c>
       <c r="B783" t="s">
@@ -12551,7 +12519,7 @@
       </c>
     </row>
     <row r="784" spans="1:2">
-      <c r="A784" s="5" t="s">
+      <c r="A784" t="s">
         <v>863</v>
       </c>
       <c r="B784" t="s">
@@ -12559,7 +12527,7 @@
       </c>
     </row>
     <row r="785" spans="1:2">
-      <c r="A785" s="5" t="s">
+      <c r="A785" t="s">
         <v>864</v>
       </c>
       <c r="B785" t="s">
@@ -12567,7 +12535,7 @@
       </c>
     </row>
     <row r="786" spans="1:2">
-      <c r="A786" s="5" t="s">
+      <c r="A786" t="s">
         <v>865</v>
       </c>
       <c r="B786" t="s">
@@ -12575,7 +12543,7 @@
       </c>
     </row>
     <row r="787" spans="1:2">
-      <c r="A787" s="5" t="s">
+      <c r="A787" t="s">
         <v>866</v>
       </c>
       <c r="B787" t="s">
@@ -12583,7 +12551,7 @@
       </c>
     </row>
     <row r="788" spans="1:2">
-      <c r="A788" s="5" t="s">
+      <c r="A788" t="s">
         <v>867</v>
       </c>
       <c r="B788" t="s">
@@ -12591,7 +12559,7 @@
       </c>
     </row>
     <row r="789" spans="1:2">
-      <c r="A789" s="5" t="s">
+      <c r="A789" t="s">
         <v>868</v>
       </c>
       <c r="B789" t="s">
@@ -12599,7 +12567,7 @@
       </c>
     </row>
     <row r="790" spans="1:2">
-      <c r="A790" s="5" t="s">
+      <c r="A790" t="s">
         <v>869</v>
       </c>
       <c r="B790" t="s">
@@ -12607,7 +12575,7 @@
       </c>
     </row>
     <row r="791" spans="1:2">
-      <c r="A791" s="5" t="s">
+      <c r="A791" t="s">
         <v>870</v>
       </c>
       <c r="B791" t="s">
@@ -12615,7 +12583,7 @@
       </c>
     </row>
     <row r="792" spans="1:2">
-      <c r="A792" s="5" t="s">
+      <c r="A792" t="s">
         <v>871</v>
       </c>
       <c r="B792" t="s">
@@ -12623,7 +12591,7 @@
       </c>
     </row>
     <row r="793" spans="1:2">
-      <c r="A793" s="5" t="s">
+      <c r="A793" t="s">
         <v>873</v>
       </c>
       <c r="B793" t="s">
@@ -12631,7 +12599,7 @@
       </c>
     </row>
     <row r="794" spans="1:2">
-      <c r="A794" s="5" t="s">
+      <c r="A794" t="s">
         <v>872</v>
       </c>
       <c r="B794" t="s">
@@ -12639,7 +12607,7 @@
       </c>
     </row>
     <row r="795" spans="1:2">
-      <c r="A795" s="5" t="s">
+      <c r="A795" t="s">
         <v>874</v>
       </c>
       <c r="B795" t="s">
@@ -12647,7 +12615,7 @@
       </c>
     </row>
     <row r="796" spans="1:2">
-      <c r="A796" s="5" t="s">
+      <c r="A796" t="s">
         <v>876</v>
       </c>
       <c r="B796" t="s">
@@ -12655,7 +12623,7 @@
       </c>
     </row>
     <row r="797" spans="1:2">
-      <c r="A797" s="5" t="s">
+      <c r="A797" t="s">
         <v>877</v>
       </c>
       <c r="B797" t="s">
@@ -12663,7 +12631,7 @@
       </c>
     </row>
     <row r="798" spans="1:2">
-      <c r="A798" s="5" t="s">
+      <c r="A798" t="s">
         <v>878</v>
       </c>
       <c r="B798" t="s">
@@ -12671,7 +12639,7 @@
       </c>
     </row>
     <row r="799" spans="1:2">
-      <c r="A799" s="5" t="s">
+      <c r="A799" t="s">
         <v>879</v>
       </c>
       <c r="B799" t="s">
@@ -12679,7 +12647,7 @@
       </c>
     </row>
     <row r="800" spans="1:2">
-      <c r="A800" s="5" t="s">
+      <c r="A800" t="s">
         <v>880</v>
       </c>
       <c r="B800" t="s">
@@ -12687,7 +12655,7 @@
       </c>
     </row>
     <row r="801" spans="1:2">
-      <c r="A801" s="5" t="s">
+      <c r="A801" t="s">
         <v>881</v>
       </c>
       <c r="B801" t="s">
@@ -12695,7 +12663,7 @@
       </c>
     </row>
     <row r="802" spans="1:2">
-      <c r="A802" s="5" t="s">
+      <c r="A802" t="s">
         <v>882</v>
       </c>
       <c r="B802" t="s">
@@ -12703,7 +12671,7 @@
       </c>
     </row>
     <row r="803" spans="1:2">
-      <c r="A803" s="5" t="s">
+      <c r="A803" t="s">
         <v>883</v>
       </c>
       <c r="B803" t="s">
@@ -12711,7 +12679,7 @@
       </c>
     </row>
     <row r="804" spans="1:2">
-      <c r="A804" s="5" t="s">
+      <c r="A804" t="s">
         <v>884</v>
       </c>
       <c r="B804" t="s">
@@ -12719,7 +12687,7 @@
       </c>
     </row>
     <row r="805" spans="1:2">
-      <c r="A805" s="5" t="s">
+      <c r="A805" t="s">
         <v>885</v>
       </c>
       <c r="B805" t="s">
@@ -12727,7 +12695,7 @@
       </c>
     </row>
     <row r="806" spans="1:2">
-      <c r="A806" s="5" t="s">
+      <c r="A806" t="s">
         <v>886</v>
       </c>
       <c r="B806" t="s">
@@ -12735,7 +12703,7 @@
       </c>
     </row>
     <row r="807" spans="1:2">
-      <c r="A807" s="5" t="s">
+      <c r="A807" t="s">
         <v>887</v>
       </c>
       <c r="B807" t="s">
@@ -12743,7 +12711,7 @@
       </c>
     </row>
     <row r="808" spans="1:2">
-      <c r="A808" s="5" t="s">
+      <c r="A808" t="s">
         <v>888</v>
       </c>
       <c r="B808" t="s">
@@ -12751,7 +12719,7 @@
       </c>
     </row>
     <row r="809" spans="1:2">
-      <c r="A809" s="5" t="s">
+      <c r="A809" t="s">
         <v>889</v>
       </c>
       <c r="B809" t="s">
@@ -12759,7 +12727,7 @@
       </c>
     </row>
     <row r="810" spans="1:2">
-      <c r="A810" s="5" t="s">
+      <c r="A810" t="s">
         <v>896</v>
       </c>
       <c r="B810" t="s">
@@ -12767,7 +12735,7 @@
       </c>
     </row>
     <row r="811" spans="1:2">
-      <c r="A811" s="5" t="s">
+      <c r="A811" t="s">
         <v>897</v>
       </c>
       <c r="B811" t="s">
@@ -12775,7 +12743,7 @@
       </c>
     </row>
     <row r="812" spans="1:2">
-      <c r="A812" s="5" t="s">
+      <c r="A812" t="s">
         <v>898</v>
       </c>
       <c r="B812" t="s">
@@ -12783,7 +12751,7 @@
       </c>
     </row>
     <row r="813" spans="1:2">
-      <c r="A813" s="5" t="s">
+      <c r="A813" t="s">
         <v>1039</v>
       </c>
       <c r="B813" t="s">
@@ -12791,7 +12759,7 @@
       </c>
     </row>
     <row r="814" spans="1:2">
-      <c r="A814" s="5" t="s">
+      <c r="A814" t="s">
         <v>899</v>
       </c>
       <c r="B814" t="s">
@@ -12799,7 +12767,7 @@
       </c>
     </row>
     <row r="815" spans="1:2">
-      <c r="A815" s="5" t="s">
+      <c r="A815" t="s">
         <v>900</v>
       </c>
       <c r="B815" t="s">
@@ -12807,7 +12775,7 @@
       </c>
     </row>
     <row r="816" spans="1:2">
-      <c r="A816" s="5" t="s">
+      <c r="A816" t="s">
         <v>901</v>
       </c>
       <c r="B816" t="s">
@@ -12815,7 +12783,7 @@
       </c>
     </row>
     <row r="817" spans="1:2">
-      <c r="A817" s="5" t="s">
+      <c r="A817" t="s">
         <v>902</v>
       </c>
       <c r="B817" t="s">
@@ -12823,7 +12791,7 @@
       </c>
     </row>
     <row r="818" spans="1:2">
-      <c r="A818" s="5" t="s">
+      <c r="A818" t="s">
         <v>903</v>
       </c>
       <c r="B818" t="s">
@@ -12831,7 +12799,7 @@
       </c>
     </row>
     <row r="819" spans="1:2">
-      <c r="A819" s="5" t="s">
+      <c r="A819" t="s">
         <v>904</v>
       </c>
       <c r="B819" t="s">
@@ -12839,7 +12807,7 @@
       </c>
     </row>
     <row r="820" spans="1:2">
-      <c r="A820" s="5" t="s">
+      <c r="A820" t="s">
         <v>907</v>
       </c>
       <c r="B820" t="s">
@@ -12847,7 +12815,7 @@
       </c>
     </row>
     <row r="821" spans="1:2">
-      <c r="A821" s="5" t="s">
+      <c r="A821" t="s">
         <v>908</v>
       </c>
       <c r="B821" t="s">
@@ -12855,7 +12823,7 @@
       </c>
     </row>
     <row r="822" spans="1:2">
-      <c r="A822" s="5" t="s">
+      <c r="A822" t="s">
         <v>909</v>
       </c>
       <c r="B822" t="s">
@@ -12863,7 +12831,7 @@
       </c>
     </row>
     <row r="823" spans="1:2">
-      <c r="A823" s="5" t="s">
+      <c r="A823" t="s">
         <v>910</v>
       </c>
       <c r="B823" t="s">
@@ -12871,7 +12839,7 @@
       </c>
     </row>
     <row r="824" spans="1:2">
-      <c r="A824" s="5" t="s">
+      <c r="A824" t="s">
         <v>911</v>
       </c>
       <c r="B824" t="s">
@@ -12879,7 +12847,7 @@
       </c>
     </row>
     <row r="825" spans="1:2">
-      <c r="A825" s="5" t="s">
+      <c r="A825" t="s">
         <v>912</v>
       </c>
       <c r="B825" t="s">
@@ -12887,7 +12855,7 @@
       </c>
     </row>
     <row r="826" spans="1:2">
-      <c r="A826" s="5" t="s">
+      <c r="A826" t="s">
         <v>913</v>
       </c>
       <c r="B826" t="s">
@@ -12895,7 +12863,7 @@
       </c>
     </row>
     <row r="827" spans="1:2">
-      <c r="A827" s="5" t="s">
+      <c r="A827" t="s">
         <v>914</v>
       </c>
       <c r="B827" t="s">
@@ -12903,7 +12871,7 @@
       </c>
     </row>
     <row r="828" spans="1:2">
-      <c r="A828" s="5" t="s">
+      <c r="A828" t="s">
         <v>915</v>
       </c>
       <c r="B828" t="s">
@@ -12911,7 +12879,7 @@
       </c>
     </row>
     <row r="829" spans="1:2">
-      <c r="A829" s="5" t="s">
+      <c r="A829" t="s">
         <v>916</v>
       </c>
       <c r="B829" t="s">
@@ -12919,7 +12887,7 @@
       </c>
     </row>
     <row r="830" spans="1:2">
-      <c r="A830" s="5" t="s">
+      <c r="A830" t="s">
         <v>917</v>
       </c>
       <c r="B830" t="s">
@@ -12927,7 +12895,7 @@
       </c>
     </row>
     <row r="831" spans="1:2">
-      <c r="A831" s="5" t="s">
+      <c r="A831" t="s">
         <v>918</v>
       </c>
       <c r="B831" t="s">
@@ -12935,7 +12903,7 @@
       </c>
     </row>
     <row r="832" spans="1:2">
-      <c r="A832" s="5" t="s">
+      <c r="A832" t="s">
         <v>922</v>
       </c>
       <c r="B832" t="s">
@@ -12943,7 +12911,7 @@
       </c>
     </row>
     <row r="833" spans="1:2">
-      <c r="A833" s="5" t="s">
+      <c r="A833" t="s">
         <v>923</v>
       </c>
       <c r="B833" t="s">
@@ -12951,7 +12919,7 @@
       </c>
     </row>
     <row r="834" spans="1:2">
-      <c r="A834" s="5" t="s">
+      <c r="A834" t="s">
         <v>924</v>
       </c>
       <c r="B834" t="s">
@@ -12959,7 +12927,7 @@
       </c>
     </row>
     <row r="835" spans="1:2">
-      <c r="A835" s="5" t="s">
+      <c r="A835" t="s">
         <v>925</v>
       </c>
       <c r="B835" t="s">
@@ -12967,7 +12935,7 @@
       </c>
     </row>
     <row r="836" spans="1:2">
-      <c r="A836" s="5" t="s">
+      <c r="A836" t="s">
         <v>926</v>
       </c>
       <c r="B836" t="s">
@@ -12975,7 +12943,7 @@
       </c>
     </row>
     <row r="837" spans="1:2">
-      <c r="A837" s="5" t="s">
+      <c r="A837" t="s">
         <v>927</v>
       </c>
       <c r="B837" t="s">
@@ -12983,7 +12951,7 @@
       </c>
     </row>
     <row r="838" spans="1:2">
-      <c r="A838" s="5" t="s">
+      <c r="A838" t="s">
         <v>928</v>
       </c>
       <c r="B838" t="s">
@@ -12991,7 +12959,7 @@
       </c>
     </row>
     <row r="839" spans="1:2">
-      <c r="A839" s="5" t="s">
+      <c r="A839" t="s">
         <v>929</v>
       </c>
       <c r="B839" t="s">
@@ -12999,7 +12967,7 @@
       </c>
     </row>
     <row r="840" spans="1:2">
-      <c r="A840" s="5" t="s">
+      <c r="A840" t="s">
         <v>930</v>
       </c>
       <c r="B840" t="s">
@@ -13007,7 +12975,7 @@
       </c>
     </row>
     <row r="841" spans="1:2">
-      <c r="A841" s="5" t="s">
+      <c r="A841" t="s">
         <v>931</v>
       </c>
       <c r="B841" t="s">
@@ -13015,7 +12983,7 @@
       </c>
     </row>
     <row r="842" spans="1:2">
-      <c r="A842" s="5" t="s">
+      <c r="A842" t="s">
         <v>932</v>
       </c>
       <c r="B842" t="s">
@@ -13023,7 +12991,7 @@
       </c>
     </row>
     <row r="843" spans="1:2">
-      <c r="A843" s="5" t="s">
+      <c r="A843" t="s">
         <v>933</v>
       </c>
       <c r="B843" t="s">
@@ -13031,7 +12999,7 @@
       </c>
     </row>
     <row r="844" spans="1:2">
-      <c r="A844" s="5" t="s">
+      <c r="A844" t="s">
         <v>934</v>
       </c>
       <c r="B844" t="s">
@@ -13039,7 +13007,7 @@
       </c>
     </row>
     <row r="845" spans="1:2">
-      <c r="A845" s="5" t="s">
+      <c r="A845" t="s">
         <v>935</v>
       </c>
       <c r="B845" t="s">
@@ -13047,7 +13015,7 @@
       </c>
     </row>
     <row r="846" spans="1:2">
-      <c r="A846" s="5" t="s">
+      <c r="A846" t="s">
         <v>936</v>
       </c>
       <c r="B846" t="s">
@@ -13055,7 +13023,7 @@
       </c>
     </row>
     <row r="847" spans="1:2">
-      <c r="A847" s="5" t="s">
+      <c r="A847" t="s">
         <v>937</v>
       </c>
       <c r="B847" t="s">
@@ -13063,7 +13031,7 @@
       </c>
     </row>
     <row r="848" spans="1:2">
-      <c r="A848" s="5" t="s">
+      <c r="A848" t="s">
         <v>938</v>
       </c>
       <c r="B848" t="s">
@@ -13071,7 +13039,7 @@
       </c>
     </row>
     <row r="849" spans="1:2">
-      <c r="A849" s="5" t="s">
+      <c r="A849" t="s">
         <v>939</v>
       </c>
       <c r="B849" t="s">
@@ -13079,7 +13047,7 @@
       </c>
     </row>
     <row r="850" spans="1:2">
-      <c r="A850" s="5" t="s">
+      <c r="A850" t="s">
         <v>940</v>
       </c>
       <c r="B850" t="s">
@@ -13087,7 +13055,7 @@
       </c>
     </row>
     <row r="851" spans="1:2">
-      <c r="A851" s="5" t="s">
+      <c r="A851" t="s">
         <v>941</v>
       </c>
       <c r="B851" t="s">
@@ -13095,7 +13063,7 @@
       </c>
     </row>
     <row r="852" spans="1:2">
-      <c r="A852" s="5" t="s">
+      <c r="A852" t="s">
         <v>942</v>
       </c>
       <c r="B852" t="s">
@@ -13103,7 +13071,7 @@
       </c>
     </row>
     <row r="853" spans="1:2">
-      <c r="A853" s="5" t="s">
+      <c r="A853" t="s">
         <v>943</v>
       </c>
       <c r="B853" t="s">
@@ -13111,7 +13079,7 @@
       </c>
     </row>
     <row r="854" spans="1:2">
-      <c r="A854" s="5" t="s">
+      <c r="A854" t="s">
         <v>944</v>
       </c>
       <c r="B854" t="s">
@@ -13119,7 +13087,7 @@
       </c>
     </row>
     <row r="855" spans="1:2">
-      <c r="A855" s="5" t="s">
+      <c r="A855" t="s">
         <v>945</v>
       </c>
       <c r="B855" t="s">
@@ -13127,7 +13095,7 @@
       </c>
     </row>
     <row r="856" spans="1:2">
-      <c r="A856" s="5" t="s">
+      <c r="A856" t="s">
         <v>946</v>
       </c>
       <c r="B856" t="s">
@@ -13135,7 +13103,7 @@
       </c>
     </row>
     <row r="857" spans="1:2">
-      <c r="A857" s="5" t="s">
+      <c r="A857" t="s">
         <v>947</v>
       </c>
       <c r="B857" t="s">
@@ -13143,7 +13111,7 @@
       </c>
     </row>
     <row r="858" spans="1:2">
-      <c r="A858" s="5" t="s">
+      <c r="A858" t="s">
         <v>948</v>
       </c>
       <c r="B858" t="s">
@@ -13151,7 +13119,7 @@
       </c>
     </row>
     <row r="859" spans="1:2">
-      <c r="A859" s="5" t="s">
+      <c r="A859" t="s">
         <v>949</v>
       </c>
       <c r="B859" t="s">
@@ -13159,7 +13127,7 @@
       </c>
     </row>
     <row r="860" spans="1:2">
-      <c r="A860" s="5" t="s">
+      <c r="A860" t="s">
         <v>950</v>
       </c>
       <c r="B860" t="s">
@@ -13167,7 +13135,7 @@
       </c>
     </row>
     <row r="861" spans="1:2">
-      <c r="A861" s="5" t="s">
+      <c r="A861" t="s">
         <v>951</v>
       </c>
       <c r="B861" t="s">
@@ -13175,7 +13143,7 @@
       </c>
     </row>
     <row r="862" spans="1:2">
-      <c r="A862" s="5" t="s">
+      <c r="A862" t="s">
         <v>953</v>
       </c>
       <c r="B862" t="s">
@@ -13183,7 +13151,7 @@
       </c>
     </row>
     <row r="863" spans="1:2">
-      <c r="A863" s="5" t="s">
+      <c r="A863" t="s">
         <v>954</v>
       </c>
       <c r="B863" t="s">
@@ -13191,7 +13159,7 @@
       </c>
     </row>
     <row r="864" spans="1:2">
-      <c r="A864" s="5" t="s">
+      <c r="A864" t="s">
         <v>955</v>
       </c>
       <c r="B864" t="s">
@@ -13199,7 +13167,7 @@
       </c>
     </row>
     <row r="865" spans="1:2">
-      <c r="A865" s="5" t="s">
+      <c r="A865" t="s">
         <v>956</v>
       </c>
       <c r="B865" t="s">
@@ -13207,7 +13175,7 @@
       </c>
     </row>
     <row r="866" spans="1:2">
-      <c r="A866" s="5" t="s">
+      <c r="A866" t="s">
         <v>957</v>
       </c>
       <c r="B866" t="s">
@@ -13247,7 +13215,7 @@
       </c>
     </row>
     <row r="871" spans="1:2">
-      <c r="A871" s="5" t="s">
+      <c r="A871" t="s">
         <v>966</v>
       </c>
       <c r="B871" t="s">
@@ -13255,7 +13223,7 @@
       </c>
     </row>
     <row r="872" spans="1:2">
-      <c r="A872" s="5" t="s">
+      <c r="A872" t="s">
         <v>967</v>
       </c>
       <c r="B872" t="s">
@@ -13263,7 +13231,7 @@
       </c>
     </row>
     <row r="873" spans="1:2">
-      <c r="A873" s="5" t="s">
+      <c r="A873" t="s">
         <v>968</v>
       </c>
       <c r="B873" t="s">
@@ -13271,7 +13239,7 @@
       </c>
     </row>
     <row r="874" spans="1:2">
-      <c r="A874" s="5" t="s">
+      <c r="A874" t="s">
         <v>969</v>
       </c>
       <c r="B874" t="s">
@@ -13279,7 +13247,7 @@
       </c>
     </row>
     <row r="875" spans="1:2">
-      <c r="A875" s="5" t="s">
+      <c r="A875" t="s">
         <v>970</v>
       </c>
       <c r="B875" t="s">
@@ -13287,7 +13255,7 @@
       </c>
     </row>
     <row r="876" spans="1:2">
-      <c r="A876" s="5" t="s">
+      <c r="A876" t="s">
         <v>971</v>
       </c>
       <c r="B876" t="s">
@@ -13295,7 +13263,7 @@
       </c>
     </row>
     <row r="877" spans="1:2">
-      <c r="A877" s="5" t="s">
+      <c r="A877" t="s">
         <v>972</v>
       </c>
       <c r="B877" t="s">
@@ -13303,7 +13271,7 @@
       </c>
     </row>
     <row r="878" spans="1:2">
-      <c r="A878" s="5" t="s">
+      <c r="A878" t="s">
         <v>973</v>
       </c>
       <c r="B878" t="s">
@@ -13311,7 +13279,7 @@
       </c>
     </row>
     <row r="879" spans="1:2">
-      <c r="A879" s="5" t="s">
+      <c r="A879" t="s">
         <v>974</v>
       </c>
       <c r="B879" t="s">
@@ -13319,7 +13287,7 @@
       </c>
     </row>
     <row r="880" spans="1:2">
-      <c r="A880" s="5" t="s">
+      <c r="A880" t="s">
         <v>975</v>
       </c>
       <c r="B880" t="s">
@@ -13327,7 +13295,7 @@
       </c>
     </row>
     <row r="881" spans="1:2">
-      <c r="A881" s="5" t="s">
+      <c r="A881" t="s">
         <v>976</v>
       </c>
       <c r="B881" t="s">
@@ -13335,7 +13303,7 @@
       </c>
     </row>
     <row r="882" spans="1:2">
-      <c r="A882" s="5" t="s">
+      <c r="A882" t="s">
         <v>977</v>
       </c>
       <c r="B882" t="s">
@@ -13343,7 +13311,7 @@
       </c>
     </row>
     <row r="883" spans="1:2">
-      <c r="A883" s="5" t="s">
+      <c r="A883" t="s">
         <v>978</v>
       </c>
       <c r="B883" t="s">
@@ -13351,7 +13319,7 @@
       </c>
     </row>
     <row r="884" spans="1:2">
-      <c r="A884" s="5" t="s">
+      <c r="A884" t="s">
         <v>979</v>
       </c>
       <c r="B884" t="s">
@@ -13359,7 +13327,7 @@
       </c>
     </row>
     <row r="885" spans="1:2">
-      <c r="A885" s="5" t="s">
+      <c r="A885" t="s">
         <v>980</v>
       </c>
       <c r="B885" t="s">
@@ -13367,7 +13335,7 @@
       </c>
     </row>
     <row r="886" spans="1:2">
-      <c r="A886" s="5" t="s">
+      <c r="A886" t="s">
         <v>981</v>
       </c>
       <c r="B886" t="s">
@@ -13375,7 +13343,7 @@
       </c>
     </row>
     <row r="887" spans="1:2">
-      <c r="A887" s="5" t="s">
+      <c r="A887" t="s">
         <v>982</v>
       </c>
       <c r="B887" t="s">
@@ -13383,7 +13351,7 @@
       </c>
     </row>
     <row r="888" spans="1:2">
-      <c r="A888" s="5" t="s">
+      <c r="A888" t="s">
         <v>983</v>
       </c>
       <c r="B888" t="s">
@@ -13391,7 +13359,7 @@
       </c>
     </row>
     <row r="889" spans="1:2">
-      <c r="A889" s="5" t="s">
+      <c r="A889" t="s">
         <v>984</v>
       </c>
       <c r="B889" t="s">
@@ -13399,7 +13367,7 @@
       </c>
     </row>
     <row r="890" spans="1:2">
-      <c r="A890" s="5" t="s">
+      <c r="A890" t="s">
         <v>985</v>
       </c>
       <c r="B890" t="s">
@@ -13407,7 +13375,7 @@
       </c>
     </row>
     <row r="891" spans="1:2">
-      <c r="A891" s="5" t="s">
+      <c r="A891" t="s">
         <v>986</v>
       </c>
       <c r="B891" t="s">
@@ -13415,7 +13383,7 @@
       </c>
     </row>
     <row r="892" spans="1:2">
-      <c r="A892" s="5" t="s">
+      <c r="A892" t="s">
         <v>987</v>
       </c>
       <c r="B892" t="s">
@@ -13423,7 +13391,7 @@
       </c>
     </row>
     <row r="893" spans="1:2">
-      <c r="A893" s="5" t="s">
+      <c r="A893" t="s">
         <v>989</v>
       </c>
       <c r="B893" t="s">
@@ -13431,7 +13399,7 @@
       </c>
     </row>
     <row r="894" spans="1:2">
-      <c r="A894" s="5" t="s">
+      <c r="A894" t="s">
         <v>990</v>
       </c>
       <c r="B894" t="s">
@@ -13439,7 +13407,7 @@
       </c>
     </row>
     <row r="895" spans="1:2">
-      <c r="A895" s="5" t="s">
+      <c r="A895" t="s">
         <v>995</v>
       </c>
       <c r="B895" t="s">
@@ -13447,7 +13415,7 @@
       </c>
     </row>
     <row r="896" spans="1:2">
-      <c r="A896" s="5" t="s">
+      <c r="A896" t="s">
         <v>996</v>
       </c>
       <c r="B896" t="s">
@@ -13455,7 +13423,7 @@
       </c>
     </row>
     <row r="897" spans="1:2">
-      <c r="A897" s="6" t="s">
+      <c r="A897" t="s">
         <v>997</v>
       </c>
       <c r="B897" t="s">
@@ -13463,7 +13431,7 @@
       </c>
     </row>
     <row r="898" spans="1:2">
-      <c r="A898" s="5" t="s">
+      <c r="A898" t="s">
         <v>998</v>
       </c>
       <c r="B898" t="s">
@@ -13471,7 +13439,7 @@
       </c>
     </row>
     <row r="899" spans="1:2">
-      <c r="A899" s="5" t="s">
+      <c r="A899" t="s">
         <v>999</v>
       </c>
       <c r="B899" t="s">
@@ -13479,7 +13447,7 @@
       </c>
     </row>
     <row r="900" spans="1:2">
-      <c r="A900" s="5" t="s">
+      <c r="A900" t="s">
         <v>1000</v>
       </c>
       <c r="B900" t="s">
@@ -13487,7 +13455,7 @@
       </c>
     </row>
     <row r="901" spans="1:2">
-      <c r="A901" s="5" t="s">
+      <c r="A901" t="s">
         <v>1001</v>
       </c>
       <c r="B901" t="s">
@@ -13495,7 +13463,7 @@
       </c>
     </row>
     <row r="902" spans="1:2">
-      <c r="A902" s="5" t="s">
+      <c r="A902" t="s">
         <v>1002</v>
       </c>
       <c r="B902" t="s">
@@ -13503,7 +13471,7 @@
       </c>
     </row>
     <row r="903" spans="1:2">
-      <c r="A903" s="5" t="s">
+      <c r="A903" t="s">
         <v>1003</v>
       </c>
       <c r="B903" t="s">
@@ -13511,7 +13479,7 @@
       </c>
     </row>
     <row r="904" spans="1:2">
-      <c r="A904" s="5" t="s">
+      <c r="A904" t="s">
         <v>1004</v>
       </c>
       <c r="B904" t="s">
@@ -13519,7 +13487,7 @@
       </c>
     </row>
     <row r="905" spans="1:2">
-      <c r="A905" s="5" t="s">
+      <c r="A905" t="s">
         <v>1005</v>
       </c>
       <c r="B905" t="s">
@@ -13527,7 +13495,7 @@
       </c>
     </row>
     <row r="906" spans="1:2">
-      <c r="A906" s="5" t="s">
+      <c r="A906" t="s">
         <v>1006</v>
       </c>
       <c r="B906" t="s">
@@ -13535,7 +13503,7 @@
       </c>
     </row>
     <row r="907" spans="1:2">
-      <c r="A907" s="5" t="s">
+      <c r="A907" t="s">
         <v>1007</v>
       </c>
       <c r="B907" t="s">
@@ -13543,7 +13511,7 @@
       </c>
     </row>
     <row r="908" spans="1:2">
-      <c r="A908" s="5" t="s">
+      <c r="A908" t="s">
         <v>1008</v>
       </c>
       <c r="B908" t="s">
@@ -13551,7 +13519,7 @@
       </c>
     </row>
     <row r="909" spans="1:2">
-      <c r="A909" s="5" t="s">
+      <c r="A909" t="s">
         <v>1010</v>
       </c>
       <c r="B909" t="s">
@@ -13559,7 +13527,7 @@
       </c>
     </row>
     <row r="910" spans="1:2">
-      <c r="A910" s="5" t="s">
+      <c r="A910" t="s">
         <v>1011</v>
       </c>
       <c r="B910" t="s">
@@ -13567,7 +13535,7 @@
       </c>
     </row>
     <row r="911" spans="1:2">
-      <c r="A911" s="5" t="s">
+      <c r="A911" t="s">
         <v>1012</v>
       </c>
       <c r="B911" t="s">
@@ -13575,7 +13543,7 @@
       </c>
     </row>
     <row r="912" spans="1:2">
-      <c r="A912" s="5" t="s">
+      <c r="A912" t="s">
         <v>1013</v>
       </c>
       <c r="B912" t="s">
@@ -13583,7 +13551,7 @@
       </c>
     </row>
     <row r="913" spans="1:2">
-      <c r="A913" s="5" t="s">
+      <c r="A913" t="s">
         <v>1014</v>
       </c>
       <c r="B913" t="s">
@@ -13591,7 +13559,7 @@
       </c>
     </row>
     <row r="914" spans="1:2">
-      <c r="A914" s="5" t="s">
+      <c r="A914" t="s">
         <v>1015</v>
       </c>
       <c r="B914" t="s">
@@ -13599,7 +13567,7 @@
       </c>
     </row>
     <row r="915" spans="1:2">
-      <c r="A915" s="5" t="s">
+      <c r="A915" t="s">
         <v>1016</v>
       </c>
       <c r="B915" t="s">
@@ -13607,7 +13575,7 @@
       </c>
     </row>
     <row r="916" spans="1:2">
-      <c r="A916" s="5" t="s">
+      <c r="A916" t="s">
         <v>1017</v>
       </c>
       <c r="B916" t="s">
@@ -13615,7 +13583,7 @@
       </c>
     </row>
     <row r="917" spans="1:2">
-      <c r="A917" s="5" t="s">
+      <c r="A917" t="s">
         <v>1020</v>
       </c>
       <c r="B917" t="s">
@@ -13623,7 +13591,7 @@
       </c>
     </row>
     <row r="918" spans="1:2">
-      <c r="A918" s="5" t="s">
+      <c r="A918" t="s">
         <v>1021</v>
       </c>
       <c r="B918" t="s">
@@ -13631,7 +13599,7 @@
       </c>
     </row>
     <row r="919" spans="1:2">
-      <c r="A919" s="5" t="s">
+      <c r="A919" t="s">
         <v>1022</v>
       </c>
       <c r="B919" t="s">
@@ -13639,7 +13607,7 @@
       </c>
     </row>
     <row r="920" spans="1:2">
-      <c r="A920" s="5" t="s">
+      <c r="A920" t="s">
         <v>1023</v>
       </c>
       <c r="B920" t="s">
@@ -13647,7 +13615,7 @@
       </c>
     </row>
     <row r="921" spans="1:2">
-      <c r="A921" s="5" t="s">
+      <c r="A921" t="s">
         <v>1024</v>
       </c>
       <c r="B921" t="s">
@@ -13655,7 +13623,7 @@
       </c>
     </row>
     <row r="922" spans="1:2">
-      <c r="A922" s="5" t="s">
+      <c r="A922" t="s">
         <v>1025</v>
       </c>
       <c r="B922" t="s">
@@ -13663,7 +13631,7 @@
       </c>
     </row>
     <row r="923" spans="1:2">
-      <c r="A923" s="5" t="s">
+      <c r="A923" t="s">
         <v>1026</v>
       </c>
       <c r="B923" t="s">
@@ -13671,7 +13639,7 @@
       </c>
     </row>
     <row r="924" spans="1:2">
-      <c r="A924" s="5" t="s">
+      <c r="A924" t="s">
         <v>1027</v>
       </c>
       <c r="B924" t="s">
@@ -13679,7 +13647,7 @@
       </c>
     </row>
     <row r="925" spans="1:2">
-      <c r="A925" s="5" t="s">
+      <c r="A925" t="s">
         <v>1028</v>
       </c>
       <c r="B925" t="s">
@@ -13687,7 +13655,7 @@
       </c>
     </row>
     <row r="926" spans="1:2">
-      <c r="A926" s="5" t="s">
+      <c r="A926" t="s">
         <v>1029</v>
       </c>
       <c r="B926" t="s">
@@ -13695,7 +13663,7 @@
       </c>
     </row>
     <row r="927" spans="1:2">
-      <c r="A927" s="5" t="s">
+      <c r="A927" t="s">
         <v>1030</v>
       </c>
       <c r="B927" t="s">
@@ -13703,7 +13671,7 @@
       </c>
     </row>
     <row r="928" spans="1:2">
-      <c r="A928" s="5" t="s">
+      <c r="A928" t="s">
         <v>1031</v>
       </c>
       <c r="B928" t="s">
@@ -13711,7 +13679,7 @@
       </c>
     </row>
     <row r="929" spans="1:2">
-      <c r="A929" s="5" t="s">
+      <c r="A929" t="s">
         <v>1032</v>
       </c>
       <c r="B929" t="s">
@@ -13719,7 +13687,7 @@
       </c>
     </row>
     <row r="930" spans="1:2">
-      <c r="A930" s="5" t="s">
+      <c r="A930" t="s">
         <v>1033</v>
       </c>
       <c r="B930" t="s">
@@ -13727,7 +13695,7 @@
       </c>
     </row>
     <row r="931" spans="1:2">
-      <c r="A931" s="5" t="s">
+      <c r="A931" t="s">
         <v>1036</v>
       </c>
       <c r="B931" t="s">
@@ -13735,7 +13703,7 @@
       </c>
     </row>
     <row r="932" spans="1:2">
-      <c r="A932" s="5" t="s">
+      <c r="A932" t="s">
         <v>1037</v>
       </c>
       <c r="B932" t="s">
@@ -13743,7 +13711,7 @@
       </c>
     </row>
     <row r="933" spans="1:2">
-      <c r="A933" s="5" t="s">
+      <c r="A933" t="s">
         <v>1038</v>
       </c>
       <c r="B933" t="s">
@@ -13751,7 +13719,7 @@
       </c>
     </row>
     <row r="934" spans="1:2">
-      <c r="A934" s="5" t="s">
+      <c r="A934" t="s">
         <v>1040</v>
       </c>
       <c r="B934" t="s">
@@ -13759,7 +13727,7 @@
       </c>
     </row>
     <row r="935" spans="1:2">
-      <c r="A935" s="5" t="s">
+      <c r="A935" t="s">
         <v>1041</v>
       </c>
       <c r="B935" t="s">
@@ -13767,7 +13735,7 @@
       </c>
     </row>
     <row r="936" spans="1:2">
-      <c r="A936" s="5" t="s">
+      <c r="A936" t="s">
         <v>1042</v>
       </c>
       <c r="B936" t="s">
@@ -13775,7 +13743,7 @@
       </c>
     </row>
     <row r="937" spans="1:2">
-      <c r="A937" s="5" t="s">
+      <c r="A937" t="s">
         <v>1043</v>
       </c>
       <c r="B937" t="s">
@@ -13783,7 +13751,7 @@
       </c>
     </row>
     <row r="938" spans="1:2">
-      <c r="A938" s="5" t="s">
+      <c r="A938" t="s">
         <v>1044</v>
       </c>
       <c r="B938" t="s">
@@ -13791,7 +13759,7 @@
       </c>
     </row>
     <row r="939" spans="1:2">
-      <c r="A939" s="5" t="s">
+      <c r="A939" t="s">
         <v>1045</v>
       </c>
       <c r="B939" t="s">
@@ -13799,7 +13767,7 @@
       </c>
     </row>
     <row r="940" spans="1:2">
-      <c r="A940" s="5" t="s">
+      <c r="A940" t="s">
         <v>1046</v>
       </c>
       <c r="B940" t="s">
@@ -13807,7 +13775,7 @@
       </c>
     </row>
     <row r="941" spans="1:2">
-      <c r="A941" s="5" t="s">
+      <c r="A941" t="s">
         <v>1047</v>
       </c>
       <c r="B941" t="s">
@@ -13815,7 +13783,7 @@
       </c>
     </row>
     <row r="942" spans="1:2">
-      <c r="A942" s="5" t="s">
+      <c r="A942" t="s">
         <v>1048</v>
       </c>
       <c r="B942" t="s">
@@ -13823,7 +13791,7 @@
       </c>
     </row>
     <row r="943" spans="1:2">
-      <c r="A943" s="5" t="s">
+      <c r="A943" t="s">
         <v>1049</v>
       </c>
       <c r="B943" t="s">
@@ -13831,7 +13799,7 @@
       </c>
     </row>
     <row r="944" spans="1:2">
-      <c r="A944" s="5" t="s">
+      <c r="A944" t="s">
         <v>1050</v>
       </c>
       <c r="B944" t="s">
@@ -13839,7 +13807,7 @@
       </c>
     </row>
     <row r="945" spans="1:2">
-      <c r="A945" s="5" t="s">
+      <c r="A945" t="s">
         <v>1051</v>
       </c>
       <c r="B945" t="s">
@@ -13847,12 +13815,12 @@
       </c>
     </row>
     <row r="948" spans="1:2">
-      <c r="A948" s="5" t="s">
+      <c r="A948" t="s">
         <v>1054</v>
       </c>
     </row>
     <row r="949" spans="1:2">
-      <c r="A949" s="5" t="s">
+      <c r="A949" t="s">
         <v>1053</v>
       </c>
       <c r="B949" t="s">
@@ -13860,7 +13828,7 @@
       </c>
     </row>
     <row r="950" spans="1:2">
-      <c r="A950" s="5" t="s">
+      <c r="A950" t="s">
         <v>1055</v>
       </c>
       <c r="B950" t="s">
@@ -13868,7 +13836,7 @@
       </c>
     </row>
     <row r="951" spans="1:2">
-      <c r="A951" s="5" t="s">
+      <c r="A951" t="s">
         <v>1056</v>
       </c>
       <c r="B951" t="s">
@@ -13876,7 +13844,7 @@
       </c>
     </row>
     <row r="952" spans="1:2">
-      <c r="A952" s="5" t="s">
+      <c r="A952" t="s">
         <v>1057</v>
       </c>
       <c r="B952" t="s">
@@ -13884,7 +13852,7 @@
       </c>
     </row>
     <row r="953" spans="1:2">
-      <c r="A953" s="5" t="s">
+      <c r="A953" t="s">
         <v>1058</v>
       </c>
       <c r="B953" t="s">
@@ -13892,7 +13860,7 @@
       </c>
     </row>
     <row r="954" spans="1:2">
-      <c r="A954" s="5" t="s">
+      <c r="A954" t="s">
         <v>1059</v>
       </c>
       <c r="B954" t="s">
@@ -13900,7 +13868,7 @@
       </c>
     </row>
     <row r="955" spans="1:2">
-      <c r="A955" s="5" t="s">
+      <c r="A955" t="s">
         <v>1060</v>
       </c>
       <c r="B955" t="s">
@@ -13908,7 +13876,7 @@
       </c>
     </row>
     <row r="956" spans="1:2">
-      <c r="A956" s="5" t="s">
+      <c r="A956" t="s">
         <v>1061</v>
       </c>
       <c r="B956" t="s">
@@ -13916,7 +13884,7 @@
       </c>
     </row>
     <row r="957" spans="1:2">
-      <c r="A957" s="5" t="s">
+      <c r="A957" t="s">
         <v>1062</v>
       </c>
       <c r="B957" t="s">
@@ -13924,7 +13892,7 @@
       </c>
     </row>
     <row r="958" spans="1:2">
-      <c r="A958" s="5" t="s">
+      <c r="A958" t="s">
         <v>1063</v>
       </c>
       <c r="B958" t="s">
@@ -13932,7 +13900,7 @@
       </c>
     </row>
     <row r="959" spans="1:2">
-      <c r="A959" s="5" t="s">
+      <c r="A959" t="s">
         <v>1064</v>
       </c>
       <c r="B959" t="s">
@@ -13940,7 +13908,7 @@
       </c>
     </row>
     <row r="960" spans="1:2">
-      <c r="A960" s="5" t="s">
+      <c r="A960" t="s">
         <v>1065</v>
       </c>
       <c r="B960" t="s">
@@ -13948,7 +13916,7 @@
       </c>
     </row>
     <row r="961" spans="1:2">
-      <c r="A961" s="5" t="s">
+      <c r="A961" t="s">
         <v>1066</v>
       </c>
       <c r="B961" t="s">
@@ -13956,7 +13924,7 @@
       </c>
     </row>
     <row r="962" spans="1:2">
-      <c r="A962" s="5" t="s">
+      <c r="A962" t="s">
         <v>1067</v>
       </c>
       <c r="B962" t="s">
@@ -13964,7 +13932,7 @@
       </c>
     </row>
     <row r="963" spans="1:2">
-      <c r="A963" s="5" t="s">
+      <c r="A963" t="s">
         <v>1068</v>
       </c>
       <c r="B963" t="s">
@@ -13972,7 +13940,7 @@
       </c>
     </row>
     <row r="964" spans="1:2">
-      <c r="A964" s="5" t="s">
+      <c r="A964" t="s">
         <v>1069</v>
       </c>
       <c r="B964" t="s">
@@ -13980,7 +13948,7 @@
       </c>
     </row>
     <row r="965" spans="1:2">
-      <c r="A965" s="5" t="s">
+      <c r="A965" t="s">
         <v>1070</v>
       </c>
       <c r="B965" t="s">
@@ -13988,7 +13956,7 @@
       </c>
     </row>
     <row r="966" spans="1:2">
-      <c r="A966" s="5" t="s">
+      <c r="A966" t="s">
         <v>1074</v>
       </c>
       <c r="B966" t="s">
@@ -13996,7 +13964,7 @@
       </c>
     </row>
     <row r="967" spans="1:2">
-      <c r="A967" s="5" t="s">
+      <c r="A967" t="s">
         <v>1075</v>
       </c>
       <c r="B967" t="s">
@@ -14004,7 +13972,7 @@
       </c>
     </row>
     <row r="968" spans="1:2">
-      <c r="A968" s="5" t="s">
+      <c r="A968" t="s">
         <v>1076</v>
       </c>
       <c r="B968" t="s">
@@ -14012,7 +13980,7 @@
       </c>
     </row>
     <row r="969" spans="1:2">
-      <c r="A969" s="5" t="s">
+      <c r="A969" t="s">
         <v>1077</v>
       </c>
       <c r="B969" t="s">
@@ -14020,7 +13988,7 @@
       </c>
     </row>
     <row r="970" spans="1:2">
-      <c r="A970" s="5" t="s">
+      <c r="A970" t="s">
         <v>1078</v>
       </c>
       <c r="B970" t="s">
@@ -14028,7 +13996,7 @@
       </c>
     </row>
     <row r="971" spans="1:2">
-      <c r="A971" s="5" t="s">
+      <c r="A971" t="s">
         <v>1079</v>
       </c>
       <c r="B971" t="s">
@@ -14036,7 +14004,7 @@
       </c>
     </row>
     <row r="972" spans="1:2">
-      <c r="A972" s="5" t="s">
+      <c r="A972" t="s">
         <v>1080</v>
       </c>
       <c r="B972" t="s">
@@ -14044,7 +14012,7 @@
       </c>
     </row>
     <row r="973" spans="1:2">
-      <c r="A973" s="5" t="s">
+      <c r="A973" t="s">
         <v>1081</v>
       </c>
       <c r="B973" t="s">
@@ -14052,7 +14020,7 @@
       </c>
     </row>
     <row r="974" spans="1:2">
-      <c r="A974" s="5" t="s">
+      <c r="A974" t="s">
         <v>1082</v>
       </c>
       <c r="B974" t="s">
@@ -14060,7 +14028,7 @@
       </c>
     </row>
     <row r="975" spans="1:2">
-      <c r="A975" s="5" t="s">
+      <c r="A975" t="s">
         <v>1083</v>
       </c>
       <c r="B975" t="s">
@@ -14068,7 +14036,7 @@
       </c>
     </row>
     <row r="976" spans="1:2">
-      <c r="A976" s="5" t="s">
+      <c r="A976" t="s">
         <v>1084</v>
       </c>
       <c r="B976" t="s">
@@ -14076,7 +14044,7 @@
       </c>
     </row>
     <row r="977" spans="1:2">
-      <c r="A977" s="5" t="s">
+      <c r="A977" t="s">
         <v>1085</v>
       </c>
       <c r="B977" t="s">
@@ -14084,7 +14052,7 @@
       </c>
     </row>
     <row r="978" spans="1:2">
-      <c r="A978" s="5" t="s">
+      <c r="A978" t="s">
         <v>1086</v>
       </c>
       <c r="B978" t="s">
@@ -14092,7 +14060,7 @@
       </c>
     </row>
     <row r="979" spans="1:2">
-      <c r="A979" s="5" t="s">
+      <c r="A979" t="s">
         <v>1087</v>
       </c>
       <c r="B979" t="s">
@@ -14100,7 +14068,7 @@
       </c>
     </row>
     <row r="980" spans="1:2">
-      <c r="A980" s="5" t="s">
+      <c r="A980" t="s">
         <v>1088</v>
       </c>
       <c r="B980" t="s">
@@ -14108,7 +14076,7 @@
       </c>
     </row>
     <row r="981" spans="1:2">
-      <c r="A981" s="5" t="s">
+      <c r="A981" t="s">
         <v>1089</v>
       </c>
       <c r="B981" t="s">
@@ -14116,7 +14084,7 @@
       </c>
     </row>
     <row r="982" spans="1:2">
-      <c r="A982" s="5" t="s">
+      <c r="A982" t="s">
         <v>1090</v>
       </c>
       <c r="B982" t="s">
@@ -14124,7 +14092,7 @@
       </c>
     </row>
     <row r="983" spans="1:2">
-      <c r="A983" s="5" t="s">
+      <c r="A983" t="s">
         <v>1091</v>
       </c>
       <c r="B983" t="s">
@@ -14132,7 +14100,7 @@
       </c>
     </row>
     <row r="984" spans="1:2">
-      <c r="A984" s="5" t="s">
+      <c r="A984" t="s">
         <v>1092</v>
       </c>
       <c r="B984" t="s">
@@ -14140,7 +14108,7 @@
       </c>
     </row>
     <row r="985" spans="1:2">
-      <c r="A985" s="5" t="s">
+      <c r="A985" t="s">
         <v>1093</v>
       </c>
       <c r="B985" t="s">
@@ -14148,7 +14116,7 @@
       </c>
     </row>
     <row r="986" spans="1:2">
-      <c r="A986" s="5" t="s">
+      <c r="A986" t="s">
         <v>1094</v>
       </c>
       <c r="B986" t="s">
@@ -14164,7 +14132,7 @@
       </c>
     </row>
     <row r="988" spans="1:2">
-      <c r="A988" s="5" t="s">
+      <c r="A988" t="s">
         <v>1096</v>
       </c>
       <c r="B988" t="s">
@@ -14172,7 +14140,7 @@
       </c>
     </row>
     <row r="989" spans="1:2">
-      <c r="A989" s="5" t="s">
+      <c r="A989" t="s">
         <v>1097</v>
       </c>
       <c r="B989" t="s">
@@ -14180,7 +14148,7 @@
       </c>
     </row>
     <row r="990" spans="1:2">
-      <c r="A990" s="5" t="s">
+      <c r="A990" t="s">
         <v>1098</v>
       </c>
       <c r="B990" t="s">
@@ -14188,7 +14156,7 @@
       </c>
     </row>
     <row r="991" spans="1:2">
-      <c r="A991" s="5" t="s">
+      <c r="A991" t="s">
         <v>1099</v>
       </c>
       <c r="B991" t="s">
@@ -14196,7 +14164,7 @@
       </c>
     </row>
     <row r="992" spans="1:2">
-      <c r="A992" s="5" t="s">
+      <c r="A992" t="s">
         <v>1100</v>
       </c>
       <c r="B992" t="s">
@@ -14204,7 +14172,7 @@
       </c>
     </row>
     <row r="993" spans="1:2">
-      <c r="A993" s="5" t="s">
+      <c r="A993" t="s">
         <v>1101</v>
       </c>
       <c r="B993" t="s">
@@ -14212,7 +14180,7 @@
       </c>
     </row>
     <row r="994" spans="1:2">
-      <c r="A994" s="5" t="s">
+      <c r="A994" t="s">
         <v>1102</v>
       </c>
       <c r="B994" t="s">
@@ -14220,7 +14188,7 @@
       </c>
     </row>
     <row r="995" spans="1:2">
-      <c r="A995" s="5" t="s">
+      <c r="A995" t="s">
         <v>1103</v>
       </c>
       <c r="B995" t="s">
@@ -14228,7 +14196,7 @@
       </c>
     </row>
     <row r="996" spans="1:2">
-      <c r="A996" s="5" t="s">
+      <c r="A996" t="s">
         <v>1104</v>
       </c>
       <c r="B996" t="s">
@@ -14236,7 +14204,7 @@
       </c>
     </row>
     <row r="997" spans="1:2">
-      <c r="A997" s="5" t="s">
+      <c r="A997" t="s">
         <v>1105</v>
       </c>
       <c r="B997" t="s">
@@ -14244,7 +14212,7 @@
       </c>
     </row>
     <row r="998" spans="1:2">
-      <c r="A998" s="5" t="s">
+      <c r="A998" t="s">
         <v>1106</v>
       </c>
       <c r="B998" t="s">
@@ -14252,7 +14220,7 @@
       </c>
     </row>
     <row r="999" spans="1:2">
-      <c r="A999" s="5" t="s">
+      <c r="A999" t="s">
         <v>1107</v>
       </c>
       <c r="B999" t="s">
@@ -14260,7 +14228,7 @@
       </c>
     </row>
     <row r="1000" spans="1:2">
-      <c r="A1000" s="5" t="s">
+      <c r="A1000" t="s">
         <v>1108</v>
       </c>
       <c r="B1000" t="s">
@@ -14268,7 +14236,7 @@
       </c>
     </row>
     <row r="1001" spans="1:2">
-      <c r="A1001" s="5" t="s">
+      <c r="A1001" t="s">
         <v>1109</v>
       </c>
       <c r="B1001" t="s">
@@ -14276,7 +14244,7 @@
       </c>
     </row>
     <row r="1002" spans="1:2">
-      <c r="A1002" s="5" t="s">
+      <c r="A1002" t="s">
         <v>1110</v>
       </c>
       <c r="B1002" t="s">
@@ -14284,7 +14252,7 @@
       </c>
     </row>
     <row r="1003" spans="1:2">
-      <c r="A1003" s="5" t="s">
+      <c r="A1003" t="s">
         <v>1111</v>
       </c>
       <c r="B1003" t="s">
@@ -14292,7 +14260,7 @@
       </c>
     </row>
     <row r="1004" spans="1:2">
-      <c r="A1004" s="5" t="s">
+      <c r="A1004" t="s">
         <v>1112</v>
       </c>
       <c r="B1004" t="s">
@@ -14300,7 +14268,7 @@
       </c>
     </row>
     <row r="1005" spans="1:2">
-      <c r="A1005" s="5" t="s">
+      <c r="A1005" t="s">
         <v>1113</v>
       </c>
       <c r="B1005" t="s">
@@ -14308,7 +14276,7 @@
       </c>
     </row>
     <row r="1006" spans="1:2">
-      <c r="A1006" s="5" t="s">
+      <c r="A1006" t="s">
         <v>1114</v>
       </c>
       <c r="B1006" t="s">
@@ -14316,7 +14284,7 @@
       </c>
     </row>
     <row r="1007" spans="1:2">
-      <c r="A1007" s="5" t="s">
+      <c r="A1007" t="s">
         <v>1115</v>
       </c>
       <c r="B1007" t="s">
@@ -14324,7 +14292,7 @@
       </c>
     </row>
     <row r="1008" spans="1:2">
-      <c r="A1008" s="5" t="s">
+      <c r="A1008" t="s">
         <v>1116</v>
       </c>
       <c r="B1008" t="s">
@@ -14332,7 +14300,7 @@
       </c>
     </row>
     <row r="1009" spans="1:2">
-      <c r="A1009" s="5" t="s">
+      <c r="A1009" t="s">
         <v>1117</v>
       </c>
       <c r="B1009" t="s">
@@ -14340,7 +14308,7 @@
       </c>
     </row>
     <row r="1010" spans="1:2">
-      <c r="A1010" s="5" t="s">
+      <c r="A1010" t="s">
         <v>1123</v>
       </c>
       <c r="B1010" t="s">
@@ -14348,7 +14316,7 @@
       </c>
     </row>
     <row r="1011" spans="1:2">
-      <c r="A1011" s="5" t="s">
+      <c r="A1011" t="s">
         <v>1124</v>
       </c>
       <c r="B1011" t="s">
@@ -14356,7 +14324,7 @@
       </c>
     </row>
     <row r="1012" spans="1:2">
-      <c r="A1012" s="5" t="s">
+      <c r="A1012" t="s">
         <v>1125</v>
       </c>
       <c r="B1012" t="s">
@@ -14364,7 +14332,7 @@
       </c>
     </row>
     <row r="1013" spans="1:2">
-      <c r="A1013" s="5" t="s">
+      <c r="A1013" t="s">
         <v>1126</v>
       </c>
       <c r="B1013" t="s">
@@ -14372,7 +14340,7 @@
       </c>
     </row>
     <row r="1014" spans="1:2">
-      <c r="A1014" s="5" t="s">
+      <c r="A1014" t="s">
         <v>1127</v>
       </c>
       <c r="B1014" t="s">
@@ -14380,7 +14348,7 @@
       </c>
     </row>
     <row r="1015" spans="1:2">
-      <c r="A1015" s="5" t="s">
+      <c r="A1015" t="s">
         <v>1128</v>
       </c>
       <c r="B1015" t="s">
@@ -14388,7 +14356,7 @@
       </c>
     </row>
     <row r="1016" spans="1:2">
-      <c r="A1016" s="5" t="s">
+      <c r="A1016" t="s">
         <v>1129</v>
       </c>
       <c r="B1016" t="s">
@@ -14396,7 +14364,7 @@
       </c>
     </row>
     <row r="1017" spans="1:2">
-      <c r="A1017" s="5" t="s">
+      <c r="A1017" t="s">
         <v>1130</v>
       </c>
       <c r="B1017" t="s">
@@ -14404,7 +14372,7 @@
       </c>
     </row>
     <row r="1018" spans="1:2">
-      <c r="A1018" s="5" t="s">
+      <c r="A1018" t="s">
         <v>1131</v>
       </c>
       <c r="B1018" t="s">
@@ -14412,7 +14380,7 @@
       </c>
     </row>
     <row r="1019" spans="1:2">
-      <c r="A1019" s="5" t="s">
+      <c r="A1019" t="s">
         <v>1132</v>
       </c>
       <c r="B1019" t="s">
@@ -14420,7 +14388,7 @@
       </c>
     </row>
     <row r="1020" spans="1:2">
-      <c r="A1020" s="5" t="s">
+      <c r="A1020" t="s">
         <v>1133</v>
       </c>
       <c r="B1020" t="s">
@@ -14428,7 +14396,7 @@
       </c>
     </row>
     <row r="1021" spans="1:2">
-      <c r="A1021" s="5" t="s">
+      <c r="A1021" t="s">
         <v>1134</v>
       </c>
       <c r="B1021" t="s">
@@ -14436,7 +14404,7 @@
       </c>
     </row>
     <row r="1022" spans="1:2">
-      <c r="A1022" s="5" t="s">
+      <c r="A1022" t="s">
         <v>1135</v>
       </c>
       <c r="B1022" t="s">
@@ -14444,7 +14412,7 @@
       </c>
     </row>
     <row r="1023" spans="1:2">
-      <c r="A1023" s="5" t="s">
+      <c r="A1023" t="s">
         <v>1137</v>
       </c>
       <c r="B1023" t="s">
@@ -14452,7 +14420,7 @@
       </c>
     </row>
     <row r="1024" spans="1:2">
-      <c r="A1024" s="5" t="s">
+      <c r="A1024" t="s">
         <v>1138</v>
       </c>
       <c r="B1024" t="s">
@@ -14460,7 +14428,7 @@
       </c>
     </row>
     <row r="1025" spans="1:2">
-      <c r="A1025" s="5" t="s">
+      <c r="A1025" t="s">
         <v>1139</v>
       </c>
       <c r="B1025" t="s">
@@ -14468,7 +14436,7 @@
       </c>
     </row>
     <row r="1026" spans="1:2">
-      <c r="A1026" s="5" t="s">
+      <c r="A1026" t="s">
         <v>1140</v>
       </c>
       <c r="B1026" t="s">
@@ -14476,7 +14444,7 @@
       </c>
     </row>
     <row r="1027" spans="1:2">
-      <c r="A1027" s="5" t="s">
+      <c r="A1027" t="s">
         <v>1141</v>
       </c>
       <c r="B1027" t="s">
@@ -14484,7 +14452,7 @@
       </c>
     </row>
     <row r="1028" spans="1:2">
-      <c r="A1028" s="5" t="s">
+      <c r="A1028" t="s">
         <v>1142</v>
       </c>
       <c r="B1028" t="s">
@@ -14492,7 +14460,7 @@
       </c>
     </row>
     <row r="1029" spans="1:2">
-      <c r="A1029" s="5" t="s">
+      <c r="A1029" t="s">
         <v>1143</v>
       </c>
       <c r="B1029" t="s">
@@ -14500,7 +14468,7 @@
       </c>
     </row>
     <row r="1030" spans="1:2">
-      <c r="A1030" s="5" t="s">
+      <c r="A1030" t="s">
         <v>1144</v>
       </c>
       <c r="B1030" t="s">
@@ -14508,7 +14476,7 @@
       </c>
     </row>
     <row r="1031" spans="1:2">
-      <c r="A1031" s="5" t="s">
+      <c r="A1031" t="s">
         <v>1145</v>
       </c>
       <c r="B1031" t="s">
@@ -14516,7 +14484,7 @@
       </c>
     </row>
     <row r="1032" spans="1:2">
-      <c r="A1032" s="5" t="s">
+      <c r="A1032" t="s">
         <v>1146</v>
       </c>
       <c r="B1032" t="s">
@@ -14524,7 +14492,7 @@
       </c>
     </row>
     <row r="1033" spans="1:2">
-      <c r="A1033" s="5" t="s">
+      <c r="A1033" t="s">
         <v>1147</v>
       </c>
       <c r="B1033" t="s">
@@ -14532,7 +14500,7 @@
       </c>
     </row>
     <row r="1034" spans="1:2">
-      <c r="A1034" s="5" t="s">
+      <c r="A1034" t="s">
         <v>1149</v>
       </c>
       <c r="B1034" t="s">
@@ -14540,7 +14508,7 @@
       </c>
     </row>
     <row r="1035" spans="1:2">
-      <c r="A1035" s="5" t="s">
+      <c r="A1035" t="s">
         <v>1150</v>
       </c>
       <c r="B1035" t="s">
@@ -14548,7 +14516,7 @@
       </c>
     </row>
     <row r="1036" spans="1:2">
-      <c r="A1036" s="5" t="s">
+      <c r="A1036" t="s">
         <v>1151</v>
       </c>
       <c r="B1036" t="s">
@@ -14556,7 +14524,7 @@
       </c>
     </row>
     <row r="1037" spans="1:2">
-      <c r="A1037" s="5" t="s">
+      <c r="A1037" t="s">
         <v>1152</v>
       </c>
       <c r="B1037" t="s">
@@ -14564,7 +14532,7 @@
       </c>
     </row>
     <row r="1038" spans="1:2">
-      <c r="A1038" s="5" t="s">
+      <c r="A1038" t="s">
         <v>1153</v>
       </c>
       <c r="B1038" t="s">
@@ -14572,7 +14540,7 @@
       </c>
     </row>
     <row r="1039" spans="1:2">
-      <c r="A1039" s="5" t="s">
+      <c r="A1039" t="s">
         <v>1154</v>
       </c>
       <c r="B1039" t="s">
@@ -14580,7 +14548,7 @@
       </c>
     </row>
     <row r="1040" spans="1:2">
-      <c r="A1040" s="5" t="s">
+      <c r="A1040" t="s">
         <v>1155</v>
       </c>
       <c r="B1040" t="s">
@@ -14588,7 +14556,7 @@
       </c>
     </row>
     <row r="1041" spans="1:2">
-      <c r="A1041" s="5" t="s">
+      <c r="A1041" t="s">
         <v>1156</v>
       </c>
       <c r="B1041" t="s">
@@ -14596,7 +14564,7 @@
       </c>
     </row>
     <row r="1042" spans="1:2">
-      <c r="A1042" s="5" t="s">
+      <c r="A1042" t="s">
         <v>1157</v>
       </c>
       <c r="B1042" t="s">
@@ -14604,7 +14572,7 @@
       </c>
     </row>
     <row r="1043" spans="1:2">
-      <c r="A1043" s="5" t="s">
+      <c r="A1043" t="s">
         <v>1158</v>
       </c>
       <c r="B1043" t="s">
@@ -14612,7 +14580,7 @@
       </c>
     </row>
     <row r="1044" spans="1:2">
-      <c r="A1044" s="5" t="s">
+      <c r="A1044" t="s">
         <v>1159</v>
       </c>
       <c r="B1044" t="s">
@@ -14620,7 +14588,7 @@
       </c>
     </row>
     <row r="1045" spans="1:2">
-      <c r="A1045" s="5" t="s">
+      <c r="A1045" t="s">
         <v>1160</v>
       </c>
       <c r="B1045" t="s">
@@ -14628,7 +14596,7 @@
       </c>
     </row>
     <row r="1046" spans="1:2">
-      <c r="A1046" s="5" t="s">
+      <c r="A1046" t="s">
         <v>1161</v>
       </c>
       <c r="B1046" t="s">
@@ -14636,7 +14604,7 @@
       </c>
     </row>
     <row r="1047" spans="1:2">
-      <c r="A1047" s="5" t="s">
+      <c r="A1047" t="s">
         <v>1162</v>
       </c>
       <c r="B1047" t="s">
@@ -14644,7 +14612,7 @@
       </c>
     </row>
     <row r="1048" spans="1:2">
-      <c r="A1048" s="5" t="s">
+      <c r="A1048" t="s">
         <v>1163</v>
       </c>
       <c r="B1048" t="s">
@@ -14652,7 +14620,7 @@
       </c>
     </row>
     <row r="1049" spans="1:2">
-      <c r="A1049" s="5" t="s">
+      <c r="A1049" t="s">
         <v>1164</v>
       </c>
       <c r="B1049" t="s">
@@ -14660,7 +14628,7 @@
       </c>
     </row>
     <row r="1050" spans="1:2">
-      <c r="A1050" s="5" t="s">
+      <c r="A1050" t="s">
         <v>1165</v>
       </c>
       <c r="B1050" t="s">
@@ -14668,7 +14636,7 @@
       </c>
     </row>
     <row r="1051" spans="1:2">
-      <c r="A1051" s="5" t="s">
+      <c r="A1051" t="s">
         <v>1167</v>
       </c>
       <c r="B1051" t="s">
@@ -14676,7 +14644,7 @@
       </c>
     </row>
     <row r="1052" spans="1:2">
-      <c r="A1052" s="5" t="s">
+      <c r="A1052" t="s">
         <v>1168</v>
       </c>
       <c r="B1052" t="s">
@@ -14684,7 +14652,7 @@
       </c>
     </row>
     <row r="1053" spans="1:2">
-      <c r="A1053" s="5" t="s">
+      <c r="A1053" t="s">
         <v>1169</v>
       </c>
       <c r="B1053" t="s">
@@ -14692,7 +14660,7 @@
       </c>
     </row>
     <row r="1054" spans="1:2">
-      <c r="A1054" s="5" t="s">
+      <c r="A1054" t="s">
         <v>1172</v>
       </c>
       <c r="B1054" t="s">
@@ -14700,7 +14668,7 @@
       </c>
     </row>
     <row r="1055" spans="1:2">
-      <c r="A1055" s="5" t="s">
+      <c r="A1055" t="s">
         <v>1173</v>
       </c>
       <c r="B1055" t="s">
@@ -14708,7 +14676,7 @@
       </c>
     </row>
     <row r="1056" spans="1:2">
-      <c r="A1056" s="5" t="s">
+      <c r="A1056" t="s">
         <v>1174</v>
       </c>
       <c r="B1056" t="s">
@@ -14716,7 +14684,7 @@
       </c>
     </row>
     <row r="1057" spans="1:2">
-      <c r="A1057" s="5" t="s">
+      <c r="A1057" t="s">
         <v>1175</v>
       </c>
       <c r="B1057" t="s">
@@ -14724,7 +14692,7 @@
       </c>
     </row>
     <row r="1058" spans="1:2">
-      <c r="A1058" s="5" t="s">
+      <c r="A1058" t="s">
         <v>1176</v>
       </c>
       <c r="B1058" t="s">
@@ -14732,7 +14700,7 @@
       </c>
     </row>
     <row r="1059" spans="1:2">
-      <c r="A1059" s="5" t="s">
+      <c r="A1059" t="s">
         <v>1177</v>
       </c>
       <c r="B1059" t="s">
@@ -14740,7 +14708,7 @@
       </c>
     </row>
     <row r="1060" spans="1:2">
-      <c r="A1060" s="5" t="s">
+      <c r="A1060" t="s">
         <v>1178</v>
       </c>
       <c r="B1060" t="s">
@@ -14748,7 +14716,7 @@
       </c>
     </row>
     <row r="1061" spans="1:2">
-      <c r="A1061" s="5" t="s">
+      <c r="A1061" t="s">
         <v>1179</v>
       </c>
       <c r="B1061" t="s">
@@ -14756,7 +14724,7 @@
       </c>
     </row>
     <row r="1062" spans="1:2">
-      <c r="A1062" s="5" t="s">
+      <c r="A1062" t="s">
         <v>1180</v>
       </c>
       <c r="B1062" t="s">
@@ -14764,7 +14732,7 @@
       </c>
     </row>
     <row r="1063" spans="1:2">
-      <c r="A1063" s="5" t="s">
+      <c r="A1063" t="s">
         <v>1181</v>
       </c>
       <c r="B1063" t="s">
@@ -14772,7 +14740,7 @@
       </c>
     </row>
     <row r="1064" spans="1:2">
-      <c r="A1064" s="5" t="s">
+      <c r="A1064" t="s">
         <v>1182</v>
       </c>
       <c r="B1064" t="s">
@@ -14780,7 +14748,7 @@
       </c>
     </row>
     <row r="1065" spans="1:2">
-      <c r="A1065" s="5" t="s">
+      <c r="A1065" t="s">
         <v>1183</v>
       </c>
       <c r="B1065" t="s">
@@ -14788,7 +14756,7 @@
       </c>
     </row>
     <row r="1066" spans="1:2">
-      <c r="A1066" s="5" t="s">
+      <c r="A1066" t="s">
         <v>1184</v>
       </c>
       <c r="B1066" t="s">
@@ -14796,7 +14764,7 @@
       </c>
     </row>
     <row r="1067" spans="1:2">
-      <c r="A1067" s="5" t="s">
+      <c r="A1067" t="s">
         <v>1185</v>
       </c>
       <c r="B1067" t="s">
@@ -14804,7 +14772,7 @@
       </c>
     </row>
     <row r="1068" spans="1:2">
-      <c r="A1068" s="5" t="s">
+      <c r="A1068" t="s">
         <v>1186</v>
       </c>
       <c r="B1068" t="s">
@@ -14812,7 +14780,7 @@
       </c>
     </row>
     <row r="1069" spans="1:2">
-      <c r="A1069" s="5" t="s">
+      <c r="A1069" t="s">
         <v>1187</v>
       </c>
       <c r="B1069" t="s">
@@ -14820,7 +14788,7 @@
       </c>
     </row>
     <row r="1070" spans="1:2">
-      <c r="A1070" s="5" t="s">
+      <c r="A1070" t="s">
         <v>1188</v>
       </c>
       <c r="B1070" t="s">
@@ -14828,7 +14796,7 @@
       </c>
     </row>
     <row r="1071" spans="1:2">
-      <c r="A1071" s="5" t="s">
+      <c r="A1071" t="s">
         <v>1189</v>
       </c>
       <c r="B1071" t="s">
@@ -14836,7 +14804,7 @@
       </c>
     </row>
     <row r="1072" spans="1:2">
-      <c r="A1072" s="5" t="s">
+      <c r="A1072" t="s">
         <v>1190</v>
       </c>
       <c r="B1072" t="s">
@@ -14844,7 +14812,7 @@
       </c>
     </row>
     <row r="1073" spans="1:2">
-      <c r="A1073" s="5" t="s">
+      <c r="A1073" t="s">
         <v>1191</v>
       </c>
       <c r="B1073" t="s">
@@ -14852,7 +14820,7 @@
       </c>
     </row>
     <row r="1074" spans="1:2">
-      <c r="A1074" s="5" t="s">
+      <c r="A1074" t="s">
         <v>1192</v>
       </c>
       <c r="B1074" t="s">
@@ -14860,7 +14828,7 @@
       </c>
     </row>
     <row r="1075" spans="1:2">
-      <c r="A1075" s="5" t="s">
+      <c r="A1075" t="s">
         <v>1193</v>
       </c>
       <c r="B1075" t="s">
@@ -14868,7 +14836,7 @@
       </c>
     </row>
     <row r="1076" spans="1:2">
-      <c r="A1076" s="5" t="s">
+      <c r="A1076" t="s">
         <v>1194</v>
       </c>
       <c r="B1076" t="s">
@@ -14876,7 +14844,7 @@
       </c>
     </row>
     <row r="1077" spans="1:2">
-      <c r="A1077" s="5" t="s">
+      <c r="A1077" t="s">
         <v>1195</v>
       </c>
       <c r="B1077" t="s">
@@ -14884,7 +14852,7 @@
       </c>
     </row>
     <row r="1078" spans="1:2">
-      <c r="A1078" s="5" t="s">
+      <c r="A1078" t="s">
         <v>1196</v>
       </c>
       <c r="B1078" t="s">
@@ -14892,7 +14860,7 @@
       </c>
     </row>
     <row r="1079" spans="1:2">
-      <c r="A1079" s="5" t="s">
+      <c r="A1079" t="s">
         <v>1197</v>
       </c>
       <c r="B1079" t="s">
@@ -14900,7 +14868,7 @@
       </c>
     </row>
     <row r="1080" spans="1:2">
-      <c r="A1080" s="5" t="s">
+      <c r="A1080" t="s">
         <v>1198</v>
       </c>
       <c r="B1080" t="s">
@@ -14908,7 +14876,7 @@
       </c>
     </row>
     <row r="1081" spans="1:2">
-      <c r="A1081" s="5" t="s">
+      <c r="A1081" t="s">
         <v>1199</v>
       </c>
       <c r="B1081" t="s">
@@ -14916,7 +14884,7 @@
       </c>
     </row>
     <row r="1082" spans="1:2">
-      <c r="A1082" s="5" t="s">
+      <c r="A1082" t="s">
         <v>1201</v>
       </c>
       <c r="B1082" t="s">
@@ -14924,7 +14892,7 @@
       </c>
     </row>
     <row r="1083" spans="1:2">
-      <c r="A1083" s="5" t="s">
+      <c r="A1083" t="s">
         <v>1202</v>
       </c>
       <c r="B1083" t="s">
@@ -14932,7 +14900,7 @@
       </c>
     </row>
     <row r="1084" spans="1:2">
-      <c r="A1084" s="5" t="s">
+      <c r="A1084" t="s">
         <v>1203</v>
       </c>
       <c r="B1084" t="s">
@@ -14940,7 +14908,7 @@
       </c>
     </row>
     <row r="1085" spans="1:2">
-      <c r="A1085" s="5" t="s">
+      <c r="A1085" t="s">
         <v>1204</v>
       </c>
       <c r="B1085" t="s">
@@ -14948,7 +14916,7 @@
       </c>
     </row>
     <row r="1086" spans="1:2">
-      <c r="A1086" s="5" t="s">
+      <c r="A1086" t="s">
         <v>1205</v>
       </c>
       <c r="B1086" t="s">
@@ -14956,7 +14924,7 @@
       </c>
     </row>
     <row r="1087" spans="1:2">
-      <c r="A1087" s="5" t="s">
+      <c r="A1087" t="s">
         <v>1206</v>
       </c>
       <c r="B1087" t="s">
@@ -14964,7 +14932,7 @@
       </c>
     </row>
     <row r="1088" spans="1:2">
-      <c r="A1088" s="5" t="s">
+      <c r="A1088" t="s">
         <v>1207</v>
       </c>
       <c r="B1088" t="s">
@@ -14972,7 +14940,7 @@
       </c>
     </row>
     <row r="1089" spans="1:2">
-      <c r="A1089" s="5" t="s">
+      <c r="A1089" t="s">
         <v>1208</v>
       </c>
       <c r="B1089" t="s">
@@ -14980,7 +14948,7 @@
       </c>
     </row>
     <row r="1090" spans="1:2">
-      <c r="A1090" s="5" t="s">
+      <c r="A1090" t="s">
         <v>1209</v>
       </c>
       <c r="B1090" t="s">
@@ -14988,7 +14956,7 @@
       </c>
     </row>
     <row r="1091" spans="1:2">
-      <c r="A1091" s="5" t="s">
+      <c r="A1091" t="s">
         <v>1210</v>
       </c>
       <c r="B1091" t="s">
@@ -14996,7 +14964,7 @@
       </c>
     </row>
     <row r="1092" spans="1:2">
-      <c r="A1092" s="5" t="s">
+      <c r="A1092" t="s">
         <v>1211</v>
       </c>
       <c r="B1092" t="s">
@@ -15009,7 +14977,7 @@
       </c>
     </row>
     <row r="1096" spans="1:2">
-      <c r="A1096" s="5" t="s">
+      <c r="A1096" t="s">
         <v>1213</v>
       </c>
       <c r="B1096" t="s">
@@ -15017,7 +14985,7 @@
       </c>
     </row>
     <row r="1097" spans="1:2">
-      <c r="A1097" s="5" t="s">
+      <c r="A1097" t="s">
         <v>1214</v>
       </c>
       <c r="B1097" t="s">
@@ -15025,7 +14993,7 @@
       </c>
     </row>
     <row r="1098" spans="1:2">
-      <c r="A1098" s="5" t="s">
+      <c r="A1098" t="s">
         <v>1215</v>
       </c>
       <c r="B1098" t="s">
@@ -15033,7 +15001,7 @@
       </c>
     </row>
     <row r="1099" spans="1:2">
-      <c r="A1099" s="5" t="s">
+      <c r="A1099" t="s">
         <v>1216</v>
       </c>
       <c r="B1099" t="s">
@@ -15041,7 +15009,7 @@
       </c>
     </row>
     <row r="1100" spans="1:2">
-      <c r="A1100" s="5" t="s">
+      <c r="A1100" t="s">
         <v>1217</v>
       </c>
       <c r="B1100" t="s">
@@ -15049,7 +15017,7 @@
       </c>
     </row>
     <row r="1101" spans="1:2">
-      <c r="A1101" s="5" t="s">
+      <c r="A1101" t="s">
         <v>1218</v>
       </c>
       <c r="B1101" t="s">
@@ -15057,7 +15025,7 @@
       </c>
     </row>
     <row r="1102" spans="1:2">
-      <c r="A1102" s="5" t="s">
+      <c r="A1102" t="s">
         <v>1219</v>
       </c>
       <c r="B1102" t="s">
@@ -15065,7 +15033,7 @@
       </c>
     </row>
     <row r="1103" spans="1:2">
-      <c r="A1103" s="5" t="s">
+      <c r="A1103" t="s">
         <v>1220</v>
       </c>
       <c r="B1103" t="s">
@@ -15073,7 +15041,7 @@
       </c>
     </row>
     <row r="1104" spans="1:2">
-      <c r="A1104" s="5" t="s">
+      <c r="A1104" t="s">
         <v>1221</v>
       </c>
       <c r="B1104" t="s">
@@ -15081,7 +15049,7 @@
       </c>
     </row>
     <row r="1105" spans="1:2">
-      <c r="A1105" s="5" t="s">
+      <c r="A1105" t="s">
         <v>1222</v>
       </c>
       <c r="B1105" t="s">
@@ -15089,7 +15057,7 @@
       </c>
     </row>
     <row r="1106" spans="1:2">
-      <c r="A1106" s="5" t="s">
+      <c r="A1106" t="s">
         <v>1223</v>
       </c>
       <c r="B1106" t="s">
@@ -15097,7 +15065,7 @@
       </c>
     </row>
     <row r="1107" spans="1:2">
-      <c r="A1107" s="5" t="s">
+      <c r="A1107" t="s">
         <v>1225</v>
       </c>
       <c r="B1107" t="s">
@@ -15105,7 +15073,7 @@
       </c>
     </row>
     <row r="1108" spans="1:2">
-      <c r="A1108" s="5" t="s">
+      <c r="A1108" t="s">
         <v>1224</v>
       </c>
       <c r="B1108" t="s">
@@ -15113,7 +15081,7 @@
       </c>
     </row>
     <row r="1109" spans="1:2">
-      <c r="A1109" s="5" t="s">
+      <c r="A1109" t="s">
         <v>1226</v>
       </c>
       <c r="B1109" t="s">
@@ -15121,7 +15089,7 @@
       </c>
     </row>
     <row r="1110" spans="1:2">
-      <c r="A1110" s="5" t="s">
+      <c r="A1110" t="s">
         <v>1227</v>
       </c>
       <c r="B1110" t="s">
@@ -15129,7 +15097,7 @@
       </c>
     </row>
     <row r="1111" spans="1:2">
-      <c r="A1111" s="5" t="s">
+      <c r="A1111" t="s">
         <v>1228</v>
       </c>
       <c r="B1111" t="s">
@@ -15137,7 +15105,7 @@
       </c>
     </row>
     <row r="1112" spans="1:2">
-      <c r="A1112" s="5" t="s">
+      <c r="A1112" t="s">
         <v>1229</v>
       </c>
       <c r="B1112" t="s">
@@ -15145,7 +15113,7 @@
       </c>
     </row>
     <row r="1113" spans="1:2">
-      <c r="A1113" s="5" t="s">
+      <c r="A1113" t="s">
         <v>1230</v>
       </c>
       <c r="B1113" t="s">
@@ -15153,7 +15121,7 @@
       </c>
     </row>
     <row r="1114" spans="1:2">
-      <c r="A1114" s="5" t="s">
+      <c r="A1114" t="s">
         <v>1231</v>
       </c>
       <c r="B1114" t="s">
@@ -15161,7 +15129,7 @@
       </c>
     </row>
     <row r="1115" spans="1:2">
-      <c r="A1115" s="5" t="s">
+      <c r="A1115" t="s">
         <v>1232</v>
       </c>
       <c r="B1115" t="s">
@@ -15169,7 +15137,7 @@
       </c>
     </row>
     <row r="1116" spans="1:2">
-      <c r="A1116" s="5" t="s">
+      <c r="A1116" t="s">
         <v>1233</v>
       </c>
       <c r="B1116" t="s">
@@ -15177,7 +15145,7 @@
       </c>
     </row>
     <row r="1117" spans="1:2">
-      <c r="A1117" s="5" t="s">
+      <c r="A1117" t="s">
         <v>1234</v>
       </c>
       <c r="B1117" t="s">
@@ -15185,7 +15153,7 @@
       </c>
     </row>
     <row r="1118" spans="1:2">
-      <c r="A1118" s="5" t="s">
+      <c r="A1118" t="s">
         <v>1235</v>
       </c>
       <c r="B1118" t="s">
@@ -15193,7 +15161,7 @@
       </c>
     </row>
     <row r="1119" spans="1:2">
-      <c r="A1119" s="5" t="s">
+      <c r="A1119" t="s">
         <v>1236</v>
       </c>
       <c r="B1119" t="s">
@@ -15209,7 +15177,7 @@
       </c>
     </row>
     <row r="1121" spans="1:2">
-      <c r="A1121" s="5" t="s">
+      <c r="A1121" t="s">
         <v>1238</v>
       </c>
       <c r="B1121" t="s">
@@ -15217,7 +15185,7 @@
       </c>
     </row>
     <row r="1122" spans="1:2">
-      <c r="A1122" s="5" t="s">
+      <c r="A1122" t="s">
         <v>1239</v>
       </c>
       <c r="B1122" t="s">
@@ -15225,7 +15193,7 @@
       </c>
     </row>
     <row r="1123" spans="1:2">
-      <c r="A1123" s="5" t="s">
+      <c r="A1123" t="s">
         <v>1240</v>
       </c>
       <c r="B1123" t="s">
@@ -15233,7 +15201,7 @@
       </c>
     </row>
     <row r="1124" spans="1:2">
-      <c r="A1124" s="5" t="s">
+      <c r="A1124" t="s">
         <v>1241</v>
       </c>
       <c r="B1124" t="s">
@@ -15241,7 +15209,7 @@
       </c>
     </row>
     <row r="1125" spans="1:2">
-      <c r="A1125" s="5" t="s">
+      <c r="A1125" t="s">
         <v>1242</v>
       </c>
       <c r="B1125" t="s">
@@ -15249,7 +15217,7 @@
       </c>
     </row>
     <row r="1126" spans="1:2">
-      <c r="A1126" s="5" t="s">
+      <c r="A1126" t="s">
         <v>1243</v>
       </c>
       <c r="B1126" t="s">
@@ -15257,7 +15225,7 @@
       </c>
     </row>
     <row r="1127" spans="1:2">
-      <c r="A1127" s="5" t="s">
+      <c r="A1127" t="s">
         <v>1244</v>
       </c>
       <c r="B1127" t="s">
@@ -15265,7 +15233,7 @@
       </c>
     </row>
     <row r="1128" spans="1:2">
-      <c r="A1128" s="5" t="s">
+      <c r="A1128" t="s">
         <v>1245</v>
       </c>
       <c r="B1128" t="s">
@@ -15273,7 +15241,7 @@
       </c>
     </row>
     <row r="1129" spans="1:2">
-      <c r="A1129" s="5" t="s">
+      <c r="A1129" t="s">
         <v>1246</v>
       </c>
       <c r="B1129" t="s">
@@ -15281,7 +15249,7 @@
       </c>
     </row>
     <row r="1130" spans="1:2">
-      <c r="A1130" s="5" t="s">
+      <c r="A1130" t="s">
         <v>1247</v>
       </c>
       <c r="B1130" t="s">
@@ -15289,7 +15257,7 @@
       </c>
     </row>
     <row r="1131" spans="1:2">
-      <c r="A1131" s="5" t="s">
+      <c r="A1131" t="s">
         <v>1248</v>
       </c>
       <c r="B1131" t="s">
@@ -15297,7 +15265,7 @@
       </c>
     </row>
     <row r="1132" spans="1:2">
-      <c r="A1132" s="5" t="s">
+      <c r="A1132" t="s">
         <v>1249</v>
       </c>
       <c r="B1132" t="s">
@@ -15305,7 +15273,7 @@
       </c>
     </row>
     <row r="1133" spans="1:2">
-      <c r="A1133" s="5" t="s">
+      <c r="A1133" t="s">
         <v>1250</v>
       </c>
       <c r="B1133" t="s">
@@ -15313,7 +15281,7 @@
       </c>
     </row>
     <row r="1134" spans="1:2">
-      <c r="A1134" s="5" t="s">
+      <c r="A1134" t="s">
         <v>1251</v>
       </c>
       <c r="B1134" t="s">
@@ -15321,7 +15289,7 @@
       </c>
     </row>
     <row r="1135" spans="1:2">
-      <c r="A1135" s="5" t="s">
+      <c r="A1135" t="s">
         <v>1252</v>
       </c>
       <c r="B1135" t="s">
@@ -15329,7 +15297,7 @@
       </c>
     </row>
     <row r="1136" spans="1:2">
-      <c r="A1136" s="5" t="s">
+      <c r="A1136" t="s">
         <v>1253</v>
       </c>
       <c r="B1136" t="s">
@@ -15337,7 +15305,7 @@
       </c>
     </row>
     <row r="1137" spans="1:2">
-      <c r="A1137" s="5" t="s">
+      <c r="A1137" t="s">
         <v>1254</v>
       </c>
       <c r="B1137" t="s">
@@ -15345,7 +15313,7 @@
       </c>
     </row>
     <row r="1138" spans="1:2">
-      <c r="A1138" s="5" t="s">
+      <c r="A1138" t="s">
         <v>1255</v>
       </c>
       <c r="B1138" t="s">
@@ -15353,7 +15321,7 @@
       </c>
     </row>
     <row r="1139" spans="1:2">
-      <c r="A1139" s="5" t="s">
+      <c r="A1139" t="s">
         <v>1256</v>
       </c>
       <c r="B1139" t="s">
@@ -15361,7 +15329,7 @@
       </c>
     </row>
     <row r="1140" spans="1:2">
-      <c r="A1140" s="5" t="s">
+      <c r="A1140" t="s">
         <v>1257</v>
       </c>
       <c r="B1140" t="s">
@@ -15369,7 +15337,7 @@
       </c>
     </row>
     <row r="1141" spans="1:2">
-      <c r="A1141" s="5" t="s">
+      <c r="A1141" t="s">
         <v>1258</v>
       </c>
       <c r="B1141" t="s">
@@ -15377,7 +15345,7 @@
       </c>
     </row>
     <row r="1142" spans="1:2">
-      <c r="A1142" s="5" t="s">
+      <c r="A1142" t="s">
         <v>1259</v>
       </c>
       <c r="B1142" t="s">
@@ -15385,7 +15353,7 @@
       </c>
     </row>
     <row r="1143" spans="1:2">
-      <c r="A1143" s="5" t="s">
+      <c r="A1143" t="s">
         <v>1260</v>
       </c>
       <c r="B1143" t="s">
@@ -15393,7 +15361,7 @@
       </c>
     </row>
     <row r="1144" spans="1:2">
-      <c r="A1144" s="5" t="s">
+      <c r="A1144" t="s">
         <v>1261</v>
       </c>
       <c r="B1144" t="s">
@@ -15401,7 +15369,7 @@
       </c>
     </row>
     <row r="1145" spans="1:2">
-      <c r="A1145" s="5" t="s">
+      <c r="A1145" t="s">
         <v>1262</v>
       </c>
       <c r="B1145" t="s">
@@ -15409,7 +15377,7 @@
       </c>
     </row>
     <row r="1146" spans="1:2">
-      <c r="A1146" s="5" t="s">
+      <c r="A1146" t="s">
         <v>1263</v>
       </c>
       <c r="B1146" t="s">
@@ -15417,7 +15385,7 @@
       </c>
     </row>
     <row r="1147" spans="1:2">
-      <c r="A1147" s="5" t="s">
+      <c r="A1147" t="s">
         <v>1264</v>
       </c>
       <c r="B1147" t="s">
@@ -15425,7 +15393,7 @@
       </c>
     </row>
     <row r="1148" spans="1:2">
-      <c r="A1148" s="5" t="s">
+      <c r="A1148" t="s">
         <v>1265</v>
       </c>
       <c r="B1148" t="s">
@@ -15433,7 +15401,7 @@
       </c>
     </row>
     <row r="1149" spans="1:2">
-      <c r="A1149" s="5" t="s">
+      <c r="A1149" t="s">
         <v>1266</v>
       </c>
       <c r="B1149" t="s">
@@ -15441,7 +15409,7 @@
       </c>
     </row>
     <row r="1150" spans="1:2">
-      <c r="A1150" s="5" t="s">
+      <c r="A1150" t="s">
         <v>1267</v>
       </c>
       <c r="B1150" t="s">
@@ -15449,7 +15417,7 @@
       </c>
     </row>
     <row r="1151" spans="1:2">
-      <c r="A1151" s="5" t="s">
+      <c r="A1151" t="s">
         <v>1268</v>
       </c>
       <c r="B1151" t="s">
@@ -15457,7 +15425,7 @@
       </c>
     </row>
     <row r="1152" spans="1:2">
-      <c r="A1152" s="5" t="s">
+      <c r="A1152" t="s">
         <v>1269</v>
       </c>
       <c r="B1152" t="s">
@@ -15465,7 +15433,7 @@
       </c>
     </row>
     <row r="1153" spans="1:2">
-      <c r="A1153" s="5" t="s">
+      <c r="A1153" t="s">
         <v>1270</v>
       </c>
       <c r="B1153" t="s">
@@ -15473,7 +15441,7 @@
       </c>
     </row>
     <row r="1154" spans="1:2">
-      <c r="A1154" s="5" t="s">
+      <c r="A1154" t="s">
         <v>1279</v>
       </c>
       <c r="B1154" t="s">
@@ -15481,7 +15449,7 @@
       </c>
     </row>
     <row r="1155" spans="1:2">
-      <c r="A1155" s="5" t="s">
+      <c r="A1155" t="s">
         <v>1280</v>
       </c>
       <c r="B1155" t="s">
@@ -15489,7 +15457,7 @@
       </c>
     </row>
     <row r="1156" spans="1:2">
-      <c r="A1156" s="5" t="s">
+      <c r="A1156" t="s">
         <v>1281</v>
       </c>
       <c r="B1156" t="s">
@@ -15497,7 +15465,7 @@
       </c>
     </row>
     <row r="1157" spans="1:2">
-      <c r="A1157" s="5" t="s">
+      <c r="A1157" t="s">
         <v>1282</v>
       </c>
       <c r="B1157" t="s">
@@ -15505,7 +15473,7 @@
       </c>
     </row>
     <row r="1158" spans="1:2">
-      <c r="A1158" s="5" t="s">
+      <c r="A1158" t="s">
         <v>1283</v>
       </c>
       <c r="B1158" t="s">
@@ -15513,7 +15481,7 @@
       </c>
     </row>
     <row r="1159" spans="1:2">
-      <c r="A1159" s="5" t="s">
+      <c r="A1159" t="s">
         <v>1284</v>
       </c>
       <c r="B1159" t="s">
@@ -15521,7 +15489,7 @@
       </c>
     </row>
     <row r="1160" spans="1:2">
-      <c r="A1160" s="5" t="s">
+      <c r="A1160" t="s">
         <v>1285</v>
       </c>
       <c r="B1160" t="s">
@@ -15529,7 +15497,7 @@
       </c>
     </row>
     <row r="1161" spans="1:2">
-      <c r="A1161" s="5" t="s">
+      <c r="A1161" t="s">
         <v>1286</v>
       </c>
       <c r="B1161" t="s">
@@ -15537,7 +15505,7 @@
       </c>
     </row>
     <row r="1162" spans="1:2">
-      <c r="A1162" s="5" t="s">
+      <c r="A1162" t="s">
         <v>1287</v>
       </c>
       <c r="B1162" t="s">
@@ -15545,7 +15513,7 @@
       </c>
     </row>
     <row r="1163" spans="1:2">
-      <c r="A1163" s="5" t="s">
+      <c r="A1163" t="s">
         <v>1288</v>
       </c>
       <c r="B1163" t="s">
@@ -15553,7 +15521,7 @@
       </c>
     </row>
     <row r="1164" spans="1:2">
-      <c r="A1164" s="5" t="s">
+      <c r="A1164" t="s">
         <v>1289</v>
       </c>
       <c r="B1164" t="s">
@@ -15561,7 +15529,7 @@
       </c>
     </row>
     <row r="1165" spans="1:2">
-      <c r="A1165" s="5" t="s">
+      <c r="A1165" t="s">
         <v>1290</v>
       </c>
       <c r="B1165" t="s">
@@ -15569,7 +15537,7 @@
       </c>
     </row>
     <row r="1166" spans="1:2">
-      <c r="A1166" s="5" t="s">
+      <c r="A1166" t="s">
         <v>1291</v>
       </c>
       <c r="B1166" t="s">
@@ -15577,7 +15545,7 @@
       </c>
     </row>
     <row r="1167" spans="1:2">
-      <c r="A1167" s="5" t="s">
+      <c r="A1167" t="s">
         <v>1292</v>
       </c>
       <c r="B1167" t="s">
@@ -15585,7 +15553,7 @@
       </c>
     </row>
     <row r="1168" spans="1:2">
-      <c r="A1168" s="5" t="s">
+      <c r="A1168" t="s">
         <v>1294</v>
       </c>
       <c r="B1168" t="s">
@@ -15593,7 +15561,7 @@
       </c>
     </row>
     <row r="1169" spans="1:2">
-      <c r="A1169" s="5" t="s">
+      <c r="A1169" t="s">
         <v>1295</v>
       </c>
       <c r="B1169" t="s">
@@ -15601,7 +15569,7 @@
       </c>
     </row>
     <row r="1170" spans="1:2">
-      <c r="A1170" s="5" t="s">
+      <c r="A1170" t="s">
         <v>1296</v>
       </c>
       <c r="B1170" t="s">
@@ -15609,7 +15577,7 @@
       </c>
     </row>
     <row r="1171" spans="1:2">
-      <c r="A1171" s="5" t="s">
+      <c r="A1171" t="s">
         <v>1297</v>
       </c>
       <c r="B1171" t="s">
@@ -15617,7 +15585,7 @@
       </c>
     </row>
     <row r="1172" spans="1:2">
-      <c r="A1172" s="5" t="s">
+      <c r="A1172" t="s">
         <v>1298</v>
       </c>
       <c r="B1172" t="s">
@@ -15625,7 +15593,7 @@
       </c>
     </row>
     <row r="1173" spans="1:2">
-      <c r="A1173" s="5" t="s">
+      <c r="A1173" t="s">
         <v>1299</v>
       </c>
       <c r="B1173" t="s">
@@ -15633,7 +15601,7 @@
       </c>
     </row>
     <row r="1174" spans="1:2">
-      <c r="A1174" s="5" t="s">
+      <c r="A1174" t="s">
         <v>1300</v>
       </c>
       <c r="B1174" t="s">
@@ -15641,7 +15609,7 @@
       </c>
     </row>
     <row r="1175" spans="1:2">
-      <c r="A1175" s="5" t="s">
+      <c r="A1175" t="s">
         <v>1301</v>
       </c>
       <c r="B1175" t="s">
@@ -15649,7 +15617,7 @@
       </c>
     </row>
     <row r="1176" spans="1:2">
-      <c r="A1176" s="5" t="s">
+      <c r="A1176" t="s">
         <v>1302</v>
       </c>
       <c r="B1176" t="s">
@@ -15657,7 +15625,7 @@
       </c>
     </row>
     <row r="1177" spans="1:2">
-      <c r="A1177" s="5" t="s">
+      <c r="A1177" t="s">
         <v>1303</v>
       </c>
       <c r="B1177" t="s">
@@ -15665,7 +15633,7 @@
       </c>
     </row>
     <row r="1178" spans="1:2">
-      <c r="A1178" s="5" t="s">
+      <c r="A1178" t="s">
         <v>1304</v>
       </c>
       <c r="B1178" t="s">
@@ -15673,7 +15641,7 @@
       </c>
     </row>
     <row r="1179" spans="1:2">
-      <c r="A1179" s="5" t="s">
+      <c r="A1179" t="s">
         <v>1305</v>
       </c>
       <c r="B1179" t="s">
@@ -15681,7 +15649,7 @@
       </c>
     </row>
     <row r="1180" spans="1:2">
-      <c r="A1180" s="5" t="s">
+      <c r="A1180" t="s">
         <v>1306</v>
       </c>
       <c r="B1180" t="s">
@@ -15689,7 +15657,7 @@
       </c>
     </row>
     <row r="1181" spans="1:2">
-      <c r="A1181" s="5" t="s">
+      <c r="A1181" t="s">
         <v>1307</v>
       </c>
       <c r="B1181" t="s">
@@ -15697,7 +15665,7 @@
       </c>
     </row>
     <row r="1182" spans="1:2">
-      <c r="A1182" s="5" t="s">
+      <c r="A1182" t="s">
         <v>1310</v>
       </c>
       <c r="B1182" t="s">
@@ -15705,7 +15673,7 @@
       </c>
     </row>
     <row r="1183" spans="1:2">
-      <c r="A1183" s="5" t="s">
+      <c r="A1183" t="s">
         <v>1311</v>
       </c>
       <c r="B1183" t="s">
@@ -15713,7 +15681,7 @@
       </c>
     </row>
     <row r="1184" spans="1:2">
-      <c r="A1184" s="5" t="s">
+      <c r="A1184" t="s">
         <v>1312</v>
       </c>
       <c r="B1184" t="s">
@@ -15721,7 +15689,7 @@
       </c>
     </row>
     <row r="1185" spans="1:2">
-      <c r="A1185" s="5" t="s">
+      <c r="A1185" t="s">
         <v>1313</v>
       </c>
       <c r="B1185" t="s">
@@ -15729,7 +15697,7 @@
       </c>
     </row>
     <row r="1186" spans="1:2">
-      <c r="A1186" s="5" t="s">
+      <c r="A1186" t="s">
         <v>1314</v>
       </c>
       <c r="B1186" t="s">
@@ -15745,7 +15713,7 @@
       </c>
     </row>
     <row r="1188" spans="1:2">
-      <c r="A1188" s="5" t="s">
+      <c r="A1188" t="s">
         <v>1317</v>
       </c>
       <c r="B1188" t="s">
@@ -15761,7 +15729,7 @@
       </c>
     </row>
     <row r="1190" spans="1:2">
-      <c r="A1190" s="5" t="s">
+      <c r="A1190" t="s">
         <v>1319</v>
       </c>
       <c r="B1190" t="s">
@@ -15769,7 +15737,7 @@
       </c>
     </row>
     <row r="1191" spans="1:2">
-      <c r="A1191" s="5" t="s">
+      <c r="A1191" t="s">
         <v>1320</v>
       </c>
       <c r="B1191" t="s">
@@ -15777,7 +15745,7 @@
       </c>
     </row>
     <row r="1192" spans="1:2">
-      <c r="A1192" s="5" t="s">
+      <c r="A1192" t="s">
         <v>1321</v>
       </c>
       <c r="B1192" t="s">
@@ -15785,7 +15753,7 @@
       </c>
     </row>
     <row r="1193" spans="1:2">
-      <c r="A1193" s="5" t="s">
+      <c r="A1193" t="s">
         <v>1322</v>
       </c>
       <c r="B1193" t="s">
@@ -15793,7 +15761,7 @@
       </c>
     </row>
     <row r="1194" spans="1:2">
-      <c r="A1194" s="5" t="s">
+      <c r="A1194" t="s">
         <v>1323</v>
       </c>
       <c r="B1194" t="s">
@@ -15801,7 +15769,7 @@
       </c>
     </row>
     <row r="1195" spans="1:2">
-      <c r="A1195" s="5" t="s">
+      <c r="A1195" t="s">
         <v>1324</v>
       </c>
       <c r="B1195" t="s">
@@ -15809,7 +15777,7 @@
       </c>
     </row>
     <row r="1196" spans="1:2">
-      <c r="A1196" s="5" t="s">
+      <c r="A1196" t="s">
         <v>1325</v>
       </c>
       <c r="B1196" t="s">
@@ -15817,7 +15785,7 @@
       </c>
     </row>
     <row r="1197" spans="1:2">
-      <c r="A1197" s="5" t="s">
+      <c r="A1197" t="s">
         <v>1326</v>
       </c>
       <c r="B1197" t="s">
@@ -15825,7 +15793,7 @@
       </c>
     </row>
     <row r="1198" spans="1:2">
-      <c r="A1198" s="5" t="s">
+      <c r="A1198" t="s">
         <v>1327</v>
       </c>
       <c r="B1198" t="s">
@@ -15833,7 +15801,7 @@
       </c>
     </row>
     <row r="1199" spans="1:2">
-      <c r="A1199" s="5" t="s">
+      <c r="A1199" t="s">
         <v>1328</v>
       </c>
       <c r="B1199" t="s">
@@ -15841,7 +15809,7 @@
       </c>
     </row>
     <row r="1200" spans="1:2">
-      <c r="A1200" s="5" t="s">
+      <c r="A1200" t="s">
         <v>1329</v>
       </c>
       <c r="B1200" t="s">
@@ -15849,7 +15817,7 @@
       </c>
     </row>
     <row r="1201" spans="1:2">
-      <c r="A1201" s="5" t="s">
+      <c r="A1201" t="s">
         <v>1330</v>
       </c>
       <c r="B1201" t="s">
@@ -15857,7 +15825,7 @@
       </c>
     </row>
     <row r="1202" spans="1:2">
-      <c r="A1202" s="5" t="s">
+      <c r="A1202" t="s">
         <v>1331</v>
       </c>
       <c r="B1202" t="s">
@@ -15865,7 +15833,7 @@
       </c>
     </row>
     <row r="1203" spans="1:2">
-      <c r="A1203" s="5" t="s">
+      <c r="A1203" t="s">
         <v>1332</v>
       </c>
       <c r="B1203" t="s">
@@ -15873,7 +15841,7 @@
       </c>
     </row>
     <row r="1204" spans="1:2">
-      <c r="A1204" s="5" t="s">
+      <c r="A1204" t="s">
         <v>1333</v>
       </c>
       <c r="B1204" t="s">
@@ -15881,7 +15849,7 @@
       </c>
     </row>
     <row r="1205" spans="1:2">
-      <c r="A1205" s="5" t="s">
+      <c r="A1205" t="s">
         <v>1334</v>
       </c>
       <c r="B1205" t="s">
@@ -15889,7 +15857,7 @@
       </c>
     </row>
     <row r="1206" spans="1:2">
-      <c r="A1206" s="5" t="s">
+      <c r="A1206" t="s">
         <v>1335</v>
       </c>
       <c r="B1206" t="s">
@@ -15897,7 +15865,7 @@
       </c>
     </row>
     <row r="1207" spans="1:2">
-      <c r="A1207" s="5" t="s">
+      <c r="A1207" t="s">
         <v>1336</v>
       </c>
       <c r="B1207" t="s">
@@ -15905,7 +15873,7 @@
       </c>
     </row>
     <row r="1208" spans="1:2">
-      <c r="A1208" s="5" t="s">
+      <c r="A1208" t="s">
         <v>1337</v>
       </c>
       <c r="B1208" t="s">
@@ -15913,7 +15881,7 @@
       </c>
     </row>
     <row r="1209" spans="1:2">
-      <c r="A1209" s="5" t="s">
+      <c r="A1209" t="s">
         <v>1338</v>
       </c>
       <c r="B1209" t="s">
@@ -15921,7 +15889,7 @@
       </c>
     </row>
     <row r="1210" spans="1:2">
-      <c r="A1210" s="5" t="s">
+      <c r="A1210" t="s">
         <v>1339</v>
       </c>
       <c r="B1210" t="s">
@@ -15929,7 +15897,7 @@
       </c>
     </row>
     <row r="1211" spans="1:2">
-      <c r="A1211" s="5" t="s">
+      <c r="A1211" t="s">
         <v>1340</v>
       </c>
       <c r="B1211" t="s">
@@ -15937,7 +15905,7 @@
       </c>
     </row>
     <row r="1212" spans="1:2">
-      <c r="A1212" s="5" t="s">
+      <c r="A1212" t="s">
         <v>1341</v>
       </c>
       <c r="B1212" t="s">
@@ -15950,7 +15918,7 @@
       </c>
     </row>
     <row r="1216" spans="1:2">
-      <c r="A1216" s="5" t="s">
+      <c r="A1216" t="s">
         <v>1344</v>
       </c>
       <c r="B1216" t="s">
@@ -15958,7 +15926,7 @@
       </c>
     </row>
     <row r="1217" spans="1:2">
-      <c r="A1217" s="5" t="s">
+      <c r="A1217" t="s">
         <v>1345</v>
       </c>
       <c r="B1217" t="s">
@@ -15966,7 +15934,7 @@
       </c>
     </row>
     <row r="1218" spans="1:2">
-      <c r="A1218" s="5" t="s">
+      <c r="A1218" t="s">
         <v>1346</v>
       </c>
       <c r="B1218" t="s">
@@ -15974,7 +15942,7 @@
       </c>
     </row>
     <row r="1219" spans="1:2">
-      <c r="A1219" s="5" t="s">
+      <c r="A1219" t="s">
         <v>1347</v>
       </c>
       <c r="B1219" t="s">
@@ -15982,7 +15950,7 @@
       </c>
     </row>
     <row r="1220" spans="1:2">
-      <c r="A1220" s="5" t="s">
+      <c r="A1220" t="s">
         <v>1348</v>
       </c>
       <c r="B1220" t="s">
@@ -15990,7 +15958,7 @@
       </c>
     </row>
     <row r="1221" spans="1:2">
-      <c r="A1221" s="5" t="s">
+      <c r="A1221" t="s">
         <v>1349</v>
       </c>
       <c r="B1221" t="s">
@@ -15998,7 +15966,7 @@
       </c>
     </row>
     <row r="1222" spans="1:2">
-      <c r="A1222" s="5" t="s">
+      <c r="A1222" t="s">
         <v>1350</v>
       </c>
       <c r="B1222" t="s">
@@ -16014,7 +15982,7 @@
       </c>
     </row>
     <row r="1224" spans="1:2">
-      <c r="A1224" s="5" t="s">
+      <c r="A1224" t="s">
         <v>1352</v>
       </c>
       <c r="B1224" t="s">
@@ -16022,7 +15990,7 @@
       </c>
     </row>
     <row r="1225" spans="1:2">
-      <c r="A1225" s="5" t="s">
+      <c r="A1225" t="s">
         <v>1353</v>
       </c>
       <c r="B1225" t="s">
@@ -16030,7 +15998,7 @@
       </c>
     </row>
     <row r="1226" spans="1:2">
-      <c r="A1226" s="5" t="s">
+      <c r="A1226" t="s">
         <v>1354</v>
       </c>
       <c r="B1226" t="s">
@@ -16038,7 +16006,7 @@
       </c>
     </row>
     <row r="1227" spans="1:2">
-      <c r="A1227" s="5" t="s">
+      <c r="A1227" t="s">
         <v>1355</v>
       </c>
       <c r="B1227" t="s">
@@ -16046,7 +16014,7 @@
       </c>
     </row>
     <row r="1228" spans="1:2">
-      <c r="A1228" s="5" t="s">
+      <c r="A1228" t="s">
         <v>1356</v>
       </c>
       <c r="B1228" t="s">
@@ -16054,7 +16022,7 @@
       </c>
     </row>
     <row r="1229" spans="1:2">
-      <c r="A1229" s="5" t="s">
+      <c r="A1229" t="s">
         <v>1357</v>
       </c>
       <c r="B1229" t="s">
@@ -16062,7 +16030,7 @@
       </c>
     </row>
     <row r="1230" spans="1:2">
-      <c r="A1230" s="5" t="s">
+      <c r="A1230" t="s">
         <v>1358</v>
       </c>
       <c r="B1230" t="s">
@@ -16070,7 +16038,7 @@
       </c>
     </row>
     <row r="1231" spans="1:2">
-      <c r="A1231" s="5" t="s">
+      <c r="A1231" t="s">
         <v>1359</v>
       </c>
       <c r="B1231" t="s">
@@ -16078,7 +16046,7 @@
       </c>
     </row>
     <row r="1232" spans="1:2">
-      <c r="A1232" s="5" t="s">
+      <c r="A1232" t="s">
         <v>1360</v>
       </c>
       <c r="B1232" t="s">
@@ -16086,7 +16054,7 @@
       </c>
     </row>
     <row r="1233" spans="1:2">
-      <c r="A1233" s="5" t="s">
+      <c r="A1233" t="s">
         <v>1361</v>
       </c>
       <c r="B1233" t="s">
@@ -16094,7 +16062,7 @@
       </c>
     </row>
     <row r="1234" spans="1:2">
-      <c r="A1234" s="5" t="s">
+      <c r="A1234" t="s">
         <v>1362</v>
       </c>
       <c r="B1234" t="s">
@@ -16102,7 +16070,7 @@
       </c>
     </row>
     <row r="1235" spans="1:2">
-      <c r="A1235" s="5" t="s">
+      <c r="A1235" t="s">
         <v>1363</v>
       </c>
       <c r="B1235" t="s">
@@ -16110,7 +16078,7 @@
       </c>
     </row>
     <row r="1236" spans="1:2">
-      <c r="A1236" s="5" t="s">
+      <c r="A1236" t="s">
         <v>1364</v>
       </c>
       <c r="B1236" t="s">
@@ -16118,7 +16086,7 @@
       </c>
     </row>
     <row r="1237" spans="1:2">
-      <c r="A1237" s="5" t="s">
+      <c r="A1237" t="s">
         <v>1365</v>
       </c>
       <c r="B1237" t="s">
@@ -16126,7 +16094,7 @@
       </c>
     </row>
     <row r="1238" spans="1:2">
-      <c r="A1238" s="5" t="s">
+      <c r="A1238" t="s">
         <v>1366</v>
       </c>
       <c r="B1238" t="s">
@@ -16142,7 +16110,7 @@
       </c>
     </row>
     <row r="1240" spans="1:2">
-      <c r="A1240" s="5" t="s">
+      <c r="A1240" t="s">
         <v>1368</v>
       </c>
       <c r="B1240" t="s">
@@ -16150,7 +16118,7 @@
       </c>
     </row>
     <row r="1241" spans="1:2">
-      <c r="A1241" s="5" t="s">
+      <c r="A1241" t="s">
         <v>1369</v>
       </c>
       <c r="B1241" t="s">
@@ -16158,7 +16126,7 @@
       </c>
     </row>
     <row r="1242" spans="1:2">
-      <c r="A1242" s="5" t="s">
+      <c r="A1242" t="s">
         <v>1370</v>
       </c>
       <c r="B1242" t="s">
@@ -16166,7 +16134,7 @@
       </c>
     </row>
     <row r="1243" spans="1:2">
-      <c r="A1243" s="5" t="s">
+      <c r="A1243" t="s">
         <v>1371</v>
       </c>
       <c r="B1243" t="s">
@@ -16174,7 +16142,7 @@
       </c>
     </row>
     <row r="1244" spans="1:2">
-      <c r="A1244" s="5" t="s">
+      <c r="A1244" t="s">
         <v>1372</v>
       </c>
       <c r="B1244" t="s">
@@ -16182,7 +16150,7 @@
       </c>
     </row>
     <row r="1245" spans="1:2">
-      <c r="A1245" s="5" t="s">
+      <c r="A1245" t="s">
         <v>1373</v>
       </c>
       <c r="B1245" t="s">
@@ -16190,7 +16158,7 @@
       </c>
     </row>
     <row r="1246" spans="1:2">
-      <c r="A1246" s="5" t="s">
+      <c r="A1246" t="s">
         <v>1374</v>
       </c>
       <c r="B1246" t="s">
@@ -16198,7 +16166,7 @@
       </c>
     </row>
     <row r="1247" spans="1:2">
-      <c r="A1247" s="5" t="s">
+      <c r="A1247" t="s">
         <v>1378</v>
       </c>
       <c r="B1247" t="s">
@@ -16206,7 +16174,7 @@
       </c>
     </row>
     <row r="1248" spans="1:2">
-      <c r="A1248" s="5" t="s">
+      <c r="A1248" t="s">
         <v>1379</v>
       </c>
       <c r="B1248" t="s">
@@ -16214,7 +16182,7 @@
       </c>
     </row>
     <row r="1249" spans="1:2">
-      <c r="A1249" s="5" t="s">
+      <c r="A1249" t="s">
         <v>1380</v>
       </c>
       <c r="B1249" t="s">
@@ -16222,7 +16190,7 @@
       </c>
     </row>
     <row r="1250" spans="1:2">
-      <c r="A1250" s="5" t="s">
+      <c r="A1250" t="s">
         <v>1381</v>
       </c>
       <c r="B1250" t="s">
@@ -16230,7 +16198,7 @@
       </c>
     </row>
     <row r="1251" spans="1:2">
-      <c r="A1251" s="5" t="s">
+      <c r="A1251" t="s">
         <v>1382</v>
       </c>
       <c r="B1251" t="s">
@@ -16238,7 +16206,7 @@
       </c>
     </row>
     <row r="1252" spans="1:2">
-      <c r="A1252" s="5" t="s">
+      <c r="A1252" t="s">
         <v>1383</v>
       </c>
       <c r="B1252" t="s">
@@ -16246,7 +16214,7 @@
       </c>
     </row>
     <row r="1253" spans="1:2">
-      <c r="A1253" s="5" t="s">
+      <c r="A1253" t="s">
         <v>1384</v>
       </c>
       <c r="B1253" t="s">
@@ -16254,7 +16222,7 @@
       </c>
     </row>
     <row r="1254" spans="1:2">
-      <c r="A1254" s="5" t="s">
+      <c r="A1254" t="s">
         <v>1385</v>
       </c>
       <c r="B1254" t="s">
@@ -16270,7 +16238,7 @@
       </c>
     </row>
     <row r="1256" spans="1:2">
-      <c r="A1256" s="5" t="s">
+      <c r="A1256" t="s">
         <v>1387</v>
       </c>
       <c r="B1256" t="s">
@@ -16278,7 +16246,7 @@
       </c>
     </row>
     <row r="1257" spans="1:2">
-      <c r="A1257" s="5" t="s">
+      <c r="A1257" t="s">
         <v>1388</v>
       </c>
       <c r="B1257" t="s">
@@ -16286,7 +16254,7 @@
       </c>
     </row>
     <row r="1258" spans="1:2">
-      <c r="A1258" s="5" t="s">
+      <c r="A1258" t="s">
         <v>1389</v>
       </c>
       <c r="B1258" t="s">
@@ -16294,7 +16262,7 @@
       </c>
     </row>
     <row r="1259" spans="1:2">
-      <c r="A1259" s="5" t="s">
+      <c r="A1259" t="s">
         <v>1390</v>
       </c>
       <c r="B1259" t="s">
@@ -16302,7 +16270,7 @@
       </c>
     </row>
     <row r="1260" spans="1:2">
-      <c r="A1260" s="5" t="s">
+      <c r="A1260" t="s">
         <v>1391</v>
       </c>
       <c r="B1260" t="s">
@@ -16310,7 +16278,7 @@
       </c>
     </row>
     <row r="1261" spans="1:2">
-      <c r="A1261" s="5" t="s">
+      <c r="A1261" t="s">
         <v>1392</v>
       </c>
       <c r="B1261" t="s">
@@ -16318,7 +16286,7 @@
       </c>
     </row>
     <row r="1262" spans="1:2">
-      <c r="A1262" s="5" t="s">
+      <c r="A1262" t="s">
         <v>1393</v>
       </c>
       <c r="B1262" t="s">
@@ -16326,7 +16294,7 @@
       </c>
     </row>
     <row r="1263" spans="1:2">
-      <c r="A1263" s="5" t="s">
+      <c r="A1263" t="s">
         <v>1394</v>
       </c>
       <c r="B1263" t="s">
@@ -16334,7 +16302,7 @@
       </c>
     </row>
     <row r="1264" spans="1:2">
-      <c r="A1264" s="5" t="s">
+      <c r="A1264" t="s">
         <v>1395</v>
       </c>
       <c r="B1264" t="s">
@@ -16342,7 +16310,7 @@
       </c>
     </row>
     <row r="1265" spans="1:2">
-      <c r="A1265" s="5" t="s">
+      <c r="A1265" t="s">
         <v>1396</v>
       </c>
       <c r="B1265" t="s">
@@ -16350,7 +16318,7 @@
       </c>
     </row>
     <row r="1266" spans="1:2">
-      <c r="A1266" s="5" t="s">
+      <c r="A1266" t="s">
         <v>1397</v>
       </c>
       <c r="B1266" t="s">
@@ -16358,7 +16326,7 @@
       </c>
     </row>
     <row r="1267" spans="1:2">
-      <c r="A1267" s="5" t="s">
+      <c r="A1267" t="s">
         <v>1401</v>
       </c>
       <c r="B1267" t="s">
@@ -16366,7 +16334,7 @@
       </c>
     </row>
     <row r="1268" spans="1:2">
-      <c r="A1268" s="5" t="s">
+      <c r="A1268" t="s">
         <v>1402</v>
       </c>
       <c r="B1268" t="s">
@@ -16374,7 +16342,7 @@
       </c>
     </row>
     <row r="1269" spans="1:2">
-      <c r="A1269" s="6" t="s">
+      <c r="A1269" t="s">
         <v>1403</v>
       </c>
       <c r="B1269" t="s">
@@ -16382,7 +16350,7 @@
       </c>
     </row>
     <row r="1270" spans="1:2">
-      <c r="A1270" s="5" t="s">
+      <c r="A1270" t="s">
         <v>1404</v>
       </c>
       <c r="B1270" t="s">
@@ -16390,7 +16358,7 @@
       </c>
     </row>
     <row r="1271" spans="1:2">
-      <c r="A1271" s="5" t="s">
+      <c r="A1271" t="s">
         <v>1405</v>
       </c>
       <c r="B1271" t="s">
@@ -16398,7 +16366,7 @@
       </c>
     </row>
     <row r="1272" spans="1:2">
-      <c r="A1272" s="5" t="s">
+      <c r="A1272" t="s">
         <v>1406</v>
       </c>
       <c r="B1272" t="s">
@@ -16406,7 +16374,7 @@
       </c>
     </row>
     <row r="1273" spans="1:2">
-      <c r="A1273" s="5" t="s">
+      <c r="A1273" t="s">
         <v>1407</v>
       </c>
       <c r="B1273" t="s">
@@ -16414,7 +16382,7 @@
       </c>
     </row>
     <row r="1274" spans="1:2">
-      <c r="A1274" s="5" t="s">
+      <c r="A1274" t="s">
         <v>1408</v>
       </c>
       <c r="B1274" t="s">
@@ -16422,7 +16390,7 @@
       </c>
     </row>
     <row r="1275" spans="1:2">
-      <c r="A1275" s="5" t="s">
+      <c r="A1275" t="s">
         <v>1409</v>
       </c>
       <c r="B1275" t="s">
@@ -16430,7 +16398,7 @@
       </c>
     </row>
     <row r="1276" spans="1:2">
-      <c r="A1276" s="5" t="s">
+      <c r="A1276" t="s">
         <v>1410</v>
       </c>
       <c r="B1276" t="s">
@@ -16438,7 +16406,7 @@
       </c>
     </row>
     <row r="1277" spans="1:2">
-      <c r="A1277" s="5" t="s">
+      <c r="A1277" t="s">
         <v>1411</v>
       </c>
       <c r="B1277" t="s">
@@ -16446,7 +16414,7 @@
       </c>
     </row>
     <row r="1278" spans="1:2">
-      <c r="A1278" s="5" t="s">
+      <c r="A1278" t="s">
         <v>1412</v>
       </c>
       <c r="B1278" t="s">
@@ -16454,7 +16422,7 @@
       </c>
     </row>
     <row r="1279" spans="1:2">
-      <c r="A1279" s="5" t="s">
+      <c r="A1279" t="s">
         <v>1413</v>
       </c>
       <c r="B1279" t="s">
@@ -16462,7 +16430,7 @@
       </c>
     </row>
     <row r="1280" spans="1:2">
-      <c r="A1280" s="5" t="s">
+      <c r="A1280" t="s">
         <v>1414</v>
       </c>
       <c r="B1280" t="s">
@@ -16470,7 +16438,7 @@
       </c>
     </row>
     <row r="1281" spans="1:2">
-      <c r="A1281" s="5" t="s">
+      <c r="A1281" t="s">
         <v>1415</v>
       </c>
       <c r="B1281" t="s">
@@ -16478,7 +16446,7 @@
       </c>
     </row>
     <row r="1282" spans="1:2">
-      <c r="A1282" s="5" t="s">
+      <c r="A1282" t="s">
         <v>1416</v>
       </c>
       <c r="B1282" t="s">
@@ -16486,7 +16454,7 @@
       </c>
     </row>
     <row r="1283" spans="1:2">
-      <c r="A1283" s="5" t="s">
+      <c r="A1283" t="s">
         <v>1417</v>
       </c>
       <c r="B1283" t="s">
@@ -16502,7 +16470,7 @@
       </c>
     </row>
     <row r="1285" spans="1:2">
-      <c r="A1285" s="5" t="s">
+      <c r="A1285" t="s">
         <v>1419</v>
       </c>
       <c r="B1285" t="s">
@@ -16510,7 +16478,7 @@
       </c>
     </row>
     <row r="1286" spans="1:2">
-      <c r="A1286" s="5" t="s">
+      <c r="A1286" t="s">
         <v>1420</v>
       </c>
       <c r="B1286" t="s">
@@ -16518,7 +16486,7 @@
       </c>
     </row>
     <row r="1287" spans="1:2">
-      <c r="A1287" s="5" t="s">
+      <c r="A1287" t="s">
         <v>1421</v>
       </c>
       <c r="B1287" t="s">
@@ -16526,7 +16494,7 @@
       </c>
     </row>
     <row r="1288" spans="1:2">
-      <c r="A1288" s="5" t="s">
+      <c r="A1288" t="s">
         <v>1422</v>
       </c>
       <c r="B1288" t="s">
@@ -16534,7 +16502,7 @@
       </c>
     </row>
     <row r="1289" spans="1:2">
-      <c r="A1289" s="5" t="s">
+      <c r="A1289" t="s">
         <v>1423</v>
       </c>
       <c r="B1289" t="s">
@@ -16542,7 +16510,7 @@
       </c>
     </row>
     <row r="1290" spans="1:2">
-      <c r="A1290" s="5" t="s">
+      <c r="A1290" t="s">
         <v>1424</v>
       </c>
       <c r="B1290" t="s">
@@ -16550,7 +16518,7 @@
       </c>
     </row>
     <row r="1291" spans="1:2">
-      <c r="A1291" s="5" t="s">
+      <c r="A1291" t="s">
         <v>1425</v>
       </c>
       <c r="B1291" t="s">
@@ -16558,7 +16526,7 @@
       </c>
     </row>
     <row r="1292" spans="1:2">
-      <c r="A1292" s="5" t="s">
+      <c r="A1292" t="s">
         <v>1426</v>
       </c>
       <c r="B1292" t="s">
@@ -16566,7 +16534,7 @@
       </c>
     </row>
     <row r="1293" spans="1:2">
-      <c r="A1293" s="5" t="s">
+      <c r="A1293" t="s">
         <v>1427</v>
       </c>
       <c r="B1293" t="s">
@@ -16574,7 +16542,7 @@
       </c>
     </row>
     <row r="1294" spans="1:2">
-      <c r="A1294" s="5" t="s">
+      <c r="A1294" t="s">
         <v>1428</v>
       </c>
       <c r="B1294" t="s">
@@ -16582,7 +16550,7 @@
       </c>
     </row>
     <row r="1295" spans="1:2">
-      <c r="A1295" s="5" t="s">
+      <c r="A1295" t="s">
         <v>1429</v>
       </c>
       <c r="B1295" t="s">
@@ -16590,7 +16558,7 @@
       </c>
     </row>
     <row r="1296" spans="1:2">
-      <c r="A1296" s="5" t="s">
+      <c r="A1296" t="s">
         <v>1430</v>
       </c>
       <c r="B1296" t="s">
@@ -16598,7 +16566,7 @@
       </c>
     </row>
     <row r="1297" spans="1:2">
-      <c r="A1297" s="5" t="s">
+      <c r="A1297" t="s">
         <v>1431</v>
       </c>
       <c r="B1297" t="s">
@@ -16606,7 +16574,7 @@
       </c>
     </row>
     <row r="1298" spans="1:2">
-      <c r="A1298" s="5" t="s">
+      <c r="A1298" t="s">
         <v>1432</v>
       </c>
       <c r="B1298" t="s">
@@ -16614,7 +16582,7 @@
       </c>
     </row>
     <row r="1299" spans="1:2">
-      <c r="A1299" s="5" t="s">
+      <c r="A1299" t="s">
         <v>1433</v>
       </c>
       <c r="B1299" t="s">
@@ -16622,7 +16590,7 @@
       </c>
     </row>
     <row r="1300" spans="1:2">
-      <c r="A1300" s="5" t="s">
+      <c r="A1300" t="s">
         <v>1434</v>
       </c>
       <c r="B1300" t="s">
@@ -16630,7 +16598,7 @@
       </c>
     </row>
     <row r="1301" spans="1:2">
-      <c r="A1301" s="5" t="s">
+      <c r="A1301" t="s">
         <v>1435</v>
       </c>
       <c r="B1301" t="s">
@@ -16638,7 +16606,7 @@
       </c>
     </row>
     <row r="1302" spans="1:2">
-      <c r="A1302" s="5" t="s">
+      <c r="A1302" t="s">
         <v>1436</v>
       </c>
       <c r="B1302" t="s">
@@ -16646,7 +16614,7 @@
       </c>
     </row>
     <row r="1303" spans="1:2">
-      <c r="A1303" s="5" t="s">
+      <c r="A1303" t="s">
         <v>1439</v>
       </c>
       <c r="B1303" t="s">
@@ -16654,7 +16622,7 @@
       </c>
     </row>
     <row r="1304" spans="1:2">
-      <c r="A1304" s="5" t="s">
+      <c r="A1304" t="s">
         <v>1441</v>
       </c>
       <c r="B1304" t="s">
@@ -16662,7 +16630,7 @@
       </c>
     </row>
     <row r="1305" spans="1:2">
-      <c r="A1305" s="5" t="s">
+      <c r="A1305" t="s">
         <v>1442</v>
       </c>
       <c r="B1305" t="s">
@@ -16670,7 +16638,7 @@
       </c>
     </row>
     <row r="1306" spans="1:2">
-      <c r="A1306" s="5" t="s">
+      <c r="A1306" t="s">
         <v>1443</v>
       </c>
       <c r="B1306" t="s">
@@ -16678,7 +16646,7 @@
       </c>
     </row>
     <row r="1307" spans="1:2">
-      <c r="A1307" s="5" t="s">
+      <c r="A1307" t="s">
         <v>1444</v>
       </c>
       <c r="B1307" t="s">
@@ -16686,7 +16654,7 @@
       </c>
     </row>
     <row r="1308" spans="1:2">
-      <c r="A1308" s="5" t="s">
+      <c r="A1308" t="s">
         <v>1445</v>
       </c>
       <c r="B1308" t="s">
@@ -16694,7 +16662,7 @@
       </c>
     </row>
     <row r="1309" spans="1:2">
-      <c r="A1309" s="5" t="s">
+      <c r="A1309" t="s">
         <v>1446</v>
       </c>
       <c r="B1309" t="s">
@@ -16702,7 +16670,7 @@
       </c>
     </row>
     <row r="1310" spans="1:2">
-      <c r="A1310" s="5" t="s">
+      <c r="A1310" t="s">
         <v>1447</v>
       </c>
       <c r="B1310" t="s">
@@ -16710,7 +16678,7 @@
       </c>
     </row>
     <row r="1311" spans="1:2">
-      <c r="A1311" s="5" t="s">
+      <c r="A1311" t="s">
         <v>1448</v>
       </c>
       <c r="B1311" t="s">
@@ -16718,7 +16686,7 @@
       </c>
     </row>
     <row r="1312" spans="1:2">
-      <c r="A1312" s="5" t="s">
+      <c r="A1312" t="s">
         <v>1449</v>
       </c>
       <c r="B1312" t="s">
@@ -16726,7 +16694,7 @@
       </c>
     </row>
     <row r="1313" spans="1:2">
-      <c r="A1313" s="5" t="s">
+      <c r="A1313" t="s">
         <v>1450</v>
       </c>
       <c r="B1313" t="s">
@@ -16734,7 +16702,7 @@
       </c>
     </row>
     <row r="1314" spans="1:2">
-      <c r="A1314" s="5" t="s">
+      <c r="A1314" t="s">
         <v>1451</v>
       </c>
       <c r="B1314" t="s">
@@ -16742,7 +16710,7 @@
       </c>
     </row>
     <row r="1315" spans="1:2">
-      <c r="A1315" s="5" t="s">
+      <c r="A1315" t="s">
         <v>1452</v>
       </c>
       <c r="B1315" t="s">
@@ -16750,7 +16718,7 @@
       </c>
     </row>
     <row r="1316" spans="1:2">
-      <c r="A1316" s="5" t="s">
+      <c r="A1316" t="s">
         <v>1453</v>
       </c>
       <c r="B1316" t="s">
@@ -16758,7 +16726,7 @@
       </c>
     </row>
     <row r="1317" spans="1:2">
-      <c r="A1317" s="5" t="s">
+      <c r="A1317" t="s">
         <v>1454</v>
       </c>
       <c r="B1317" t="s">
@@ -16774,7 +16742,7 @@
       </c>
     </row>
     <row r="1319" spans="1:2">
-      <c r="A1319" s="5" t="s">
+      <c r="A1319" t="s">
         <v>1456</v>
       </c>
       <c r="B1319" t="s">
@@ -16782,7 +16750,7 @@
       </c>
     </row>
     <row r="1320" spans="1:2">
-      <c r="A1320" s="5" t="s">
+      <c r="A1320" t="s">
         <v>1457</v>
       </c>
       <c r="B1320" t="s">
@@ -16790,7 +16758,7 @@
       </c>
     </row>
     <row r="1321" spans="1:2">
-      <c r="A1321" s="5" t="s">
+      <c r="A1321" t="s">
         <v>1458</v>
       </c>
       <c r="B1321" t="s">
@@ -16798,7 +16766,7 @@
       </c>
     </row>
     <row r="1322" spans="1:2">
-      <c r="A1322" s="5" t="s">
+      <c r="A1322" t="s">
         <v>1459</v>
       </c>
       <c r="B1322" t="s">
@@ -16806,7 +16774,7 @@
       </c>
     </row>
     <row r="1323" spans="1:2">
-      <c r="A1323" s="5" t="s">
+      <c r="A1323" t="s">
         <v>1460</v>
       </c>
       <c r="B1323" t="s">
@@ -16814,7 +16782,7 @@
       </c>
     </row>
     <row r="1324" spans="1:2">
-      <c r="A1324" s="5" t="s">
+      <c r="A1324" t="s">
         <v>1461</v>
       </c>
       <c r="B1324" t="s">
@@ -16822,7 +16790,7 @@
       </c>
     </row>
     <row r="1325" spans="1:2">
-      <c r="A1325" s="5" t="s">
+      <c r="A1325" t="s">
         <v>1463</v>
       </c>
       <c r="B1325" t="s">
@@ -16830,7 +16798,7 @@
       </c>
     </row>
     <row r="1326" spans="1:2">
-      <c r="A1326" s="5" t="s">
+      <c r="A1326" t="s">
         <v>1464</v>
       </c>
       <c r="B1326" t="s">
@@ -16838,7 +16806,7 @@
       </c>
     </row>
     <row r="1327" spans="1:2">
-      <c r="A1327" s="5" t="s">
+      <c r="A1327" t="s">
         <v>1465</v>
       </c>
       <c r="B1327" t="s">
@@ -16846,7 +16814,7 @@
       </c>
     </row>
     <row r="1328" spans="1:2">
-      <c r="A1328" s="5" t="s">
+      <c r="A1328" t="s">
         <v>1466</v>
       </c>
       <c r="B1328" t="s">
@@ -16854,7 +16822,7 @@
       </c>
     </row>
     <row r="1329" spans="1:2">
-      <c r="A1329" s="5" t="s">
+      <c r="A1329" t="s">
         <v>1467</v>
       </c>
       <c r="B1329" t="s">
@@ -16862,7 +16830,7 @@
       </c>
     </row>
     <row r="1330" spans="1:2">
-      <c r="A1330" s="5" t="s">
+      <c r="A1330" t="s">
         <v>1468</v>
       </c>
       <c r="B1330" t="s">
@@ -16870,7 +16838,7 @@
       </c>
     </row>
     <row r="1331" spans="1:2">
-      <c r="A1331" s="5" t="s">
+      <c r="A1331" t="s">
         <v>1469</v>
       </c>
       <c r="B1331" t="s">
@@ -16878,7 +16846,7 @@
       </c>
     </row>
     <row r="1332" spans="1:2">
-      <c r="A1332" s="5" t="s">
+      <c r="A1332" t="s">
         <v>1470</v>
       </c>
       <c r="B1332" t="s">
@@ -16886,7 +16854,7 @@
       </c>
     </row>
     <row r="1333" spans="1:2">
-      <c r="A1333" s="5" t="s">
+      <c r="A1333" t="s">
         <v>1471</v>
       </c>
       <c r="B1333" t="s">
@@ -16894,7 +16862,7 @@
       </c>
     </row>
     <row r="1334" spans="1:2">
-      <c r="A1334" s="5" t="s">
+      <c r="A1334" t="s">
         <v>1472</v>
       </c>
       <c r="B1334" t="s">
@@ -16902,7 +16870,7 @@
       </c>
     </row>
     <row r="1335" spans="1:2">
-      <c r="A1335" s="5" t="s">
+      <c r="A1335" t="s">
         <v>1473</v>
       </c>
       <c r="B1335" t="s">
@@ -16910,7 +16878,7 @@
       </c>
     </row>
     <row r="1336" spans="1:2">
-      <c r="A1336" s="5" t="s">
+      <c r="A1336" t="s">
         <v>1474</v>
       </c>
       <c r="B1336" t="s">
@@ -16918,7 +16886,7 @@
       </c>
     </row>
     <row r="1337" spans="1:2">
-      <c r="A1337" s="5" t="s">
+      <c r="A1337" t="s">
         <v>1475</v>
       </c>
       <c r="B1337" t="s">
@@ -16926,7 +16894,7 @@
       </c>
     </row>
     <row r="1338" spans="1:2">
-      <c r="A1338" s="5" t="s">
+      <c r="A1338" t="s">
         <v>1476</v>
       </c>
       <c r="B1338" t="s">
@@ -16934,7 +16902,7 @@
       </c>
     </row>
     <row r="1339" spans="1:2">
-      <c r="A1339" s="5" t="s">
+      <c r="A1339" t="s">
         <v>1477</v>
       </c>
       <c r="B1339" t="s">
@@ -16942,7 +16910,7 @@
       </c>
     </row>
     <row r="1340" spans="1:2">
-      <c r="A1340" s="5" t="s">
+      <c r="A1340" t="s">
         <v>1478</v>
       </c>
       <c r="B1340" t="s">
@@ -16950,7 +16918,7 @@
       </c>
     </row>
     <row r="1341" spans="1:2">
-      <c r="A1341" s="5" t="s">
+      <c r="A1341" t="s">
         <v>1479</v>
       </c>
       <c r="B1341" t="s">
@@ -16958,7 +16926,7 @@
       </c>
     </row>
     <row r="1342" spans="1:2">
-      <c r="A1342" s="5" t="s">
+      <c r="A1342" t="s">
         <v>1480</v>
       </c>
       <c r="B1342" t="s">
@@ -16966,7 +16934,7 @@
       </c>
     </row>
     <row r="1343" spans="1:2">
-      <c r="A1343" s="5" t="s">
+      <c r="A1343" t="s">
         <v>1481</v>
       </c>
       <c r="B1343" t="s">
@@ -16974,7 +16942,7 @@
       </c>
     </row>
     <row r="1344" spans="1:2">
-      <c r="A1344" s="5" t="s">
+      <c r="A1344" t="s">
         <v>1482</v>
       </c>
       <c r="B1344" t="s">
@@ -16982,7 +16950,7 @@
       </c>
     </row>
     <row r="1345" spans="1:2">
-      <c r="A1345" s="5" t="s">
+      <c r="A1345" t="s">
         <v>1483</v>
       </c>
       <c r="B1345" t="s">
@@ -16990,7 +16958,7 @@
       </c>
     </row>
     <row r="1346" spans="1:2">
-      <c r="A1346" s="5" t="s">
+      <c r="A1346" t="s">
         <v>1484</v>
       </c>
       <c r="B1346" t="s">
@@ -16998,7 +16966,7 @@
       </c>
     </row>
     <row r="1347" spans="1:2">
-      <c r="A1347" s="5" t="s">
+      <c r="A1347" t="s">
         <v>1485</v>
       </c>
       <c r="B1347" t="s">
@@ -17006,7 +16974,7 @@
       </c>
     </row>
     <row r="1348" spans="1:2">
-      <c r="A1348" s="5" t="s">
+      <c r="A1348" t="s">
         <v>1486</v>
       </c>
       <c r="B1348" t="s">
@@ -17014,7 +16982,7 @@
       </c>
     </row>
     <row r="1349" spans="1:2">
-      <c r="A1349" s="5" t="s">
+      <c r="A1349" t="s">
         <v>1487</v>
       </c>
       <c r="B1349" t="s">
@@ -17022,7 +16990,7 @@
       </c>
     </row>
     <row r="1350" spans="1:2">
-      <c r="A1350" s="5" t="s">
+      <c r="A1350" t="s">
         <v>1489</v>
       </c>
       <c r="B1350" t="s">
@@ -17030,7 +16998,7 @@
       </c>
     </row>
     <row r="1351" spans="1:2">
-      <c r="A1351" s="5" t="s">
+      <c r="A1351" t="s">
         <v>1490</v>
       </c>
       <c r="B1351" t="s">
@@ -17038,7 +17006,7 @@
       </c>
     </row>
     <row r="1352" spans="1:2">
-      <c r="A1352" s="5" t="s">
+      <c r="A1352" t="s">
         <v>1491</v>
       </c>
       <c r="B1352" t="s">
@@ -17046,7 +17014,7 @@
       </c>
     </row>
     <row r="1353" spans="1:2">
-      <c r="A1353" s="5" t="s">
+      <c r="A1353" t="s">
         <v>1492</v>
       </c>
       <c r="B1353" t="s">
@@ -17054,7 +17022,7 @@
       </c>
     </row>
     <row r="1354" spans="1:2">
-      <c r="A1354" s="5" t="s">
+      <c r="A1354" t="s">
         <v>1493</v>
       </c>
       <c r="B1354" t="s">
@@ -17062,7 +17030,7 @@
       </c>
     </row>
     <row r="1355" spans="1:2">
-      <c r="A1355" s="5" t="s">
+      <c r="A1355" t="s">
         <v>1494</v>
       </c>
       <c r="B1355" t="s">
@@ -17070,7 +17038,7 @@
       </c>
     </row>
     <row r="1356" spans="1:2">
-      <c r="A1356" s="5" t="s">
+      <c r="A1356" t="s">
         <v>1495</v>
       </c>
       <c r="B1356" t="s">
@@ -17078,7 +17046,7 @@
       </c>
     </row>
     <row r="1357" spans="1:2">
-      <c r="A1357" s="5" t="s">
+      <c r="A1357" t="s">
         <v>1496</v>
       </c>
       <c r="B1357" t="s">
@@ -17086,7 +17054,7 @@
       </c>
     </row>
     <row r="1358" spans="1:2">
-      <c r="A1358" s="5" t="s">
+      <c r="A1358" t="s">
         <v>1497</v>
       </c>
       <c r="B1358" t="s">
@@ -17094,7 +17062,7 @@
       </c>
     </row>
     <row r="1359" spans="1:2">
-      <c r="A1359" s="5" t="s">
+      <c r="A1359" t="s">
         <v>1498</v>
       </c>
       <c r="B1359" t="s">
@@ -17102,7 +17070,7 @@
       </c>
     </row>
     <row r="1360" spans="1:2">
-      <c r="A1360" s="5" t="s">
+      <c r="A1360" t="s">
         <v>1499</v>
       </c>
       <c r="B1360" t="s">
@@ -17110,7 +17078,7 @@
       </c>
     </row>
     <row r="1361" spans="1:2">
-      <c r="A1361" s="5" t="s">
+      <c r="A1361" t="s">
         <v>1500</v>
       </c>
       <c r="B1361" t="s">
@@ -17118,7 +17086,7 @@
       </c>
     </row>
     <row r="1362" spans="1:2">
-      <c r="A1362" s="5" t="s">
+      <c r="A1362" t="s">
         <v>1501</v>
       </c>
       <c r="B1362" t="s">
@@ -17126,7 +17094,7 @@
       </c>
     </row>
     <row r="1363" spans="1:2">
-      <c r="A1363" s="5" t="s">
+      <c r="A1363" t="s">
         <v>1502</v>
       </c>
       <c r="B1363" t="s">
@@ -17134,7 +17102,7 @@
       </c>
     </row>
     <row r="1364" spans="1:2">
-      <c r="A1364" s="5" t="s">
+      <c r="A1364" t="s">
         <v>1503</v>
       </c>
       <c r="B1364" t="s">
@@ -17142,7 +17110,7 @@
       </c>
     </row>
     <row r="1365" spans="1:2">
-      <c r="A1365" s="5" t="s">
+      <c r="A1365" t="s">
         <v>1504</v>
       </c>
       <c r="B1365" t="s">
@@ -17150,7 +17118,7 @@
       </c>
     </row>
     <row r="1366" spans="1:2">
-      <c r="A1366" s="5" t="s">
+      <c r="A1366" t="s">
         <v>1505</v>
       </c>
       <c r="B1366" t="s">
@@ -17158,7 +17126,7 @@
       </c>
     </row>
     <row r="1367" spans="1:2">
-      <c r="A1367" s="5" t="s">
+      <c r="A1367" t="s">
         <v>1506</v>
       </c>
       <c r="B1367" t="s">
@@ -17166,7 +17134,7 @@
       </c>
     </row>
     <row r="1368" spans="1:2">
-      <c r="A1368" s="5" t="s">
+      <c r="A1368" t="s">
         <v>1507</v>
       </c>
       <c r="B1368" t="s">
@@ -17174,7 +17142,7 @@
       </c>
     </row>
     <row r="1369" spans="1:2">
-      <c r="A1369" s="5" t="s">
+      <c r="A1369" t="s">
         <v>1508</v>
       </c>
       <c r="B1369" t="s">
@@ -17182,7 +17150,7 @@
       </c>
     </row>
     <row r="1370" spans="1:2">
-      <c r="A1370" s="5" t="s">
+      <c r="A1370" t="s">
         <v>1509</v>
       </c>
       <c r="B1370" t="s">
@@ -17190,7 +17158,7 @@
       </c>
     </row>
     <row r="1371" spans="1:2">
-      <c r="A1371" s="5" t="s">
+      <c r="A1371" t="s">
         <v>1510</v>
       </c>
       <c r="B1371" t="s">
@@ -17198,7 +17166,7 @@
       </c>
     </row>
     <row r="1372" spans="1:2">
-      <c r="A1372" s="5" t="s">
+      <c r="A1372" t="s">
         <v>1511</v>
       </c>
       <c r="B1372" t="s">
@@ -17206,7 +17174,7 @@
       </c>
     </row>
     <row r="1373" spans="1:2">
-      <c r="A1373" s="5" t="s">
+      <c r="A1373" t="s">
         <v>1512</v>
       </c>
       <c r="B1373" t="s">
@@ -17214,7 +17182,7 @@
       </c>
     </row>
     <row r="1374" spans="1:2">
-      <c r="A1374" s="5" t="s">
+      <c r="A1374" t="s">
         <v>1513</v>
       </c>
       <c r="B1374" t="s">
@@ -17222,7 +17190,7 @@
       </c>
     </row>
     <row r="1375" spans="1:2">
-      <c r="A1375" s="5" t="s">
+      <c r="A1375" t="s">
         <v>1514</v>
       </c>
       <c r="B1375" t="s">
@@ -17230,7 +17198,7 @@
       </c>
     </row>
     <row r="1376" spans="1:2">
-      <c r="A1376" s="5" t="s">
+      <c r="A1376" t="s">
         <v>1515</v>
       </c>
       <c r="B1376" t="s">
@@ -17238,7 +17206,7 @@
       </c>
     </row>
     <row r="1377" spans="1:2">
-      <c r="A1377" s="5" t="s">
+      <c r="A1377" t="s">
         <v>1516</v>
       </c>
       <c r="B1377" t="s">
@@ -17246,7 +17214,7 @@
       </c>
     </row>
     <row r="1378" spans="1:2">
-      <c r="A1378" s="5" t="s">
+      <c r="A1378" t="s">
         <v>1519</v>
       </c>
       <c r="B1378" t="s">
@@ -17254,7 +17222,7 @@
       </c>
     </row>
     <row r="1379" spans="1:2">
-      <c r="A1379" s="5" t="s">
+      <c r="A1379" t="s">
         <v>1520</v>
       </c>
       <c r="B1379" t="s">
@@ -17262,7 +17230,7 @@
       </c>
     </row>
     <row r="1380" spans="1:2">
-      <c r="A1380" s="5" t="s">
+      <c r="A1380" t="s">
         <v>1521</v>
       </c>
       <c r="B1380" t="s">
@@ -17270,7 +17238,7 @@
       </c>
     </row>
     <row r="1381" spans="1:2">
-      <c r="A1381" s="5" t="s">
+      <c r="A1381" t="s">
         <v>1522</v>
       </c>
       <c r="B1381" t="s">
@@ -17278,7 +17246,7 @@
       </c>
     </row>
     <row r="1382" spans="1:2">
-      <c r="A1382" s="5" t="s">
+      <c r="A1382" t="s">
         <v>1523</v>
       </c>
       <c r="B1382" t="s">
@@ -17286,7 +17254,7 @@
       </c>
     </row>
     <row r="1383" spans="1:2">
-      <c r="A1383" s="5" t="s">
+      <c r="A1383" t="s">
         <v>1524</v>
       </c>
       <c r="B1383" t="s">
@@ -17294,7 +17262,7 @@
       </c>
     </row>
     <row r="1384" spans="1:2">
-      <c r="A1384" s="5" t="s">
+      <c r="A1384" t="s">
         <v>1525</v>
       </c>
       <c r="B1384" t="s">
@@ -17302,7 +17270,7 @@
       </c>
     </row>
     <row r="1385" spans="1:2">
-      <c r="A1385" s="5" t="s">
+      <c r="A1385" t="s">
         <v>1526</v>
       </c>
       <c r="B1385" t="s">
@@ -17310,7 +17278,7 @@
       </c>
     </row>
     <row r="1386" spans="1:2">
-      <c r="A1386" s="5" t="s">
+      <c r="A1386" t="s">
         <v>1527</v>
       </c>
       <c r="B1386" t="s">
@@ -17318,7 +17286,7 @@
       </c>
     </row>
     <row r="1387" spans="1:2">
-      <c r="A1387" s="5" t="s">
+      <c r="A1387" t="s">
         <v>1528</v>
       </c>
       <c r="B1387" t="s">
@@ -17326,7 +17294,7 @@
       </c>
     </row>
     <row r="1388" spans="1:2">
-      <c r="A1388" s="5" t="s">
+      <c r="A1388" t="s">
         <v>1529</v>
       </c>
       <c r="B1388" t="s">
@@ -17334,7 +17302,7 @@
       </c>
     </row>
     <row r="1389" spans="1:2">
-      <c r="A1389" s="5" t="s">
+      <c r="A1389" t="s">
         <v>1530</v>
       </c>
       <c r="B1389" t="s">
@@ -17342,7 +17310,7 @@
       </c>
     </row>
     <row r="1390" spans="1:2">
-      <c r="A1390" s="5" t="s">
+      <c r="A1390" t="s">
         <v>1531</v>
       </c>
       <c r="B1390" t="s">
@@ -17350,7 +17318,7 @@
       </c>
     </row>
     <row r="1391" spans="1:2">
-      <c r="A1391" s="5" t="s">
+      <c r="A1391" t="s">
         <v>1532</v>
       </c>
       <c r="B1391" t="s">
@@ -17358,7 +17326,7 @@
       </c>
     </row>
     <row r="1392" spans="1:2">
-      <c r="A1392" s="5" t="s">
+      <c r="A1392" t="s">
         <v>1533</v>
       </c>
       <c r="B1392" t="s">
@@ -17366,7 +17334,7 @@
       </c>
     </row>
     <row r="1393" spans="1:2">
-      <c r="A1393" s="5" t="s">
+      <c r="A1393" t="s">
         <v>1534</v>
       </c>
       <c r="B1393" t="s">
@@ -17374,7 +17342,7 @@
       </c>
     </row>
     <row r="1394" spans="1:2">
-      <c r="A1394" s="5" t="s">
+      <c r="A1394" t="s">
         <v>1535</v>
       </c>
       <c r="B1394" t="s">
@@ -17382,7 +17350,7 @@
       </c>
     </row>
     <row r="1395" spans="1:2">
-      <c r="A1395" s="5" t="s">
+      <c r="A1395" t="s">
         <v>1536</v>
       </c>
       <c r="B1395" t="s">
@@ -17390,7 +17358,7 @@
       </c>
     </row>
     <row r="1396" spans="1:2">
-      <c r="A1396" s="5" t="s">
+      <c r="A1396" t="s">
         <v>1537</v>
       </c>
       <c r="B1396" t="s">
@@ -17398,7 +17366,7 @@
       </c>
     </row>
     <row r="1397" spans="1:2">
-      <c r="A1397" s="5" t="s">
+      <c r="A1397" t="s">
         <v>1538</v>
       </c>
       <c r="B1397" t="s">
@@ -17406,7 +17374,7 @@
       </c>
     </row>
     <row r="1398" spans="1:2">
-      <c r="A1398" s="4" t="s">
+      <c r="A1398" s="2" t="s">
         <v>1540</v>
       </c>
       <c r="B1398" t="s">
@@ -17414,7 +17382,7 @@
       </c>
     </row>
     <row r="1399" spans="1:2">
-      <c r="A1399" s="3" t="s">
+      <c r="A1399" s="2" t="s">
         <v>1542</v>
       </c>
       <c r="B1399" t="s">
@@ -17430,7 +17398,7 @@
       </c>
     </row>
     <row r="1401" spans="1:2">
-      <c r="A1401" s="3" t="s">
+      <c r="A1401" s="2" t="s">
         <v>1544</v>
       </c>
       <c r="B1401" t="s">
@@ -17438,7 +17406,7 @@
       </c>
     </row>
     <row r="1402" spans="1:2">
-      <c r="A1402" s="4" t="s">
+      <c r="A1402" s="2" t="s">
         <v>1545</v>
       </c>
       <c r="B1402" t="s">
@@ -17454,7 +17422,7 @@
       </c>
     </row>
     <row r="1404" spans="1:2">
-      <c r="A1404" s="4" t="s">
+      <c r="A1404" s="2" t="s">
         <v>1547</v>
       </c>
       <c r="B1404" t="s">
@@ -17495,19 +17463,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="A1398" r:id="rId1" display="https://www.jorudan.co.jp/time/eki_%E6%9B%BD%E6%A0%B9%E7%94%B0_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{68ACE546-A750-4F60-AED4-E07901AC3288}"/>
-    <hyperlink ref="A1399" r:id="rId2" display="https://www.jorudan.co.jp/time/eki_%E7%BE%8E%E8%A1%93%E9%A4%A8%E5%9B%B3%E6%9B%B8%E9%A4%A8%E5%89%8D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{28EE59C4-EA83-4E89-B034-6FD4AAD99E24}"/>
-    <hyperlink ref="A1400" r:id="rId3" display="https://www.jorudan.co.jp/time/eki_%E5%B2%A9%E4%BB%A3%E6%B8%85%E6%B0%B4_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{E1829E4B-BE00-4B4B-9C93-EBACFAC95BF7}"/>
-    <hyperlink ref="A1401" r:id="rId4" display="https://www.jorudan.co.jp/time/eki_%E6%B3%89%EF%BC%88%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%EF%BC%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{99D58D68-BA64-4C3F-B934-A4D08A1C303D}"/>
-    <hyperlink ref="A1402" r:id="rId5" display="https://www.jorudan.co.jp/time/eki_%E4%B8%8A%E6%9D%BE%E5%B7%9D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{E886F647-D1CC-4E57-88DB-E2CF61B5B64D}"/>
-    <hyperlink ref="A1403" r:id="rId6" display="https://www.jorudan.co.jp/time/eki_%E7%AC%B9%E8%B0%B7_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{F142FFF2-AD53-477A-8681-688EC66C51D3}"/>
-    <hyperlink ref="A1404" r:id="rId7" display="https://www.jorudan.co.jp/time/eki_%E6%A1%9C%E6%B0%B4_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{ACF6A996-D26F-475F-8321-2FCF98842525}"/>
-    <hyperlink ref="A1405" r:id="rId8" display="https://www.jorudan.co.jp/time/eki_%E5%B9%B3%E9%87%8E%EF%BC%88%E7%A6%8F%E5%B3%B6%EF%BC%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{55ED7298-022F-4823-BAF4-7F4FC1E5ACD6}"/>
-    <hyperlink ref="A1406" r:id="rId9" display="https://www.jorudan.co.jp/time/eki_%E5%8C%BB%E7%8E%8B%E5%AF%BA%E5%89%8D_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{3F5B7580-48A7-4529-B87F-13D558B2B700}"/>
-    <hyperlink ref="A1407" r:id="rId10" display="https://www.jorudan.co.jp/time/eki_%E8%8A%B1%E6%B0%B4%E5%9D%82_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{62680C19-8AA2-4379-A265-56EF70ABA63F}"/>
-    <hyperlink ref="A1408" r:id="rId11" display="https://www.jorudan.co.jp/time/eki_%E9%A3%AF%E5%9D%82%E6%B8%A9%E6%B3%89_%E7%A6%8F%E5%B3%B6%E4%BA%A4%E9%80%9A%E9%A3%AF%E5%9D%82%E7%B7%9A.html" xr:uid="{B472157B-450F-4DB5-96FD-6C63E26D7034}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BB3AD8-2F56-4035-9827-1A789E0D7667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D35D8C7-2EDE-46C0-96CE-218B8402A9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17292" windowHeight="8880" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="1699">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -5908,6 +5908,537 @@
   </si>
   <si>
     <t>飯坂温泉</t>
+  </si>
+  <si>
+    <t>茨城</t>
+    <rPh sb="0" eb="2">
+      <t>イバラキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>潮来</t>
+  </si>
+  <si>
+    <t>延方</t>
+  </si>
+  <si>
+    <t>鹿島神宮</t>
+  </si>
+  <si>
+    <t>鹿島サッカースタジアム</t>
+  </si>
+  <si>
+    <t>鹿島線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鹿島線、鹿島臨海鉄道大洗鹿島線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大津港</t>
+  </si>
+  <si>
+    <t>磯原</t>
+  </si>
+  <si>
+    <t>南中郷</t>
+  </si>
+  <si>
+    <t>高萩</t>
+  </si>
+  <si>
+    <t>十王</t>
+  </si>
+  <si>
+    <t>小木津</t>
+  </si>
+  <si>
+    <t>日立</t>
+  </si>
+  <si>
+    <t>常陸多賀</t>
+  </si>
+  <si>
+    <t>大甕</t>
+  </si>
+  <si>
+    <t>東海</t>
+  </si>
+  <si>
+    <t>佐和（茨城）</t>
+  </si>
+  <si>
+    <t>勝田</t>
+  </si>
+  <si>
+    <t>水戸</t>
+  </si>
+  <si>
+    <t>偕楽園</t>
+  </si>
+  <si>
+    <t>赤塚（茨城）</t>
+  </si>
+  <si>
+    <t>内原</t>
+  </si>
+  <si>
+    <t>友部</t>
+  </si>
+  <si>
+    <t>岩間</t>
+  </si>
+  <si>
+    <t>羽鳥</t>
+  </si>
+  <si>
+    <t>石岡</t>
+  </si>
+  <si>
+    <t>高浜（茨城）</t>
+  </si>
+  <si>
+    <t>神立</t>
+  </si>
+  <si>
+    <t>土浦</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荒川沖</t>
+  </si>
+  <si>
+    <t>ひたち野うしく</t>
+  </si>
+  <si>
+    <t>牛久</t>
+  </si>
+  <si>
+    <t>龍ヶ崎市</t>
+  </si>
+  <si>
+    <t>藤代</t>
+  </si>
+  <si>
+    <t>取手</t>
+  </si>
+  <si>
+    <t>常磐線、水戸線、ひたちなか海浜鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>カイヒンテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、水郡線、鹿島臨海鉄道大洗鹿島線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スイグンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常陸青柳</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常陸津田</t>
+  </si>
+  <si>
+    <t>後台</t>
+  </si>
+  <si>
+    <t>下菅谷</t>
+  </si>
+  <si>
+    <t>中菅谷</t>
+  </si>
+  <si>
+    <t>上菅谷</t>
+  </si>
+  <si>
+    <t>南酒出</t>
+  </si>
+  <si>
+    <t>額田（茨城）</t>
+  </si>
+  <si>
+    <t>河合（茨城）</t>
+  </si>
+  <si>
+    <t>谷河原</t>
+  </si>
+  <si>
+    <t>常陸太田</t>
+  </si>
+  <si>
+    <t>常陸鴻巣</t>
+  </si>
+  <si>
+    <t>瓜連</t>
+  </si>
+  <si>
+    <t>静（茨城）</t>
+  </si>
+  <si>
+    <t>常陸大宮</t>
+  </si>
+  <si>
+    <t>玉川村</t>
+  </si>
+  <si>
+    <t>野上原</t>
+  </si>
+  <si>
+    <t>山方宿</t>
+  </si>
+  <si>
+    <t>中舟生</t>
+  </si>
+  <si>
+    <t>下小川</t>
+  </si>
+  <si>
+    <t>西金</t>
+  </si>
+  <si>
+    <t>上小川</t>
+  </si>
+  <si>
+    <t>袋田</t>
+  </si>
+  <si>
+    <t>常陸大子</t>
+  </si>
+  <si>
+    <t>下野宮</t>
+  </si>
+  <si>
+    <t>水戸線</t>
+    <rPh sb="0" eb="3">
+      <t>ミトセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小田林</t>
+  </si>
+  <si>
+    <t>結城</t>
+  </si>
+  <si>
+    <t>東結城</t>
+  </si>
+  <si>
+    <t>川島</t>
+  </si>
+  <si>
+    <t>玉戸</t>
+  </si>
+  <si>
+    <t>下館</t>
+  </si>
+  <si>
+    <t>新治</t>
+  </si>
+  <si>
+    <t>大和（茨城）</t>
+  </si>
+  <si>
+    <t>岩瀬</t>
+  </si>
+  <si>
+    <t>羽黒（茨城）</t>
+  </si>
+  <si>
+    <t>福原</t>
+  </si>
+  <si>
+    <t>稲田</t>
+  </si>
+  <si>
+    <t>笠間</t>
+  </si>
+  <si>
+    <t>宍戸</t>
+  </si>
+  <si>
+    <t>水戸線、関東鉄道常総線、真岡鐵道</t>
+    <rPh sb="0" eb="3">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="4" eb="11">
+      <t>カントウテツドウジョウソウセン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モオカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古河</t>
+    <rPh sb="0" eb="2">
+      <t>コガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひたちなか海浜鉄道</t>
+  </si>
+  <si>
+    <t>工機前</t>
+  </si>
+  <si>
+    <t>金上</t>
+  </si>
+  <si>
+    <t>中根</t>
+  </si>
+  <si>
+    <t>高田の鉄橋</t>
+  </si>
+  <si>
+    <t>那珂湊</t>
+  </si>
+  <si>
+    <t>殿山</t>
+  </si>
+  <si>
+    <t>平磯</t>
+  </si>
+  <si>
+    <t>美乃浜学園</t>
+  </si>
+  <si>
+    <t>磯崎</t>
+  </si>
+  <si>
+    <t>阿字ヶ浦</t>
+  </si>
+  <si>
+    <t>宇都宮線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、関東鉄道常総線、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>カントウテツドウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ジョウソウセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関東鉄道常総線</t>
+  </si>
+  <si>
+    <t>西取手</t>
+  </si>
+  <si>
+    <t>寺原</t>
+  </si>
+  <si>
+    <t>新取手</t>
+  </si>
+  <si>
+    <t>ゆめみ野</t>
+  </si>
+  <si>
+    <t>稲戸井</t>
+  </si>
+  <si>
+    <t>戸頭</t>
+  </si>
+  <si>
+    <t>南守谷</t>
+  </si>
+  <si>
+    <t>守谷</t>
+  </si>
+  <si>
+    <t>新守谷</t>
+  </si>
+  <si>
+    <t>小絹</t>
+  </si>
+  <si>
+    <t>水海道</t>
+  </si>
+  <si>
+    <t>北水海道</t>
+  </si>
+  <si>
+    <t>中妻</t>
+  </si>
+  <si>
+    <t>三妻</t>
+  </si>
+  <si>
+    <t>南石下</t>
+  </si>
+  <si>
+    <t>石下</t>
+  </si>
+  <si>
+    <t>玉村</t>
+  </si>
+  <si>
+    <t>宗道</t>
+  </si>
+  <si>
+    <t>下妻</t>
+  </si>
+  <si>
+    <t>大宝</t>
+  </si>
+  <si>
+    <t>騰波ノ江</t>
+  </si>
+  <si>
+    <t>黒子</t>
+  </si>
+  <si>
+    <t>大田郷</t>
+  </si>
+  <si>
+    <t>関東鉄道常総線、つくばエクスプレス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関東鉄道竜ヶ崎線</t>
+  </si>
+  <si>
+    <t>佐貫</t>
+  </si>
+  <si>
+    <t>入地</t>
+  </si>
+  <si>
+    <t>竜ヶ崎</t>
+  </si>
+  <si>
+    <t>鹿島臨海鉄道大洗鹿島線</t>
+  </si>
+  <si>
+    <t>東水戸</t>
+  </si>
+  <si>
+    <t>常澄</t>
+  </si>
+  <si>
+    <t>大洗</t>
+  </si>
+  <si>
+    <t>涸沼</t>
+  </si>
+  <si>
+    <t>鹿島旭</t>
+  </si>
+  <si>
+    <t>徳宿</t>
+  </si>
+  <si>
+    <t>新鉾田</t>
+  </si>
+  <si>
+    <t>北浦湖畔</t>
+  </si>
+  <si>
+    <t>大洋</t>
+  </si>
+  <si>
+    <t>鹿島灘</t>
+  </si>
+  <si>
+    <t>鹿島大野</t>
+  </si>
+  <si>
+    <t>はまなす公園前</t>
+  </si>
+  <si>
+    <t>荒野台</t>
+  </si>
+  <si>
+    <t>下館二高前</t>
+  </si>
+  <si>
+    <t>折本</t>
+  </si>
+  <si>
+    <t>ひぐち（茨城）</t>
+  </si>
+  <si>
+    <t>真岡鐵道</t>
+    <rPh sb="0" eb="2">
+      <t>モオカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つくばエクスプレス</t>
+  </si>
+  <si>
+    <t>みらい平</t>
+  </si>
+  <si>
+    <t>みどりの</t>
+  </si>
+  <si>
+    <t>万博記念公園（茨城）</t>
+  </si>
+  <si>
+    <t>研究学園</t>
+  </si>
+  <si>
+    <t>つくば</t>
   </si>
 </sst>
 </file>
@@ -6307,7 +6838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B1408"/>
+  <dimension ref="A1:B1541"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -17461,6 +17992,1048 @@
         <v>1539</v>
       </c>
     </row>
+    <row r="1411" spans="1:2">
+      <c r="A1411" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2">
+      <c r="A1412" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:2">
+      <c r="A1413" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:2">
+      <c r="A1414" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:2">
+      <c r="A1415" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2">
+      <c r="A1416" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:2">
+      <c r="A1417" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:2">
+      <c r="A1418" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:2">
+      <c r="A1419" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:2">
+      <c r="A1420" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:2">
+      <c r="A1421" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:2">
+      <c r="A1422" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:2">
+      <c r="A1423" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:2">
+      <c r="A1424" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:2">
+      <c r="A1425" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:2">
+      <c r="A1426" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:2">
+      <c r="A1427" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2">
+      <c r="A1428" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2">
+      <c r="A1429" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2">
+      <c r="A1430" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2">
+      <c r="A1431" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2">
+      <c r="A1432" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2">
+      <c r="A1433" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2">
+      <c r="A1434" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2">
+      <c r="A1435" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2">
+      <c r="A1436" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2">
+      <c r="A1437" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:2">
+      <c r="A1438" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2">
+      <c r="A1439" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2">
+      <c r="A1440" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2">
+      <c r="A1441" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2">
+      <c r="A1442" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2">
+      <c r="A1443" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2">
+      <c r="A1444" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2">
+      <c r="A1445" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:2">
+      <c r="A1446" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:2">
+      <c r="A1447" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:2">
+      <c r="A1448" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:2">
+      <c r="A1449" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:2">
+      <c r="A1450" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:2">
+      <c r="A1451" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:2">
+      <c r="A1452" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:2">
+      <c r="A1453" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:2">
+      <c r="A1454" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:2">
+      <c r="A1455" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:2">
+      <c r="A1456" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:2">
+      <c r="A1457" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:2">
+      <c r="A1458" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:2">
+      <c r="A1459" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:2">
+      <c r="A1460" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:2">
+      <c r="A1461" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:2">
+      <c r="A1462" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:2">
+      <c r="A1463" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:2">
+      <c r="A1464" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:2">
+      <c r="A1465" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:2">
+      <c r="A1466" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:2">
+      <c r="A1467" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:2">
+      <c r="A1468" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:2">
+      <c r="A1469" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:2">
+      <c r="A1470" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:2">
+      <c r="A1471" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:2">
+      <c r="A1472" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:2">
+      <c r="A1473" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:2">
+      <c r="A1474" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:2">
+      <c r="A1475" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:2">
+      <c r="A1476" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:2">
+      <c r="A1477" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:2">
+      <c r="A1478" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:2">
+      <c r="A1479" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:2">
+      <c r="A1480" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:2">
+      <c r="A1481" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:2">
+      <c r="A1482" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:2">
+      <c r="A1483" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:2">
+      <c r="A1484" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:2">
+      <c r="A1485" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:2">
+      <c r="A1486" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:2">
+      <c r="A1487" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:2">
+      <c r="A1488" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:2">
+      <c r="A1489" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:2">
+      <c r="A1490" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:2">
+      <c r="A1491" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:2">
+      <c r="A1492" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:2">
+      <c r="A1493" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:2">
+      <c r="A1494" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:2">
+      <c r="A1495" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:2">
+      <c r="A1496" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:2">
+      <c r="A1497" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:2">
+      <c r="A1498" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:2">
+      <c r="A1499" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:2">
+      <c r="A1500" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:2">
+      <c r="A1501" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:2">
+      <c r="A1502" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:2">
+      <c r="A1503" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:2">
+      <c r="A1504" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:2">
+      <c r="A1505" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:2">
+      <c r="A1506" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:2">
+      <c r="A1507" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:2">
+      <c r="A1508" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:2">
+      <c r="A1509" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:2">
+      <c r="A1510" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:2">
+      <c r="A1511" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:2">
+      <c r="A1512" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:2">
+      <c r="A1513" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:2">
+      <c r="A1514" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:2">
+      <c r="A1515" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:2">
+      <c r="A1516" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:2">
+      <c r="A1517" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:2">
+      <c r="A1518" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:2">
+      <c r="A1519" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:2">
+      <c r="A1520" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:2">
+      <c r="A1521" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:2">
+      <c r="A1522" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:2">
+      <c r="A1523" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:2">
+      <c r="A1524" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:2">
+      <c r="A1525" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:2">
+      <c r="A1526" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:2">
+      <c r="A1527" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:2">
+      <c r="A1528" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:2">
+      <c r="A1529" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:2">
+      <c r="A1530" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:2">
+      <c r="A1531" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:2">
+      <c r="A1532" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:2">
+      <c r="A1533" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:2">
+      <c r="A1534" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:2">
+      <c r="A1535" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:2">
+      <c r="A1536" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:2">
+      <c r="A1537" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:2">
+      <c r="A1538" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:2">
+      <c r="A1539" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:2">
+      <c r="A1540" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:2">
+      <c r="A1541" s="2" t="s">
+        <v>1698</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D35D8C7-2EDE-46C0-96CE-218B8402A9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{718787A7-7B82-4005-9FF9-6CCD2951A242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="1699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3315" uniqueCount="1861">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -5404,28 +5404,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>水郡線、東北本線、磐越東線、磐越西線、東北新幹線、山形新幹線</t>
-    <rPh sb="0" eb="3">
-      <t>スイグンセン</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>トウホクホンセン</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>バンエツトウセン</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>バンエツサイセン</t>
-    </rPh>
-    <rPh sb="19" eb="24">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <rPh sb="25" eb="30">
-      <t>ヤマガタシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>只見線</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -6025,42 +6003,6 @@
     <t>取手</t>
   </si>
   <si>
-    <t>常磐線、水戸線、ひたちなか海浜鉄道</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>カイヒンテツドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常磐線、水戸線、水郡線、鹿島臨海鉄道大洗鹿島線</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>スイグンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常磐線、水戸線</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>常陸青柳</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -6242,19 +6184,6 @@
     <t>阿字ヶ浦</t>
   </si>
   <si>
-    <t>宇都宮線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="4">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>常磐線、関東鉄道常総線、（上野東京ライン）</t>
     <rPh sb="0" eb="3">
       <t>ジョウバンセン</t>
@@ -6439,6 +6368,743 @@
   </si>
   <si>
     <t>つくば</t>
+  </si>
+  <si>
+    <t>栃木県</t>
+    <rPh sb="0" eb="3">
+      <t>トチギケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮</t>
+  </si>
+  <si>
+    <t>岡本（栃木）</t>
+  </si>
+  <si>
+    <t>宝積寺</t>
+  </si>
+  <si>
+    <t>下野花岡</t>
+  </si>
+  <si>
+    <t>仁井田（栃木）</t>
+  </si>
+  <si>
+    <t>鴻野山</t>
+  </si>
+  <si>
+    <t>大金</t>
+  </si>
+  <si>
+    <t>小塙</t>
+  </si>
+  <si>
+    <t>滝（栃木）</t>
+  </si>
+  <si>
+    <t>烏山</t>
+  </si>
+  <si>
+    <t>烏山線</t>
+    <rPh sb="0" eb="3">
+      <t>カラスヤマセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>烏山線、宇都宮線</t>
+    <rPh sb="0" eb="3">
+      <t>カラスヤマセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水郡線、東北本線、磐越東線、磐越西線、東北新幹線</t>
+    <rPh sb="0" eb="3">
+      <t>スイグンセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>トウホクホンセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>バンエツトウセン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>バンエツサイセン</t>
+    </rPh>
+    <rPh sb="19" eb="24">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小山</t>
+    <rPh sb="0" eb="2">
+      <t>オヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>那須塩原</t>
+  </si>
+  <si>
+    <t>東北新幹線、宇都宮線</t>
+    <rPh sb="0" eb="5">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒磯</t>
+  </si>
+  <si>
+    <t>高久</t>
+  </si>
+  <si>
+    <t>黒田原</t>
+  </si>
+  <si>
+    <t>豊原</t>
+  </si>
+  <si>
+    <t>東北本線、宇都宮線</t>
+    <rPh sb="0" eb="2">
+      <t>トウホク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ウツノミヤ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東北本線</t>
+    <rPh sb="0" eb="2">
+      <t>トウホク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西那須野</t>
+  </si>
+  <si>
+    <t>野崎（栃木）</t>
+  </si>
+  <si>
+    <t>矢板</t>
+  </si>
+  <si>
+    <t>片岡</t>
+  </si>
+  <si>
+    <t>蒲須坂</t>
+  </si>
+  <si>
+    <t>氏家</t>
+  </si>
+  <si>
+    <t>雀宮</t>
+  </si>
+  <si>
+    <t>石橋（栃木）</t>
+  </si>
+  <si>
+    <t>自治医大</t>
+  </si>
+  <si>
+    <t>小金井</t>
+  </si>
+  <si>
+    <t>間々田</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野木</t>
+  </si>
+  <si>
+    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>烏山線、宇都宮線、日光線、東北新幹線、（湘南新宿ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>カラスヤマセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ニッコウセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水戸線、両毛線、宇都宮線、東北新幹線、（湘南新宿ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、ひたちなか海浜鉄道、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>カイヒンテツドウ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、水郡線、鹿島臨海鉄道大洗鹿島線、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スイグンセン</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮線、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日光</t>
+  </si>
+  <si>
+    <t>今市</t>
+  </si>
+  <si>
+    <t>下野大沢</t>
+  </si>
+  <si>
+    <t>文挟</t>
+  </si>
+  <si>
+    <t>鹿沼</t>
+  </si>
+  <si>
+    <t>鶴田</t>
+  </si>
+  <si>
+    <t>日光線</t>
+    <rPh sb="0" eb="3">
+      <t>ニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>思川</t>
+  </si>
+  <si>
+    <t>栃木</t>
+  </si>
+  <si>
+    <t>大平下</t>
+  </si>
+  <si>
+    <t>岩舟</t>
+  </si>
+  <si>
+    <t>佐野</t>
+  </si>
+  <si>
+    <t>富田（栃木）</t>
+  </si>
+  <si>
+    <t>あしかがフラワーパーク</t>
+  </si>
+  <si>
+    <t>足利</t>
+  </si>
+  <si>
+    <t>山前</t>
+  </si>
+  <si>
+    <t>小俣（栃木）</t>
+  </si>
+  <si>
+    <t>両毛線</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両毛線、東武日光線</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両毛線、東武佐野線</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>トウブサノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わたらせ渓谷鐵道</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原向</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通洞</t>
+  </si>
+  <si>
+    <t>足尾</t>
+  </si>
+  <si>
+    <t>間藤</t>
+  </si>
+  <si>
+    <t>真岡鐵道</t>
+  </si>
+  <si>
+    <t>久下田</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寺内</t>
+  </si>
+  <si>
+    <t>真岡</t>
+  </si>
+  <si>
+    <t>北真岡</t>
+  </si>
+  <si>
+    <t>西田井（栃木）</t>
+  </si>
+  <si>
+    <t>北山（栃木）</t>
+  </si>
+  <si>
+    <t>益子</t>
+  </si>
+  <si>
+    <t>七井</t>
+  </si>
+  <si>
+    <t>多田羅（栃木）</t>
+  </si>
+  <si>
+    <t>市塙</t>
+  </si>
+  <si>
+    <t>笹原田</t>
+  </si>
+  <si>
+    <t>天矢場</t>
+  </si>
+  <si>
+    <t>茂木</t>
+  </si>
+  <si>
+    <t>野州山辺</t>
+  </si>
+  <si>
+    <t>足利市</t>
+  </si>
+  <si>
+    <t>東武和泉</t>
+  </si>
+  <si>
+    <t>福居</t>
+  </si>
+  <si>
+    <t>県</t>
+  </si>
+  <si>
+    <t>東武伊勢崎線</t>
+    <rPh sb="0" eb="6">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新栃木</t>
+  </si>
+  <si>
+    <t>野州平川</t>
+  </si>
+  <si>
+    <t>野州大塚</t>
+  </si>
+  <si>
+    <t>壬生</t>
+  </si>
+  <si>
+    <t>国谷</t>
+  </si>
+  <si>
+    <t>おもちゃのまち</t>
+  </si>
+  <si>
+    <t>安塚</t>
+  </si>
+  <si>
+    <t>西川田</t>
+  </si>
+  <si>
+    <t>江曽島</t>
+  </si>
+  <si>
+    <t>南宇都宮</t>
+  </si>
+  <si>
+    <t>東武宇都宮</t>
+  </si>
+  <si>
+    <t>東武宇都宮線</t>
+    <rPh sb="0" eb="5">
+      <t>トウブウツノミヤ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武宇都宮線、東武日光線</t>
+    <rPh sb="0" eb="5">
+      <t>トウブウツノミヤ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武鬼怒川線</t>
+  </si>
+  <si>
+    <t>下今市</t>
+  </si>
+  <si>
+    <t>大谷向</t>
+  </si>
+  <si>
+    <t>大桑（栃木）</t>
+  </si>
+  <si>
+    <t>新高徳</t>
+  </si>
+  <si>
+    <t>小佐越</t>
+  </si>
+  <si>
+    <t>東武ワールドスクウェア</t>
+  </si>
+  <si>
+    <t>鬼怒川温泉</t>
+  </si>
+  <si>
+    <t>鬼怒川公園</t>
+  </si>
+  <si>
+    <t>新藤原</t>
+  </si>
+  <si>
+    <t>東武鬼怒川線</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キヌガワ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武鬼怒川線、東武日光線</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キヌガワ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武鬼怒川線、野岩鉄道会津鬼怒川線</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キヌガワ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武佐野線</t>
+  </si>
+  <si>
+    <t>田島</t>
+  </si>
+  <si>
+    <t>佐野市</t>
+  </si>
+  <si>
+    <t>堀米</t>
+  </si>
+  <si>
+    <t>吉水</t>
+  </si>
+  <si>
+    <t>田沼</t>
+  </si>
+  <si>
+    <t>多田（栃木）</t>
+  </si>
+  <si>
+    <t>葛生</t>
+  </si>
+  <si>
+    <t>東武日光線</t>
+  </si>
+  <si>
+    <t>藤岡</t>
+  </si>
+  <si>
+    <t>静和</t>
+  </si>
+  <si>
+    <t>新大平下</t>
+  </si>
+  <si>
+    <t>合戦場</t>
+  </si>
+  <si>
+    <t>家中</t>
+  </si>
+  <si>
+    <t>東武金崎</t>
+  </si>
+  <si>
+    <t>楡木</t>
+  </si>
+  <si>
+    <t>樅山</t>
+  </si>
+  <si>
+    <t>新鹿沼</t>
+  </si>
+  <si>
+    <t>北鹿沼</t>
+  </si>
+  <si>
+    <t>板荷</t>
+  </si>
+  <si>
+    <t>下小代</t>
+  </si>
+  <si>
+    <t>明神</t>
+  </si>
+  <si>
+    <t>上今市</t>
+  </si>
+  <si>
+    <t>東武日光</t>
+  </si>
+  <si>
+    <t>野岩鉄道会津鬼怒川線</t>
+  </si>
+  <si>
+    <t>龍王峡</t>
+  </si>
+  <si>
+    <t>川治温泉</t>
+  </si>
+  <si>
+    <t>川治湯元</t>
+  </si>
+  <si>
+    <t>湯西川温泉</t>
+  </si>
+  <si>
+    <t>中三依温泉</t>
+  </si>
+  <si>
+    <t>上三依塩原温泉口</t>
+  </si>
+  <si>
+    <t>男鹿高原</t>
+  </si>
+  <si>
+    <t>宇都宮芳賀ライトレール線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮駅東口</t>
+  </si>
+  <si>
+    <t>東宿郷</t>
+  </si>
+  <si>
+    <t>駅東公園前</t>
+  </si>
+  <si>
+    <t>峰</t>
+  </si>
+  <si>
+    <t>陽東３丁目</t>
+  </si>
+  <si>
+    <t>宇都宮大学陽東キャンパス</t>
+  </si>
+  <si>
+    <t>平石（栃木）</t>
+  </si>
+  <si>
+    <t>平石中央小学校前</t>
+  </si>
+  <si>
+    <t>飛山城跡</t>
+  </si>
+  <si>
+    <t>清陵高校前</t>
+  </si>
+  <si>
+    <t>清原地区市民センター前</t>
+  </si>
+  <si>
+    <t>グリーンスタジアム前</t>
+  </si>
+  <si>
+    <t>ゆいの杜西</t>
+  </si>
+  <si>
+    <t>ゆいの杜中央</t>
+  </si>
+  <si>
+    <t>ゆいの杜東</t>
+  </si>
+  <si>
+    <t>芳賀台</t>
+  </si>
+  <si>
+    <t>芳賀町工業団地管理センター前</t>
+  </si>
+  <si>
+    <t>かしの森公園前</t>
+  </si>
+  <si>
+    <t>芳賀・高根沢工業団地</t>
   </si>
 </sst>
 </file>
@@ -6838,7 +7504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B1541"/>
+  <dimension ref="A1:B1678"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -16853,308 +17519,308 @@
         <v>1397</v>
       </c>
       <c r="B1266" t="s">
-        <v>1399</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1267" spans="1:2">
       <c r="A1267" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B1267" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1268" spans="1:2">
       <c r="A1268" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B1268" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1269" spans="1:2">
       <c r="A1269" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B1269" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1270" spans="1:2">
       <c r="A1270" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B1270" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1271" spans="1:2">
       <c r="A1271" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B1271" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1272" spans="1:2">
       <c r="A1272" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B1272" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1273" spans="1:2">
       <c r="A1273" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1273" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1274" spans="1:2">
       <c r="A1274" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1274" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1275" spans="1:2">
       <c r="A1275" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1275" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1276" spans="1:2">
       <c r="A1276" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B1276" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1277" spans="1:2">
       <c r="A1277" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B1277" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1278" spans="1:2">
       <c r="A1278" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B1278" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1279" spans="1:2">
       <c r="A1279" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1279" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1280" spans="1:2">
       <c r="A1280" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B1280" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1281" spans="1:2">
       <c r="A1281" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B1281" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1282" spans="1:2">
       <c r="A1282" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B1282" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1283" spans="1:2">
       <c r="A1283" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B1283" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1284" spans="1:2">
       <c r="A1284" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B1284" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1285" spans="1:2">
       <c r="A1285" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B1285" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1286" spans="1:2">
       <c r="A1286" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B1286" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1287" spans="1:2">
       <c r="A1287" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B1287" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1288" spans="1:2">
       <c r="A1288" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B1288" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1289" spans="1:2">
       <c r="A1289" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B1289" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1290" spans="1:2">
       <c r="A1290" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B1290" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1291" spans="1:2">
       <c r="A1291" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B1291" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1292" spans="1:2">
       <c r="A1292" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1292" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1293" spans="1:2">
       <c r="A1293" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1293" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1294" spans="1:2">
       <c r="A1294" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B1294" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1295" spans="1:2">
       <c r="A1295" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B1295" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1296" spans="1:2">
       <c r="A1296" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1296" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1297" spans="1:2">
       <c r="A1297" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1297" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1298" spans="1:2">
       <c r="A1298" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1298" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1299" spans="1:2">
       <c r="A1299" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1299" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1300" spans="1:2">
       <c r="A1300" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1300" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1301" spans="1:2">
       <c r="A1301" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1301" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1302" spans="1:2">
       <c r="A1302" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1302" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1303" spans="1:2">
       <c r="A1303" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B1303" t="s">
         <v>1439</v>
-      </c>
-      <c r="B1303" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="1304" spans="1:2">
       <c r="A1304" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1304" t="s">
         <v>764</v>
@@ -17162,7 +17828,7 @@
     </row>
     <row r="1305" spans="1:2">
       <c r="A1305" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1305" t="s">
         <v>764</v>
@@ -17170,7 +17836,7 @@
     </row>
     <row r="1306" spans="1:2">
       <c r="A1306" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1306" t="s">
         <v>764</v>
@@ -17178,7 +17844,7 @@
     </row>
     <row r="1307" spans="1:2">
       <c r="A1307" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B1307" t="s">
         <v>764</v>
@@ -17186,7 +17852,7 @@
     </row>
     <row r="1308" spans="1:2">
       <c r="A1308" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B1308" t="s">
         <v>764</v>
@@ -17194,7 +17860,7 @@
     </row>
     <row r="1309" spans="1:2">
       <c r="A1309" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B1309" t="s">
         <v>764</v>
@@ -17202,7 +17868,7 @@
     </row>
     <row r="1310" spans="1:2">
       <c r="A1310" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1310" t="s">
         <v>764</v>
@@ -17210,7 +17876,7 @@
     </row>
     <row r="1311" spans="1:2">
       <c r="A1311" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1311" t="s">
         <v>764</v>
@@ -17218,7 +17884,7 @@
     </row>
     <row r="1312" spans="1:2">
       <c r="A1312" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B1312" t="s">
         <v>764</v>
@@ -17226,7 +17892,7 @@
     </row>
     <row r="1313" spans="1:2">
       <c r="A1313" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B1313" t="s">
         <v>764</v>
@@ -17234,7 +17900,7 @@
     </row>
     <row r="1314" spans="1:2">
       <c r="A1314" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1314" t="s">
         <v>764</v>
@@ -17242,7 +17908,7 @@
     </row>
     <row r="1315" spans="1:2">
       <c r="A1315" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1315" t="s">
         <v>764</v>
@@ -17250,7 +17916,7 @@
     </row>
     <row r="1316" spans="1:2">
       <c r="A1316" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1316" t="s">
         <v>764</v>
@@ -17258,7 +17924,7 @@
     </row>
     <row r="1317" spans="1:2">
       <c r="A1317" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1317" t="s">
         <v>764</v>
@@ -17266,7 +17932,7 @@
     </row>
     <row r="1318" spans="1:2">
       <c r="A1318" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1318" t="s">
         <v>764</v>
@@ -17274,7 +17940,7 @@
     </row>
     <row r="1319" spans="1:2">
       <c r="A1319" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1319" t="s">
         <v>764</v>
@@ -17282,7 +17948,7 @@
     </row>
     <row r="1320" spans="1:2">
       <c r="A1320" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1320" t="s">
         <v>764</v>
@@ -17290,7 +17956,7 @@
     </row>
     <row r="1321" spans="1:2">
       <c r="A1321" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1321" t="s">
         <v>764</v>
@@ -17298,7 +17964,7 @@
     </row>
     <row r="1322" spans="1:2">
       <c r="A1322" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1322" t="s">
         <v>764</v>
@@ -17306,7 +17972,7 @@
     </row>
     <row r="1323" spans="1:2">
       <c r="A1323" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1323" t="s">
         <v>764</v>
@@ -17314,7 +17980,7 @@
     </row>
     <row r="1324" spans="1:2">
       <c r="A1324" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1324" t="s">
         <v>764</v>
@@ -17322,319 +17988,319 @@
     </row>
     <row r="1325" spans="1:2">
       <c r="A1325" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1325" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1326" spans="1:2">
       <c r="A1326" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1326" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1327" spans="1:2">
       <c r="A1327" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B1327" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1328" spans="1:2">
       <c r="A1328" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1328" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1329" spans="1:2">
       <c r="A1329" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B1329" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1330" spans="1:2">
       <c r="A1330" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1330" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1331" spans="1:2">
       <c r="A1331" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1331" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1332" spans="1:2">
       <c r="A1332" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1332" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1333" spans="1:2">
       <c r="A1333" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1333" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1334" spans="1:2">
       <c r="A1334" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1334" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1335" spans="1:2">
       <c r="A1335" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1335" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1336" spans="1:2">
       <c r="A1336" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1336" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1337" spans="1:2">
       <c r="A1337" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1337" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1338" spans="1:2">
       <c r="A1338" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1338" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1339" spans="1:2">
       <c r="A1339" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1339" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1340" spans="1:2">
       <c r="A1340" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1340" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1341" spans="1:2">
       <c r="A1341" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1341" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1342" spans="1:2">
       <c r="A1342" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1342" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1343" spans="1:2">
       <c r="A1343" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B1343" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1344" spans="1:2">
       <c r="A1344" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1344" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1345" spans="1:2">
       <c r="A1345" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1345" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1346" spans="1:2">
       <c r="A1346" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1346" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1347" spans="1:2">
       <c r="A1347" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1347" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1348" spans="1:2">
       <c r="A1348" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B1348" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1349" spans="1:2">
       <c r="A1349" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1349" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1350" spans="1:2">
       <c r="A1350" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B1350" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
       <c r="A1351" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B1351" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
       <c r="A1352" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B1352" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1353" spans="1:2">
       <c r="A1353" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B1353" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1354" spans="1:2">
       <c r="A1354" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B1354" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1355" spans="1:2">
       <c r="A1355" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B1355" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1356" spans="1:2">
       <c r="A1356" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B1356" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1357" spans="1:2">
       <c r="A1357" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1357" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1358" spans="1:2">
       <c r="A1358" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B1358" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1359" spans="1:2">
       <c r="A1359" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B1359" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1360" spans="1:2">
       <c r="A1360" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1360" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1361" spans="1:2">
       <c r="A1361" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B1361" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1362" spans="1:2">
       <c r="A1362" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B1362" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1363" spans="1:2">
       <c r="A1363" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B1363" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1364" spans="1:2">
       <c r="A1364" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B1364" t="s">
         <v>1018</v>
@@ -17642,7 +18308,7 @@
     </row>
     <row r="1365" spans="1:2">
       <c r="A1365" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B1365" t="s">
         <v>1018</v>
@@ -17650,7 +18316,7 @@
     </row>
     <row r="1366" spans="1:2">
       <c r="A1366" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B1366" t="s">
         <v>1018</v>
@@ -17658,7 +18324,7 @@
     </row>
     <row r="1367" spans="1:2">
       <c r="A1367" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B1367" t="s">
         <v>1018</v>
@@ -17666,7 +18332,7 @@
     </row>
     <row r="1368" spans="1:2">
       <c r="A1368" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B1368" t="s">
         <v>1018</v>
@@ -17674,7 +18340,7 @@
     </row>
     <row r="1369" spans="1:2">
       <c r="A1369" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B1369" t="s">
         <v>1018</v>
@@ -17682,7 +18348,7 @@
     </row>
     <row r="1370" spans="1:2">
       <c r="A1370" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B1370" t="s">
         <v>1018</v>
@@ -17690,7 +18356,7 @@
     </row>
     <row r="1371" spans="1:2">
       <c r="A1371" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1371" t="s">
         <v>1018</v>
@@ -17698,7 +18364,7 @@
     </row>
     <row r="1372" spans="1:2">
       <c r="A1372" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B1372" t="s">
         <v>1018</v>
@@ -17706,7 +18372,7 @@
     </row>
     <row r="1373" spans="1:2">
       <c r="A1373" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1373" t="s">
         <v>1018</v>
@@ -17714,7 +18380,7 @@
     </row>
     <row r="1374" spans="1:2">
       <c r="A1374" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1374" t="s">
         <v>1018</v>
@@ -17722,7 +18388,7 @@
     </row>
     <row r="1375" spans="1:2">
       <c r="A1375" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B1375" t="s">
         <v>1018</v>
@@ -17730,7 +18396,7 @@
     </row>
     <row r="1376" spans="1:2">
       <c r="A1376" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B1376" t="s">
         <v>1018</v>
@@ -17738,7 +18404,7 @@
     </row>
     <row r="1377" spans="1:2">
       <c r="A1377" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B1377" t="s">
         <v>1018</v>
@@ -17746,1292 +18412,2372 @@
     </row>
     <row r="1378" spans="1:2">
       <c r="A1378" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B1378" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1379" spans="1:2">
       <c r="A1379" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B1379" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1380" spans="1:2">
       <c r="A1380" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1380" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1381" spans="1:2">
       <c r="A1381" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1381" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1382" spans="1:2">
       <c r="A1382" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B1382" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1383" spans="1:2">
       <c r="A1383" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B1383" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1384" spans="1:2">
       <c r="A1384" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B1384" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1385" spans="1:2">
       <c r="A1385" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B1385" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1386" spans="1:2">
       <c r="A1386" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B1386" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1387" spans="1:2">
       <c r="A1387" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1387" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1388" spans="1:2">
       <c r="A1388" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1388" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1389" spans="1:2">
       <c r="A1389" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B1389" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1390" spans="1:2">
       <c r="A1390" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1390" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1391" spans="1:2">
       <c r="A1391" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B1391" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1392" spans="1:2">
       <c r="A1392" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B1392" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1393" spans="1:2">
       <c r="A1393" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1393" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1394" spans="1:2">
       <c r="A1394" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B1394" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1395" spans="1:2">
       <c r="A1395" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1395" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1396" spans="1:2">
       <c r="A1396" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B1396" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1397" spans="1:2">
       <c r="A1397" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:2">
+      <c r="A1398" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B1398" t="s">
         <v>1538</v>
       </c>
-      <c r="B1397" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="1398" spans="1:2">
-      <c r="A1398" s="2" t="s">
-        <v>1540</v>
-      </c>
-      <c r="B1398" t="s">
-        <v>1539</v>
-      </c>
     </row>
     <row r="1399" spans="1:2">
-      <c r="A1399" s="2" t="s">
+      <c r="A1399" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:2">
+      <c r="A1400" t="s">
         <v>1542</v>
       </c>
-      <c r="B1399" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1400" spans="1:2">
-      <c r="A1400" s="2" t="s">
+      <c r="B1400" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:2">
+      <c r="A1401" t="s">
         <v>1543</v>
       </c>
-      <c r="B1400" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1401" spans="1:2">
-      <c r="A1401" s="2" t="s">
+      <c r="B1401" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:2">
+      <c r="A1402" t="s">
         <v>1544</v>
       </c>
-      <c r="B1401" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1402" spans="1:2">
-      <c r="A1402" s="2" t="s">
+      <c r="B1402" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:2">
+      <c r="A1403" t="s">
         <v>1545</v>
       </c>
-      <c r="B1402" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1403" spans="1:2">
-      <c r="A1403" s="2" t="s">
+      <c r="B1403" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:2">
+      <c r="A1404" t="s">
         <v>1546</v>
       </c>
-      <c r="B1403" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1404" spans="1:2">
-      <c r="A1404" s="2" t="s">
+      <c r="B1404" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:2">
+      <c r="A1405" t="s">
         <v>1547</v>
       </c>
-      <c r="B1404" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1405" spans="1:2">
-      <c r="A1405" s="2" t="s">
+      <c r="B1405" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:2">
+      <c r="A1406" t="s">
         <v>1548</v>
       </c>
-      <c r="B1405" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1406" spans="1:2">
-      <c r="A1406" s="2" t="s">
+      <c r="B1406" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:2">
+      <c r="A1407" t="s">
         <v>1549</v>
       </c>
-      <c r="B1406" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1407" spans="1:2">
-      <c r="A1407" s="2" t="s">
+      <c r="B1407" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:2">
+      <c r="A1408" t="s">
         <v>1550</v>
       </c>
-      <c r="B1407" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1408" spans="1:2">
-      <c r="A1408" s="2" t="s">
-        <v>1551</v>
-      </c>
       <c r="B1408" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1411" spans="1:2">
       <c r="A1411" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2">
+      <c r="A1412" t="s">
         <v>1552</v>
       </c>
-    </row>
-    <row r="1412" spans="1:2">
-      <c r="A1412" s="2" t="s">
-        <v>1553</v>
-      </c>
       <c r="B1412" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1413" spans="1:2">
       <c r="A1413" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1413" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1414" spans="1:2">
       <c r="A1414" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B1414" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1415" spans="1:2">
       <c r="A1415" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B1415" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2">
+      <c r="A1416" t="s">
         <v>1558</v>
-      </c>
-    </row>
-    <row r="1416" spans="1:2">
-      <c r="A1416" s="2" t="s">
-        <v>1559</v>
       </c>
       <c r="B1416" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1417" spans="1:2">
-      <c r="A1417" s="2" t="s">
-        <v>1560</v>
+      <c r="A1417" t="s">
+        <v>1559</v>
       </c>
       <c r="B1417" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1418" spans="1:2">
-      <c r="A1418" s="2" t="s">
-        <v>1561</v>
+      <c r="A1418" t="s">
+        <v>1560</v>
       </c>
       <c r="B1418" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1419" spans="1:2">
-      <c r="A1419" s="2" t="s">
-        <v>1562</v>
+      <c r="A1419" t="s">
+        <v>1561</v>
       </c>
       <c r="B1419" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1420" spans="1:2">
-      <c r="A1420" s="2" t="s">
-        <v>1563</v>
+      <c r="A1420" t="s">
+        <v>1562</v>
       </c>
       <c r="B1420" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1421" spans="1:2">
-      <c r="A1421" s="2" t="s">
-        <v>1564</v>
+      <c r="A1421" t="s">
+        <v>1563</v>
       </c>
       <c r="B1421" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1422" spans="1:2">
-      <c r="A1422" s="2" t="s">
-        <v>1565</v>
+      <c r="A1422" t="s">
+        <v>1564</v>
       </c>
       <c r="B1422" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1423" spans="1:2">
-      <c r="A1423" s="2" t="s">
-        <v>1566</v>
+      <c r="A1423" t="s">
+        <v>1565</v>
       </c>
       <c r="B1423" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1424" spans="1:2">
-      <c r="A1424" s="2" t="s">
-        <v>1567</v>
+      <c r="A1424" t="s">
+        <v>1566</v>
       </c>
       <c r="B1424" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1425" spans="1:2">
-      <c r="A1425" s="2" t="s">
-        <v>1568</v>
+      <c r="A1425" t="s">
+        <v>1567</v>
       </c>
       <c r="B1425" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1426" spans="1:2">
-      <c r="A1426" s="2" t="s">
-        <v>1569</v>
+      <c r="A1426" t="s">
+        <v>1568</v>
       </c>
       <c r="B1426" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="1427" spans="1:2">
-      <c r="A1427" s="2" t="s">
+      <c r="A1427" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2">
+      <c r="A1428" t="s">
         <v>1570</v>
       </c>
-      <c r="B1427" t="s">
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="1428" spans="1:2">
-      <c r="A1428" s="2" t="s">
+      <c r="B1428" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2">
+      <c r="A1429" t="s">
         <v>1571</v>
       </c>
-      <c r="B1428" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="1429" spans="1:2">
-      <c r="A1429" s="2" t="s">
+      <c r="B1429" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2">
+      <c r="A1430" t="s">
         <v>1572</v>
       </c>
-      <c r="B1429" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="1430" spans="1:2">
-      <c r="A1430" s="2" t="s">
+      <c r="B1430" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2">
+      <c r="A1431" t="s">
         <v>1573</v>
       </c>
-      <c r="B1430" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="1431" spans="1:2">
-      <c r="A1431" s="2" t="s">
+      <c r="B1431" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2">
+      <c r="A1432" t="s">
         <v>1574</v>
       </c>
-      <c r="B1431" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="1432" spans="1:2">
-      <c r="A1432" s="2" t="s">
+      <c r="B1432" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2">
+      <c r="A1433" t="s">
         <v>1575</v>
       </c>
-      <c r="B1432" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="1433" spans="1:2">
-      <c r="A1433" s="2" t="s">
+      <c r="B1433" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2">
+      <c r="A1434" t="s">
         <v>1576</v>
       </c>
-      <c r="B1433" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1434" spans="1:2">
-      <c r="A1434" s="2" t="s">
+      <c r="B1434" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2">
+      <c r="A1435" t="s">
         <v>1577</v>
       </c>
-      <c r="B1434" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1435" spans="1:2">
-      <c r="A1435" s="2" t="s">
+      <c r="B1435" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2">
+      <c r="A1436" t="s">
         <v>1578</v>
       </c>
-      <c r="B1435" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1436" spans="1:2">
-      <c r="A1436" s="2" t="s">
+      <c r="B1436" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2">
+      <c r="A1437" t="s">
         <v>1579</v>
       </c>
-      <c r="B1436" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1437" spans="1:2">
-      <c r="A1437" s="2" t="s">
-        <v>1580</v>
-      </c>
       <c r="B1437" t="s">
-        <v>890</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1438" spans="1:2">
       <c r="A1438" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2">
+      <c r="A1439" t="s">
         <v>1581</v>
       </c>
-      <c r="B1438" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1439" spans="1:2">
-      <c r="A1439" s="2" t="s">
+      <c r="B1439" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2">
+      <c r="A1440" t="s">
         <v>1582</v>
       </c>
-      <c r="B1439" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1440" spans="1:2">
-      <c r="A1440" s="2" t="s">
+      <c r="B1440" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2">
+      <c r="A1441" t="s">
         <v>1583</v>
       </c>
-      <c r="B1440" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1441" spans="1:2">
-      <c r="A1441" s="2" t="s">
+      <c r="B1441" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2">
+      <c r="A1442" t="s">
         <v>1584</v>
       </c>
-      <c r="B1441" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1442" spans="1:2">
-      <c r="A1442" s="2" t="s">
+      <c r="B1442" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2">
+      <c r="A1443" t="s">
         <v>1585</v>
       </c>
-      <c r="B1442" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1443" spans="1:2">
-      <c r="A1443" s="2" t="s">
+      <c r="B1443" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2">
+      <c r="A1444" t="s">
         <v>1586</v>
       </c>
-      <c r="B1443" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="1444" spans="1:2">
-      <c r="A1444" s="2" t="s">
+      <c r="B1444" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2">
+      <c r="A1445" t="s">
         <v>1587</v>
-      </c>
-      <c r="B1444" t="s">
-        <v>1645</v>
-      </c>
-    </row>
-    <row r="1445" spans="1:2">
-      <c r="A1445" s="2" t="s">
-        <v>1591</v>
       </c>
       <c r="B1445" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1446" spans="1:2">
-      <c r="A1446" s="2" t="s">
-        <v>1592</v>
+      <c r="A1446" t="s">
+        <v>1588</v>
       </c>
       <c r="B1446" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1447" spans="1:2">
-      <c r="A1447" s="2" t="s">
-        <v>1593</v>
+      <c r="A1447" t="s">
+        <v>1589</v>
       </c>
       <c r="B1447" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1448" spans="1:2">
-      <c r="A1448" s="2" t="s">
-        <v>1594</v>
+      <c r="A1448" t="s">
+        <v>1590</v>
       </c>
       <c r="B1448" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1449" spans="1:2">
-      <c r="A1449" s="2" t="s">
-        <v>1595</v>
+      <c r="A1449" t="s">
+        <v>1591</v>
       </c>
       <c r="B1449" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1450" spans="1:2">
-      <c r="A1450" s="2" t="s">
-        <v>1596</v>
+      <c r="A1450" t="s">
+        <v>1592</v>
       </c>
       <c r="B1450" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1451" spans="1:2">
-      <c r="A1451" s="2" t="s">
-        <v>1597</v>
+      <c r="A1451" t="s">
+        <v>1593</v>
       </c>
       <c r="B1451" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1452" spans="1:2">
-      <c r="A1452" s="2" t="s">
-        <v>1598</v>
+      <c r="A1452" t="s">
+        <v>1594</v>
       </c>
       <c r="B1452" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1453" spans="1:2">
-      <c r="A1453" s="2" t="s">
-        <v>1599</v>
+      <c r="A1453" t="s">
+        <v>1595</v>
       </c>
       <c r="B1453" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1454" spans="1:2">
-      <c r="A1454" s="2" t="s">
-        <v>1600</v>
+      <c r="A1454" t="s">
+        <v>1596</v>
       </c>
       <c r="B1454" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1455" spans="1:2">
-      <c r="A1455" s="2" t="s">
-        <v>1601</v>
+      <c r="A1455" t="s">
+        <v>1597</v>
       </c>
       <c r="B1455" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1456" spans="1:2">
-      <c r="A1456" s="2" t="s">
-        <v>1602</v>
+      <c r="A1456" t="s">
+        <v>1598</v>
       </c>
       <c r="B1456" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1457" spans="1:2">
-      <c r="A1457" s="2" t="s">
-        <v>1603</v>
+      <c r="A1457" t="s">
+        <v>1599</v>
       </c>
       <c r="B1457" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1458" spans="1:2">
-      <c r="A1458" s="2" t="s">
-        <v>1604</v>
+      <c r="A1458" t="s">
+        <v>1600</v>
       </c>
       <c r="B1458" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1459" spans="1:2">
-      <c r="A1459" s="2" t="s">
-        <v>1605</v>
+      <c r="A1459" t="s">
+        <v>1601</v>
       </c>
       <c r="B1459" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1460" spans="1:2">
-      <c r="A1460" s="2" t="s">
-        <v>1606</v>
+      <c r="A1460" t="s">
+        <v>1602</v>
       </c>
       <c r="B1460" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1461" spans="1:2">
-      <c r="A1461" s="2" t="s">
-        <v>1607</v>
+      <c r="A1461" t="s">
+        <v>1603</v>
       </c>
       <c r="B1461" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1462" spans="1:2">
-      <c r="A1462" s="2" t="s">
-        <v>1608</v>
+      <c r="A1462" t="s">
+        <v>1604</v>
       </c>
       <c r="B1462" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1463" spans="1:2">
-      <c r="A1463" s="2" t="s">
-        <v>1609</v>
+      <c r="A1463" t="s">
+        <v>1605</v>
       </c>
       <c r="B1463" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1464" spans="1:2">
-      <c r="A1464" s="2" t="s">
-        <v>1610</v>
+      <c r="A1464" t="s">
+        <v>1606</v>
       </c>
       <c r="B1464" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1465" spans="1:2">
-      <c r="A1465" s="2" t="s">
-        <v>1611</v>
+      <c r="A1465" t="s">
+        <v>1607</v>
       </c>
       <c r="B1465" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1466" spans="1:2">
-      <c r="A1466" s="2" t="s">
-        <v>1612</v>
+      <c r="A1466" t="s">
+        <v>1608</v>
       </c>
       <c r="B1466" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1467" spans="1:2">
-      <c r="A1467" s="2" t="s">
-        <v>1613</v>
+      <c r="A1467" t="s">
+        <v>1609</v>
       </c>
       <c r="B1467" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1468" spans="1:2">
-      <c r="A1468" s="2" t="s">
-        <v>1614</v>
+      <c r="A1468" t="s">
+        <v>1610</v>
       </c>
       <c r="B1468" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1469" spans="1:2">
-      <c r="A1469" s="2" t="s">
-        <v>1615</v>
+      <c r="A1469" t="s">
+        <v>1611</v>
       </c>
       <c r="B1469" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="1470" spans="1:2">
-      <c r="A1470" s="2" t="s">
+      <c r="A1470" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:2">
+      <c r="A1471" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:2">
+      <c r="A1472" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:2">
+      <c r="A1473" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:2">
+      <c r="A1474" t="s">
         <v>1617</v>
       </c>
-      <c r="B1470" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1471" spans="1:2">
-      <c r="A1471" s="2" t="s">
+      <c r="B1474" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:2">
+      <c r="A1475" t="s">
         <v>1618</v>
       </c>
-      <c r="B1471" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1472" spans="1:2">
-      <c r="A1472" s="2" t="s">
+      <c r="B1475" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:2">
+      <c r="A1476" t="s">
         <v>1619</v>
       </c>
-      <c r="B1472" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1473" spans="1:2">
-      <c r="A1473" s="2" t="s">
+      <c r="B1476" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:2">
+      <c r="A1477" t="s">
         <v>1620</v>
       </c>
-      <c r="B1473" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1474" spans="1:2">
-      <c r="A1474" s="2" t="s">
+      <c r="B1477" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:2">
+      <c r="A1478" t="s">
         <v>1621</v>
       </c>
-      <c r="B1474" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1475" spans="1:2">
-      <c r="A1475" s="2" t="s">
+      <c r="B1478" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:2">
+      <c r="A1479" t="s">
         <v>1622</v>
       </c>
-      <c r="B1475" t="s">
+      <c r="B1479" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:2">
+      <c r="A1480" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:2">
+      <c r="A1481" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:2">
+      <c r="A1482" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:2">
+      <c r="A1483" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:2">
+      <c r="A1484" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:2">
+      <c r="A1485" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:2">
+      <c r="A1486" t="s">
         <v>1631</v>
       </c>
-    </row>
-    <row r="1476" spans="1:2">
-      <c r="A1476" s="2" t="s">
-        <v>1623</v>
-      </c>
-      <c r="B1476" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1477" spans="1:2">
-      <c r="A1477" s="2" t="s">
-        <v>1624</v>
-      </c>
-      <c r="B1477" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1478" spans="1:2">
-      <c r="A1478" s="2" t="s">
-        <v>1625</v>
-      </c>
-      <c r="B1478" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1479" spans="1:2">
-      <c r="A1479" s="2" t="s">
-        <v>1626</v>
-      </c>
-      <c r="B1479" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1480" spans="1:2">
-      <c r="A1480" s="2" t="s">
-        <v>1627</v>
-      </c>
-      <c r="B1480" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1481" spans="1:2">
-      <c r="A1481" s="2" t="s">
-        <v>1628</v>
-      </c>
-      <c r="B1481" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1482" spans="1:2">
-      <c r="A1482" s="2" t="s">
+      <c r="B1486" t="s">
         <v>1629</v>
       </c>
-      <c r="B1482" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1483" spans="1:2">
-      <c r="A1483" s="2" t="s">
-        <v>1630</v>
-      </c>
-      <c r="B1483" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="1484" spans="1:2">
-      <c r="A1484" s="2" t="s">
+    </row>
+    <row r="1487" spans="1:2">
+      <c r="A1487" t="s">
         <v>1632</v>
       </c>
-      <c r="B1484" t="s">
+      <c r="B1487" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:2">
+      <c r="A1488" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:2">
+      <c r="A1489" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:2">
+      <c r="A1490" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:2">
+      <c r="A1491" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:2">
+      <c r="A1492" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:2">
+      <c r="A1493" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:2">
+      <c r="A1494" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:2">
+      <c r="A1495" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:2">
+      <c r="A1496" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:2">
+      <c r="A1497" t="s">
         <v>1644</v>
       </c>
-    </row>
-    <row r="1485" spans="1:2">
-      <c r="A1485" s="2" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B1485" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1486" spans="1:2">
-      <c r="A1486" s="2" t="s">
-        <v>1635</v>
-      </c>
-      <c r="B1486" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1487" spans="1:2">
-      <c r="A1487" s="2" t="s">
-        <v>1636</v>
-      </c>
-      <c r="B1487" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1488" spans="1:2">
-      <c r="A1488" s="2" t="s">
-        <v>1637</v>
-      </c>
-      <c r="B1488" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1489" spans="1:2">
-      <c r="A1489" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="B1489" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1490" spans="1:2">
-      <c r="A1490" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B1490" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1491" spans="1:2">
-      <c r="A1491" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B1491" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1492" spans="1:2">
-      <c r="A1492" s="2" t="s">
+      <c r="B1497" t="s">
         <v>1641</v>
       </c>
-      <c r="B1492" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1493" spans="1:2">
-      <c r="A1493" s="2" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B1493" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1494" spans="1:2">
-      <c r="A1494" s="2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="B1494" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="1495" spans="1:2">
-      <c r="A1495" s="2" t="s">
+    </row>
+    <row r="1498" spans="1:2">
+      <c r="A1498" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:2">
+      <c r="A1499" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:2">
+      <c r="A1500" t="s">
         <v>1647</v>
       </c>
-      <c r="B1495" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1496" spans="1:2">
-      <c r="A1496" s="2" t="s">
+      <c r="B1500" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:2">
+      <c r="A1501" t="s">
         <v>1648</v>
       </c>
-      <c r="B1496" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1497" spans="1:2">
-      <c r="A1497" s="2" t="s">
+      <c r="B1501" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:2">
+      <c r="A1502" t="s">
         <v>1649</v>
       </c>
-      <c r="B1497" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1498" spans="1:2">
-      <c r="A1498" s="2" t="s">
+      <c r="B1502" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:2">
+      <c r="A1503" t="s">
         <v>1650</v>
       </c>
-      <c r="B1498" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1499" spans="1:2">
-      <c r="A1499" s="2" t="s">
+      <c r="B1503" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:2">
+      <c r="A1504" t="s">
         <v>1651</v>
       </c>
-      <c r="B1499" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1500" spans="1:2">
-      <c r="A1500" s="2" t="s">
+      <c r="B1504" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:2">
+      <c r="A1505" t="s">
         <v>1652</v>
       </c>
-      <c r="B1500" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1501" spans="1:2">
-      <c r="A1501" s="2" t="s">
+      <c r="B1505" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:2">
+      <c r="A1506" t="s">
         <v>1653</v>
       </c>
-      <c r="B1501" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1502" spans="1:2">
-      <c r="A1502" s="2" t="s">
+      <c r="B1506" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:2">
+      <c r="A1507" t="s">
         <v>1654</v>
       </c>
-      <c r="B1502" t="s">
+      <c r="B1507" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:2">
+      <c r="A1508" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:2">
+      <c r="A1509" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:2">
+      <c r="A1510" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:2">
+      <c r="A1511" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:2">
+      <c r="A1512" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:2">
+      <c r="A1513" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:2">
+      <c r="A1514" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:2">
+      <c r="A1515" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:2">
+      <c r="A1516" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:2">
+      <c r="A1517" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:2">
+      <c r="A1518" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:2">
+      <c r="A1519" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:2">
+      <c r="A1520" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:2">
+      <c r="A1521" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1521" t="s">
         <v>1670</v>
       </c>
     </row>
-    <row r="1503" spans="1:2">
-      <c r="A1503" s="2" t="s">
-        <v>1655</v>
-      </c>
-      <c r="B1503" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1504" spans="1:2">
-      <c r="A1504" s="2" t="s">
-        <v>1656</v>
-      </c>
-      <c r="B1504" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1505" spans="1:2">
-      <c r="A1505" s="2" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B1505" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1506" spans="1:2">
-      <c r="A1506" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B1506" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1507" spans="1:2">
-      <c r="A1507" s="2" t="s">
-        <v>1659</v>
-      </c>
-      <c r="B1507" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1508" spans="1:2">
-      <c r="A1508" s="2" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B1508" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1509" spans="1:2">
-      <c r="A1509" s="2" t="s">
-        <v>1661</v>
-      </c>
-      <c r="B1509" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1510" spans="1:2">
-      <c r="A1510" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B1510" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1511" spans="1:2">
-      <c r="A1511" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="B1511" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1512" spans="1:2">
-      <c r="A1512" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="B1512" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1513" spans="1:2">
-      <c r="A1513" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="B1513" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1514" spans="1:2">
-      <c r="A1514" s="2" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B1514" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1515" spans="1:2">
-      <c r="A1515" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="B1515" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1516" spans="1:2">
-      <c r="A1516" s="2" t="s">
-        <v>1668</v>
-      </c>
-      <c r="B1516" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1517" spans="1:2">
-      <c r="A1517" s="2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="B1517" t="s">
-        <v>1646</v>
-      </c>
-    </row>
-    <row r="1518" spans="1:2">
-      <c r="A1518" s="2" t="s">
+    <row r="1522" spans="1:2">
+      <c r="A1522" t="s">
         <v>1672</v>
       </c>
-      <c r="B1518" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="1519" spans="1:2">
-      <c r="A1519" s="2" t="s">
+      <c r="B1522" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:2">
+      <c r="A1523" t="s">
         <v>1673</v>
       </c>
-      <c r="B1519" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="1520" spans="1:2">
-      <c r="A1520" s="2" t="s">
+      <c r="B1523" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:2">
+      <c r="A1524" t="s">
         <v>1674</v>
       </c>
-      <c r="B1520" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="1521" spans="1:2">
-      <c r="A1521" s="2" t="s">
+      <c r="B1524" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:2">
+      <c r="A1525" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:2">
+      <c r="A1526" t="s">
         <v>1676</v>
       </c>
-      <c r="B1521" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1522" spans="1:2">
-      <c r="A1522" s="2" t="s">
+      <c r="B1526" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:2">
+      <c r="A1527" t="s">
         <v>1677</v>
       </c>
-      <c r="B1522" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1523" spans="1:2">
-      <c r="A1523" s="2" t="s">
+      <c r="B1527" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:2">
+      <c r="A1528" t="s">
         <v>1678</v>
       </c>
-      <c r="B1523" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1524" spans="1:2">
-      <c r="A1524" s="2" t="s">
+      <c r="B1528" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:2">
+      <c r="A1529" t="s">
         <v>1679</v>
       </c>
-      <c r="B1524" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1525" spans="1:2">
-      <c r="A1525" s="2" t="s">
+      <c r="B1529" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:2">
+      <c r="A1530" t="s">
         <v>1680</v>
       </c>
-      <c r="B1525" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1526" spans="1:2">
-      <c r="A1526" s="2" t="s">
+      <c r="B1530" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:2">
+      <c r="A1531" t="s">
         <v>1681</v>
       </c>
-      <c r="B1526" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1527" spans="1:2">
-      <c r="A1527" s="2" t="s">
+      <c r="B1531" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:2">
+      <c r="A1532" t="s">
         <v>1682</v>
       </c>
-      <c r="B1527" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1528" spans="1:2">
-      <c r="A1528" s="2" t="s">
+      <c r="B1532" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:2">
+      <c r="A1533" t="s">
         <v>1683</v>
       </c>
-      <c r="B1528" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1529" spans="1:2">
-      <c r="A1529" s="2" t="s">
+      <c r="B1533" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:2">
+      <c r="A1534" t="s">
         <v>1684</v>
       </c>
-      <c r="B1529" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1530" spans="1:2">
-      <c r="A1530" s="2" t="s">
+      <c r="B1534" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:2">
+      <c r="A1535" t="s">
         <v>1685</v>
       </c>
-      <c r="B1530" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1531" spans="1:2">
-      <c r="A1531" s="2" t="s">
+      <c r="B1535" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:2">
+      <c r="A1536" t="s">
         <v>1686</v>
       </c>
-      <c r="B1531" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1532" spans="1:2">
-      <c r="A1532" s="2" t="s">
+      <c r="B1536" t="s">
         <v>1687</v>
       </c>
-      <c r="B1532" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1533" spans="1:2">
-      <c r="A1533" s="2" t="s">
+    </row>
+    <row r="1537" spans="1:2">
+      <c r="A1537" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1537" t="s">
         <v>1688</v>
       </c>
-      <c r="B1533" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="1534" spans="1:2">
-      <c r="A1534" s="2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="B1534" t="s">
+    </row>
+    <row r="1538" spans="1:2">
+      <c r="A1538" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:2">
+      <c r="A1539" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:2">
+      <c r="A1540" t="s">
         <v>1692</v>
       </c>
-    </row>
-    <row r="1535" spans="1:2">
-      <c r="A1535" s="2" t="s">
-        <v>1690</v>
-      </c>
-      <c r="B1535" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="1536" spans="1:2">
-      <c r="A1536" s="2" t="s">
-        <v>1691</v>
-      </c>
-      <c r="B1536" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="1537" spans="1:2">
-      <c r="A1537" s="2" t="s">
+      <c r="B1540" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:2">
+      <c r="A1541" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:2">
+      <c r="A1544" t="s">
         <v>1694</v>
       </c>
-      <c r="B1537" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="1538" spans="1:2">
-      <c r="A1538" s="2" t="s">
+    </row>
+    <row r="1545" spans="1:2">
+      <c r="A1545" s="2" t="s">
         <v>1695</v>
       </c>
-      <c r="B1538" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="1539" spans="1:2">
-      <c r="A1539" s="2" t="s">
+      <c r="B1545" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:2">
+      <c r="A1546" s="2" t="s">
         <v>1696</v>
       </c>
-      <c r="B1539" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="1540" spans="1:2">
-      <c r="A1540" s="2" t="s">
+      <c r="B1546" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:2">
+      <c r="A1547" s="2" t="s">
         <v>1697</v>
       </c>
-      <c r="B1540" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="1541" spans="1:2">
-      <c r="A1541" s="2" t="s">
+      <c r="B1547" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:2">
+      <c r="A1548" s="2" t="s">
         <v>1698</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:2">
+      <c r="A1549" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:2">
+      <c r="A1550" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:2">
+      <c r="A1551" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:2">
+      <c r="A1552" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:2">
+      <c r="A1553" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:2">
+      <c r="A1554" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:2">
+      <c r="A1555" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:2">
+      <c r="A1556" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:2">
+      <c r="A1557" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:2">
+      <c r="A1558" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:2">
+      <c r="A1559" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:2">
+      <c r="A1560" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:2">
+      <c r="A1561" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:2">
+      <c r="A1562" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:2">
+      <c r="A1563" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:2">
+      <c r="A1564" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:2">
+      <c r="A1565" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:2">
+      <c r="A1566" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:2">
+      <c r="A1567" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:2">
+      <c r="A1568" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:2">
+      <c r="A1569" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:2">
+      <c r="A1570" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:2">
+      <c r="A1571" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:2">
+      <c r="A1572" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:2">
+      <c r="A1573" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:2">
+      <c r="A1574" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:2">
+      <c r="A1575" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:2">
+      <c r="A1576" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:2">
+      <c r="A1577" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:2">
+      <c r="A1578" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:2">
+      <c r="A1579" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:2">
+      <c r="A1580" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:2">
+      <c r="A1581" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:2">
+      <c r="A1582" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:2">
+      <c r="A1583" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:2">
+      <c r="A1584" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:2">
+      <c r="A1585" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:2">
+      <c r="A1586" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:2">
+      <c r="A1587" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:2">
+      <c r="A1588" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:2">
+      <c r="A1589" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:2">
+      <c r="A1590" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:2">
+      <c r="A1591" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:2">
+      <c r="A1592" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:2">
+      <c r="A1593" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:2">
+      <c r="A1594" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:2">
+      <c r="A1595" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:2">
+      <c r="A1596" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:2">
+      <c r="A1597" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:2">
+      <c r="A1598" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:2">
+      <c r="A1599" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:2">
+      <c r="A1600" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:2">
+      <c r="A1601" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:2">
+      <c r="A1602" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:2">
+      <c r="A1603" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:2">
+      <c r="A1604" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:2">
+      <c r="A1605" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:2">
+      <c r="A1606" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:2">
+      <c r="A1607" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:2">
+      <c r="A1608" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:2">
+      <c r="A1609" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:2">
+      <c r="A1610" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:2">
+      <c r="A1611" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:2">
+      <c r="A1612" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:2">
+      <c r="A1613" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:2">
+      <c r="A1614" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:2">
+      <c r="A1615" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:2">
+      <c r="A1616" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:2">
+      <c r="A1617" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:2">
+      <c r="A1618" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:2">
+      <c r="A1619" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:2">
+      <c r="A1620" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:2">
+      <c r="A1621" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:2">
+      <c r="A1622" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:2">
+      <c r="A1623" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:2">
+      <c r="A1624" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:2">
+      <c r="A1625" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:2">
+      <c r="A1626" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:2">
+      <c r="A1627" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:2">
+      <c r="A1628" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:2">
+      <c r="A1629" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:2">
+      <c r="A1630" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:2">
+      <c r="A1631" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:2">
+      <c r="A1632" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:2">
+      <c r="A1633" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:2">
+      <c r="A1634" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:2">
+      <c r="A1635" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:2">
+      <c r="A1636" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:2">
+      <c r="A1637" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:2">
+      <c r="A1638" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:2">
+      <c r="A1639" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:2">
+      <c r="A1640" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:2">
+      <c r="A1641" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:2">
+      <c r="A1642" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:2">
+      <c r="A1643" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:2">
+      <c r="A1644" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:2">
+      <c r="A1645" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:2">
+      <c r="A1646" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:2">
+      <c r="A1647" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:2">
+      <c r="A1648" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:2">
+      <c r="A1649" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:2">
+      <c r="A1650" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:2">
+      <c r="A1651" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:2">
+      <c r="A1652" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:2">
+      <c r="A1653" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:2">
+      <c r="A1654" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:2">
+      <c r="A1655" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:2">
+      <c r="A1656" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:2">
+      <c r="A1657" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:2">
+      <c r="A1658" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:2">
+      <c r="A1659" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:2">
+      <c r="A1660" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:2">
+      <c r="A1661" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:2">
+      <c r="A1662" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:2">
+      <c r="A1663" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:2">
+      <c r="A1664" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:2">
+      <c r="A1665" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:2">
+      <c r="A1666" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:2">
+      <c r="A1667" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:2">
+      <c r="A1668" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:2">
+      <c r="A1669" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:2">
+      <c r="A1670" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:2">
+      <c r="A1671" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:2">
+      <c r="A1672" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:2">
+      <c r="A1673" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:2">
+      <c r="A1674" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:2">
+      <c r="A1675" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:2">
+      <c r="A1676" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:2">
+      <c r="A1677" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:2">
+      <c r="A1678" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>1841</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{718787A7-7B82-4005-9FF9-6CCD2951A242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3037AF-F9A4-4546-BFCF-BE4D8C8FE3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3315" uniqueCount="1861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3584" uniqueCount="2021">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -6538,48 +6538,6 @@
     <t>野木</t>
   </si>
   <si>
-    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
-    <rPh sb="0" eb="4">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>烏山線、宇都宮線、日光線、東北新幹線、（湘南新宿ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>カラスヤマセン</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ニッコウセン</t>
-    </rPh>
-    <rPh sb="13" eb="18">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>水戸線、両毛線、宇都宮線、東北新幹線、（湘南新宿ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="13" eb="18">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>常磐線、水戸線、ひたちなか海浜鉄道、（上野東京ライン）</t>
     <rPh sb="0" eb="3">
       <t>ジョウバンセン</t>
@@ -6645,19 +6603,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
-    <rPh sb="0" eb="4">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>日光</t>
   </si>
   <si>
@@ -7105,6 +7050,739 @@
   </si>
   <si>
     <t>芳賀・高根沢工業団地</t>
+  </si>
+  <si>
+    <t>群馬県</t>
+    <rPh sb="0" eb="3">
+      <t>グンマケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎</t>
+  </si>
+  <si>
+    <t>倉賀野</t>
+  </si>
+  <si>
+    <t>新町（群馬）</t>
+  </si>
+  <si>
+    <t>高崎問屋町</t>
+  </si>
+  <si>
+    <t>井野（群馬）</t>
+  </si>
+  <si>
+    <t>新前橋</t>
+  </si>
+  <si>
+    <t>群馬総社</t>
+  </si>
+  <si>
+    <t>上越線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吾妻線、上越線</t>
+    <rPh sb="0" eb="3">
+      <t>アガヅマセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八木原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渋川</t>
+  </si>
+  <si>
+    <t>金島（群馬）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吾妻線</t>
+    <rPh sb="0" eb="3">
+      <t>アガヅマセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>祖母島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮線、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ウツノミヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ウエノ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>烏山線、宇都宮線、日光線、東北新幹線、湘南新宿ライン</t>
+    <rPh sb="0" eb="3">
+      <t>カラスヤマセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ニッコウセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水戸線、両毛線、宇都宮線、東北新幹線、湘南新宿ライン</t>
+    <rPh sb="0" eb="3">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、上越線、両毛線、吾妻線、上信電鉄、信越本線、八高線、上越新幹線、北陸新幹線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>アガヅマセン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ジョウシンデンテツ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>シンエツホンセン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="30" eb="35">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <rPh sb="36" eb="41">
+      <t>ホクリクシンカンセン</t>
+    </rPh>
+    <rPh sb="51" eb="55">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、八高線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吾妻線、上越線、両毛線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>アガヅマセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="49" eb="53">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小野上</t>
+  </si>
+  <si>
+    <t>小野上温泉</t>
+  </si>
+  <si>
+    <t>市城</t>
+  </si>
+  <si>
+    <t>中之条</t>
+  </si>
+  <si>
+    <t>群馬原町</t>
+  </si>
+  <si>
+    <t>郷原</t>
+  </si>
+  <si>
+    <t>矢倉</t>
+  </si>
+  <si>
+    <t>岩島</t>
+  </si>
+  <si>
+    <t>川原湯温泉</t>
+  </si>
+  <si>
+    <t>長野原草津口</t>
+  </si>
+  <si>
+    <t>群馬大津</t>
+  </si>
+  <si>
+    <t>羽根尾</t>
+  </si>
+  <si>
+    <t>袋倉</t>
+  </si>
+  <si>
+    <t>万座・鹿沢口</t>
+  </si>
+  <si>
+    <t>大前</t>
+  </si>
+  <si>
+    <t>上毛高原</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウモウコウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上越新幹線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>安中榛名</t>
+  </si>
+  <si>
+    <t>北陸新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>ホクリクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敷島</t>
+  </si>
+  <si>
+    <t>津久田</t>
+  </si>
+  <si>
+    <t>岩本</t>
+  </si>
+  <si>
+    <t>沼田</t>
+  </si>
+  <si>
+    <t>後閑</t>
+  </si>
+  <si>
+    <t>上牧（群馬）</t>
+  </si>
+  <si>
+    <t>水上</t>
+  </si>
+  <si>
+    <t>湯檜曽</t>
+  </si>
+  <si>
+    <t>土合</t>
+  </si>
+  <si>
+    <t>北高崎</t>
+  </si>
+  <si>
+    <t>群馬八幡</t>
+  </si>
+  <si>
+    <t>安中</t>
+  </si>
+  <si>
+    <t>磯部（群馬）</t>
+  </si>
+  <si>
+    <t>松井田</t>
+  </si>
+  <si>
+    <t>西松井田</t>
+  </si>
+  <si>
+    <t>横川（群馬）</t>
+  </si>
+  <si>
+    <t>信越本線</t>
+    <rPh sb="0" eb="4">
+      <t>シンエツホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八高線</t>
+  </si>
+  <si>
+    <t>群馬藤岡</t>
+  </si>
+  <si>
+    <t>北藤岡</t>
+  </si>
+  <si>
+    <t>前橋</t>
+  </si>
+  <si>
+    <t>両毛線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前橋大島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駒形</t>
+  </si>
+  <si>
+    <t>伊勢崎</t>
+  </si>
+  <si>
+    <t>国定</t>
+  </si>
+  <si>
+    <t>岩宿</t>
+  </si>
+  <si>
+    <t>桐生</t>
+  </si>
+  <si>
+    <t>両毛線、東武伊勢崎線</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="4" eb="10">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両毛線、わたらせ渓谷鐵道</t>
+    <rPh sb="0" eb="3">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わたらせ渓谷鐵道</t>
+  </si>
+  <si>
+    <t>下新田</t>
+  </si>
+  <si>
+    <t>相老（群馬）</t>
+  </si>
+  <si>
+    <t>運動公園（群馬）</t>
+  </si>
+  <si>
+    <t>大間々</t>
+  </si>
+  <si>
+    <t>上神梅</t>
+  </si>
+  <si>
+    <t>本宿（群馬）</t>
+  </si>
+  <si>
+    <t>水沼</t>
+  </si>
+  <si>
+    <t>花輪</t>
+  </si>
+  <si>
+    <t>中野（群馬）</t>
+  </si>
+  <si>
+    <t>小中</t>
+  </si>
+  <si>
+    <t>神戸（群馬）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沢入</t>
+  </si>
+  <si>
+    <t>わたらせ渓谷鐵道、東武桐生線</t>
+    <rPh sb="9" eb="11">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>キリュウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上信電鉄</t>
+  </si>
+  <si>
+    <t>南高崎</t>
+  </si>
+  <si>
+    <t>佐野のわたし</t>
+  </si>
+  <si>
+    <t>根小屋</t>
+  </si>
+  <si>
+    <t>高崎商科大学前</t>
+  </si>
+  <si>
+    <t>山名</t>
+  </si>
+  <si>
+    <t>西山名</t>
+  </si>
+  <si>
+    <t>馬庭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吉井（群馬）</t>
+  </si>
+  <si>
+    <t>西吉井</t>
+  </si>
+  <si>
+    <t>上州新屋</t>
+  </si>
+  <si>
+    <t>上州福島</t>
+  </si>
+  <si>
+    <t>東富岡</t>
+  </si>
+  <si>
+    <t>上州富岡</t>
+  </si>
+  <si>
+    <t>西富岡</t>
+  </si>
+  <si>
+    <t>上州七日市</t>
+  </si>
+  <si>
+    <t>上州一ノ宮</t>
+  </si>
+  <si>
+    <t>神農原</t>
+  </si>
+  <si>
+    <t>南蛇井</t>
+  </si>
+  <si>
+    <t>千平</t>
+  </si>
+  <si>
+    <t>下仁田</t>
+  </si>
+  <si>
+    <t>上毛電気鉄道</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央前橋</t>
+  </si>
+  <si>
+    <t>城東</t>
+  </si>
+  <si>
+    <t>三俣</t>
+  </si>
+  <si>
+    <t>片貝</t>
+  </si>
+  <si>
+    <t>上泉</t>
+  </si>
+  <si>
+    <t>赤坂（群馬）</t>
+  </si>
+  <si>
+    <t>心臓血管センター</t>
+  </si>
+  <si>
+    <t>江木</t>
+  </si>
+  <si>
+    <t>大胡</t>
+  </si>
+  <si>
+    <t>樋越</t>
+  </si>
+  <si>
+    <t>北原</t>
+  </si>
+  <si>
+    <t>新屋（群馬）</t>
+  </si>
+  <si>
+    <t>粕川</t>
+  </si>
+  <si>
+    <t>膳</t>
+  </si>
+  <si>
+    <t>新里（群馬）</t>
+  </si>
+  <si>
+    <t>新川（群馬）</t>
+  </si>
+  <si>
+    <t>東新川（群馬）</t>
+  </si>
+  <si>
+    <t>赤城（群馬）</t>
+  </si>
+  <si>
+    <t>桐生球場前</t>
+  </si>
+  <si>
+    <t>天王宿</t>
+  </si>
+  <si>
+    <t>富士山下</t>
+  </si>
+  <si>
+    <t>丸山下</t>
+  </si>
+  <si>
+    <t>西桐生</t>
+  </si>
+  <si>
+    <t>上毛電気鉄道、東武桐生線</t>
+    <rPh sb="7" eb="9">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キリウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新伊勢崎</t>
+  </si>
+  <si>
+    <t>剛志</t>
+  </si>
+  <si>
+    <t>境町</t>
+  </si>
+  <si>
+    <t>世良田</t>
+  </si>
+  <si>
+    <t>木崎</t>
+  </si>
+  <si>
+    <t>細谷（群馬）</t>
+  </si>
+  <si>
+    <t>太田（群馬）</t>
+  </si>
+  <si>
+    <t>韮川</t>
+  </si>
+  <si>
+    <t>東武伊勢崎線、東武小泉線、東武桐生線</t>
+    <rPh sb="0" eb="6">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>トウブコイズミセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三枚橋</t>
+  </si>
+  <si>
+    <t>治良門橋</t>
+  </si>
+  <si>
+    <t>藪塚</t>
+  </si>
+  <si>
+    <t>阿左美</t>
+  </si>
+  <si>
+    <t>新桐生</t>
+  </si>
+  <si>
+    <t>東武桐生線</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キリウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武伊勢崎線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武桐生線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多々良（群馬）</t>
+  </si>
+  <si>
+    <t>館林</t>
+  </si>
+  <si>
+    <t>茂林寺前</t>
+  </si>
+  <si>
+    <t>川俣</t>
+  </si>
+  <si>
+    <t>東武伊勢崎線、東武佐野線、東武小泉線</t>
+    <rPh sb="7" eb="12">
+      <t>トウブサノセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウブコイズミセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渡瀬（群馬）</t>
+  </si>
+  <si>
+    <t>東武小泉線</t>
+  </si>
+  <si>
+    <t>西小泉</t>
+  </si>
+  <si>
+    <t>小泉町（群馬）</t>
+  </si>
+  <si>
+    <t>東小泉</t>
+  </si>
+  <si>
+    <t>篠塚</t>
+  </si>
+  <si>
+    <t>本中野</t>
+  </si>
+  <si>
+    <t>成島（群馬）</t>
+  </si>
+  <si>
+    <t>竜舞</t>
+  </si>
+  <si>
+    <t>板倉東洋大前</t>
+    <rPh sb="0" eb="5">
+      <t>イタクラトウヨウダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -7185,6 +7863,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7504,11 +8186,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B1678"/>
+  <dimension ref="A1:B1815"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="2" max="2" width="47.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -18788,7 +19470,7 @@
         <v>1569</v>
       </c>
       <c r="B1427" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1428" spans="1:2">
@@ -18796,7 +19478,7 @@
         <v>1570</v>
       </c>
       <c r="B1428" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1429" spans="1:2">
@@ -18804,7 +19486,7 @@
         <v>1571</v>
       </c>
       <c r="B1429" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1430" spans="1:2">
@@ -18812,7 +19494,7 @@
         <v>1572</v>
       </c>
       <c r="B1430" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1431" spans="1:2">
@@ -18820,7 +19502,7 @@
         <v>1573</v>
       </c>
       <c r="B1431" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1432" spans="1:2">
@@ -18828,7 +19510,7 @@
         <v>1574</v>
       </c>
       <c r="B1432" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1433" spans="1:2">
@@ -18836,7 +19518,7 @@
         <v>1575</v>
       </c>
       <c r="B1433" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1434" spans="1:2">
@@ -18844,7 +19526,7 @@
         <v>1576</v>
       </c>
       <c r="B1434" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1435" spans="1:2">
@@ -18852,7 +19534,7 @@
         <v>1577</v>
       </c>
       <c r="B1435" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1436" spans="1:2">
@@ -18860,7 +19542,7 @@
         <v>1578</v>
       </c>
       <c r="B1436" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1437" spans="1:2">
@@ -18868,7 +19550,7 @@
         <v>1579</v>
       </c>
       <c r="B1437" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1438" spans="1:2">
@@ -18876,7 +19558,7 @@
         <v>1580</v>
       </c>
       <c r="B1438" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1439" spans="1:2">
@@ -18884,7 +19566,7 @@
         <v>1581</v>
       </c>
       <c r="B1439" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1440" spans="1:2">
@@ -18892,7 +19574,7 @@
         <v>1582</v>
       </c>
       <c r="B1440" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1441" spans="1:2">
@@ -18900,7 +19582,7 @@
         <v>1583</v>
       </c>
       <c r="B1441" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1442" spans="1:2">
@@ -18908,7 +19590,7 @@
         <v>1584</v>
       </c>
       <c r="B1442" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1443" spans="1:2">
@@ -18916,7 +19598,7 @@
         <v>1585</v>
       </c>
       <c r="B1443" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1444" spans="1:2">
@@ -19244,7 +19926,7 @@
         <v>1628</v>
       </c>
       <c r="B1484" t="s">
-        <v>1729</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1485" spans="1:2">
@@ -19709,15 +20391,15 @@
       </c>
     </row>
     <row r="1545" spans="1:2">
-      <c r="A1545" s="2" t="s">
+      <c r="A1545" t="s">
         <v>1695</v>
       </c>
       <c r="B1545" t="s">
-        <v>1730</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1546" spans="1:2">
-      <c r="A1546" s="2" t="s">
+      <c r="A1546" t="s">
         <v>1696</v>
       </c>
       <c r="B1546" t="s">
@@ -19725,7 +20407,7 @@
       </c>
     </row>
     <row r="1547" spans="1:2">
-      <c r="A1547" s="2" t="s">
+      <c r="A1547" t="s">
         <v>1697</v>
       </c>
       <c r="B1547" t="s">
@@ -19733,7 +20415,7 @@
       </c>
     </row>
     <row r="1548" spans="1:2">
-      <c r="A1548" s="2" t="s">
+      <c r="A1548" t="s">
         <v>1698</v>
       </c>
       <c r="B1548" t="s">
@@ -19741,7 +20423,7 @@
       </c>
     </row>
     <row r="1549" spans="1:2">
-      <c r="A1549" s="2" t="s">
+      <c r="A1549" t="s">
         <v>1699</v>
       </c>
       <c r="B1549" t="s">
@@ -19749,7 +20431,7 @@
       </c>
     </row>
     <row r="1550" spans="1:2">
-      <c r="A1550" s="2" t="s">
+      <c r="A1550" t="s">
         <v>1700</v>
       </c>
       <c r="B1550" t="s">
@@ -19757,7 +20439,7 @@
       </c>
     </row>
     <row r="1551" spans="1:2">
-      <c r="A1551" s="2" t="s">
+      <c r="A1551" t="s">
         <v>1701</v>
       </c>
       <c r="B1551" t="s">
@@ -19765,7 +20447,7 @@
       </c>
     </row>
     <row r="1552" spans="1:2">
-      <c r="A1552" s="2" t="s">
+      <c r="A1552" t="s">
         <v>1702</v>
       </c>
       <c r="B1552" t="s">
@@ -19773,7 +20455,7 @@
       </c>
     </row>
     <row r="1553" spans="1:2">
-      <c r="A1553" s="2" t="s">
+      <c r="A1553" t="s">
         <v>1703</v>
       </c>
       <c r="B1553" t="s">
@@ -19781,7 +20463,7 @@
       </c>
     </row>
     <row r="1554" spans="1:2">
-      <c r="A1554" s="2" t="s">
+      <c r="A1554" t="s">
         <v>1704</v>
       </c>
       <c r="B1554" t="s">
@@ -19789,15 +20471,15 @@
       </c>
     </row>
     <row r="1555" spans="1:2">
-      <c r="A1555" s="2" t="s">
+      <c r="A1555" t="s">
         <v>1708</v>
       </c>
       <c r="B1555" t="s">
-        <v>1731</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1556" spans="1:2">
-      <c r="A1556" s="2" t="s">
+      <c r="A1556" t="s">
         <v>1709</v>
       </c>
       <c r="B1556" t="s">
@@ -19805,7 +20487,7 @@
       </c>
     </row>
     <row r="1557" spans="1:2">
-      <c r="A1557" s="2" t="s">
+      <c r="A1557" t="s">
         <v>1711</v>
       </c>
       <c r="B1557" t="s">
@@ -19813,7 +20495,7 @@
       </c>
     </row>
     <row r="1558" spans="1:2">
-      <c r="A1558" s="2" t="s">
+      <c r="A1558" t="s">
         <v>1712</v>
       </c>
       <c r="B1558" t="s">
@@ -19821,7 +20503,7 @@
       </c>
     </row>
     <row r="1559" spans="1:2">
-      <c r="A1559" s="2" t="s">
+      <c r="A1559" t="s">
         <v>1713</v>
       </c>
       <c r="B1559" t="s">
@@ -19829,7 +20511,7 @@
       </c>
     </row>
     <row r="1560" spans="1:2">
-      <c r="A1560" s="2" t="s">
+      <c r="A1560" t="s">
         <v>1714</v>
       </c>
       <c r="B1560" t="s">
@@ -19837,947 +20519,2024 @@
       </c>
     </row>
     <row r="1561" spans="1:2">
-      <c r="A1561" s="2" t="s">
+      <c r="A1561" t="s">
         <v>1717</v>
       </c>
       <c r="B1561" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:2">
+      <c r="A1562" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:2">
+      <c r="A1563" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:2">
+      <c r="A1564" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:2">
+      <c r="A1565" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:2">
+      <c r="A1566" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:2">
+      <c r="A1567" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:2">
+      <c r="A1568" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:2">
+      <c r="A1569" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:2">
+      <c r="A1570" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:2">
+      <c r="A1571" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:2">
+      <c r="A1572" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:2">
+      <c r="A1573" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:2">
+      <c r="A1574" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:2">
+      <c r="A1575" t="s">
         <v>1736</v>
       </c>
-    </row>
-    <row r="1562" spans="1:2">
-      <c r="A1562" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="B1562" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="1563" spans="1:2">
-      <c r="A1563" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="B1563" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="1564" spans="1:2">
-      <c r="A1564" s="2" t="s">
-        <v>1720</v>
-      </c>
-      <c r="B1564" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="1565" spans="1:2">
-      <c r="A1565" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="B1565" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="1566" spans="1:2">
-      <c r="A1566" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B1566" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="1567" spans="1:2">
-      <c r="A1567" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="B1567" t="s">
+      <c r="B1575" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:2">
+      <c r="A1576" t="s">
         <v>1737</v>
       </c>
-    </row>
-    <row r="1568" spans="1:2">
-      <c r="A1568" s="2" t="s">
-        <v>1724</v>
-      </c>
-      <c r="B1568" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="1569" spans="1:2">
-      <c r="A1569" s="2" t="s">
-        <v>1725</v>
-      </c>
-      <c r="B1569" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="1570" spans="1:2">
-      <c r="A1570" s="2" t="s">
-        <v>1726</v>
-      </c>
-      <c r="B1570" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="1571" spans="1:2">
-      <c r="A1571" s="2" t="s">
-        <v>1727</v>
-      </c>
-      <c r="B1571" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="1572" spans="1:2">
-      <c r="A1572" s="2" t="s">
-        <v>1728</v>
-      </c>
-      <c r="B1572" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="1573" spans="1:2">
-      <c r="A1573" s="2" t="s">
+      <c r="B1576" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:2">
+      <c r="A1577" t="s">
         <v>1738</v>
       </c>
-      <c r="B1573" t="s">
+      <c r="B1577" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:2">
+      <c r="A1578" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:2">
+      <c r="A1579" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:2">
+      <c r="A1580" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:2">
+      <c r="A1581" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:2">
+      <c r="A1582" t="s">
         <v>1744</v>
       </c>
-    </row>
-    <row r="1574" spans="1:2">
-      <c r="A1574" s="2" t="s">
-        <v>1739</v>
-      </c>
-      <c r="B1574" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="1575" spans="1:2">
-      <c r="A1575" s="2" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B1575" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="1576" spans="1:2">
-      <c r="A1576" s="2" t="s">
-        <v>1741</v>
-      </c>
-      <c r="B1576" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="1577" spans="1:2">
-      <c r="A1577" s="2" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B1577" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="1578" spans="1:2">
-      <c r="A1578" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B1578" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="1579" spans="1:2">
-      <c r="A1579" s="2" t="s">
+      <c r="B1582" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:2">
+      <c r="A1583" t="s">
         <v>1745</v>
       </c>
-      <c r="B1579" t="s">
+      <c r="B1583" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:2">
+      <c r="A1584" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:2">
+      <c r="A1585" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:2">
+      <c r="A1586" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:2">
+      <c r="A1587" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:2">
+      <c r="A1588" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:2">
+      <c r="A1589" t="s">
         <v>1755</v>
       </c>
-    </row>
-    <row r="1580" spans="1:2">
-      <c r="A1580" s="2" t="s">
-        <v>1746</v>
-      </c>
-      <c r="B1580" t="s">
+      <c r="B1589" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:2">
+      <c r="A1590" t="s">
         <v>1756</v>
       </c>
-    </row>
-    <row r="1581" spans="1:2">
-      <c r="A1581" s="2" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1581" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1582" spans="1:2">
-      <c r="A1582" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B1582" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1583" spans="1:2">
-      <c r="A1583" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="B1583" t="s">
+      <c r="B1590" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:2">
+      <c r="A1591" t="s">
         <v>1757</v>
       </c>
-    </row>
-    <row r="1584" spans="1:2">
-      <c r="A1584" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1584" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1585" spans="1:2">
-      <c r="A1585" s="2" t="s">
-        <v>1751</v>
-      </c>
-      <c r="B1585" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1586" spans="1:2">
-      <c r="A1586" s="2" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B1586" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1587" spans="1:2">
-      <c r="A1587" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="B1587" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1588" spans="1:2">
-      <c r="A1588" s="2" t="s">
+      <c r="B1591" t="s">
         <v>1754</v>
       </c>
-      <c r="B1588" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="1589" spans="1:2">
-      <c r="A1589" s="2" t="s">
-        <v>1759</v>
-      </c>
-      <c r="B1589" t="s">
+    </row>
+    <row r="1592" spans="1:2">
+      <c r="A1592" t="s">
         <v>1758</v>
       </c>
-    </row>
-    <row r="1590" spans="1:2">
-      <c r="A1590" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="B1590" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="1591" spans="1:2">
-      <c r="A1591" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="B1591" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="1592" spans="1:2">
-      <c r="A1592" s="2" t="s">
-        <v>1762</v>
-      </c>
       <c r="B1592" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1593" spans="1:2">
       <c r="A1593" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:2">
+      <c r="A1594" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:2">
+      <c r="A1595" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:2">
+      <c r="A1596" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:2">
+      <c r="A1597" t="s">
         <v>1764</v>
       </c>
-      <c r="B1593" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1594" spans="1:2">
-      <c r="A1594" s="2" t="s">
+      <c r="B1597" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:2">
+      <c r="A1598" t="s">
         <v>1765</v>
       </c>
-      <c r="B1594" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1595" spans="1:2">
-      <c r="A1595" s="2" t="s">
+      <c r="B1598" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:2">
+      <c r="A1599" t="s">
         <v>1766</v>
       </c>
-      <c r="B1595" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1596" spans="1:2">
-      <c r="A1596" s="2" t="s">
+      <c r="B1599" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:2">
+      <c r="A1600" t="s">
         <v>1767</v>
       </c>
-      <c r="B1596" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1597" spans="1:2">
-      <c r="A1597" s="2" t="s">
+      <c r="B1600" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:2">
+      <c r="A1601" t="s">
         <v>1768</v>
       </c>
-      <c r="B1597" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1598" spans="1:2">
-      <c r="A1598" s="2" t="s">
+      <c r="B1601" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:2">
+      <c r="A1602" t="s">
         <v>1769</v>
       </c>
-      <c r="B1598" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1599" spans="1:2">
-      <c r="A1599" s="2" t="s">
+      <c r="B1602" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:2">
+      <c r="A1603" t="s">
         <v>1770</v>
       </c>
-      <c r="B1599" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1600" spans="1:2">
-      <c r="A1600" s="2" t="s">
+      <c r="B1603" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:2">
+      <c r="A1604" t="s">
         <v>1771</v>
       </c>
-      <c r="B1600" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1601" spans="1:2">
-      <c r="A1601" s="2" t="s">
+      <c r="B1604" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:2">
+      <c r="A1605" t="s">
         <v>1772</v>
       </c>
-      <c r="B1601" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1602" spans="1:2">
-      <c r="A1602" s="2" t="s">
+      <c r="B1605" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:2">
+      <c r="A1606" t="s">
         <v>1773</v>
       </c>
-      <c r="B1602" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1603" spans="1:2">
-      <c r="A1603" s="2" t="s">
+      <c r="B1606" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:2">
+      <c r="A1607" t="s">
         <v>1774</v>
       </c>
-      <c r="B1603" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1604" spans="1:2">
-      <c r="A1604" s="2" t="s">
+      <c r="B1607" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:2">
+      <c r="A1608" t="s">
         <v>1775</v>
       </c>
-      <c r="B1604" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1605" spans="1:2">
-      <c r="A1605" s="2" t="s">
+      <c r="B1608" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:2">
+      <c r="A1609" t="s">
         <v>1776</v>
       </c>
-      <c r="B1605" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="1606" spans="1:2">
-      <c r="A1606" s="2" t="s">
+      <c r="B1609" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:2">
+      <c r="A1610" t="s">
         <v>1777</v>
       </c>
-      <c r="B1606" t="s">
+      <c r="B1610" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:2">
+      <c r="A1611" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:2">
+      <c r="A1612" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:2">
+      <c r="A1613" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:2">
+      <c r="A1614" t="s">
         <v>1782</v>
       </c>
-    </row>
-    <row r="1607" spans="1:2">
-      <c r="A1607" s="2" t="s">
+      <c r="B1614" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:2">
+      <c r="A1615" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:2">
+      <c r="A1616" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:2">
+      <c r="A1617" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:2">
+      <c r="A1618" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:2">
+      <c r="A1619" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:2">
+      <c r="A1620" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:2">
+      <c r="A1621" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:2">
+      <c r="A1622" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:2">
+      <c r="A1623" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:2">
+      <c r="A1624" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:2">
+      <c r="A1625" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:2">
+      <c r="A1626" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:2">
+      <c r="A1627" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:2">
+      <c r="A1628" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:2">
+      <c r="A1629" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:2">
+      <c r="A1630" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:2">
+      <c r="A1631" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:2">
+      <c r="A1632" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:2">
+      <c r="A1633" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:2">
+      <c r="A1634" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:2">
+      <c r="A1635" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:2">
+      <c r="A1636" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:2">
+      <c r="A1637" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:2">
+      <c r="A1638" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:2">
+      <c r="A1639" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:2">
+      <c r="A1640" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:2">
+      <c r="A1641" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:2">
+      <c r="A1642" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:2">
+      <c r="A1643" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:2">
+      <c r="A1644" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:2">
+      <c r="A1645" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:2">
+      <c r="A1646" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:2">
+      <c r="A1647" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:2">
+      <c r="A1648" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:2">
+      <c r="A1649" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:2">
+      <c r="A1650" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:2">
+      <c r="A1651" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:2">
+      <c r="A1652" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:2">
+      <c r="A1653" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:2">
+      <c r="A1654" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:2">
+      <c r="A1655" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:2">
+      <c r="A1656" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:2">
+      <c r="A1657" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:2">
+      <c r="A1658" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:2">
+      <c r="A1659" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:2">
+      <c r="A1660" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:2">
+      <c r="A1661" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:2">
+      <c r="A1662" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:2">
+      <c r="A1663" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:2">
+      <c r="A1664" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:2">
+      <c r="A1665" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:2">
+      <c r="A1666" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:2">
+      <c r="A1667" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:2">
+      <c r="A1668" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:2">
+      <c r="A1669" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:2">
+      <c r="A1670" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:2">
+      <c r="A1671" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:2">
+      <c r="A1672" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:2">
+      <c r="A1673" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:2">
+      <c r="A1674" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:2">
+      <c r="A1675" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:2">
+      <c r="A1676" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:2">
+      <c r="A1677" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:2">
+      <c r="A1678" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:2">
+      <c r="A1681" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:2">
+      <c r="A1682" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:2">
+      <c r="A1683" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:2">
+      <c r="A1684" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:2">
+      <c r="A1685" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:2">
+      <c r="A1686" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:2">
+      <c r="A1687" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:2">
+      <c r="A1688" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:2">
+      <c r="A1689" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:2">
+      <c r="A1690" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:2">
+      <c r="A1691" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:2">
+      <c r="A1692" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:2">
+      <c r="A1693" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:2">
+      <c r="A1694" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:2">
+      <c r="A1695" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:2">
+      <c r="A1696" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:2">
+      <c r="A1697" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:2">
+      <c r="A1698" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:2">
+      <c r="A1699" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:2">
+      <c r="A1700" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:2">
+      <c r="A1701" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:2">
+      <c r="A1702" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:2">
+      <c r="A1703" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:2">
+      <c r="A1704" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:2">
+      <c r="A1705" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:2">
+      <c r="A1706" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:2">
+      <c r="A1707" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:2">
+      <c r="A1708" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:2">
+      <c r="A1709" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:2">
+      <c r="A1710" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:2">
+      <c r="A1711" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:2">
+      <c r="A1712" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:2">
+      <c r="A1713" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:2">
+      <c r="A1714" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:2">
+      <c r="A1715" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:2">
+      <c r="A1716" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:2">
+      <c r="A1717" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:2">
+      <c r="A1718" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:2">
+      <c r="A1719" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:2">
+      <c r="A1720" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:2">
+      <c r="A1721" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:2">
+      <c r="A1722" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:2">
+      <c r="A1723" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:2">
+      <c r="A1724" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:2">
+      <c r="A1725" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:2">
+      <c r="A1726" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:2">
+      <c r="A1727" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:2">
+      <c r="A1728" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:2">
+      <c r="A1729" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:2">
+      <c r="A1730" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:2">
+      <c r="A1731" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:2">
+      <c r="A1732" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:2">
+      <c r="A1733" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:2">
+      <c r="A1734" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:2">
+      <c r="A1736" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:2">
+      <c r="A1737" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:2">
+      <c r="A1738" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:2">
+      <c r="A1739" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:2">
+      <c r="A1740" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:2">
+      <c r="A1741" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:2">
+      <c r="A1742" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:2">
+      <c r="A1743" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:2">
+      <c r="A1744" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:2">
+      <c r="A1745" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:2">
+      <c r="A1746" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:2">
+      <c r="A1747" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:2">
+      <c r="A1748" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:2">
+      <c r="A1749" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:2">
+      <c r="A1750" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:2">
+      <c r="A1751" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:2">
+      <c r="A1752" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:2">
+      <c r="A1753" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:2">
+      <c r="A1754" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:2">
+      <c r="A1755" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:2">
+      <c r="A1756" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:2">
+      <c r="A1757" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:2">
+      <c r="A1758" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:2">
+      <c r="A1759" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:2">
+      <c r="A1760" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:2">
+      <c r="A1761" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:2">
+      <c r="A1762" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:2">
+      <c r="A1763" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:2">
+      <c r="A1764" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:2">
+      <c r="A1765" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:2">
+      <c r="A1766" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:2">
+      <c r="A1767" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:2">
+      <c r="A1768" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:2">
+      <c r="A1769" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:2">
+      <c r="A1770" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:2">
+      <c r="A1771" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:2">
+      <c r="A1772" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:2">
+      <c r="A1773" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:2">
+      <c r="A1774" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:2">
+      <c r="A1775" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:2">
+      <c r="A1776" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:2">
+      <c r="A1777" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:2">
+      <c r="A1778" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:2">
+      <c r="A1779" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:2">
+      <c r="A1780" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:2">
+      <c r="A1781" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:2">
+      <c r="A1782" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:2">
+      <c r="A1783" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:2">
+      <c r="A1784" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:2">
+      <c r="A1785" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:2">
+      <c r="A1786" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:2">
+      <c r="A1787" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:2">
+      <c r="A1788" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:2">
+      <c r="A1789" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:2">
+      <c r="A1790" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1790" t="s">
         <v>1778</v>
       </c>
-      <c r="B1607" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="1608" spans="1:2">
-      <c r="A1608" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B1608" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="1609" spans="1:2">
-      <c r="A1609" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="B1609" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="1610" spans="1:2">
-      <c r="A1610" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="B1610" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="1611" spans="1:2">
-      <c r="A1611" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B1611" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="1612" spans="1:2">
-      <c r="A1612" s="2" t="s">
-        <v>1784</v>
-      </c>
-      <c r="B1612" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1613" spans="1:2">
-      <c r="A1613" s="2" t="s">
-        <v>1785</v>
-      </c>
-      <c r="B1613" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1614" spans="1:2">
-      <c r="A1614" s="2" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B1614" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1615" spans="1:2">
-      <c r="A1615" s="2" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B1615" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1616" spans="1:2">
-      <c r="A1616" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B1616" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1617" spans="1:2">
-      <c r="A1617" s="2" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B1617" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1618" spans="1:2">
-      <c r="A1618" s="2" t="s">
-        <v>1790</v>
-      </c>
-      <c r="B1618" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1619" spans="1:2">
-      <c r="A1619" s="2" t="s">
-        <v>1791</v>
-      </c>
-      <c r="B1619" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1620" spans="1:2">
-      <c r="A1620" s="2" t="s">
-        <v>1792</v>
-      </c>
-      <c r="B1620" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1621" spans="1:2">
-      <c r="A1621" s="2" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B1621" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="1622" spans="1:2">
-      <c r="A1622" s="2" t="s">
-        <v>1797</v>
-      </c>
-      <c r="B1622" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="1623" spans="1:2">
-      <c r="A1623" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="B1623" t="s">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="1624" spans="1:2">
-      <c r="A1624" s="2" t="s">
-        <v>1799</v>
-      </c>
-      <c r="B1624" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1625" spans="1:2">
-      <c r="A1625" s="2" t="s">
-        <v>1800</v>
-      </c>
-      <c r="B1625" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1626" spans="1:2">
-      <c r="A1626" s="2" t="s">
-        <v>1801</v>
-      </c>
-      <c r="B1626" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1627" spans="1:2">
-      <c r="A1627" s="2" t="s">
-        <v>1802</v>
-      </c>
-      <c r="B1627" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1628" spans="1:2">
-      <c r="A1628" s="2" t="s">
-        <v>1803</v>
-      </c>
-      <c r="B1628" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1629" spans="1:2">
-      <c r="A1629" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="B1629" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="1630" spans="1:2">
-      <c r="A1630" s="2" t="s">
+    </row>
+    <row r="1791" spans="1:2">
+      <c r="A1791" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:2">
+      <c r="A1792" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:2">
+      <c r="A1793" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:2">
+      <c r="A1794" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:2">
+      <c r="A1795" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:2">
+      <c r="A1796" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:2">
+      <c r="A1797" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:2">
+      <c r="A1798" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:2">
+      <c r="A1799" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:2">
+      <c r="A1800" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:2">
+      <c r="A1801" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:2">
+      <c r="A1802" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:2">
+      <c r="A1803" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:2">
+      <c r="A1804" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:2">
+      <c r="A1805" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:2">
+      <c r="A1806" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:2">
+      <c r="A1807" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1807" t="s">
         <v>1805</v>
       </c>
-      <c r="B1630" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="1631" spans="1:2">
-      <c r="A1631" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B1631" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1632" spans="1:2">
-      <c r="A1632" s="2" t="s">
-        <v>1811</v>
-      </c>
-      <c r="B1632" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1633" spans="1:2">
-      <c r="A1633" s="2" t="s">
-        <v>1812</v>
-      </c>
-      <c r="B1633" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1634" spans="1:2">
-      <c r="A1634" s="2" t="s">
+    </row>
+    <row r="1808" spans="1:2">
+      <c r="A1808" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:2">
+      <c r="A1809" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:2">
+      <c r="A1810" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:2">
+      <c r="A1811" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:2">
+      <c r="A1812" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:2">
+      <c r="A1813" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:2">
+      <c r="A1814" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:2">
+      <c r="A1815" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1815" t="s">
         <v>1813</v>
-      </c>
-      <c r="B1634" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1635" spans="1:2">
-      <c r="A1635" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="B1635" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1636" spans="1:2">
-      <c r="A1636" s="2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="B1636" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1637" spans="1:2">
-      <c r="A1637" s="2" t="s">
-        <v>1816</v>
-      </c>
-      <c r="B1637" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="1638" spans="1:2">
-      <c r="A1638" s="2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B1638" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1639" spans="1:2">
-      <c r="A1639" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="B1639" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1640" spans="1:2">
-      <c r="A1640" s="2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="B1640" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1641" spans="1:2">
-      <c r="A1641" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="B1641" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1642" spans="1:2">
-      <c r="A1642" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B1642" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1643" spans="1:2">
-      <c r="A1643" s="2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="B1643" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1644" spans="1:2">
-      <c r="A1644" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B1644" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1645" spans="1:2">
-      <c r="A1645" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1645" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1646" spans="1:2">
-      <c r="A1646" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1646" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1647" spans="1:2">
-      <c r="A1647" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="B1647" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1648" spans="1:2">
-      <c r="A1648" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B1648" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1649" spans="1:2">
-      <c r="A1649" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B1649" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1650" spans="1:2">
-      <c r="A1650" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="B1650" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1651" spans="1:2">
-      <c r="A1651" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B1651" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1652" spans="1:2">
-      <c r="A1652" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B1652" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="1653" spans="1:2">
-      <c r="A1653" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B1653" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1654" spans="1:2">
-      <c r="A1654" s="2" t="s">
-        <v>1835</v>
-      </c>
-      <c r="B1654" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1655" spans="1:2">
-      <c r="A1655" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B1655" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1656" spans="1:2">
-      <c r="A1656" s="2" t="s">
-        <v>1837</v>
-      </c>
-      <c r="B1656" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1657" spans="1:2">
-      <c r="A1657" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B1657" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1658" spans="1:2">
-      <c r="A1658" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="B1658" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1659" spans="1:2">
-      <c r="A1659" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B1659" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="1660" spans="1:2">
-      <c r="A1660" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B1660" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1661" spans="1:2">
-      <c r="A1661" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="B1661" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1662" spans="1:2">
-      <c r="A1662" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B1662" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1663" spans="1:2">
-      <c r="A1663" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B1663" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1664" spans="1:2">
-      <c r="A1664" s="2" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B1664" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1665" spans="1:2">
-      <c r="A1665" s="2" t="s">
-        <v>1847</v>
-      </c>
-      <c r="B1665" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1666" spans="1:2">
-      <c r="A1666" s="2" t="s">
-        <v>1848</v>
-      </c>
-      <c r="B1666" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1667" spans="1:2">
-      <c r="A1667" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B1667" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1668" spans="1:2">
-      <c r="A1668" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B1668" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1669" spans="1:2">
-      <c r="A1669" s="2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B1669" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1670" spans="1:2">
-      <c r="A1670" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B1670" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1671" spans="1:2">
-      <c r="A1671" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B1671" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1672" spans="1:2">
-      <c r="A1672" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B1672" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1673" spans="1:2">
-      <c r="A1673" s="2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B1673" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1674" spans="1:2">
-      <c r="A1674" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B1674" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1675" spans="1:2">
-      <c r="A1675" s="2" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B1675" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1676" spans="1:2">
-      <c r="A1676" s="2" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B1676" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1677" spans="1:2">
-      <c r="A1677" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="B1677" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="1678" spans="1:2">
-      <c r="A1678" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B1678" t="s">
-        <v>1841</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3037AF-F9A4-4546-BFCF-BE4D8C8FE3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0D031B0-458E-4564-9EF8-BA7FA3AEC1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="11364" yWindow="0" windowWidth="11772" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3584" uniqueCount="2021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="2300">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -6538,51 +6539,6 @@
     <t>野木</t>
   </si>
   <si>
-    <t>常磐線、水戸線、ひたちなか海浜鉄道、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>カイヒンテツドウ</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常磐線、水戸線、水郡線、鹿島臨海鉄道大洗鹿島線、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>スイグンセン</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常磐線、水戸線、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>ジョウバンセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>常磐線、（上野東京ライン）</t>
     <rPh sb="0" eb="3">
       <t>ジョウバンセン</t>
@@ -7248,19 +7204,7 @@
       <t>リョウモウセン</t>
     </rPh>
     <rPh sb="21" eb="25">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <rPh sb="30" eb="33">
-      <t>ジョウエツセン</t>
-    </rPh>
-    <rPh sb="34" eb="37">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="39" eb="43">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="49" eb="53">
-      <t>ウエノトウキョウ</t>
+      <t>ウエノトウキョウジョウエツセンリョウモウセンショウナンシンジュクウエノトウキョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7783,6 +7727,1191 @@
       <t>マエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>埼玉県</t>
+    <rPh sb="0" eb="3">
+      <t>サイタマケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、ひたちなか海浜鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>カイヒンテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線、水郡線、鹿島臨海鉄道大洗鹿島線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スイグンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、水戸線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミトセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大宮（埼玉）</t>
+  </si>
+  <si>
+    <t>さいたま新都心</t>
+  </si>
+  <si>
+    <t>与野</t>
+  </si>
+  <si>
+    <t>北浦和</t>
+  </si>
+  <si>
+    <t>浦和</t>
+  </si>
+  <si>
+    <t>南浦和</t>
+  </si>
+  <si>
+    <t>蕨</t>
+  </si>
+  <si>
+    <t>西川口</t>
+  </si>
+  <si>
+    <t>川口</t>
+  </si>
+  <si>
+    <t>京浜東北線</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、埼京線、川越線、東武アーバンパークライン、埼玉新都市交通ニューシャトル、東北新幹線、上越新幹線、北陸新幹線、（上野東京ライン）</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>サイキョウセン</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>カワゴエセン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="59" eb="64">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="65" eb="70">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <rPh sb="71" eb="76">
+      <t>ホクリクシンカンセン</t>
+    </rPh>
+    <rPh sb="78" eb="82">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、高崎線、（上野東京ライン）</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京浜東北線、武蔵野線</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ムサシノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神保原</t>
+  </si>
+  <si>
+    <t>本庄</t>
+  </si>
+  <si>
+    <t>岡部</t>
+  </si>
+  <si>
+    <t>深谷</t>
+  </si>
+  <si>
+    <t>籠原</t>
+  </si>
+  <si>
+    <t>熊谷</t>
+  </si>
+  <si>
+    <t>行田</t>
+  </si>
+  <si>
+    <t>吹上（埼玉）</t>
+  </si>
+  <si>
+    <t>北鴻巣</t>
+  </si>
+  <si>
+    <t>鴻巣</t>
+  </si>
+  <si>
+    <t>北本</t>
+  </si>
+  <si>
+    <t>桶川</t>
+  </si>
+  <si>
+    <t>北上尾</t>
+  </si>
+  <si>
+    <t>上尾</t>
+  </si>
+  <si>
+    <t>宮原</t>
+  </si>
+  <si>
+    <t>高崎線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="4" eb="8">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、湘南新宿ライン、（上野東京ライン）、秩父鉄道、上越新幹線、北陸新幹線</t>
+    <rPh sb="4" eb="8">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>チチブテツドウ</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <rPh sb="33" eb="38">
+      <t>ホクリクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>埼京線</t>
+  </si>
+  <si>
+    <t>戸田公園</t>
+  </si>
+  <si>
+    <t>戸田（埼玉）</t>
+  </si>
+  <si>
+    <t>北戸田</t>
+  </si>
+  <si>
+    <t>武蔵浦和</t>
+  </si>
+  <si>
+    <t>中浦和</t>
+  </si>
+  <si>
+    <t>南与野</t>
+  </si>
+  <si>
+    <t>与野本町</t>
+  </si>
+  <si>
+    <t>北与野</t>
+  </si>
+  <si>
+    <t>埼京線、武蔵野線</t>
+    <rPh sb="4" eb="8">
+      <t>ムサシノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上越新幹線、北陸新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>ホクリクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本庄早稲田</t>
+    <rPh sb="0" eb="5">
+      <t>ホンジョウワセダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川越線</t>
+  </si>
+  <si>
+    <t>日進（埼玉）</t>
+  </si>
+  <si>
+    <t>西大宮</t>
+  </si>
+  <si>
+    <t>指扇</t>
+  </si>
+  <si>
+    <t>南古谷</t>
+  </si>
+  <si>
+    <t>川越</t>
+  </si>
+  <si>
+    <t>西川越</t>
+  </si>
+  <si>
+    <t>的場</t>
+  </si>
+  <si>
+    <t>笠幡</t>
+  </si>
+  <si>
+    <t>武蔵高萩</t>
+  </si>
+  <si>
+    <t>高麗川</t>
+  </si>
+  <si>
+    <t>川越線、東武東上線</t>
+    <rPh sb="4" eb="9">
+      <t>トウブトウジョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川越線、八高線</t>
+    <rPh sb="4" eb="7">
+      <t>ハチコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>栗橋</t>
+  </si>
+  <si>
+    <t>東鷲宮</t>
+  </si>
+  <si>
+    <t>久喜</t>
+  </si>
+  <si>
+    <t>新白岡</t>
+  </si>
+  <si>
+    <t>白岡</t>
+  </si>
+  <si>
+    <t>蓮田</t>
+  </si>
+  <si>
+    <t>東大宮</t>
+  </si>
+  <si>
+    <t>土呂</t>
+  </si>
+  <si>
+    <t>宇都宮線、東武日光線、湘南新宿ライン、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇都宮線、東武伊勢崎線、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="5" eb="11">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八高線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金子</t>
+  </si>
+  <si>
+    <t>東飯能</t>
+  </si>
+  <si>
+    <t>毛呂</t>
+  </si>
+  <si>
+    <t>越生</t>
+  </si>
+  <si>
+    <t>明覚</t>
+  </si>
+  <si>
+    <t>小川町（埼玉）</t>
+  </si>
+  <si>
+    <t>竹沢</t>
+  </si>
+  <si>
+    <t>折原</t>
+  </si>
+  <si>
+    <t>寄居</t>
+  </si>
+  <si>
+    <t>用土</t>
+  </si>
+  <si>
+    <t>松久</t>
+  </si>
+  <si>
+    <t>児玉</t>
+  </si>
+  <si>
+    <t>丹荘</t>
+  </si>
+  <si>
+    <t>八高線、西武秩父線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>セイブチチブセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八高線、東武越生線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オゴセ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八高線、東武東上線</t>
+    <rPh sb="0" eb="3">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>トウブトウジョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八高線、東武東上線、秩父鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>トウブトウジョウセン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>チチブテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武蔵野線</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東所沢</t>
+  </si>
+  <si>
+    <t>新座</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北朝霞</t>
+  </si>
+  <si>
+    <t>西浦和</t>
+  </si>
+  <si>
+    <t>東浦和</t>
+  </si>
+  <si>
+    <t>東川口</t>
+  </si>
+  <si>
+    <t>南越谷</t>
+  </si>
+  <si>
+    <t>越谷レイクタウン</t>
+  </si>
+  <si>
+    <t>吉川（埼玉）</t>
+  </si>
+  <si>
+    <t>吉川美南</t>
+  </si>
+  <si>
+    <t>新三郷</t>
+  </si>
+  <si>
+    <t>三郷（埼玉）</t>
+  </si>
+  <si>
+    <t>武蔵野線、埼玉高速鉄道</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <rPh sb="5" eb="11">
+      <t>サイタマコウソクテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>埼玉新都市交通ニューシャトル</t>
+  </si>
+  <si>
+    <t>鉄道博物館</t>
+  </si>
+  <si>
+    <t>加茂宮（埼玉）</t>
+  </si>
+  <si>
+    <t>東宮原</t>
+  </si>
+  <si>
+    <t>今羽</t>
+  </si>
+  <si>
+    <t>吉野原</t>
+  </si>
+  <si>
+    <t>原市</t>
+  </si>
+  <si>
+    <t>沼南</t>
+  </si>
+  <si>
+    <t>丸山（埼玉）</t>
+  </si>
+  <si>
+    <t>志久</t>
+  </si>
+  <si>
+    <t>伊奈中央</t>
+  </si>
+  <si>
+    <t>羽貫</t>
+  </si>
+  <si>
+    <t>内宿</t>
+  </si>
+  <si>
+    <t>西武狭山線</t>
+  </si>
+  <si>
+    <t>西所沢</t>
+  </si>
+  <si>
+    <t>下山口</t>
+  </si>
+  <si>
+    <t>西武球場前</t>
+  </si>
+  <si>
+    <t>西武狭山線、西武池袋線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西武狭山線、西武山口線</t>
+    <rPh sb="6" eb="11">
+      <t>セイブヤマグチセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西武山口線</t>
+  </si>
+  <si>
+    <t>多摩湖</t>
+  </si>
+  <si>
+    <t>西武園ゆうえんち</t>
+  </si>
+  <si>
+    <t>西武山口線、西武多摩湖線</t>
+    <rPh sb="6" eb="12">
+      <t>セイブタマコセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西武新宿線</t>
+  </si>
+  <si>
+    <t>所沢</t>
+  </si>
+  <si>
+    <t>航空公園</t>
+  </si>
+  <si>
+    <t>新所沢</t>
+  </si>
+  <si>
+    <t>入曽</t>
+  </si>
+  <si>
+    <t>狭山市</t>
+  </si>
+  <si>
+    <t>新狭山</t>
+  </si>
+  <si>
+    <t>南大塚</t>
+  </si>
+  <si>
+    <t>本川越</t>
+  </si>
+  <si>
+    <t>西武新宿線、西武池袋線</t>
+    <rPh sb="6" eb="11">
+      <t>セイブイケブクロセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小手指</t>
+  </si>
+  <si>
+    <t>狭山ヶ丘</t>
+  </si>
+  <si>
+    <t>武蔵藤沢</t>
+  </si>
+  <si>
+    <t>稲荷山公園</t>
+  </si>
+  <si>
+    <t>入間市</t>
+  </si>
+  <si>
+    <t>仏子</t>
+  </si>
+  <si>
+    <t>元加治</t>
+  </si>
+  <si>
+    <t>飯能</t>
+  </si>
+  <si>
+    <t>西武池袋線</t>
+    <rPh sb="0" eb="5">
+      <t>セイブイケブクロセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西武池袋線、西武秩父線</t>
+    <rPh sb="0" eb="5">
+      <t>セイブイケブクロセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>セイブチチブセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西武秩父線</t>
+    <rPh sb="0" eb="5">
+      <t>セイブチチブセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高麗</t>
+  </si>
+  <si>
+    <t>武蔵横手</t>
+  </si>
+  <si>
+    <t>東吾野</t>
+  </si>
+  <si>
+    <t>吾野</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西吾野</t>
+  </si>
+  <si>
+    <t>正丸</t>
+  </si>
+  <si>
+    <t>芦ヶ久保</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>横瀬</t>
+  </si>
+  <si>
+    <t>西武秩父</t>
+  </si>
+  <si>
+    <t>西武秩父線、秩父鉄道</t>
+    <rPh sb="0" eb="5">
+      <t>セイブチチブセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チチブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秩父鉄道</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三峰口</t>
+  </si>
+  <si>
+    <t>白久</t>
+  </si>
+  <si>
+    <t>武州日野</t>
+  </si>
+  <si>
+    <t>武州中川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浦山口</t>
+  </si>
+  <si>
+    <t>影森</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>御花畑（芝桜）</t>
+    <rPh sb="4" eb="6">
+      <t>シバザクラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秩父鉄道、西武秩父線</t>
+    <rPh sb="5" eb="10">
+      <t>セイブチチブセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秩父</t>
+  </si>
+  <si>
+    <t>大野原</t>
+  </si>
+  <si>
+    <t>和銅黒谷</t>
+  </si>
+  <si>
+    <t>皆野</t>
+  </si>
+  <si>
+    <t>親鼻</t>
+  </si>
+  <si>
+    <t>上長瀞</t>
+  </si>
+  <si>
+    <t>長瀞</t>
+  </si>
+  <si>
+    <t>野上</t>
+  </si>
+  <si>
+    <t>樋口（埼玉）</t>
+  </si>
+  <si>
+    <t>波久礼</t>
+  </si>
+  <si>
+    <t>桜沢（埼玉）</t>
+  </si>
+  <si>
+    <t>小前田</t>
+  </si>
+  <si>
+    <t>ふかや花園</t>
+  </si>
+  <si>
+    <t>永田（埼玉）</t>
+  </si>
+  <si>
+    <t>武川</t>
+  </si>
+  <si>
+    <t>明戸</t>
+  </si>
+  <si>
+    <t>大麻生</t>
+  </si>
+  <si>
+    <t>ひろせ野鳥の森</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石原（埼玉）</t>
+  </si>
+  <si>
+    <t>上熊谷</t>
+  </si>
+  <si>
+    <t>ソシオ流通センター</t>
+  </si>
+  <si>
+    <t>持田</t>
+  </si>
+  <si>
+    <t>行田市</t>
+  </si>
+  <si>
+    <t>東行田</t>
+  </si>
+  <si>
+    <t>武州荒木</t>
+  </si>
+  <si>
+    <t>新郷（埼玉）</t>
+  </si>
+  <si>
+    <t>西羽生</t>
+  </si>
+  <si>
+    <t>羽生</t>
+  </si>
+  <si>
+    <t>秩父鉄道</t>
+    <rPh sb="0" eb="4">
+      <t>チチブテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秩父鉄道、東武伊勢崎線</t>
+    <rPh sb="0" eb="4">
+      <t>チチブテツドウ</t>
+    </rPh>
+    <rPh sb="5" eb="11">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京メトロ有楽町線、東京メトロ副都心線、東武東上線</t>
+    <rPh sb="10" eb="12">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>フクトシンセン</t>
+    </rPh>
+    <rPh sb="20" eb="25">
+      <t>トウブトウジョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和光市</t>
+    <rPh sb="0" eb="3">
+      <t>ワコウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南羽生</t>
+  </si>
+  <si>
+    <t>加須</t>
+  </si>
+  <si>
+    <t>花崎</t>
+  </si>
+  <si>
+    <t>鷲宮</t>
+  </si>
+  <si>
+    <t>和戸</t>
+  </si>
+  <si>
+    <t>東武動物公園</t>
+  </si>
+  <si>
+    <t>東武伊勢崎線（スカイツリーライン）、東武日光線</t>
+    <rPh sb="0" eb="6">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <rPh sb="18" eb="23">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武伊勢崎線（スカイツリーライン）</t>
+    <rPh sb="0" eb="6">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>谷塚</t>
+  </si>
+  <si>
+    <t>草加</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>獨協大学前</t>
+  </si>
+  <si>
+    <t>新田（埼玉）</t>
+  </si>
+  <si>
+    <t>蒲生</t>
+  </si>
+  <si>
+    <t>新越谷</t>
+  </si>
+  <si>
+    <t>越谷</t>
+  </si>
+  <si>
+    <t>北越谷</t>
+  </si>
+  <si>
+    <t>大袋</t>
+  </si>
+  <si>
+    <t>せんげん台</t>
+  </si>
+  <si>
+    <t>武里</t>
+  </si>
+  <si>
+    <t>一ノ割</t>
+  </si>
+  <si>
+    <t>春日部</t>
+  </si>
+  <si>
+    <t>北春日部</t>
+  </si>
+  <si>
+    <t>姫宮</t>
+  </si>
+  <si>
+    <t>東武伊勢崎線（スカイツリーライン）、東武アーバンパークライン</t>
+    <rPh sb="0" eb="6">
+      <t>トウブイセサキセン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武越生線</t>
+  </si>
+  <si>
+    <t>坂戸（埼玉）</t>
+  </si>
+  <si>
+    <t>一本松（埼玉）</t>
+  </si>
+  <si>
+    <t>西大家</t>
+  </si>
+  <si>
+    <t>川角</t>
+  </si>
+  <si>
+    <t>武州長瀬</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東毛呂</t>
+  </si>
+  <si>
+    <t>武州唐沢</t>
+  </si>
+  <si>
+    <t>東武越生線、東武東上線</t>
+    <rPh sb="6" eb="11">
+      <t>トウブトウジョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武東上線</t>
+  </si>
+  <si>
+    <t>朝霞</t>
+  </si>
+  <si>
+    <t>朝霞台</t>
+  </si>
+  <si>
+    <t>志木</t>
+  </si>
+  <si>
+    <t>柳瀬川</t>
+  </si>
+  <si>
+    <t>みずほ台</t>
+  </si>
+  <si>
+    <t>鶴瀬</t>
+  </si>
+  <si>
+    <t>ふじみ野</t>
+  </si>
+  <si>
+    <t>上福岡</t>
+  </si>
+  <si>
+    <t>新河岸</t>
+  </si>
+  <si>
+    <t>川越市</t>
+  </si>
+  <si>
+    <t>霞ヶ関（埼玉）</t>
+  </si>
+  <si>
+    <t>鶴ヶ島</t>
+  </si>
+  <si>
+    <t>若葉</t>
+  </si>
+  <si>
+    <t>北坂戸</t>
+  </si>
+  <si>
+    <t>高坂</t>
+  </si>
+  <si>
+    <t>東松山</t>
+  </si>
+  <si>
+    <t>森林公園（埼玉）</t>
+  </si>
+  <si>
+    <t>つきのわ</t>
+  </si>
+  <si>
+    <t>武蔵嵐山</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武竹沢</t>
+  </si>
+  <si>
+    <t>みなみ寄居</t>
+  </si>
+  <si>
+    <t>男衾</t>
+  </si>
+  <si>
+    <t>鉢形</t>
+  </si>
+  <si>
+    <t>玉淀</t>
+  </si>
+  <si>
+    <t>杉戸高野台</t>
+  </si>
+  <si>
+    <t>幸手</t>
+  </si>
+  <si>
+    <t>南栗橋</t>
+  </si>
+  <si>
+    <t>新古河</t>
+  </si>
+  <si>
+    <t>柳生</t>
+  </si>
+  <si>
+    <t>東武日光線</t>
+    <rPh sb="0" eb="5">
+      <t>トウブニッコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北大宮</t>
+  </si>
+  <si>
+    <t>大宮公園</t>
+  </si>
+  <si>
+    <t>大和田（埼玉）</t>
+  </si>
+  <si>
+    <t>七里</t>
+  </si>
+  <si>
+    <t>岩槻</t>
+  </si>
+  <si>
+    <t>東岩槻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>豊春</t>
+  </si>
+  <si>
+    <t>八木崎</t>
+  </si>
+  <si>
+    <t>藤の牛島</t>
+  </si>
+  <si>
+    <t>南桜井（埼玉）</t>
+  </si>
+  <si>
+    <t>東武アーバンパークライン</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>埼玉高速鉄道線</t>
+  </si>
+  <si>
+    <t>川口元郷</t>
+  </si>
+  <si>
+    <t>南鳩ヶ谷</t>
+  </si>
+  <si>
+    <t>鳩ヶ谷</t>
+  </si>
+  <si>
+    <t>新井宿</t>
+  </si>
+  <si>
+    <t>戸塚安行</t>
+  </si>
+  <si>
+    <t>浦和美園</t>
+  </si>
+  <si>
+    <t>八潮</t>
+  </si>
+  <si>
+    <t>三郷中央</t>
   </si>
 </sst>
 </file>
@@ -7863,10 +8992,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8186,7 +9311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B1815"/>
+  <dimension ref="A1:B2047"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -19422,7 +20547,7 @@
         <v>1563</v>
       </c>
       <c r="B1421" t="s">
-        <v>890</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1422" spans="1:2">
@@ -19470,7 +20595,7 @@
         <v>1569</v>
       </c>
       <c r="B1427" t="s">
-        <v>1729</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1428" spans="1:2">
@@ -19478,7 +20603,7 @@
         <v>1570</v>
       </c>
       <c r="B1428" t="s">
-        <v>1730</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1429" spans="1:2">
@@ -19486,7 +20611,7 @@
         <v>1571</v>
       </c>
       <c r="B1429" t="s">
-        <v>1731</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1430" spans="1:2">
@@ -19494,7 +20619,7 @@
         <v>1572</v>
       </c>
       <c r="B1430" t="s">
-        <v>1731</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1431" spans="1:2">
@@ -19502,7 +20627,7 @@
         <v>1573</v>
       </c>
       <c r="B1431" t="s">
-        <v>1731</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1432" spans="1:2">
@@ -19510,7 +20635,7 @@
         <v>1574</v>
       </c>
       <c r="B1432" t="s">
-        <v>1731</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1433" spans="1:2">
@@ -19518,7 +20643,7 @@
         <v>1575</v>
       </c>
       <c r="B1433" t="s">
-        <v>1732</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1434" spans="1:2">
@@ -19526,7 +20651,7 @@
         <v>1576</v>
       </c>
       <c r="B1434" t="s">
-        <v>1732</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1435" spans="1:2">
@@ -19534,7 +20659,7 @@
         <v>1577</v>
       </c>
       <c r="B1435" t="s">
-        <v>1732</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1436" spans="1:2">
@@ -19542,7 +20667,7 @@
         <v>1578</v>
       </c>
       <c r="B1436" t="s">
-        <v>1732</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1437" spans="1:2">
@@ -19550,7 +20675,7 @@
         <v>1579</v>
       </c>
       <c r="B1437" t="s">
-        <v>1732</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1438" spans="1:2">
@@ -19558,7 +20683,7 @@
         <v>1580</v>
       </c>
       <c r="B1438" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1439" spans="1:2">
@@ -19566,7 +20691,7 @@
         <v>1581</v>
       </c>
       <c r="B1439" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1440" spans="1:2">
@@ -19574,7 +20699,7 @@
         <v>1582</v>
       </c>
       <c r="B1440" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1441" spans="1:2">
@@ -19582,7 +20707,7 @@
         <v>1583</v>
       </c>
       <c r="B1441" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1442" spans="1:2">
@@ -19590,7 +20715,7 @@
         <v>1584</v>
       </c>
       <c r="B1442" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1443" spans="1:2">
@@ -19598,7 +20723,7 @@
         <v>1585</v>
       </c>
       <c r="B1443" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1444" spans="1:2">
@@ -19926,7 +21051,7 @@
         <v>1628</v>
       </c>
       <c r="B1484" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1485" spans="1:2">
@@ -20395,7 +21520,7 @@
         <v>1695</v>
       </c>
       <c r="B1545" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1546" spans="1:2">
@@ -20475,7 +21600,7 @@
         <v>1708</v>
       </c>
       <c r="B1555" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1556" spans="1:2">
@@ -20523,7 +21648,7 @@
         <v>1717</v>
       </c>
       <c r="B1561" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1562" spans="1:2">
@@ -20531,7 +21656,7 @@
         <v>1718</v>
       </c>
       <c r="B1562" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1563" spans="1:2">
@@ -20539,7 +21664,7 @@
         <v>1719</v>
       </c>
       <c r="B1563" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1564" spans="1:2">
@@ -20547,7 +21672,7 @@
         <v>1720</v>
       </c>
       <c r="B1564" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1565" spans="1:2">
@@ -20555,7 +21680,7 @@
         <v>1721</v>
       </c>
       <c r="B1565" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1566" spans="1:2">
@@ -20563,7 +21688,7 @@
         <v>1722</v>
       </c>
       <c r="B1566" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1567" spans="1:2">
@@ -20571,7 +21696,7 @@
         <v>1723</v>
       </c>
       <c r="B1567" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1568" spans="1:2">
@@ -20579,7 +21704,7 @@
         <v>1724</v>
       </c>
       <c r="B1568" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1569" spans="1:2">
@@ -20587,7 +21712,7 @@
         <v>1725</v>
       </c>
       <c r="B1569" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1570" spans="1:2">
@@ -20595,7 +21720,7 @@
         <v>1726</v>
       </c>
       <c r="B1570" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1571" spans="1:2">
@@ -20603,7 +21728,7 @@
         <v>1727</v>
       </c>
       <c r="B1571" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1572" spans="1:2">
@@ -20611,1932 +21736,3769 @@
         <v>1728</v>
       </c>
       <c r="B1572" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1573" spans="1:2">
       <c r="A1573" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="B1573" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
       <c r="A1574" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="B1574" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1575" spans="1:2">
       <c r="A1575" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="B1575" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1576" spans="1:2">
       <c r="A1576" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1576" t="s">
         <v>1737</v>
-      </c>
-      <c r="B1576" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="1577" spans="1:2">
       <c r="A1577" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="B1577" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1578" spans="1:2">
       <c r="A1578" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="B1578" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1579" spans="1:2">
       <c r="A1579" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="B1579" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1580" spans="1:2">
       <c r="A1580" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="B1580" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1581" spans="1:2">
       <c r="A1581" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="B1581" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1582" spans="1:2">
       <c r="A1582" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="B1582" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1583" spans="1:2">
       <c r="A1583" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="B1583" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1584" spans="1:2">
       <c r="A1584" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="B1584" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1585" spans="1:2">
       <c r="A1585" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="B1585" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1586" spans="1:2">
       <c r="A1586" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1586" t="s">
         <v>1748</v>
-      </c>
-      <c r="B1586" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="1587" spans="1:2">
       <c r="A1587" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="B1587" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1588" spans="1:2">
       <c r="A1588" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B1588" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1589" spans="1:2">
       <c r="A1589" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="B1589" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1590" spans="1:2">
       <c r="A1590" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="B1590" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1591" spans="1:2">
       <c r="A1591" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="B1591" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1592" spans="1:2">
       <c r="A1592" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="B1592" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1593" spans="1:2">
       <c r="A1593" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="B1593" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1594" spans="1:2">
       <c r="A1594" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="B1594" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1595" spans="1:2">
       <c r="A1595" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="B1595" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1596" spans="1:2">
       <c r="A1596" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="B1596" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1597" spans="1:2">
       <c r="A1597" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="B1597" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1598" spans="1:2">
       <c r="A1598" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="B1598" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1599" spans="1:2">
       <c r="A1599" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="B1599" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1600" spans="1:2">
       <c r="A1600" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="B1600" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1601" spans="1:2">
       <c r="A1601" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="B1601" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1602" spans="1:2">
       <c r="A1602" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="B1602" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1603" spans="1:2">
       <c r="A1603" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="B1603" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1604" spans="1:2">
       <c r="A1604" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="B1604" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1605" spans="1:2">
       <c r="A1605" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="B1605" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1606" spans="1:2">
       <c r="A1606" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="B1606" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1607" spans="1:2">
       <c r="A1607" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="B1607" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1608" spans="1:2">
       <c r="A1608" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1608" t="s">
         <v>1775</v>
-      </c>
-      <c r="B1608" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="1609" spans="1:2">
       <c r="A1609" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="B1609" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1610" spans="1:2">
       <c r="A1610" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="B1610" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1611" spans="1:2">
       <c r="A1611" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="B1611" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1612" spans="1:2">
       <c r="A1612" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="B1612" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1613" spans="1:2">
       <c r="A1613" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="B1613" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1614" spans="1:2">
       <c r="A1614" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="B1614" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1615" spans="1:2">
       <c r="A1615" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="B1615" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1616" spans="1:2">
       <c r="A1616" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="B1616" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1617" spans="1:2">
       <c r="A1617" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="B1617" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1618" spans="1:2">
       <c r="A1618" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="B1618" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1619" spans="1:2">
       <c r="A1619" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1619" t="s">
         <v>1787</v>
-      </c>
-      <c r="B1619" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="1620" spans="1:2">
       <c r="A1620" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="B1620" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1621" spans="1:2">
       <c r="A1621" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="B1621" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1622" spans="1:2">
       <c r="A1622" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="B1622" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1623" spans="1:2">
       <c r="A1623" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="B1623" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1624" spans="1:2">
       <c r="A1624" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="B1624" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1625" spans="1:2">
       <c r="A1625" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="B1625" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1626" spans="1:2">
       <c r="A1626" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="B1626" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1627" spans="1:2">
       <c r="A1627" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="B1627" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1628" spans="1:2">
       <c r="A1628" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1628" t="s">
         <v>1799</v>
-      </c>
-      <c r="B1628" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="1629" spans="1:2">
       <c r="A1629" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="B1629" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1630" spans="1:2">
       <c r="A1630" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1630" t="s">
         <v>1801</v>
-      </c>
-      <c r="B1630" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="1631" spans="1:2">
       <c r="A1631" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="B1631" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1632" spans="1:2">
       <c r="A1632" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="B1632" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1633" spans="1:2">
       <c r="A1633" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="B1633" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1634" spans="1:2">
       <c r="A1634" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="B1634" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1635" spans="1:2">
       <c r="A1635" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="B1635" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1636" spans="1:2">
       <c r="A1636" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="B1636" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1637" spans="1:2">
       <c r="A1637" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="B1637" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1638" spans="1:2">
       <c r="A1638" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="B1638" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1639" spans="1:2">
       <c r="A1639" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="B1639" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1640" spans="1:2">
       <c r="A1640" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="B1640" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1641" spans="1:2">
       <c r="A1641" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="B1641" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1642" spans="1:2">
       <c r="A1642" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="B1642" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1643" spans="1:2">
       <c r="A1643" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="B1643" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1644" spans="1:2">
       <c r="A1644" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="B1644" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1645" spans="1:2">
       <c r="A1645" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="B1645" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1646" spans="1:2">
       <c r="A1646" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="B1646" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1647" spans="1:2">
       <c r="A1647" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="B1647" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1648" spans="1:2">
       <c r="A1648" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="B1648" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1649" spans="1:2">
       <c r="A1649" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="B1649" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1650" spans="1:2">
       <c r="A1650" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="B1650" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1651" spans="1:2">
       <c r="A1651" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="B1651" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1652" spans="1:2">
       <c r="A1652" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="B1652" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1653" spans="1:2">
       <c r="A1653" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
       <c r="B1653" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1654" spans="1:2">
       <c r="A1654" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="B1654" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1655" spans="1:2">
       <c r="A1655" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="B1655" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1656" spans="1:2">
       <c r="A1656" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="B1656" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1657" spans="1:2">
       <c r="A1657" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="B1657" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1658" spans="1:2">
       <c r="A1658" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="B1658" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1659" spans="1:2">
       <c r="A1659" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="B1659" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1660" spans="1:2">
       <c r="A1660" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="B1660" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1661" spans="1:2">
       <c r="A1661" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="B1661" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1662" spans="1:2">
       <c r="A1662" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="B1662" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1663" spans="1:2">
       <c r="A1663" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="B1663" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1664" spans="1:2">
       <c r="A1664" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="B1664" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1665" spans="1:2">
       <c r="A1665" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="B1665" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1666" spans="1:2">
       <c r="A1666" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="B1666" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1667" spans="1:2">
       <c r="A1667" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
       <c r="B1667" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1668" spans="1:2">
       <c r="A1668" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
       <c r="B1668" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1669" spans="1:2">
       <c r="A1669" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="B1669" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1670" spans="1:2">
       <c r="A1670" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="B1670" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1671" spans="1:2">
       <c r="A1671" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="B1671" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1672" spans="1:2">
       <c r="A1672" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
       <c r="B1672" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1673" spans="1:2">
       <c r="A1673" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
       <c r="B1673" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1674" spans="1:2">
       <c r="A1674" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
       <c r="B1674" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1675" spans="1:2">
       <c r="A1675" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="B1675" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1676" spans="1:2">
       <c r="A1676" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="B1676" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1677" spans="1:2">
       <c r="A1677" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="B1677" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1678" spans="1:2">
       <c r="A1678" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="B1678" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1681" spans="1:2">
       <c r="A1681" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:2">
+      <c r="A1682" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:2">
+      <c r="A1683" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:2">
+      <c r="A1684" t="s">
         <v>1857</v>
       </c>
-    </row>
-    <row r="1682" spans="1:2">
-      <c r="A1682" s="2" t="s">
+      <c r="B1684" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:2">
+      <c r="A1685" t="s">
         <v>1858</v>
       </c>
-      <c r="B1682" t="s">
+      <c r="B1685" t="s">
         <v>1876</v>
       </c>
     </row>
-    <row r="1683" spans="1:2">
-      <c r="A1683" s="2" t="s">
+    <row r="1686" spans="1:2">
+      <c r="A1686" t="s">
         <v>1859</v>
       </c>
-      <c r="B1683" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="1684" spans="1:2">
-      <c r="A1684" s="2" t="s">
+      <c r="B1686" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:2">
+      <c r="A1687" t="s">
         <v>1860</v>
       </c>
-      <c r="B1684" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="1685" spans="1:2">
-      <c r="A1685" s="2" t="s">
+      <c r="B1687" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:2">
+      <c r="A1688" t="s">
         <v>1861</v>
       </c>
-      <c r="B1685" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="1686" spans="1:2">
-      <c r="A1686" s="2" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B1686" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="1687" spans="1:2">
-      <c r="A1687" s="2" t="s">
+      <c r="B1688" t="s">
         <v>1863</v>
       </c>
-      <c r="B1687" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="1688" spans="1:2">
-      <c r="A1688" s="2" t="s">
+    </row>
+    <row r="1689" spans="1:2">
+      <c r="A1689" t="s">
         <v>1864</v>
       </c>
-      <c r="B1688" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="1689" spans="1:2">
-      <c r="A1689" s="2" t="s">
-        <v>1867</v>
-      </c>
       <c r="B1689" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1690" spans="1:2">
-      <c r="A1690" s="2" t="s">
-        <v>1868</v>
+      <c r="A1690" t="s">
+        <v>1865</v>
       </c>
       <c r="B1690" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1691" spans="1:2">
       <c r="A1691" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="B1691" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1692" spans="1:2">
       <c r="A1692" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="B1692" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1693" spans="1:2">
-      <c r="A1693" s="2" t="s">
+      <c r="A1693" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:2">
+      <c r="A1694" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:2">
+      <c r="A1695" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:2">
+      <c r="A1696" t="s">
         <v>1880</v>
       </c>
-      <c r="B1693" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1694" spans="1:2">
-      <c r="A1694" s="2" t="s">
+      <c r="B1696" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:2">
+      <c r="A1697" t="s">
         <v>1881</v>
       </c>
-      <c r="B1694" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1695" spans="1:2">
-      <c r="A1695" s="2" t="s">
+      <c r="B1697" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:2">
+      <c r="A1698" t="s">
         <v>1882</v>
       </c>
-      <c r="B1695" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1696" spans="1:2">
-      <c r="A1696" s="2" t="s">
+      <c r="B1698" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:2">
+      <c r="A1699" t="s">
         <v>1883</v>
       </c>
-      <c r="B1696" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1697" spans="1:2">
-      <c r="A1697" s="2" t="s">
+      <c r="B1699" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:2">
+      <c r="A1700" t="s">
         <v>1884</v>
       </c>
-      <c r="B1697" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1698" spans="1:2">
-      <c r="A1698" s="2" t="s">
+      <c r="B1700" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:2">
+      <c r="A1701" t="s">
         <v>1885</v>
       </c>
-      <c r="B1698" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1699" spans="1:2">
-      <c r="A1699" s="2" t="s">
+      <c r="B1701" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:2">
+      <c r="A1702" t="s">
         <v>1886</v>
       </c>
-      <c r="B1699" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1700" spans="1:2">
-      <c r="A1700" s="2" t="s">
+      <c r="B1702" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:2">
+      <c r="A1703" t="s">
         <v>1887</v>
       </c>
-      <c r="B1700" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1701" spans="1:2">
-      <c r="A1701" s="2" t="s">
+      <c r="B1703" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:2">
+      <c r="A1704" t="s">
         <v>1888</v>
       </c>
-      <c r="B1701" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1702" spans="1:2">
-      <c r="A1702" s="2" t="s">
+      <c r="B1704" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:2">
+      <c r="A1705" t="s">
         <v>1889</v>
       </c>
-      <c r="B1702" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1703" spans="1:2">
-      <c r="A1703" s="2" t="s">
+      <c r="B1705" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:2">
+      <c r="A1706" t="s">
         <v>1890</v>
       </c>
-      <c r="B1703" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1704" spans="1:2">
-      <c r="A1704" s="2" t="s">
+      <c r="B1706" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:2">
+      <c r="A1707" t="s">
         <v>1891</v>
       </c>
-      <c r="B1704" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1705" spans="1:2">
-      <c r="A1705" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B1705" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1706" spans="1:2">
-      <c r="A1706" s="2" t="s">
-        <v>1893</v>
-      </c>
-      <c r="B1706" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="1707" spans="1:2">
-      <c r="A1707" s="2" t="s">
-        <v>1894</v>
-      </c>
       <c r="B1707" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1708" spans="1:2">
       <c r="A1708" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:2">
+      <c r="A1709" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1709" t="s">
         <v>1895</v>
       </c>
-      <c r="B1708" t="s">
+    </row>
+    <row r="1710" spans="1:2">
+      <c r="A1710" t="s">
         <v>1896</v>
       </c>
-    </row>
-    <row r="1709" spans="1:2">
-      <c r="A1709" s="2" t="s">
+      <c r="B1710" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:2">
+      <c r="A1711" t="s">
         <v>1897</v>
       </c>
-      <c r="B1709" t="s">
+      <c r="B1711" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:2">
+      <c r="A1712" t="s">
         <v>1898</v>
       </c>
-    </row>
-    <row r="1710" spans="1:2">
-      <c r="A1710" s="2" t="s">
+      <c r="B1712" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:2">
+      <c r="A1713" t="s">
         <v>1899</v>
       </c>
-      <c r="B1710" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1711" spans="1:2">
-      <c r="A1711" s="2" t="s">
+      <c r="B1713" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:2">
+      <c r="A1714" t="s">
         <v>1900</v>
       </c>
-      <c r="B1711" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1712" spans="1:2">
-      <c r="A1712" s="2" t="s">
+      <c r="B1714" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:2">
+      <c r="A1715" t="s">
         <v>1901</v>
       </c>
-      <c r="B1712" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1713" spans="1:2">
-      <c r="A1713" s="2" t="s">
+      <c r="B1715" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:2">
+      <c r="A1716" t="s">
         <v>1902</v>
       </c>
-      <c r="B1713" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1714" spans="1:2">
-      <c r="A1714" s="2" t="s">
+      <c r="B1716" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:2">
+      <c r="A1717" t="s">
         <v>1903</v>
       </c>
-      <c r="B1714" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1715" spans="1:2">
-      <c r="A1715" s="2" t="s">
+      <c r="B1717" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:2">
+      <c r="A1718" t="s">
         <v>1904</v>
       </c>
-      <c r="B1715" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1716" spans="1:2">
-      <c r="A1716" s="2" t="s">
+      <c r="B1718" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:2">
+      <c r="A1719" t="s">
         <v>1905</v>
       </c>
-      <c r="B1716" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1717" spans="1:2">
-      <c r="A1717" s="2" t="s">
+      <c r="B1719" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:2">
+      <c r="A1720" t="s">
         <v>1906</v>
       </c>
-      <c r="B1717" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1718" spans="1:2">
-      <c r="A1718" s="2" t="s">
+      <c r="B1720" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:2">
+      <c r="A1721" t="s">
         <v>1907</v>
       </c>
-      <c r="B1718" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="1719" spans="1:2">
-      <c r="A1719" s="2" t="s">
+      <c r="B1721" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:2">
+      <c r="A1722" t="s">
         <v>1908</v>
       </c>
-      <c r="B1719" t="s">
+      <c r="B1722" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:2">
+      <c r="A1723" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:2">
+      <c r="A1724" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:2">
+      <c r="A1725" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:2">
+      <c r="A1726" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:2">
+      <c r="A1727" t="s">
         <v>1915</v>
       </c>
-    </row>
-    <row r="1720" spans="1:2">
-      <c r="A1720" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B1720" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1721" spans="1:2">
-      <c r="A1721" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B1721" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1722" spans="1:2">
-      <c r="A1722" s="2" t="s">
-        <v>1911</v>
-      </c>
-      <c r="B1722" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1723" spans="1:2">
-      <c r="A1723" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B1723" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1724" spans="1:2">
-      <c r="A1724" s="2" t="s">
+      <c r="B1727" t="s">
         <v>1913</v>
       </c>
-      <c r="B1724" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1725" spans="1:2">
-      <c r="A1725" s="2" t="s">
-        <v>1914</v>
-      </c>
-      <c r="B1725" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="1726" spans="1:2">
-      <c r="A1726" s="2" t="s">
+    </row>
+    <row r="1728" spans="1:2">
+      <c r="A1728" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B1728" t="s">
         <v>1917</v>
-      </c>
-      <c r="B1726" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="1727" spans="1:2">
-      <c r="A1727" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B1727" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="1728" spans="1:2">
-      <c r="A1728" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="B1728" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="1729" spans="1:2">
       <c r="A1729" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:2">
+      <c r="A1730" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:2">
+      <c r="A1731" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:2">
+      <c r="A1732" t="s">
         <v>1921</v>
       </c>
-      <c r="B1729" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="1730" spans="1:2">
-      <c r="A1730" s="2" t="s">
+      <c r="B1732" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:2">
+      <c r="A1733" t="s">
         <v>1922</v>
       </c>
-      <c r="B1730" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="1731" spans="1:2">
-      <c r="A1731" s="2" t="s">
+      <c r="B1733" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:2">
+      <c r="A1734" t="s">
         <v>1923</v>
       </c>
-      <c r="B1731" t="s">
+      <c r="B1734" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" t="s">
         <v>1927</v>
       </c>
-    </row>
-    <row r="1732" spans="1:2">
-      <c r="A1732" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B1732" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="1733" spans="1:2">
-      <c r="A1733" s="2" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B1733" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="1734" spans="1:2">
-      <c r="A1734" s="2" t="s">
+      <c r="B1735" t="s">
         <v>1926</v>
       </c>
-      <c r="B1734" t="s">
+    </row>
+    <row r="1736" spans="1:2">
+      <c r="A1736" t="s">
         <v>1928</v>
       </c>
-    </row>
-    <row r="1735" spans="1:2">
-      <c r="A1735" s="2" t="s">
+      <c r="B1736" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:2">
+      <c r="A1737" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:2">
+      <c r="A1738" t="s">
         <v>1930</v>
       </c>
-      <c r="B1735" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1736" spans="1:2">
-      <c r="A1736" s="2" t="s">
+      <c r="B1738" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:2">
+      <c r="A1739" t="s">
         <v>1931</v>
       </c>
-      <c r="B1736" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="1737" spans="1:2">
-      <c r="A1737" s="2" t="s">
+      <c r="B1739" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:2">
+      <c r="A1740" t="s">
         <v>1932</v>
       </c>
-      <c r="B1737" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1738" spans="1:2">
-      <c r="A1738" s="2" t="s">
+      <c r="B1740" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:2">
+      <c r="A1741" t="s">
         <v>1933</v>
       </c>
-      <c r="B1738" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1739" spans="1:2">
-      <c r="A1739" s="2" t="s">
+      <c r="B1741" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:2">
+      <c r="A1742" t="s">
         <v>1934</v>
       </c>
-      <c r="B1739" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1740" spans="1:2">
-      <c r="A1740" s="2" t="s">
+      <c r="B1742" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:2">
+      <c r="A1743" t="s">
         <v>1935</v>
       </c>
-      <c r="B1740" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1741" spans="1:2">
-      <c r="A1741" s="2" t="s">
+      <c r="B1743" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:2">
+      <c r="A1744" t="s">
         <v>1936</v>
       </c>
-      <c r="B1741" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1742" spans="1:2">
-      <c r="A1742" s="2" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B1742" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1743" spans="1:2">
-      <c r="A1743" s="2" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B1743" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1744" spans="1:2">
-      <c r="A1744" s="2" t="s">
-        <v>1939</v>
-      </c>
       <c r="B1744" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1745" spans="1:2">
       <c r="A1745" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:2">
+      <c r="A1746" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:2">
+      <c r="A1747" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1747" t="s">
         <v>1940</v>
       </c>
-      <c r="B1745" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1746" spans="1:2">
-      <c r="A1746" s="2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="B1746" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="1747" spans="1:2">
-      <c r="A1747" s="2" t="s">
+    </row>
+    <row r="1748" spans="1:2">
+      <c r="A1748" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:2">
+      <c r="A1749" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:2">
+      <c r="A1750" t="s">
         <v>1944</v>
       </c>
-      <c r="B1747" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1748" spans="1:2">
-      <c r="A1748" s="2" t="s">
+      <c r="B1750" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:2">
+      <c r="A1751" t="s">
         <v>1945</v>
       </c>
-      <c r="B1748" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1749" spans="1:2">
-      <c r="A1749" s="2" t="s">
+      <c r="B1751" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:2">
+      <c r="A1752" t="s">
         <v>1946</v>
       </c>
-      <c r="B1749" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1750" spans="1:2">
-      <c r="A1750" s="2" t="s">
-        <v>1947</v>
-      </c>
-      <c r="B1750" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1751" spans="1:2">
-      <c r="A1751" s="2" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B1751" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1752" spans="1:2">
-      <c r="A1752" s="2" t="s">
-        <v>1949</v>
-      </c>
       <c r="B1752" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1753" spans="1:2">
       <c r="A1753" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:2">
+      <c r="A1754" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:2">
+      <c r="A1755" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:2">
+      <c r="A1756" t="s">
         <v>1950</v>
       </c>
-      <c r="B1753" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1754" spans="1:2">
-      <c r="A1754" s="2" t="s">
+      <c r="B1756" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:2">
+      <c r="A1757" t="s">
         <v>1951</v>
       </c>
-      <c r="B1754" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1755" spans="1:2">
-      <c r="A1755" s="2" t="s">
+      <c r="B1757" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:2">
+      <c r="A1758" t="s">
         <v>1952</v>
       </c>
-      <c r="B1755" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1756" spans="1:2">
-      <c r="A1756" s="2" t="s">
+      <c r="B1758" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:2">
+      <c r="A1759" t="s">
         <v>1953</v>
       </c>
-      <c r="B1756" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1757" spans="1:2">
-      <c r="A1757" s="2" t="s">
+      <c r="B1759" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:2">
+      <c r="A1760" t="s">
         <v>1954</v>
       </c>
-      <c r="B1757" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1758" spans="1:2">
-      <c r="A1758" s="2" t="s">
+      <c r="B1760" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:2">
+      <c r="A1761" t="s">
         <v>1955</v>
       </c>
-      <c r="B1758" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1759" spans="1:2">
-      <c r="A1759" s="2" t="s">
+      <c r="B1761" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:2">
+      <c r="A1762" t="s">
         <v>1956</v>
       </c>
-      <c r="B1759" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1760" spans="1:2">
-      <c r="A1760" s="2" t="s">
+      <c r="B1762" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:2">
+      <c r="A1763" t="s">
         <v>1957</v>
       </c>
-      <c r="B1760" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1761" spans="1:2">
-      <c r="A1761" s="2" t="s">
+      <c r="B1763" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:2">
+      <c r="A1764" t="s">
         <v>1958</v>
       </c>
-      <c r="B1761" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1762" spans="1:2">
-      <c r="A1762" s="2" t="s">
+      <c r="B1764" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:2">
+      <c r="A1765" t="s">
         <v>1959</v>
       </c>
-      <c r="B1762" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1763" spans="1:2">
-      <c r="A1763" s="2" t="s">
+      <c r="B1765" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:2">
+      <c r="A1766" t="s">
         <v>1960</v>
       </c>
-      <c r="B1763" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1764" spans="1:2">
-      <c r="A1764" s="2" t="s">
+      <c r="B1766" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:2">
+      <c r="A1767" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1767" t="s">
         <v>1961</v>
       </c>
-      <c r="B1764" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1765" spans="1:2">
-      <c r="A1765" s="2" t="s">
-        <v>1962</v>
-      </c>
-      <c r="B1765" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1766" spans="1:2">
-      <c r="A1766" s="2" t="s">
+    </row>
+    <row r="1768" spans="1:2">
+      <c r="A1768" t="s">
         <v>1963</v>
       </c>
-      <c r="B1766" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="1767" spans="1:2">
-      <c r="A1767" s="2" t="s">
+      <c r="B1768" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:2">
+      <c r="A1769" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:2">
+      <c r="A1770" t="s">
         <v>1965</v>
       </c>
-      <c r="B1767" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1768" spans="1:2">
-      <c r="A1768" s="2" t="s">
+      <c r="B1770" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:2">
+      <c r="A1771" t="s">
         <v>1966</v>
       </c>
-      <c r="B1768" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1769" spans="1:2">
-      <c r="A1769" s="2" t="s">
+      <c r="B1771" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:2">
+      <c r="A1772" t="s">
         <v>1967</v>
       </c>
-      <c r="B1769" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1770" spans="1:2">
-      <c r="A1770" s="2" t="s">
+      <c r="B1772" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:2">
+      <c r="A1773" t="s">
         <v>1968</v>
       </c>
-      <c r="B1770" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1771" spans="1:2">
-      <c r="A1771" s="2" t="s">
+      <c r="B1773" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:2">
+      <c r="A1774" t="s">
         <v>1969</v>
       </c>
-      <c r="B1771" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1772" spans="1:2">
-      <c r="A1772" s="2" t="s">
+      <c r="B1774" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:2">
+      <c r="A1775" t="s">
         <v>1970</v>
       </c>
-      <c r="B1772" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1773" spans="1:2">
-      <c r="A1773" s="2" t="s">
+      <c r="B1775" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:2">
+      <c r="A1776" t="s">
         <v>1971</v>
       </c>
-      <c r="B1773" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1774" spans="1:2">
-      <c r="A1774" s="2" t="s">
+      <c r="B1776" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:2">
+      <c r="A1777" t="s">
         <v>1972</v>
       </c>
-      <c r="B1774" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1775" spans="1:2">
-      <c r="A1775" s="2" t="s">
+      <c r="B1777" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:2">
+      <c r="A1778" t="s">
         <v>1973</v>
       </c>
-      <c r="B1775" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1776" spans="1:2">
-      <c r="A1776" s="2" t="s">
+      <c r="B1778" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:2">
+      <c r="A1779" t="s">
         <v>1974</v>
       </c>
-      <c r="B1776" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1777" spans="1:2">
-      <c r="A1777" s="2" t="s">
+      <c r="B1779" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:2">
+      <c r="A1780" t="s">
         <v>1975</v>
       </c>
-      <c r="B1777" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1778" spans="1:2">
-      <c r="A1778" s="2" t="s">
+      <c r="B1780" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:2">
+      <c r="A1781" t="s">
         <v>1976</v>
       </c>
-      <c r="B1778" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1779" spans="1:2">
-      <c r="A1779" s="2" t="s">
+      <c r="B1781" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:2">
+      <c r="A1782" t="s">
         <v>1977</v>
       </c>
-      <c r="B1779" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1780" spans="1:2">
-      <c r="A1780" s="2" t="s">
+      <c r="B1782" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:2">
+      <c r="A1783" t="s">
         <v>1978</v>
       </c>
-      <c r="B1780" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1781" spans="1:2">
-      <c r="A1781" s="2" t="s">
+      <c r="B1783" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:2">
+      <c r="A1784" t="s">
         <v>1979</v>
       </c>
-      <c r="B1781" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1782" spans="1:2">
-      <c r="A1782" s="2" t="s">
+      <c r="B1784" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:2">
+      <c r="A1785" t="s">
         <v>1980</v>
       </c>
-      <c r="B1782" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1783" spans="1:2">
-      <c r="A1783" s="2" t="s">
+      <c r="B1785" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:2">
+      <c r="A1786" t="s">
         <v>1981</v>
       </c>
-      <c r="B1783" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1784" spans="1:2">
-      <c r="A1784" s="2" t="s">
+      <c r="B1786" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:2">
+      <c r="A1787" t="s">
         <v>1982</v>
       </c>
-      <c r="B1784" t="s">
+      <c r="B1787" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:2">
+      <c r="A1788" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:2">
+      <c r="A1789" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:2">
+      <c r="A1790" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:2">
+      <c r="A1791" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:2">
+      <c r="A1792" t="s">
         <v>1988</v>
       </c>
-    </row>
-    <row r="1785" spans="1:2">
-      <c r="A1785" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B1785" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1786" spans="1:2">
-      <c r="A1786" s="2" t="s">
-        <v>1984</v>
-      </c>
-      <c r="B1786" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1787" spans="1:2">
-      <c r="A1787" s="2" t="s">
-        <v>1985</v>
-      </c>
-      <c r="B1787" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1788" spans="1:2">
-      <c r="A1788" s="2" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B1788" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1789" spans="1:2">
-      <c r="A1789" s="2" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B1789" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="1790" spans="1:2">
-      <c r="A1790" s="2" t="s">
+      <c r="B1792" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:2">
+      <c r="A1793" t="s">
         <v>1989</v>
       </c>
-      <c r="B1790" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1791" spans="1:2">
-      <c r="A1791" s="2" t="s">
+      <c r="B1793" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:2">
+      <c r="A1794" t="s">
         <v>1990</v>
       </c>
-      <c r="B1791" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1792" spans="1:2">
-      <c r="A1792" s="2" t="s">
+      <c r="B1794" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:2">
+      <c r="A1795" t="s">
         <v>1991</v>
       </c>
-      <c r="B1792" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1793" spans="1:2">
-      <c r="A1793" s="2" t="s">
+      <c r="B1795" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:2">
+      <c r="A1796" t="s">
         <v>1992</v>
       </c>
-      <c r="B1793" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1794" spans="1:2">
-      <c r="A1794" s="2" t="s">
+      <c r="B1796" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:2">
+      <c r="A1797" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:2">
+      <c r="A1798" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:2">
+      <c r="A1799" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:2">
+      <c r="A1800" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:2">
+      <c r="A1801" t="s">
         <v>1993</v>
       </c>
-      <c r="B1794" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1795" spans="1:2">
-      <c r="A1795" s="2" t="s">
-        <v>1994</v>
-      </c>
-      <c r="B1795" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="1796" spans="1:2">
-      <c r="A1796" s="2" t="s">
+      <c r="B1801" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:2">
+      <c r="A1802" t="s">
         <v>1995</v>
       </c>
-      <c r="B1796" t="s">
+      <c r="B1802" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:2">
+      <c r="A1803" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:2">
+      <c r="A1804" t="s">
         <v>1997</v>
       </c>
-    </row>
-    <row r="1797" spans="1:2">
-      <c r="A1797" s="2" t="s">
-        <v>2006</v>
-      </c>
-      <c r="B1797" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="1798" spans="1:2">
-      <c r="A1798" s="2" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B1798" t="s">
+      <c r="B1804" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:2">
+      <c r="A1805" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:2">
+      <c r="A1806" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:2">
+      <c r="A1807" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:2">
+      <c r="A1808" t="s">
         <v>2010</v>
       </c>
-    </row>
-    <row r="1799" spans="1:2">
-      <c r="A1799" s="2" t="s">
-        <v>2008</v>
-      </c>
-      <c r="B1799" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="1800" spans="1:2">
-      <c r="A1800" s="2" t="s">
+      <c r="B1808" t="s">
         <v>2009</v>
       </c>
-      <c r="B1800" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="1801" spans="1:2">
-      <c r="A1801" s="2" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B1801" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="1802" spans="1:2">
-      <c r="A1802" s="2" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B1802" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="1803" spans="1:2">
-      <c r="A1803" s="2" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B1803" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="1804" spans="1:2">
-      <c r="A1804" s="2" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B1804" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="1805" spans="1:2">
-      <c r="A1805" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B1805" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="1806" spans="1:2">
-      <c r="A1806" s="2" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B1806" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="1807" spans="1:2">
-      <c r="A1807" s="2" t="s">
+    </row>
+    <row r="1809" spans="1:2">
+      <c r="A1809" t="s">
         <v>2011</v>
       </c>
-      <c r="B1807" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="1808" spans="1:2">
-      <c r="A1808" s="2" t="s">
+      <c r="B1809" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:2">
+      <c r="A1810" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:2">
+      <c r="A1811" t="s">
         <v>2013</v>
       </c>
-      <c r="B1808" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1809" spans="1:2">
-      <c r="A1809" s="2" t="s">
+      <c r="B1811" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:2">
+      <c r="A1812" t="s">
         <v>2014</v>
       </c>
-      <c r="B1809" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1810" spans="1:2">
-      <c r="A1810" s="2" t="s">
+      <c r="B1812" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:2">
+      <c r="A1813" t="s">
         <v>2015</v>
       </c>
-      <c r="B1810" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1811" spans="1:2">
-      <c r="A1811" s="2" t="s">
+      <c r="B1813" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:2">
+      <c r="A1814" t="s">
         <v>2016</v>
       </c>
-      <c r="B1811" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1812" spans="1:2">
-      <c r="A1812" s="2" t="s">
-        <v>2017</v>
-      </c>
-      <c r="B1812" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1813" spans="1:2">
-      <c r="A1813" s="2" t="s">
-        <v>2018</v>
-      </c>
-      <c r="B1813" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="1814" spans="1:2">
-      <c r="A1814" s="2" t="s">
-        <v>2019</v>
-      </c>
       <c r="B1814" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1815" spans="1:2">
       <c r="A1815" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B1815" t="s">
-        <v>1813</v>
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:2">
+      <c r="A1818" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:2">
+      <c r="A1819" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:2">
+      <c r="A1820" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:2">
+      <c r="A1821" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:2">
+      <c r="A1822" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:2">
+      <c r="A1823" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:2">
+      <c r="A1824" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:2">
+      <c r="A1825" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:2">
+      <c r="A1826" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:2">
+      <c r="A1827" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:2">
+      <c r="A1828" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:2">
+      <c r="A1829" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:2">
+      <c r="A1830" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:2">
+      <c r="A1831" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:2">
+      <c r="A1832" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:2">
+      <c r="A1833" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:2">
+      <c r="A1834" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:2">
+      <c r="A1835" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:2">
+      <c r="A1836" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:2">
+      <c r="A1837" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:2">
+      <c r="A1838" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:2">
+      <c r="A1839" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:2">
+      <c r="A1840" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:2">
+      <c r="A1841" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:2">
+      <c r="A1842" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:2">
+      <c r="A1843" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1843" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:2">
+      <c r="A1844" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1844" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:2">
+      <c r="A1845" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1845" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:2">
+      <c r="A1846" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1846" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:2">
+      <c r="A1847" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1847" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:2">
+      <c r="A1848" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1848" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:2">
+      <c r="A1849" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1849" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:2">
+      <c r="A1850" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:2">
+      <c r="A1851" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:2">
+      <c r="A1852" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:2">
+      <c r="A1853" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:2">
+      <c r="A1854" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:2">
+      <c r="A1855" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:2">
+      <c r="A1856" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:2">
+      <c r="A1857" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:2">
+      <c r="A1858" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:2">
+      <c r="A1859" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:2">
+      <c r="A1860" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:2">
+      <c r="A1861" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:2">
+      <c r="A1862" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:2">
+      <c r="A1863" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:2">
+      <c r="A1864" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:2">
+      <c r="A1865" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:2">
+      <c r="A1866" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:2">
+      <c r="A1867" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:2">
+      <c r="A1868" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:2">
+      <c r="A1869" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:2">
+      <c r="A1870" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:2">
+      <c r="A1871" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:2">
+      <c r="A1872" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:2">
+      <c r="A1873" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:2">
+      <c r="A1874" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:2">
+      <c r="A1875" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:2">
+      <c r="A1876" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:2">
+      <c r="A1877" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:2">
+      <c r="A1878" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:2">
+      <c r="A1879" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:2">
+      <c r="A1880" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:2">
+      <c r="A1881" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:2">
+      <c r="A1882" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:2">
+      <c r="A1883" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:2">
+      <c r="A1884" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:2">
+      <c r="A1885" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:2">
+      <c r="A1886" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:2">
+      <c r="A1887" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:2">
+      <c r="A1888" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:2">
+      <c r="A1889" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:2">
+      <c r="A1890" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:2">
+      <c r="A1891" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:2">
+      <c r="A1892" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:2">
+      <c r="A1893" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:2">
+      <c r="A1894" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:2">
+      <c r="A1895" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:2">
+      <c r="A1896" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:2">
+      <c r="A1897" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:2">
+      <c r="A1898" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:2">
+      <c r="A1899" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:2">
+      <c r="A1900" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:2">
+      <c r="A1901" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:2">
+      <c r="A1902" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:2">
+      <c r="A1903" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:2">
+      <c r="A1904" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:2">
+      <c r="A1905" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:2">
+      <c r="A1906" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:2">
+      <c r="A1907" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:2">
+      <c r="A1908" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:2">
+      <c r="A1909" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:2">
+      <c r="A1910" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:2">
+      <c r="A1911" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:2">
+      <c r="A1912" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:2">
+      <c r="A1913" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:2">
+      <c r="A1914" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:2">
+      <c r="A1915" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:2">
+      <c r="A1916" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:2">
+      <c r="A1917" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:2">
+      <c r="A1918" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:2">
+      <c r="A1919" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:2">
+      <c r="A1920" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:2">
+      <c r="A1921" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:2">
+      <c r="A1922" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:2">
+      <c r="A1923" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:2">
+      <c r="A1924" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:2">
+      <c r="A1925" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:2">
+      <c r="A1926" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:2">
+      <c r="A1927" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:2">
+      <c r="A1928" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:2">
+      <c r="A1929" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:2">
+      <c r="A1930" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:2">
+      <c r="A1931" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:2">
+      <c r="A1932" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:2">
+      <c r="A1933" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:2">
+      <c r="A1934" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:2">
+      <c r="A1935" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:2">
+      <c r="A1936" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:2">
+      <c r="A1937" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:2">
+      <c r="A1938" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:2">
+      <c r="A1939" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:2">
+      <c r="A1940" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:2">
+      <c r="A1941" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:2">
+      <c r="A1942" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:2">
+      <c r="A1943" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:2">
+      <c r="A1944" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:2">
+      <c r="A1945" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:2">
+      <c r="A1946" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:2">
+      <c r="A1947" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:2">
+      <c r="A1948" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:2">
+      <c r="A1949" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:2">
+      <c r="A1950" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:2">
+      <c r="A1951" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:2">
+      <c r="A1952" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:2">
+      <c r="A1953" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:2">
+      <c r="A1954" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:2">
+      <c r="A1955" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:2">
+      <c r="A1956" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:2">
+      <c r="A1957" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:2">
+      <c r="A1958" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:2">
+      <c r="A1959" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:2">
+      <c r="A1960" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:2">
+      <c r="A1961" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:2">
+      <c r="A1962" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:2">
+      <c r="A1963" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:2">
+      <c r="A1964" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:2">
+      <c r="A1965" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:2">
+      <c r="A1966" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:2">
+      <c r="A1967" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:2">
+      <c r="A1968" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:2">
+      <c r="A1969" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:2">
+      <c r="A1970" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:2">
+      <c r="A1971" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:2">
+      <c r="A1972" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:2">
+      <c r="A1973" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:2">
+      <c r="A1974" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:2">
+      <c r="A1975" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:2">
+      <c r="A1976" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:2">
+      <c r="A1977" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:2">
+      <c r="A1978" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:2">
+      <c r="A1979" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:2">
+      <c r="A1980" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:2">
+      <c r="A1981" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:2">
+      <c r="A1982" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:2">
+      <c r="A1983" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:2">
+      <c r="A1984" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:2">
+      <c r="A1985" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:2">
+      <c r="A1986" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:2">
+      <c r="A1987" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:2">
+      <c r="A1988" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:2">
+      <c r="A1989" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:2">
+      <c r="A1990" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:2">
+      <c r="A1991" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:2">
+      <c r="A1992" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:2">
+      <c r="A1993" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:2">
+      <c r="A1994" s="2" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:2">
+      <c r="A1995" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:2">
+      <c r="A1996" s="2" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:2">
+      <c r="A1997" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:2">
+      <c r="A1998" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:2">
+      <c r="A1999" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:2">
+      <c r="A2000" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:2">
+      <c r="A2001" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:2">
+      <c r="A2002" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:2">
+      <c r="A2003" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:2">
+      <c r="A2004" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:2">
+      <c r="A2005" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:2">
+      <c r="A2006" s="2" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:2">
+      <c r="A2007" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:2">
+      <c r="A2008" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:2">
+      <c r="A2009" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:2">
+      <c r="A2010" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:2">
+      <c r="A2011" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:2">
+      <c r="A2012" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:2">
+      <c r="A2013" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:2">
+      <c r="A2014" s="2" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:2">
+      <c r="A2015" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:2">
+      <c r="A2016" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:2">
+      <c r="A2017" s="2" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:2">
+      <c r="A2018" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:2">
+      <c r="A2019" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:2">
+      <c r="A2020" s="2" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:2">
+      <c r="A2021" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:2">
+      <c r="A2022" s="2" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:2">
+      <c r="A2023" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:2">
+      <c r="A2024" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:2">
+      <c r="A2025" s="2" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B2025" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:2">
+      <c r="A2026" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B2026" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:2">
+      <c r="A2027" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:2">
+      <c r="A2028" s="2" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:2">
+      <c r="A2029" s="2" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:2">
+      <c r="A2030" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B2030" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:2">
+      <c r="A2031" s="2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B2031" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:2">
+      <c r="A2032" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B2032" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:2">
+      <c r="A2033" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B2033" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:2">
+      <c r="A2034" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:2">
+      <c r="A2035" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:2">
+      <c r="A2036" s="2" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B2036" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:2">
+      <c r="A2037" s="2" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:2">
+      <c r="A2038" s="2" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:2">
+      <c r="A2039" s="2" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B2039" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:2">
+      <c r="A2040" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:2">
+      <c r="A2041" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B2041" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:2">
+      <c r="A2042" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:2">
+      <c r="A2043" s="2" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:2">
+      <c r="A2044" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:2">
+      <c r="A2045" s="2" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:2">
+      <c r="A2046" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:2">
+      <c r="A2047" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>1688</v>
       </c>
     </row>
   </sheetData>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0D031B0-458E-4564-9EF8-BA7FA3AEC1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557F49EF-4AA0-45C8-BA78-543F11B5B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11364" yWindow="0" windowWidth="11772" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -7810,43 +7810,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、埼京線、川越線、東武アーバンパークライン、埼玉新都市交通ニューシャトル、東北新幹線、上越新幹線、北陸新幹線、（上野東京ライン）</t>
-    <rPh sb="0" eb="5">
-      <t>ケイヒントウホクセン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>サイキョウセン</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>カワゴエセン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>トウブ</t>
-    </rPh>
-    <rPh sb="59" eb="64">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <rPh sb="65" eb="70">
-      <t>ジョウエツシンカンセン</t>
-    </rPh>
-    <rPh sb="71" eb="76">
-      <t>ホクリクシンカンセン</t>
-    </rPh>
-    <rPh sb="78" eb="82">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、（上野東京ライン）</t>
     <rPh sb="0" eb="5">
       <t>ケイヒントウホクセン</t>
@@ -7947,25 +7910,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>高崎線、湘南新宿ライン、（上野東京ライン）、秩父鉄道、上越新幹線、北陸新幹線</t>
-    <rPh sb="4" eb="8">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>チチブテツドウ</t>
-    </rPh>
-    <rPh sb="27" eb="32">
-      <t>ジョウエツシンカンセン</t>
-    </rPh>
-    <rPh sb="33" eb="38">
-      <t>ホクリクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>埼京線</t>
   </si>
   <si>
@@ -8000,16 +7944,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>上越新幹線、北陸新幹線</t>
-    <rPh sb="0" eb="5">
-      <t>ジョウエツシンカンセン</t>
-    </rPh>
-    <rPh sb="6" eb="11">
-      <t>ホクリクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>本庄早稲田</t>
     <rPh sb="0" eb="5">
       <t>ホンジョウワセダ</t>
@@ -8912,6 +8846,63 @@
   </si>
   <si>
     <t>三郷中央</t>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、埼京線、川越線、東武アーバンパークライン、埼玉新都市交通ニューシャトル、東北新幹線、上越新幹線、（上野東京ライン）</t>
+    <rPh sb="0" eb="5">
+      <t>ケイヒントウホクセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>サイキョウセン</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>カワゴエセン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="59" eb="64">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <rPh sb="65" eb="70">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <rPh sb="72" eb="76">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上越新幹線</t>
+    <rPh sb="0" eb="5">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、湘南新宿ライン、（上野東京ライン）、秩父鉄道、上越新幹線</t>
+    <rPh sb="4" eb="8">
+      <t>ショウナンシンジュク</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>チチブテツドウ</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>ジョウエツシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -23674,7 +23665,7 @@
         <v>2023</v>
       </c>
       <c r="B1819" t="s">
-        <v>2033</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
@@ -23682,7 +23673,7 @@
         <v>2024</v>
       </c>
       <c r="B1820" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
@@ -23706,7 +23697,7 @@
         <v>2027</v>
       </c>
       <c r="B1823" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1824" spans="1:2">
@@ -23714,7 +23705,7 @@
         <v>2028</v>
       </c>
       <c r="B1824" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1825" spans="1:2">
@@ -23743,287 +23734,287 @@
     </row>
     <row r="1828" spans="1:2">
       <c r="A1828" s="2" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B1828" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1829" spans="1:2">
       <c r="A1829" s="2" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B1829" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1830" spans="1:2">
       <c r="A1830" s="2" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B1830" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
       <c r="A1831" s="2" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1831" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1832" spans="1:2">
       <c r="A1832" s="2" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1832" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1833" spans="1:2">
       <c r="A1833" s="2" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1833" t="s">
-        <v>2053</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="1834" spans="1:2">
       <c r="A1834" s="2" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B1834" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="2" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B1835" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="2" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1836" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="2" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1837" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" s="2" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B1838" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" s="2" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1839" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" s="2" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B1840" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" s="2" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B1841" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1842" spans="1:2">
       <c r="A1842" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1842" t="s">
         <v>2051</v>
-      </c>
-      <c r="B1842" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="1843" spans="1:2">
       <c r="A1843" s="2" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="B1843" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1844" spans="1:2">
       <c r="A1844" s="2" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="B1844" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1845" spans="1:2">
       <c r="A1845" s="2" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="B1845" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1846" spans="1:2">
       <c r="A1846" s="2" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="B1846" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1847" spans="1:2">
       <c r="A1847" s="2" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="B1847" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1848" spans="1:2">
       <c r="A1848" s="2" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="B1848" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1849" spans="1:2">
       <c r="A1849" s="2" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="B1849" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1850" spans="1:2">
       <c r="A1850" s="2" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="B1850" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1851" spans="1:2">
       <c r="A1851" s="2" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="B1851" t="s">
-        <v>2064</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1852" spans="1:2">
       <c r="A1852" s="2" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="B1852" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1853" spans="1:2">
       <c r="A1853" s="2" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="B1853" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1854" spans="1:2">
       <c r="A1854" s="2" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="B1854" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1855" spans="1:2">
       <c r="A1855" s="2" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="B1855" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1856" spans="1:2">
       <c r="A1856" s="2" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="B1856" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1857" spans="1:2">
       <c r="A1857" s="2" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="B1857" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1858" spans="1:2">
       <c r="A1858" s="2" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="B1858" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1859" spans="1:2">
       <c r="A1859" s="2" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="B1859" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1860" spans="1:2">
       <c r="A1860" s="2" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="B1860" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1861" spans="1:2">
       <c r="A1861" s="2" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="B1861" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1862" spans="1:2">
       <c r="A1862" s="2" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="B1862" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1863" spans="1:2">
       <c r="A1863" s="2" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="B1863" t="s">
         <v>1730</v>
@@ -24031,15 +24022,15 @@
     </row>
     <row r="1864" spans="1:2">
       <c r="A1864" s="2" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="B1864" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1865" spans="1:2">
       <c r="A1865" s="2" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="B1865" t="s">
         <v>1730</v>
@@ -24047,7 +24038,7 @@
     </row>
     <row r="1866" spans="1:2">
       <c r="A1866" s="2" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="B1866" t="s">
         <v>1730</v>
@@ -24055,7 +24046,7 @@
     </row>
     <row r="1867" spans="1:2">
       <c r="A1867" s="2" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B1867" t="s">
         <v>1730</v>
@@ -24063,7 +24054,7 @@
     </row>
     <row r="1868" spans="1:2">
       <c r="A1868" s="2" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="B1868" t="s">
         <v>1730</v>
@@ -24071,7 +24062,7 @@
     </row>
     <row r="1869" spans="1:2">
       <c r="A1869" s="2" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="B1869" t="s">
         <v>1730</v>
@@ -24079,831 +24070,831 @@
     </row>
     <row r="1870" spans="1:2">
       <c r="A1870" s="2" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="B1870" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1871" spans="1:2">
       <c r="A1871" s="2" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="B1871" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1872" spans="1:2">
       <c r="A1872" s="2" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="B1872" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1873" spans="1:2">
       <c r="A1873" s="2" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="B1873" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1874" spans="1:2">
       <c r="A1874" s="2" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="B1874" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1875" spans="1:2">
       <c r="A1875" s="2" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="B1875" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1876" spans="1:2">
       <c r="A1876" s="2" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="B1876" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1877" spans="1:2">
       <c r="A1877" s="2" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="B1877" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1878" spans="1:2">
       <c r="A1878" s="2" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="B1878" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1879" spans="1:2">
       <c r="A1879" s="2" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="B1879" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1880" spans="1:2">
       <c r="A1880" s="2" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="B1880" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1881" spans="1:2">
       <c r="A1881" s="2" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="B1881" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1882" spans="1:2">
       <c r="A1882" s="2" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="B1882" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1883" spans="1:2">
       <c r="A1883" s="2" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="B1883" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1884" spans="1:2">
       <c r="A1884" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="B1884" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1885" spans="1:2">
       <c r="A1885" s="2" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="B1885" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1886" spans="1:2">
       <c r="A1886" s="2" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="B1886" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1887" spans="1:2">
       <c r="A1887" s="2" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="B1887" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1888" spans="1:2">
       <c r="A1888" s="2" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="B1888" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1889" spans="1:2">
       <c r="A1889" s="2" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="B1889" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1890" spans="1:2">
       <c r="A1890" s="2" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="B1890" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1891" spans="1:2">
       <c r="A1891" s="2" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="B1891" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1892" spans="1:2">
       <c r="A1892" s="2" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="B1892" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1893" spans="1:2">
       <c r="A1893" s="2" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="B1893" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1894" spans="1:2">
       <c r="A1894" s="2" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="B1894" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1895" spans="1:2">
       <c r="A1895" s="2" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="B1895" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1896" spans="1:2">
       <c r="A1896" s="2" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="B1896" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1897" spans="1:2">
       <c r="A1897" s="2" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="B1897" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1898" spans="1:2">
       <c r="A1898" s="2" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="B1898" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1899" spans="1:2">
       <c r="A1899" s="2" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="B1899" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1900" spans="1:2">
       <c r="A1900" s="2" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="B1900" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1901" spans="1:2">
       <c r="A1901" s="2" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="B1901" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1902" spans="1:2">
       <c r="A1902" s="2" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="B1902" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1903" spans="1:2">
       <c r="A1903" s="2" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="B1903" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1904" spans="1:2">
       <c r="A1904" s="2" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="B1904" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1905" spans="1:2">
       <c r="A1905" s="2" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="B1905" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1906" spans="1:2">
       <c r="A1906" s="2" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="B1906" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1907" spans="1:2">
       <c r="A1907" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1907" t="s">
         <v>2135</v>
-      </c>
-      <c r="B1907" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="1908" spans="1:2">
       <c r="A1908" s="2" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="B1908" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1909" spans="1:2">
       <c r="A1909" s="2" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="B1909" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1910" spans="1:2">
       <c r="A1910" s="2" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="B1910" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1911" spans="1:2">
       <c r="A1911" s="2" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="B1911" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1912" spans="1:2">
       <c r="A1912" s="2" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="B1912" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1913" spans="1:2">
       <c r="A1913" s="2" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="B1913" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1914" spans="1:2">
       <c r="A1914" s="2" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="B1914" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1915" spans="1:2">
       <c r="A1915" s="2" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="B1915" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1916" spans="1:2">
       <c r="A1916" s="2" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="B1916" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1917" spans="1:2">
       <c r="A1917" s="2" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="B1917" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1918" spans="1:2">
       <c r="A1918" s="2" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="B1918" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1919" spans="1:2">
       <c r="A1919" s="2" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="B1919" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1920" spans="1:2">
       <c r="A1920" s="2" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="B1920" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1921" spans="1:2">
       <c r="A1921" s="2" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="B1921" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1922" spans="1:2">
       <c r="A1922" s="2" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="B1922" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1923" spans="1:2">
       <c r="A1923" s="2" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="B1923" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1924" spans="1:2">
       <c r="A1924" s="2" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="B1924" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1925" spans="1:2">
       <c r="A1925" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1925" t="s">
         <v>2159</v>
-      </c>
-      <c r="B1925" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="1926" spans="1:2">
       <c r="A1926" s="2" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B1926" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1927" spans="1:2">
       <c r="A1927" s="2" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="B1927" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1928" spans="1:2">
       <c r="A1928" s="2" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="B1928" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1929" spans="1:2">
       <c r="A1929" s="2" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="B1929" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1930" spans="1:2">
       <c r="A1930" s="2" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="B1930" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1931" spans="1:2">
       <c r="A1931" s="2" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="B1931" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1932" spans="1:2">
       <c r="A1932" s="2" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="B1932" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1933" spans="1:2">
       <c r="A1933" s="2" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="B1933" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1934" spans="1:2">
       <c r="A1934" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="B1934" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1935" spans="1:2">
       <c r="A1935" s="2" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="B1935" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1936" spans="1:2">
       <c r="A1936" s="2" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="B1936" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1937" spans="1:2">
       <c r="A1937" s="2" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="B1937" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1938" spans="1:2">
       <c r="A1938" s="2" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="B1938" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1939" spans="1:2">
       <c r="A1939" s="2" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="B1939" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1940" spans="1:2">
       <c r="A1940" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="B1940" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1941" spans="1:2">
       <c r="A1941" s="2" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="B1941" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1942" spans="1:2">
       <c r="A1942" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="B1942" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1943" spans="1:2">
       <c r="A1943" s="2" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="B1943" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1944" spans="1:2">
       <c r="A1944" s="2" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="B1944" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1945" spans="1:2">
       <c r="A1945" s="2" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="B1945" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1946" spans="1:2">
       <c r="A1946" s="2" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B1946" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1947" spans="1:2">
       <c r="A1947" s="2" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="B1947" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1948" spans="1:2">
       <c r="A1948" s="2" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B1948" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1949" spans="1:2">
       <c r="A1949" s="2" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="B1949" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1950" spans="1:2">
       <c r="A1950" s="2" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="B1950" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1951" spans="1:2">
       <c r="A1951" s="2" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="B1951" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1952" spans="1:2">
       <c r="A1952" s="2" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="B1952" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1953" spans="1:2">
       <c r="A1953" s="2" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="B1953" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1954" spans="1:2">
       <c r="A1954" s="2" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="B1954" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1955" spans="1:2">
       <c r="A1955" s="2" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="B1955" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1956" spans="1:2">
       <c r="A1956" s="2" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="B1956" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1957" spans="1:2">
       <c r="A1957" s="2" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="B1957" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1958" spans="1:2">
       <c r="A1958" s="2" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="B1958" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1959" spans="1:2">
       <c r="A1959" s="2" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="B1959" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1960" spans="1:2">
       <c r="A1960" s="2" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B1960" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1961" spans="1:2">
       <c r="A1961" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="B1961" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1962" spans="1:2">
       <c r="A1962" s="2" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="B1962" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1963" spans="1:2">
       <c r="A1963" s="2" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="B1963" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1964" spans="1:2">
       <c r="A1964" s="2" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="B1964" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1965" spans="1:2">
       <c r="A1965" s="2" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="B1965" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1966" spans="1:2">
       <c r="A1966" s="2" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B1966" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1967" spans="1:2">
       <c r="A1967" s="2" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="B1967" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1968" spans="1:2">
       <c r="A1968" s="2" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="B1968" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1969" spans="1:2">
       <c r="A1969" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1969" t="s">
         <v>2209</v>
-      </c>
-      <c r="B1969" t="s">
-        <v>2212</v>
       </c>
     </row>
     <row r="1970" spans="1:2">
       <c r="A1970" s="2" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="B1970" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1971" spans="1:2">
       <c r="A1971" s="2" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="B1971" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="1972" spans="1:2">
       <c r="A1972" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="B1972" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1973" spans="1:2">
       <c r="A1973" s="2" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="B1973" t="s">
         <v>1775</v>
@@ -24911,7 +24902,7 @@
     </row>
     <row r="1974" spans="1:2">
       <c r="A1974" s="2" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="B1974" t="s">
         <v>1775</v>
@@ -24919,7 +24910,7 @@
     </row>
     <row r="1975" spans="1:2">
       <c r="A1975" s="2" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="B1975" t="s">
         <v>1775</v>
@@ -24927,7 +24918,7 @@
     </row>
     <row r="1976" spans="1:2">
       <c r="A1976" s="2" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="B1976" t="s">
         <v>1775</v>
@@ -24935,7 +24926,7 @@
     </row>
     <row r="1977" spans="1:2">
       <c r="A1977" s="2" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="B1977" t="s">
         <v>1775</v>
@@ -24943,551 +24934,551 @@
     </row>
     <row r="1978" spans="1:2">
       <c r="A1978" s="2" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="B1978" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1979" spans="1:2">
       <c r="A1979" s="2" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="B1979" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1980" spans="1:2">
       <c r="A1980" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="B1980" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1981" spans="1:2">
       <c r="A1981" s="2" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="B1981" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1982" spans="1:2">
       <c r="A1982" s="2" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="B1982" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1983" spans="1:2">
       <c r="A1983" s="2" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="B1983" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1984" spans="1:2">
       <c r="A1984" s="2" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="B1984" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1985" spans="1:2">
       <c r="A1985" s="2" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="B1985" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1986" spans="1:2">
       <c r="A1986" s="2" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="B1986" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1987" spans="1:2">
       <c r="A1987" s="2" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="B1987" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1988" spans="1:2">
       <c r="A1988" s="2" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="B1988" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1989" spans="1:2">
       <c r="A1989" s="2" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="B1989" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1990" spans="1:2">
       <c r="A1990" s="2" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="B1990" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1991" spans="1:2">
       <c r="A1991" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1991" t="s">
         <v>2236</v>
-      </c>
-      <c r="B1991" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="1992" spans="1:2">
       <c r="A1992" s="2" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="B1992" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1993" spans="1:2">
       <c r="A1993" s="2" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B1993" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1994" spans="1:2">
       <c r="A1994" s="2" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B1994" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="1995" spans="1:2">
       <c r="A1995" s="2" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="B1995" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1996" spans="1:2">
       <c r="A1996" s="2" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="B1996" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1997" spans="1:2">
       <c r="A1997" s="2" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="B1997" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1998" spans="1:2">
       <c r="A1998" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="B1998" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1999" spans="1:2">
       <c r="A1999" s="2" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B1999" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="2000" spans="1:2">
       <c r="A2000" s="2" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="B2000" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="2001" spans="1:2">
       <c r="A2001" s="2" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="B2001" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2002" spans="1:2">
       <c r="A2002" s="2" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B2002" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2003" spans="1:2">
       <c r="A2003" s="2" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="B2003" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2004" spans="1:2">
       <c r="A2004" s="2" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B2004" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2005" spans="1:2">
       <c r="A2005" s="2" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="B2005" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2006" spans="1:2">
       <c r="A2006" s="2" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="B2006" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2007" spans="1:2">
       <c r="A2007" s="2" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="B2007" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2008" spans="1:2">
       <c r="A2008" s="2" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="B2008" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2009" spans="1:2">
       <c r="A2009" s="2" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="B2009" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2010" spans="1:2">
       <c r="A2010" s="2" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="B2010" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2011" spans="1:2">
       <c r="A2011" s="2" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B2011" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2012" spans="1:2">
       <c r="A2012" s="2" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="B2012" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2013" spans="1:2">
       <c r="A2013" s="2" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="B2013" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2014" spans="1:2">
       <c r="A2014" s="2" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B2014" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2015" spans="1:2">
       <c r="A2015" s="2" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="B2015" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2016" spans="1:2">
       <c r="A2016" s="2" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B2016" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2017" spans="1:2">
       <c r="A2017" s="2" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B2017" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2018" spans="1:2">
       <c r="A2018" s="2" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B2018" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2019" spans="1:2">
       <c r="A2019" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B2019" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2020" spans="1:2">
       <c r="A2020" s="2" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B2020" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2021" spans="1:2">
       <c r="A2021" s="2" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B2021" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2022" spans="1:2">
       <c r="A2022" s="2" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="B2022" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2023" spans="1:2">
       <c r="A2023" s="2" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B2023" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2024" spans="1:2">
       <c r="A2024" s="2" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="B2024" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="2025" spans="1:2">
       <c r="A2025" s="2" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="B2025" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2026" spans="1:2">
       <c r="A2026" s="2" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="B2026" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2027" spans="1:2">
       <c r="A2027" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B2027" t="s">
         <v>2276</v>
-      </c>
-      <c r="B2027" t="s">
-        <v>2279</v>
       </c>
     </row>
     <row r="2028" spans="1:2">
       <c r="A2028" s="2" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="B2028" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2029" spans="1:2">
       <c r="A2029" s="2" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="B2029" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2030" spans="1:2">
       <c r="A2030" s="2" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="B2030" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2031" spans="1:2">
       <c r="A2031" s="2" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="B2031" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2032" spans="1:2">
       <c r="A2032" s="2" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="B2032" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2033" spans="1:2">
       <c r="A2033" s="2" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="B2033" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2034" spans="1:2">
       <c r="A2034" s="2" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B2034" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2035" spans="1:2">
       <c r="A2035" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="B2035" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2036" spans="1:2">
       <c r="A2036" s="2" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="B2036" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2037" spans="1:2">
       <c r="A2037" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B2037" t="s">
         <v>2287</v>
-      </c>
-      <c r="B2037" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="2038" spans="1:2">
       <c r="A2038" s="2" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="B2038" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2039" spans="1:2">
       <c r="A2039" s="2" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="B2039" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="2040" spans="1:2">
       <c r="A2040" s="2" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="B2040" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2041" spans="1:2">
       <c r="A2041" s="2" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B2041" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2042" spans="1:2">
       <c r="A2042" s="2" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="B2042" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2043" spans="1:2">
       <c r="A2043" s="2" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="B2043" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2044" spans="1:2">
       <c r="A2044" s="2" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B2044" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2045" spans="1:2">
       <c r="A2045" s="2" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="B2045" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="2046" spans="1:2">
       <c r="A2046" s="2" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B2046" t="s">
         <v>1688</v>
@@ -25495,7 +25486,7 @@
     </row>
     <row r="2047" spans="1:2">
       <c r="A2047" s="2" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B2047" t="s">
         <v>1688</v>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557F49EF-4AA0-45C8-BA78-543F11B5B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FEDA3F6-F126-42F6-AA1C-445C56654785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11364" yWindow="0" windowWidth="11772" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="2300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="2301">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -7094,121 +7094,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>宇都宮線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="4">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>烏山線、宇都宮線、日光線、東北新幹線、湘南新宿ライン</t>
-    <rPh sb="0" eb="3">
-      <t>カラスヤマセン</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ニッコウセン</t>
-    </rPh>
-    <rPh sb="13" eb="18">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>水戸線、両毛線、宇都宮線、東北新幹線、湘南新宿ライン</t>
-    <rPh sb="0" eb="3">
-      <t>ミトセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="13" eb="18">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>高崎線、上越線、両毛線、吾妻線、上信電鉄、信越本線、八高線、上越新幹線、北陸新幹線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ジョウエツセン</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>アガヅマセン</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ジョウシンデンテツ</t>
-    </rPh>
-    <rPh sb="21" eb="25">
-      <t>シンエツホンセン</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>ハチコウセン</t>
-    </rPh>
-    <rPh sb="30" eb="35">
-      <t>ジョウエツシンカンセン</t>
-    </rPh>
-    <rPh sb="36" eb="41">
-      <t>ホクリクシンカンセン</t>
-    </rPh>
-    <rPh sb="51" eb="55">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>高崎線、八高線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ハチコウセン</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>高崎線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>吾妻線、上越線、両毛線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>アガヅマセン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ジョウエツセン</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="21" eb="25">
-      <t>ウエノトウキョウジョウエツセンリョウモウセンショウナンシンジュクウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>小野上</t>
   </si>
   <si>
@@ -7342,19 +7227,6 @@
     <t>前橋</t>
   </si>
   <si>
-    <t>両毛線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="3">
-      <t>リョウモウセン</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>前橋大島</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7810,41 +7682,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="5">
-      <t>ケイヒントウホクセン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="24" eb="28">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>京浜東北線、宇都宮線、高崎線、（上野東京ライン）</t>
-    <rPh sb="0" eb="5">
-      <t>ケイヒントウホクセン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>京浜東北線、武蔵野線</t>
     <rPh sb="0" eb="5">
       <t>ケイヒントウホクセン</t>
@@ -7900,16 +7737,6 @@
     <t>宮原</t>
   </si>
   <si>
-    <t>高崎線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="4" eb="8">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>埼京線</t>
   </si>
   <si>
@@ -8022,22 +7849,6 @@
     <t>土呂</t>
   </si>
   <si>
-    <t>宇都宮線、東武日光線、湘南新宿ライン、（上野東京ライン）</t>
-    <rPh sb="0" eb="4">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="5" eb="10">
-      <t>トウブニッコウセン</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="20" eb="24">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>宇都宮線、東武伊勢崎線、（上野東京ライン）</t>
     <rPh sb="0" eb="4">
       <t>ウツノミヤセン</t>
@@ -8848,40 +8659,6 @@
     <t>三郷中央</t>
   </si>
   <si>
-    <t>京浜東北線、宇都宮線、高崎線、湘南新宿ライン、埼京線、川越線、東武アーバンパークライン、埼玉新都市交通ニューシャトル、東北新幹線、上越新幹線、（上野東京ライン）</t>
-    <rPh sb="0" eb="5">
-      <t>ケイヒントウホクセン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ウツノミヤセン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>タカサキセン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>サイキョウセン</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>カワゴエセン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>トウブ</t>
-    </rPh>
-    <rPh sb="59" eb="64">
-      <t>トウホクシンカンセン</t>
-    </rPh>
-    <rPh sb="65" eb="70">
-      <t>ジョウエツシンカンセン</t>
-    </rPh>
-    <rPh sb="72" eb="76">
-      <t>ウエノトウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>上越新幹線</t>
     <rPh sb="0" eb="5">
       <t>ジョウエツシンカンセン</t>
@@ -8889,18 +8666,90 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>高崎線、湘南新宿ライン、（上野東京ライン）、秩父鉄道、上越新幹線</t>
-    <rPh sb="4" eb="8">
-      <t>ショウナンシンジュク</t>
-    </rPh>
-    <rPh sb="13" eb="17">
+    <t>高崎線、上越線、両毛線、吾妻線、上信電鉄、信越本線、八高線、上越新幹線、北陸新幹線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>高崎線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>吾妻線、上越線、両毛線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>両毛線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>高崎線、（湘南新宿ライン）、（上野東京ライン）、秩父鉄道、上越新幹線</t>
+  </si>
+  <si>
+    <t>宇都宮線、東武日光線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>烏山線、宇都宮線、日光線、東北新幹線、（湘南新宿ライン）</t>
+  </si>
+  <si>
+    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、高崎線、埼京線、川越線、東武アーバンパークライン、埼玉新都市交通ニューシャトル、東北新幹線、上越新幹線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>京浜東北線、宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
+  </si>
+  <si>
+    <t>宇都宮線、（湘南新宿ライン）、（上野東京ライン）</t>
+    <rPh sb="0" eb="4">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
       <t>ウエノトウキョウ</t>
     </rPh>
-    <rPh sb="22" eb="26">
-      <t>チチブテツドウ</t>
-    </rPh>
-    <rPh sb="27" eb="32">
-      <t>ジョウエツシンカンセン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水戸線、両毛線、宇都宮線、東北新幹線、（湘南新宿ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>ミトセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ウツノミヤセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>トウホクシンカンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高崎線、八高線、（湘南新宿ライン）、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>タカサキセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハチコウセン</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ウエノトウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吾妻線、上越線、両毛線、（湘南新宿ライン）、（上野東京ライン）</t>
+    <rPh sb="0" eb="3">
+      <t>アガヅマセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウエツセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>リョウモウセン</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ウエノトウキョウジョウエツセンリョウモウセンショウナンシンジュクウエノトウキョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8983,6 +8832,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20538,7 +20391,7 @@
         <v>1563</v>
       </c>
       <c r="B1421" t="s">
-        <v>2022</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1422" spans="1:2">
@@ -20586,7 +20439,7 @@
         <v>1569</v>
       </c>
       <c r="B1427" t="s">
-        <v>2019</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1428" spans="1:2">
@@ -20594,7 +20447,7 @@
         <v>1570</v>
       </c>
       <c r="B1428" t="s">
-        <v>2020</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1429" spans="1:2">
@@ -20602,7 +20455,7 @@
         <v>1571</v>
       </c>
       <c r="B1429" t="s">
-        <v>2021</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1430" spans="1:2">
@@ -20610,7 +20463,7 @@
         <v>1572</v>
       </c>
       <c r="B1430" t="s">
-        <v>2021</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1431" spans="1:2">
@@ -20618,7 +20471,7 @@
         <v>1573</v>
       </c>
       <c r="B1431" t="s">
-        <v>2021</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1432" spans="1:2">
@@ -20626,7 +20479,7 @@
         <v>1574</v>
       </c>
       <c r="B1432" t="s">
-        <v>2021</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1433" spans="1:2">
@@ -21042,7 +20895,7 @@
         <v>1628</v>
       </c>
       <c r="B1484" t="s">
-        <v>1870</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1485" spans="1:2">
@@ -21511,7 +21364,7 @@
         <v>1695</v>
       </c>
       <c r="B1545" t="s">
-        <v>1871</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1546" spans="1:2">
@@ -21591,7 +21444,7 @@
         <v>1708</v>
       </c>
       <c r="B1555" t="s">
-        <v>1872</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1556" spans="1:2">
@@ -21687,7 +21540,7 @@
         <v>1723</v>
       </c>
       <c r="B1567" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1568" spans="1:2">
@@ -21695,7 +21548,7 @@
         <v>1724</v>
       </c>
       <c r="B1568" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1569" spans="1:2">
@@ -21703,7 +21556,7 @@
         <v>1725</v>
       </c>
       <c r="B1569" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1570" spans="1:2">
@@ -21711,7 +21564,7 @@
         <v>1726</v>
       </c>
       <c r="B1570" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1571" spans="1:2">
@@ -21719,7 +21572,7 @@
         <v>1727</v>
       </c>
       <c r="B1571" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1572" spans="1:2">
@@ -21727,7 +21580,7 @@
         <v>1728</v>
       </c>
       <c r="B1572" t="s">
-        <v>1870</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1573" spans="1:2">
@@ -22588,7 +22441,7 @@
         <v>1855</v>
       </c>
       <c r="B1682" t="s">
-        <v>1873</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1683" spans="1:2">
@@ -22596,7 +22449,7 @@
         <v>1856</v>
       </c>
       <c r="B1683" t="s">
-        <v>1874</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="1684" spans="1:2">
@@ -22604,7 +22457,7 @@
         <v>1857</v>
       </c>
       <c r="B1684" t="s">
-        <v>1875</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1685" spans="1:2">
@@ -22612,7 +22465,7 @@
         <v>1858</v>
       </c>
       <c r="B1685" t="s">
-        <v>1876</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1686" spans="1:2">
@@ -22620,7 +22473,7 @@
         <v>1859</v>
       </c>
       <c r="B1686" t="s">
-        <v>1876</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1687" spans="1:2">
@@ -22628,7 +22481,7 @@
         <v>1860</v>
       </c>
       <c r="B1687" t="s">
-        <v>1876</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1688" spans="1:2">
@@ -22673,7 +22526,7 @@
     </row>
     <row r="1693" spans="1:2">
       <c r="A1693" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
       <c r="B1693" t="s">
         <v>1867</v>
@@ -22681,7 +22534,7 @@
     </row>
     <row r="1694" spans="1:2">
       <c r="A1694" t="s">
-        <v>1878</v>
+        <v>1871</v>
       </c>
       <c r="B1694" t="s">
         <v>1867</v>
@@ -22689,7 +22542,7 @@
     </row>
     <row r="1695" spans="1:2">
       <c r="A1695" t="s">
-        <v>1879</v>
+        <v>1872</v>
       </c>
       <c r="B1695" t="s">
         <v>1867</v>
@@ -22697,7 +22550,7 @@
     </row>
     <row r="1696" spans="1:2">
       <c r="A1696" t="s">
-        <v>1880</v>
+        <v>1873</v>
       </c>
       <c r="B1696" t="s">
         <v>1867</v>
@@ -22705,7 +22558,7 @@
     </row>
     <row r="1697" spans="1:2">
       <c r="A1697" t="s">
-        <v>1881</v>
+        <v>1874</v>
       </c>
       <c r="B1697" t="s">
         <v>1867</v>
@@ -22713,7 +22566,7 @@
     </row>
     <row r="1698" spans="1:2">
       <c r="A1698" t="s">
-        <v>1882</v>
+        <v>1875</v>
       </c>
       <c r="B1698" t="s">
         <v>1867</v>
@@ -22721,7 +22574,7 @@
     </row>
     <row r="1699" spans="1:2">
       <c r="A1699" t="s">
-        <v>1883</v>
+        <v>1876</v>
       </c>
       <c r="B1699" t="s">
         <v>1867</v>
@@ -22729,7 +22582,7 @@
     </row>
     <row r="1700" spans="1:2">
       <c r="A1700" t="s">
-        <v>1884</v>
+        <v>1877</v>
       </c>
       <c r="B1700" t="s">
         <v>1867</v>
@@ -22737,7 +22590,7 @@
     </row>
     <row r="1701" spans="1:2">
       <c r="A1701" t="s">
-        <v>1885</v>
+        <v>1878</v>
       </c>
       <c r="B1701" t="s">
         <v>1867</v>
@@ -22745,7 +22598,7 @@
     </row>
     <row r="1702" spans="1:2">
       <c r="A1702" t="s">
-        <v>1886</v>
+        <v>1879</v>
       </c>
       <c r="B1702" t="s">
         <v>1867</v>
@@ -22753,7 +22606,7 @@
     </row>
     <row r="1703" spans="1:2">
       <c r="A1703" t="s">
-        <v>1887</v>
+        <v>1880</v>
       </c>
       <c r="B1703" t="s">
         <v>1867</v>
@@ -22761,7 +22614,7 @@
     </row>
     <row r="1704" spans="1:2">
       <c r="A1704" t="s">
-        <v>1888</v>
+        <v>1881</v>
       </c>
       <c r="B1704" t="s">
         <v>1867</v>
@@ -22769,7 +22622,7 @@
     </row>
     <row r="1705" spans="1:2">
       <c r="A1705" t="s">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="B1705" t="s">
         <v>1867</v>
@@ -22777,7 +22630,7 @@
     </row>
     <row r="1706" spans="1:2">
       <c r="A1706" t="s">
-        <v>1890</v>
+        <v>1883</v>
       </c>
       <c r="B1706" t="s">
         <v>1867</v>
@@ -22785,7 +22638,7 @@
     </row>
     <row r="1707" spans="1:2">
       <c r="A1707" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
       <c r="B1707" t="s">
         <v>1867</v>
@@ -22793,23 +22646,23 @@
     </row>
     <row r="1708" spans="1:2">
       <c r="A1708" t="s">
-        <v>1892</v>
+        <v>1885</v>
       </c>
       <c r="B1708" t="s">
-        <v>1893</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1709" spans="1:2">
       <c r="A1709" t="s">
-        <v>1894</v>
+        <v>1887</v>
       </c>
       <c r="B1709" t="s">
-        <v>1895</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1710" spans="1:2">
       <c r="A1710" t="s">
-        <v>1896</v>
+        <v>1889</v>
       </c>
       <c r="B1710" t="s">
         <v>1862</v>
@@ -22817,7 +22670,7 @@
     </row>
     <row r="1711" spans="1:2">
       <c r="A1711" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="B1711" t="s">
         <v>1862</v>
@@ -22825,7 +22678,7 @@
     </row>
     <row r="1712" spans="1:2">
       <c r="A1712" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="B1712" t="s">
         <v>1862</v>
@@ -22833,7 +22686,7 @@
     </row>
     <row r="1713" spans="1:2">
       <c r="A1713" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="B1713" t="s">
         <v>1862</v>
@@ -22841,7 +22694,7 @@
     </row>
     <row r="1714" spans="1:2">
       <c r="A1714" t="s">
-        <v>1900</v>
+        <v>1893</v>
       </c>
       <c r="B1714" t="s">
         <v>1862</v>
@@ -22849,7 +22702,7 @@
     </row>
     <row r="1715" spans="1:2">
       <c r="A1715" t="s">
-        <v>1901</v>
+        <v>1894</v>
       </c>
       <c r="B1715" t="s">
         <v>1862</v>
@@ -22857,7 +22710,7 @@
     </row>
     <row r="1716" spans="1:2">
       <c r="A1716" t="s">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="B1716" t="s">
         <v>1862</v>
@@ -22865,7 +22718,7 @@
     </row>
     <row r="1717" spans="1:2">
       <c r="A1717" t="s">
-        <v>1903</v>
+        <v>1896</v>
       </c>
       <c r="B1717" t="s">
         <v>1862</v>
@@ -22873,7 +22726,7 @@
     </row>
     <row r="1718" spans="1:2">
       <c r="A1718" t="s">
-        <v>1904</v>
+        <v>1897</v>
       </c>
       <c r="B1718" t="s">
         <v>1862</v>
@@ -22881,87 +22734,87 @@
     </row>
     <row r="1719" spans="1:2">
       <c r="A1719" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1719" t="s">
         <v>1905</v>
-      </c>
-      <c r="B1719" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="1720" spans="1:2">
       <c r="A1720" t="s">
-        <v>1906</v>
+        <v>1899</v>
       </c>
       <c r="B1720" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1721" spans="1:2">
       <c r="A1721" t="s">
-        <v>1907</v>
+        <v>1900</v>
       </c>
       <c r="B1721" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1722" spans="1:2">
       <c r="A1722" t="s">
-        <v>1908</v>
+        <v>1901</v>
       </c>
       <c r="B1722" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1723" spans="1:2">
       <c r="A1723" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
       <c r="B1723" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1724" spans="1:2">
       <c r="A1724" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="B1724" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1725" spans="1:2">
       <c r="A1725" t="s">
-        <v>1911</v>
+        <v>1904</v>
       </c>
       <c r="B1725" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1726" spans="1:2">
       <c r="A1726" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B1726" t="s">
-        <v>1913</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1727" spans="1:2">
       <c r="A1727" t="s">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="B1727" t="s">
-        <v>1913</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1728" spans="1:2">
       <c r="A1728" t="s">
-        <v>1916</v>
+        <v>1909</v>
       </c>
       <c r="B1728" t="s">
-        <v>1917</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1729" spans="1:2">
       <c r="A1729" t="s">
-        <v>1918</v>
+        <v>1910</v>
       </c>
       <c r="B1729" t="s">
         <v>1748</v>
@@ -22969,7 +22822,7 @@
     </row>
     <row r="1730" spans="1:2">
       <c r="A1730" t="s">
-        <v>1919</v>
+        <v>1911</v>
       </c>
       <c r="B1730" t="s">
         <v>1748</v>
@@ -22977,15 +22830,15 @@
     </row>
     <row r="1731" spans="1:2">
       <c r="A1731" t="s">
-        <v>1920</v>
+        <v>1912</v>
       </c>
       <c r="B1731" t="s">
-        <v>1924</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1732" spans="1:2">
       <c r="A1732" t="s">
-        <v>1921</v>
+        <v>1913</v>
       </c>
       <c r="B1732" t="s">
         <v>1748</v>
@@ -22993,7 +22846,7 @@
     </row>
     <row r="1733" spans="1:2">
       <c r="A1733" t="s">
-        <v>1922</v>
+        <v>1914</v>
       </c>
       <c r="B1733" t="s">
         <v>1748</v>
@@ -23001,455 +22854,455 @@
     </row>
     <row r="1734" spans="1:2">
       <c r="A1734" t="s">
-        <v>1923</v>
+        <v>1915</v>
       </c>
       <c r="B1734" t="s">
-        <v>1925</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1735" spans="1:2">
       <c r="A1735" t="s">
-        <v>1927</v>
+        <v>1919</v>
       </c>
       <c r="B1735" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1736" spans="1:2">
       <c r="A1736" t="s">
-        <v>1928</v>
+        <v>1920</v>
       </c>
       <c r="B1736" t="s">
-        <v>1939</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1737" spans="1:2">
       <c r="A1737" t="s">
-        <v>1929</v>
+        <v>1921</v>
       </c>
       <c r="B1737" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1738" spans="1:2">
       <c r="A1738" t="s">
-        <v>1930</v>
+        <v>1922</v>
       </c>
       <c r="B1738" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1739" spans="1:2">
       <c r="A1739" t="s">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="B1739" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1740" spans="1:2">
       <c r="A1740" t="s">
-        <v>1932</v>
+        <v>1924</v>
       </c>
       <c r="B1740" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1741" spans="1:2">
       <c r="A1741" t="s">
-        <v>1933</v>
+        <v>1925</v>
       </c>
       <c r="B1741" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1742" spans="1:2">
       <c r="A1742" t="s">
-        <v>1934</v>
+        <v>1926</v>
       </c>
       <c r="B1742" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1743" spans="1:2">
       <c r="A1743" t="s">
-        <v>1935</v>
+        <v>1927</v>
       </c>
       <c r="B1743" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1744" spans="1:2">
       <c r="A1744" t="s">
-        <v>1936</v>
+        <v>1928</v>
       </c>
       <c r="B1744" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1745" spans="1:2">
       <c r="A1745" t="s">
-        <v>1937</v>
+        <v>1929</v>
       </c>
       <c r="B1745" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1746" spans="1:2">
       <c r="A1746" t="s">
-        <v>1938</v>
+        <v>1930</v>
       </c>
       <c r="B1746" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1747" spans="1:2">
       <c r="A1747" t="s">
-        <v>1941</v>
+        <v>1933</v>
       </c>
       <c r="B1747" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1748" spans="1:2">
       <c r="A1748" t="s">
-        <v>1942</v>
+        <v>1934</v>
       </c>
       <c r="B1748" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1749" spans="1:2">
       <c r="A1749" t="s">
-        <v>1943</v>
+        <v>1935</v>
       </c>
       <c r="B1749" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1750" spans="1:2">
       <c r="A1750" t="s">
-        <v>1944</v>
+        <v>1936</v>
       </c>
       <c r="B1750" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1751" spans="1:2">
       <c r="A1751" t="s">
-        <v>1945</v>
+        <v>1937</v>
       </c>
       <c r="B1751" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1752" spans="1:2">
       <c r="A1752" t="s">
-        <v>1946</v>
+        <v>1938</v>
       </c>
       <c r="B1752" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1753" spans="1:2">
       <c r="A1753" t="s">
-        <v>1947</v>
+        <v>1939</v>
       </c>
       <c r="B1753" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1754" spans="1:2">
       <c r="A1754" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
       <c r="B1754" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1755" spans="1:2">
       <c r="A1755" t="s">
-        <v>1949</v>
+        <v>1941</v>
       </c>
       <c r="B1755" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1756" spans="1:2">
       <c r="A1756" t="s">
-        <v>1950</v>
+        <v>1942</v>
       </c>
       <c r="B1756" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1757" spans="1:2">
       <c r="A1757" t="s">
-        <v>1951</v>
+        <v>1943</v>
       </c>
       <c r="B1757" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1758" spans="1:2">
       <c r="A1758" t="s">
-        <v>1952</v>
+        <v>1944</v>
       </c>
       <c r="B1758" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1759" spans="1:2">
       <c r="A1759" t="s">
-        <v>1953</v>
+        <v>1945</v>
       </c>
       <c r="B1759" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1760" spans="1:2">
       <c r="A1760" t="s">
-        <v>1954</v>
+        <v>1946</v>
       </c>
       <c r="B1760" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1761" spans="1:2">
       <c r="A1761" t="s">
-        <v>1955</v>
+        <v>1947</v>
       </c>
       <c r="B1761" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1762" spans="1:2">
       <c r="A1762" t="s">
-        <v>1956</v>
+        <v>1948</v>
       </c>
       <c r="B1762" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1763" spans="1:2">
       <c r="A1763" t="s">
-        <v>1957</v>
+        <v>1949</v>
       </c>
       <c r="B1763" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1764" spans="1:2">
       <c r="A1764" t="s">
-        <v>1958</v>
+        <v>1950</v>
       </c>
       <c r="B1764" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1765" spans="1:2">
       <c r="A1765" t="s">
-        <v>1959</v>
+        <v>1951</v>
       </c>
       <c r="B1765" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1766" spans="1:2">
       <c r="A1766" t="s">
-        <v>1960</v>
+        <v>1952</v>
       </c>
       <c r="B1766" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1767" spans="1:2">
       <c r="A1767" t="s">
-        <v>1962</v>
+        <v>1954</v>
       </c>
       <c r="B1767" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1768" spans="1:2">
       <c r="A1768" t="s">
-        <v>1963</v>
+        <v>1955</v>
       </c>
       <c r="B1768" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1769" spans="1:2">
       <c r="A1769" t="s">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="B1769" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1770" spans="1:2">
       <c r="A1770" t="s">
-        <v>1965</v>
+        <v>1957</v>
       </c>
       <c r="B1770" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1771" spans="1:2">
       <c r="A1771" t="s">
-        <v>1966</v>
+        <v>1958</v>
       </c>
       <c r="B1771" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1772" spans="1:2">
       <c r="A1772" t="s">
-        <v>1967</v>
+        <v>1959</v>
       </c>
       <c r="B1772" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1773" spans="1:2">
       <c r="A1773" t="s">
-        <v>1968</v>
+        <v>1960</v>
       </c>
       <c r="B1773" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1774" spans="1:2">
       <c r="A1774" t="s">
-        <v>1969</v>
+        <v>1961</v>
       </c>
       <c r="B1774" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1775" spans="1:2">
       <c r="A1775" t="s">
-        <v>1970</v>
+        <v>1962</v>
       </c>
       <c r="B1775" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1776" spans="1:2">
       <c r="A1776" t="s">
-        <v>1971</v>
+        <v>1963</v>
       </c>
       <c r="B1776" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1777" spans="1:2">
       <c r="A1777" t="s">
-        <v>1972</v>
+        <v>1964</v>
       </c>
       <c r="B1777" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1778" spans="1:2">
       <c r="A1778" t="s">
-        <v>1973</v>
+        <v>1965</v>
       </c>
       <c r="B1778" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1779" spans="1:2">
       <c r="A1779" t="s">
-        <v>1974</v>
+        <v>1966</v>
       </c>
       <c r="B1779" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1780" spans="1:2">
       <c r="A1780" t="s">
-        <v>1975</v>
+        <v>1967</v>
       </c>
       <c r="B1780" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1781" spans="1:2">
       <c r="A1781" t="s">
-        <v>1976</v>
+        <v>1968</v>
       </c>
       <c r="B1781" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1782" spans="1:2">
       <c r="A1782" t="s">
-        <v>1977</v>
+        <v>1969</v>
       </c>
       <c r="B1782" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1783" spans="1:2">
       <c r="A1783" t="s">
-        <v>1978</v>
+        <v>1970</v>
       </c>
       <c r="B1783" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1784" spans="1:2">
       <c r="A1784" t="s">
-        <v>1979</v>
+        <v>1971</v>
       </c>
       <c r="B1784" t="s">
-        <v>1985</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1785" spans="1:2">
       <c r="A1785" t="s">
-        <v>1980</v>
+        <v>1972</v>
       </c>
       <c r="B1785" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1786" spans="1:2">
       <c r="A1786" t="s">
-        <v>1981</v>
+        <v>1973</v>
       </c>
       <c r="B1786" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1787" spans="1:2">
       <c r="A1787" t="s">
-        <v>1982</v>
+        <v>1974</v>
       </c>
       <c r="B1787" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1788" spans="1:2">
       <c r="A1788" t="s">
-        <v>1983</v>
+        <v>1975</v>
       </c>
       <c r="B1788" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1789" spans="1:2">
       <c r="A1789" t="s">
-        <v>1984</v>
+        <v>1976</v>
       </c>
       <c r="B1789" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1790" spans="1:2">
       <c r="A1790" t="s">
-        <v>1986</v>
+        <v>1978</v>
       </c>
       <c r="B1790" t="s">
         <v>1775</v>
@@ -23457,7 +23310,7 @@
     </row>
     <row r="1791" spans="1:2">
       <c r="A1791" t="s">
-        <v>1987</v>
+        <v>1979</v>
       </c>
       <c r="B1791" t="s">
         <v>1775</v>
@@ -23465,7 +23318,7 @@
     </row>
     <row r="1792" spans="1:2">
       <c r="A1792" t="s">
-        <v>1988</v>
+        <v>1980</v>
       </c>
       <c r="B1792" t="s">
         <v>1775</v>
@@ -23473,7 +23326,7 @@
     </row>
     <row r="1793" spans="1:2">
       <c r="A1793" t="s">
-        <v>1989</v>
+        <v>1981</v>
       </c>
       <c r="B1793" t="s">
         <v>1775</v>
@@ -23481,7 +23334,7 @@
     </row>
     <row r="1794" spans="1:2">
       <c r="A1794" t="s">
-        <v>1990</v>
+        <v>1982</v>
       </c>
       <c r="B1794" t="s">
         <v>1775</v>
@@ -23489,7 +23342,7 @@
     </row>
     <row r="1795" spans="1:2">
       <c r="A1795" t="s">
-        <v>1991</v>
+        <v>1983</v>
       </c>
       <c r="B1795" t="s">
         <v>1775</v>
@@ -23497,95 +23350,95 @@
     </row>
     <row r="1796" spans="1:2">
       <c r="A1796" t="s">
-        <v>1992</v>
+        <v>1984</v>
       </c>
       <c r="B1796" t="s">
-        <v>1994</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1797" spans="1:2">
       <c r="A1797" t="s">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B1797" t="s">
-        <v>2001</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1798" spans="1:2">
       <c r="A1798" t="s">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B1798" t="s">
-        <v>2007</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1799" spans="1:2">
       <c r="A1799" t="s">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B1799" t="s">
-        <v>2001</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1800" spans="1:2">
       <c r="A1800" t="s">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B1800" t="s">
-        <v>2001</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1801" spans="1:2">
       <c r="A1801" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1801" t="s">
         <v>1993</v>
-      </c>
-      <c r="B1801" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="1802" spans="1:2">
       <c r="A1802" t="s">
-        <v>1995</v>
+        <v>1987</v>
       </c>
       <c r="B1802" t="s">
-        <v>2002</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1803" spans="1:2">
       <c r="A1803" t="s">
-        <v>1996</v>
+        <v>1988</v>
       </c>
       <c r="B1803" t="s">
-        <v>2000</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1804" spans="1:2">
       <c r="A1804" t="s">
-        <v>1997</v>
+        <v>1989</v>
       </c>
       <c r="B1804" t="s">
-        <v>2000</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1805" spans="1:2">
       <c r="A1805" t="s">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B1805" t="s">
-        <v>2000</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1806" spans="1:2">
       <c r="A1806" t="s">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B1806" t="s">
-        <v>2000</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1807" spans="1:2">
       <c r="A1807" t="s">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B1807" t="s">
         <v>1802</v>
@@ -23593,63 +23446,63 @@
     </row>
     <row r="1808" spans="1:2">
       <c r="A1808" t="s">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B1808" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1809" spans="1:2">
       <c r="A1809" t="s">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B1809" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1810" spans="1:2">
       <c r="A1810" t="s">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B1810" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1811" spans="1:2">
       <c r="A1811" t="s">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B1811" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1812" spans="1:2">
       <c r="A1812" t="s">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B1812" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1813" spans="1:2">
       <c r="A1813" t="s">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B1813" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1814" spans="1:2">
       <c r="A1814" t="s">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B1814" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1815" spans="1:2">
       <c r="A1815" t="s">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B1815" t="s">
         <v>1810</v>
@@ -23657,364 +23510,364 @@
     </row>
     <row r="1818" spans="1:2">
       <c r="A1818" t="s">
-        <v>2018</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1819" spans="1:2">
       <c r="A1819" s="2" t="s">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B1819" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
       <c r="A1820" s="2" t="s">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="B1820" t="s">
-        <v>2034</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
       <c r="A1821" s="2" t="s">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B1821" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1822" spans="1:2">
       <c r="A1822" s="2" t="s">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="B1822" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1823" spans="1:2">
       <c r="A1823" s="2" t="s">
-        <v>2027</v>
+        <v>2019</v>
       </c>
       <c r="B1823" t="s">
-        <v>2033</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="1824" spans="1:2">
       <c r="A1824" s="2" t="s">
-        <v>2028</v>
+        <v>2020</v>
       </c>
       <c r="B1824" t="s">
-        <v>2035</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1825" spans="1:2">
       <c r="A1825" s="2" t="s">
-        <v>2029</v>
+        <v>2021</v>
       </c>
       <c r="B1825" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1826" spans="1:2">
       <c r="A1826" s="2" t="s">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="B1826" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1827" spans="1:2">
       <c r="A1827" s="2" t="s">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="B1827" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1828" spans="1:2">
       <c r="A1828" s="2" t="s">
-        <v>2036</v>
+        <v>2026</v>
       </c>
       <c r="B1828" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1829" spans="1:2">
       <c r="A1829" s="2" t="s">
-        <v>2037</v>
+        <v>2027</v>
       </c>
       <c r="B1829" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1830" spans="1:2">
       <c r="A1830" s="2" t="s">
-        <v>2038</v>
+        <v>2028</v>
       </c>
       <c r="B1830" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
       <c r="A1831" s="2" t="s">
-        <v>2039</v>
+        <v>2029</v>
       </c>
       <c r="B1831" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1832" spans="1:2">
       <c r="A1832" s="2" t="s">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B1832" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1833" spans="1:2">
       <c r="A1833" s="2" t="s">
-        <v>2041</v>
+        <v>2031</v>
       </c>
       <c r="B1833" t="s">
-        <v>2299</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1834" spans="1:2">
       <c r="A1834" s="2" t="s">
-        <v>2042</v>
+        <v>2032</v>
       </c>
       <c r="B1834" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="2" t="s">
-        <v>2043</v>
+        <v>2033</v>
       </c>
       <c r="B1835" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="2" t="s">
-        <v>2044</v>
+        <v>2034</v>
       </c>
       <c r="B1836" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="2" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="B1837" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" s="2" t="s">
-        <v>2046</v>
+        <v>2036</v>
       </c>
       <c r="B1838" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" s="2" t="s">
-        <v>2047</v>
+        <v>2037</v>
       </c>
       <c r="B1839" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" s="2" t="s">
-        <v>2048</v>
+        <v>2038</v>
       </c>
       <c r="B1840" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" s="2" t="s">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="B1841" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1842" spans="1:2">
       <c r="A1842" s="2" t="s">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B1842" t="s">
-        <v>2051</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1843" spans="1:2">
       <c r="A1843" s="2" t="s">
-        <v>2053</v>
+        <v>2042</v>
       </c>
       <c r="B1843" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1844" spans="1:2">
       <c r="A1844" s="2" t="s">
-        <v>2054</v>
+        <v>2043</v>
       </c>
       <c r="B1844" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1845" spans="1:2">
       <c r="A1845" s="2" t="s">
-        <v>2055</v>
+        <v>2044</v>
       </c>
       <c r="B1845" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1846" spans="1:2">
       <c r="A1846" s="2" t="s">
-        <v>2056</v>
+        <v>2045</v>
       </c>
       <c r="B1846" t="s">
-        <v>2061</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1847" spans="1:2">
       <c r="A1847" s="2" t="s">
-        <v>2057</v>
+        <v>2046</v>
       </c>
       <c r="B1847" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1848" spans="1:2">
       <c r="A1848" s="2" t="s">
-        <v>2058</v>
+        <v>2047</v>
       </c>
       <c r="B1848" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1849" spans="1:2">
       <c r="A1849" s="2" t="s">
-        <v>2059</v>
+        <v>2048</v>
       </c>
       <c r="B1849" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1850" spans="1:2">
       <c r="A1850" s="2" t="s">
-        <v>2060</v>
+        <v>2049</v>
       </c>
       <c r="B1850" t="s">
-        <v>2052</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1851" spans="1:2">
       <c r="A1851" s="2" t="s">
-        <v>2062</v>
+        <v>2051</v>
       </c>
       <c r="B1851" t="s">
-        <v>2298</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1852" spans="1:2">
       <c r="A1852" s="2" t="s">
-        <v>2064</v>
+        <v>2053</v>
       </c>
       <c r="B1852" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1853" spans="1:2">
       <c r="A1853" s="2" t="s">
-        <v>2065</v>
+        <v>2054</v>
       </c>
       <c r="B1853" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1854" spans="1:2">
       <c r="A1854" s="2" t="s">
-        <v>2066</v>
+        <v>2055</v>
       </c>
       <c r="B1854" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1855" spans="1:2">
       <c r="A1855" s="2" t="s">
-        <v>2067</v>
+        <v>2056</v>
       </c>
       <c r="B1855" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1856" spans="1:2">
       <c r="A1856" s="2" t="s">
-        <v>2068</v>
+        <v>2057</v>
       </c>
       <c r="B1856" t="s">
-        <v>2074</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1857" spans="1:2">
       <c r="A1857" s="2" t="s">
-        <v>2069</v>
+        <v>2058</v>
       </c>
       <c r="B1857" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1858" spans="1:2">
       <c r="A1858" s="2" t="s">
-        <v>2070</v>
+        <v>2059</v>
       </c>
       <c r="B1858" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1859" spans="1:2">
       <c r="A1859" s="2" t="s">
-        <v>2071</v>
+        <v>2060</v>
       </c>
       <c r="B1859" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1860" spans="1:2">
       <c r="A1860" s="2" t="s">
-        <v>2072</v>
+        <v>2061</v>
       </c>
       <c r="B1860" t="s">
-        <v>2063</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1861" spans="1:2">
       <c r="A1861" s="2" t="s">
-        <v>2073</v>
+        <v>2062</v>
       </c>
       <c r="B1861" t="s">
-        <v>2075</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1862" spans="1:2">
       <c r="A1862" s="2" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="B1862" t="s">
-        <v>2084</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1863" spans="1:2">
       <c r="A1863" s="2" t="s">
-        <v>2077</v>
+        <v>2066</v>
       </c>
       <c r="B1863" t="s">
         <v>1730</v>
@@ -24022,15 +23875,15 @@
     </row>
     <row r="1864" spans="1:2">
       <c r="A1864" s="2" t="s">
-        <v>2078</v>
+        <v>2067</v>
       </c>
       <c r="B1864" t="s">
-        <v>2085</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1865" spans="1:2">
       <c r="A1865" s="2" t="s">
-        <v>2079</v>
+        <v>2068</v>
       </c>
       <c r="B1865" t="s">
         <v>1730</v>
@@ -24038,7 +23891,7 @@
     </row>
     <row r="1866" spans="1:2">
       <c r="A1866" s="2" t="s">
-        <v>2080</v>
+        <v>2069</v>
       </c>
       <c r="B1866" t="s">
         <v>1730</v>
@@ -24046,7 +23899,7 @@
     </row>
     <row r="1867" spans="1:2">
       <c r="A1867" s="2" t="s">
-        <v>2081</v>
+        <v>2070</v>
       </c>
       <c r="B1867" t="s">
         <v>1730</v>
@@ -24054,7 +23907,7 @@
     </row>
     <row r="1868" spans="1:2">
       <c r="A1868" s="2" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="B1868" t="s">
         <v>1730</v>
@@ -24062,7 +23915,7 @@
     </row>
     <row r="1869" spans="1:2">
       <c r="A1869" s="2" t="s">
-        <v>2083</v>
+        <v>2072</v>
       </c>
       <c r="B1869" t="s">
         <v>1730</v>
@@ -24070,831 +23923,831 @@
     </row>
     <row r="1870" spans="1:2">
       <c r="A1870" s="2" t="s">
-        <v>2087</v>
+        <v>2075</v>
       </c>
       <c r="B1870" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1871" spans="1:2">
       <c r="A1871" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1871" t="s">
         <v>2088</v>
-      </c>
-      <c r="B1871" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="1872" spans="1:2">
       <c r="A1872" s="2" t="s">
-        <v>2089</v>
+        <v>2077</v>
       </c>
       <c r="B1872" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1873" spans="1:2">
       <c r="A1873" s="2" t="s">
-        <v>2090</v>
+        <v>2078</v>
       </c>
       <c r="B1873" t="s">
-        <v>2101</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1874" spans="1:2">
       <c r="A1874" s="2" t="s">
-        <v>2091</v>
+        <v>2079</v>
       </c>
       <c r="B1874" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1875" spans="1:2">
       <c r="A1875" s="2" t="s">
-        <v>2092</v>
+        <v>2080</v>
       </c>
       <c r="B1875" t="s">
-        <v>2102</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1876" spans="1:2">
       <c r="A1876" s="2" t="s">
-        <v>2093</v>
+        <v>2081</v>
       </c>
       <c r="B1876" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1877" spans="1:2">
       <c r="A1877" s="2" t="s">
-        <v>2094</v>
+        <v>2082</v>
       </c>
       <c r="B1877" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1878" spans="1:2">
       <c r="A1878" s="2" t="s">
-        <v>2095</v>
+        <v>2083</v>
       </c>
       <c r="B1878" t="s">
-        <v>2103</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1879" spans="1:2">
       <c r="A1879" s="2" t="s">
-        <v>2096</v>
+        <v>2084</v>
       </c>
       <c r="B1879" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1880" spans="1:2">
       <c r="A1880" s="2" t="s">
-        <v>2097</v>
+        <v>2085</v>
       </c>
       <c r="B1880" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1881" spans="1:2">
       <c r="A1881" s="2" t="s">
-        <v>2098</v>
+        <v>2086</v>
       </c>
       <c r="B1881" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1882" spans="1:2">
       <c r="A1882" s="2" t="s">
-        <v>2099</v>
+        <v>2087</v>
       </c>
       <c r="B1882" t="s">
-        <v>2086</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1883" spans="1:2">
       <c r="A1883" s="2" t="s">
-        <v>2105</v>
+        <v>2093</v>
       </c>
       <c r="B1883" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1884" spans="1:2">
       <c r="A1884" t="s">
-        <v>2106</v>
+        <v>2094</v>
       </c>
       <c r="B1884" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1885" spans="1:2">
       <c r="A1885" s="2" t="s">
-        <v>2107</v>
+        <v>2095</v>
       </c>
       <c r="B1885" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1886" spans="1:2">
       <c r="A1886" s="2" t="s">
-        <v>2108</v>
+        <v>2096</v>
       </c>
       <c r="B1886" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1887" spans="1:2">
       <c r="A1887" s="2" t="s">
-        <v>2109</v>
+        <v>2097</v>
       </c>
       <c r="B1887" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1888" spans="1:2">
       <c r="A1888" s="2" t="s">
-        <v>2110</v>
+        <v>2098</v>
       </c>
       <c r="B1888" t="s">
-        <v>2117</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1889" spans="1:2">
       <c r="A1889" s="2" t="s">
-        <v>2111</v>
+        <v>2099</v>
       </c>
       <c r="B1889" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1890" spans="1:2">
       <c r="A1890" s="2" t="s">
-        <v>2112</v>
+        <v>2100</v>
       </c>
       <c r="B1890" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1891" spans="1:2">
       <c r="A1891" s="2" t="s">
-        <v>2113</v>
+        <v>2101</v>
       </c>
       <c r="B1891" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1892" spans="1:2">
       <c r="A1892" s="2" t="s">
-        <v>2114</v>
+        <v>2102</v>
       </c>
       <c r="B1892" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1893" spans="1:2">
       <c r="A1893" s="2" t="s">
-        <v>2115</v>
+        <v>2103</v>
       </c>
       <c r="B1893" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1894" spans="1:2">
       <c r="A1894" s="2" t="s">
-        <v>2116</v>
+        <v>2104</v>
       </c>
       <c r="B1894" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1895" spans="1:2">
       <c r="A1895" s="2" t="s">
-        <v>2119</v>
+        <v>2107</v>
       </c>
       <c r="B1895" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1896" spans="1:2">
       <c r="A1896" s="2" t="s">
-        <v>2120</v>
+        <v>2108</v>
       </c>
       <c r="B1896" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1897" spans="1:2">
       <c r="A1897" s="2" t="s">
-        <v>2121</v>
+        <v>2109</v>
       </c>
       <c r="B1897" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1898" spans="1:2">
       <c r="A1898" s="2" t="s">
-        <v>2122</v>
+        <v>2110</v>
       </c>
       <c r="B1898" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1899" spans="1:2">
       <c r="A1899" s="2" t="s">
-        <v>2123</v>
+        <v>2111</v>
       </c>
       <c r="B1899" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1900" spans="1:2">
       <c r="A1900" s="2" t="s">
-        <v>2124</v>
+        <v>2112</v>
       </c>
       <c r="B1900" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1901" spans="1:2">
       <c r="A1901" s="2" t="s">
-        <v>2125</v>
+        <v>2113</v>
       </c>
       <c r="B1901" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1902" spans="1:2">
       <c r="A1902" s="2" t="s">
-        <v>2126</v>
+        <v>2114</v>
       </c>
       <c r="B1902" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1903" spans="1:2">
       <c r="A1903" s="2" t="s">
-        <v>2127</v>
+        <v>2115</v>
       </c>
       <c r="B1903" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1904" spans="1:2">
       <c r="A1904" s="2" t="s">
-        <v>2128</v>
+        <v>2116</v>
       </c>
       <c r="B1904" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1905" spans="1:2">
       <c r="A1905" s="2" t="s">
-        <v>2129</v>
+        <v>2117</v>
       </c>
       <c r="B1905" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1906" spans="1:2">
       <c r="A1906" s="2" t="s">
-        <v>2130</v>
+        <v>2118</v>
       </c>
       <c r="B1906" t="s">
-        <v>2118</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1907" spans="1:2">
       <c r="A1907" s="2" t="s">
-        <v>2132</v>
+        <v>2120</v>
       </c>
       <c r="B1907" t="s">
-        <v>2135</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1908" spans="1:2">
       <c r="A1908" s="2" t="s">
-        <v>2133</v>
+        <v>2121</v>
       </c>
       <c r="B1908" t="s">
-        <v>2131</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1909" spans="1:2">
       <c r="A1909" s="2" t="s">
-        <v>2134</v>
+        <v>2122</v>
       </c>
       <c r="B1909" t="s">
-        <v>2136</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1910" spans="1:2">
       <c r="A1910" s="2" t="s">
-        <v>2138</v>
+        <v>2126</v>
       </c>
       <c r="B1910" t="s">
-        <v>2140</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1911" spans="1:2">
       <c r="A1911" s="2" t="s">
-        <v>2139</v>
+        <v>2127</v>
       </c>
       <c r="B1911" t="s">
-        <v>2137</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1912" spans="1:2">
       <c r="A1912" s="2" t="s">
-        <v>2142</v>
+        <v>2130</v>
       </c>
       <c r="B1912" t="s">
-        <v>2150</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1913" spans="1:2">
       <c r="A1913" s="2" t="s">
-        <v>2143</v>
+        <v>2131</v>
       </c>
       <c r="B1913" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1914" spans="1:2">
       <c r="A1914" s="2" t="s">
-        <v>2144</v>
+        <v>2132</v>
       </c>
       <c r="B1914" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1915" spans="1:2">
       <c r="A1915" s="2" t="s">
-        <v>2145</v>
+        <v>2133</v>
       </c>
       <c r="B1915" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1916" spans="1:2">
       <c r="A1916" s="2" t="s">
-        <v>2146</v>
+        <v>2134</v>
       </c>
       <c r="B1916" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1917" spans="1:2">
       <c r="A1917" s="2" t="s">
-        <v>2147</v>
+        <v>2135</v>
       </c>
       <c r="B1917" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1918" spans="1:2">
       <c r="A1918" s="2" t="s">
-        <v>2148</v>
+        <v>2136</v>
       </c>
       <c r="B1918" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1919" spans="1:2">
       <c r="A1919" s="2" t="s">
-        <v>2149</v>
+        <v>2137</v>
       </c>
       <c r="B1919" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1920" spans="1:2">
       <c r="A1920" s="2" t="s">
-        <v>2151</v>
+        <v>2139</v>
       </c>
       <c r="B1920" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1921" spans="1:2">
       <c r="A1921" s="2" t="s">
-        <v>2152</v>
+        <v>2140</v>
       </c>
       <c r="B1921" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1922" spans="1:2">
       <c r="A1922" s="2" t="s">
-        <v>2153</v>
+        <v>2141</v>
       </c>
       <c r="B1922" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1923" spans="1:2">
       <c r="A1923" s="2" t="s">
-        <v>2154</v>
+        <v>2142</v>
       </c>
       <c r="B1923" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1924" spans="1:2">
       <c r="A1924" s="2" t="s">
-        <v>2155</v>
+        <v>2143</v>
       </c>
       <c r="B1924" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1925" spans="1:2">
       <c r="A1925" s="2" t="s">
-        <v>2156</v>
+        <v>2144</v>
       </c>
       <c r="B1925" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1926" spans="1:2">
       <c r="A1926" s="2" t="s">
-        <v>2157</v>
+        <v>2145</v>
       </c>
       <c r="B1926" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1927" spans="1:2">
       <c r="A1927" s="2" t="s">
-        <v>2158</v>
+        <v>2146</v>
       </c>
       <c r="B1927" t="s">
-        <v>2160</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1928" spans="1:2">
       <c r="A1928" s="2" t="s">
-        <v>2162</v>
+        <v>2150</v>
       </c>
       <c r="B1928" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1929" spans="1:2">
       <c r="A1929" s="2" t="s">
-        <v>2163</v>
+        <v>2151</v>
       </c>
       <c r="B1929" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1930" spans="1:2">
       <c r="A1930" s="2" t="s">
-        <v>2164</v>
+        <v>2152</v>
       </c>
       <c r="B1930" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1931" spans="1:2">
       <c r="A1931" s="2" t="s">
-        <v>2165</v>
+        <v>2153</v>
       </c>
       <c r="B1931" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1932" spans="1:2">
       <c r="A1932" s="2" t="s">
-        <v>2166</v>
+        <v>2154</v>
       </c>
       <c r="B1932" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1933" spans="1:2">
       <c r="A1933" s="2" t="s">
-        <v>2167</v>
+        <v>2155</v>
       </c>
       <c r="B1933" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1934" spans="1:2">
       <c r="A1934" t="s">
-        <v>2168</v>
+        <v>2156</v>
       </c>
       <c r="B1934" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1935" spans="1:2">
       <c r="A1935" s="2" t="s">
-        <v>2169</v>
+        <v>2157</v>
       </c>
       <c r="B1935" t="s">
-        <v>2161</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1936" spans="1:2">
       <c r="A1936" s="2" t="s">
-        <v>2170</v>
+        <v>2158</v>
       </c>
       <c r="B1936" t="s">
-        <v>2171</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1937" spans="1:2">
       <c r="A1937" s="2" t="s">
-        <v>2173</v>
+        <v>2161</v>
       </c>
       <c r="B1937" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1938" spans="1:2">
       <c r="A1938" s="2" t="s">
-        <v>2174</v>
+        <v>2162</v>
       </c>
       <c r="B1938" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1939" spans="1:2">
       <c r="A1939" s="2" t="s">
-        <v>2175</v>
+        <v>2163</v>
       </c>
       <c r="B1939" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1940" spans="1:2">
       <c r="A1940" t="s">
-        <v>2176</v>
+        <v>2164</v>
       </c>
       <c r="B1940" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1941" spans="1:2">
       <c r="A1941" s="2" t="s">
-        <v>2177</v>
+        <v>2165</v>
       </c>
       <c r="B1941" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1942" spans="1:2">
       <c r="A1942" t="s">
-        <v>2178</v>
+        <v>2166</v>
       </c>
       <c r="B1942" t="s">
-        <v>2172</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1943" spans="1:2">
       <c r="A1943" s="2" t="s">
-        <v>2179</v>
+        <v>2167</v>
       </c>
       <c r="B1943" t="s">
-        <v>2180</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1944" spans="1:2">
       <c r="A1944" s="2" t="s">
-        <v>2181</v>
+        <v>2169</v>
       </c>
       <c r="B1944" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1945" spans="1:2">
       <c r="A1945" s="2" t="s">
-        <v>2182</v>
+        <v>2170</v>
       </c>
       <c r="B1945" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1946" spans="1:2">
       <c r="A1946" s="2" t="s">
-        <v>2183</v>
+        <v>2171</v>
       </c>
       <c r="B1946" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1947" spans="1:2">
       <c r="A1947" s="2" t="s">
-        <v>2184</v>
+        <v>2172</v>
       </c>
       <c r="B1947" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1948" spans="1:2">
       <c r="A1948" s="2" t="s">
-        <v>2185</v>
+        <v>2173</v>
       </c>
       <c r="B1948" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1949" spans="1:2">
       <c r="A1949" s="2" t="s">
-        <v>2186</v>
+        <v>2174</v>
       </c>
       <c r="B1949" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1950" spans="1:2">
       <c r="A1950" s="2" t="s">
-        <v>2187</v>
+        <v>2175</v>
       </c>
       <c r="B1950" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1951" spans="1:2">
       <c r="A1951" s="2" t="s">
-        <v>2188</v>
+        <v>2176</v>
       </c>
       <c r="B1951" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1952" spans="1:2">
       <c r="A1952" s="2" t="s">
-        <v>2189</v>
+        <v>2177</v>
       </c>
       <c r="B1952" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1953" spans="1:2">
       <c r="A1953" s="2" t="s">
-        <v>2190</v>
+        <v>2178</v>
       </c>
       <c r="B1953" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1954" spans="1:2">
       <c r="A1954" s="2" t="s">
-        <v>2191</v>
+        <v>2179</v>
       </c>
       <c r="B1954" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1955" spans="1:2">
       <c r="A1955" s="2" t="s">
-        <v>2192</v>
+        <v>2180</v>
       </c>
       <c r="B1955" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1956" spans="1:2">
       <c r="A1956" s="2" t="s">
-        <v>2193</v>
+        <v>2181</v>
       </c>
       <c r="B1956" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1957" spans="1:2">
       <c r="A1957" s="2" t="s">
-        <v>2194</v>
+        <v>2182</v>
       </c>
       <c r="B1957" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1958" spans="1:2">
       <c r="A1958" s="2" t="s">
-        <v>2195</v>
+        <v>2183</v>
       </c>
       <c r="B1958" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1959" spans="1:2">
       <c r="A1959" s="2" t="s">
-        <v>2196</v>
+        <v>2184</v>
       </c>
       <c r="B1959" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1960" spans="1:2">
       <c r="A1960" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1960" t="s">
         <v>2197</v>
-      </c>
-      <c r="B1960" t="s">
-        <v>2209</v>
       </c>
     </row>
     <row r="1961" spans="1:2">
       <c r="A1961" t="s">
-        <v>2198</v>
+        <v>2186</v>
       </c>
       <c r="B1961" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1962" spans="1:2">
       <c r="A1962" s="2" t="s">
-        <v>2199</v>
+        <v>2187</v>
       </c>
       <c r="B1962" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1963" spans="1:2">
       <c r="A1963" s="2" t="s">
-        <v>2200</v>
+        <v>2188</v>
       </c>
       <c r="B1963" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1964" spans="1:2">
       <c r="A1964" s="2" t="s">
-        <v>2201</v>
+        <v>2189</v>
       </c>
       <c r="B1964" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1965" spans="1:2">
       <c r="A1965" s="2" t="s">
-        <v>2202</v>
+        <v>2190</v>
       </c>
       <c r="B1965" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1966" spans="1:2">
       <c r="A1966" s="2" t="s">
-        <v>2203</v>
+        <v>2191</v>
       </c>
       <c r="B1966" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1967" spans="1:2">
       <c r="A1967" s="2" t="s">
-        <v>2204</v>
+        <v>2192</v>
       </c>
       <c r="B1967" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1968" spans="1:2">
       <c r="A1968" s="2" t="s">
-        <v>2205</v>
+        <v>2193</v>
       </c>
       <c r="B1968" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1969" spans="1:2">
       <c r="A1969" s="2" t="s">
-        <v>2206</v>
+        <v>2194</v>
       </c>
       <c r="B1969" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1970" spans="1:2">
       <c r="A1970" s="2" t="s">
-        <v>2207</v>
+        <v>2195</v>
       </c>
       <c r="B1970" t="s">
-        <v>2209</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1971" spans="1:2">
       <c r="A1971" s="2" t="s">
-        <v>2208</v>
+        <v>2196</v>
       </c>
       <c r="B1971" t="s">
-        <v>2210</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1972" spans="1:2">
       <c r="A1972" t="s">
-        <v>2212</v>
+        <v>2200</v>
       </c>
       <c r="B1972" t="s">
-        <v>2211</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1973" spans="1:2">
       <c r="A1973" s="2" t="s">
-        <v>2213</v>
+        <v>2201</v>
       </c>
       <c r="B1973" t="s">
         <v>1775</v>
@@ -24902,7 +24755,7 @@
     </row>
     <row r="1974" spans="1:2">
       <c r="A1974" s="2" t="s">
-        <v>2214</v>
+        <v>2202</v>
       </c>
       <c r="B1974" t="s">
         <v>1775</v>
@@ -24910,7 +24763,7 @@
     </row>
     <row r="1975" spans="1:2">
       <c r="A1975" s="2" t="s">
-        <v>2215</v>
+        <v>2203</v>
       </c>
       <c r="B1975" t="s">
         <v>1775</v>
@@ -24918,7 +24771,7 @@
     </row>
     <row r="1976" spans="1:2">
       <c r="A1976" s="2" t="s">
-        <v>2216</v>
+        <v>2204</v>
       </c>
       <c r="B1976" t="s">
         <v>1775</v>
@@ -24926,7 +24779,7 @@
     </row>
     <row r="1977" spans="1:2">
       <c r="A1977" s="2" t="s">
-        <v>2217</v>
+        <v>2205</v>
       </c>
       <c r="B1977" t="s">
         <v>1775</v>
@@ -24934,551 +24787,551 @@
     </row>
     <row r="1978" spans="1:2">
       <c r="A1978" s="2" t="s">
-        <v>2218</v>
+        <v>2206</v>
       </c>
       <c r="B1978" t="s">
-        <v>2219</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1979" spans="1:2">
       <c r="A1979" s="2" t="s">
-        <v>2221</v>
+        <v>2209</v>
       </c>
       <c r="B1979" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1980" spans="1:2">
       <c r="A1980" t="s">
-        <v>2222</v>
+        <v>2210</v>
       </c>
       <c r="B1980" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1981" spans="1:2">
       <c r="A1981" s="2" t="s">
-        <v>2223</v>
+        <v>2211</v>
       </c>
       <c r="B1981" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1982" spans="1:2">
       <c r="A1982" s="2" t="s">
-        <v>2224</v>
+        <v>2212</v>
       </c>
       <c r="B1982" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1983" spans="1:2">
       <c r="A1983" s="2" t="s">
-        <v>2225</v>
+        <v>2213</v>
       </c>
       <c r="B1983" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1984" spans="1:2">
       <c r="A1984" s="2" t="s">
-        <v>2226</v>
+        <v>2214</v>
       </c>
       <c r="B1984" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1985" spans="1:2">
       <c r="A1985" s="2" t="s">
-        <v>2227</v>
+        <v>2215</v>
       </c>
       <c r="B1985" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1986" spans="1:2">
       <c r="A1986" s="2" t="s">
-        <v>2228</v>
+        <v>2216</v>
       </c>
       <c r="B1986" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1987" spans="1:2">
       <c r="A1987" s="2" t="s">
-        <v>2229</v>
+        <v>2217</v>
       </c>
       <c r="B1987" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1988" spans="1:2">
       <c r="A1988" s="2" t="s">
-        <v>2230</v>
+        <v>2218</v>
       </c>
       <c r="B1988" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1989" spans="1:2">
       <c r="A1989" s="2" t="s">
-        <v>2231</v>
+        <v>2219</v>
       </c>
       <c r="B1989" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1990" spans="1:2">
       <c r="A1990" s="2" t="s">
-        <v>2232</v>
+        <v>2220</v>
       </c>
       <c r="B1990" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1991" spans="1:2">
       <c r="A1991" s="2" t="s">
-        <v>2233</v>
+        <v>2221</v>
       </c>
       <c r="B1991" t="s">
-        <v>2236</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1992" spans="1:2">
       <c r="A1992" s="2" t="s">
-        <v>2234</v>
+        <v>2222</v>
       </c>
       <c r="B1992" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1993" spans="1:2">
       <c r="A1993" s="2" t="s">
-        <v>2235</v>
+        <v>2223</v>
       </c>
       <c r="B1993" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1994" spans="1:2">
       <c r="A1994" s="2" t="s">
-        <v>2238</v>
+        <v>2226</v>
       </c>
       <c r="B1994" t="s">
-        <v>2245</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1995" spans="1:2">
       <c r="A1995" s="2" t="s">
-        <v>2239</v>
+        <v>2227</v>
       </c>
       <c r="B1995" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1996" spans="1:2">
       <c r="A1996" s="2" t="s">
-        <v>2240</v>
+        <v>2228</v>
       </c>
       <c r="B1996" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1997" spans="1:2">
       <c r="A1997" s="2" t="s">
-        <v>2241</v>
+        <v>2229</v>
       </c>
       <c r="B1997" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1998" spans="1:2">
       <c r="A1998" t="s">
-        <v>2242</v>
+        <v>2230</v>
       </c>
       <c r="B1998" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1999" spans="1:2">
       <c r="A1999" s="2" t="s">
-        <v>2243</v>
+        <v>2231</v>
       </c>
       <c r="B1999" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="2000" spans="1:2">
       <c r="A2000" s="2" t="s">
-        <v>2244</v>
+        <v>2232</v>
       </c>
       <c r="B2000" t="s">
-        <v>2237</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="2001" spans="1:2">
       <c r="A2001" s="2" t="s">
-        <v>2247</v>
+        <v>2235</v>
       </c>
       <c r="B2001" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2002" spans="1:2">
       <c r="A2002" s="2" t="s">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="B2002" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2003" spans="1:2">
       <c r="A2003" s="2" t="s">
-        <v>2249</v>
+        <v>2237</v>
       </c>
       <c r="B2003" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2004" spans="1:2">
       <c r="A2004" s="2" t="s">
-        <v>2250</v>
+        <v>2238</v>
       </c>
       <c r="B2004" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2005" spans="1:2">
       <c r="A2005" s="2" t="s">
-        <v>2251</v>
+        <v>2239</v>
       </c>
       <c r="B2005" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2006" spans="1:2">
       <c r="A2006" s="2" t="s">
-        <v>2252</v>
+        <v>2240</v>
       </c>
       <c r="B2006" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2007" spans="1:2">
       <c r="A2007" s="2" t="s">
-        <v>2253</v>
+        <v>2241</v>
       </c>
       <c r="B2007" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2008" spans="1:2">
       <c r="A2008" s="2" t="s">
-        <v>2254</v>
+        <v>2242</v>
       </c>
       <c r="B2008" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2009" spans="1:2">
       <c r="A2009" s="2" t="s">
-        <v>2255</v>
+        <v>2243</v>
       </c>
       <c r="B2009" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2010" spans="1:2">
       <c r="A2010" s="2" t="s">
-        <v>2256</v>
+        <v>2244</v>
       </c>
       <c r="B2010" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2011" spans="1:2">
       <c r="A2011" s="2" t="s">
-        <v>2257</v>
+        <v>2245</v>
       </c>
       <c r="B2011" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2012" spans="1:2">
       <c r="A2012" s="2" t="s">
-        <v>2258</v>
+        <v>2246</v>
       </c>
       <c r="B2012" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2013" spans="1:2">
       <c r="A2013" s="2" t="s">
-        <v>2259</v>
+        <v>2247</v>
       </c>
       <c r="B2013" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2014" spans="1:2">
       <c r="A2014" s="2" t="s">
-        <v>2260</v>
+        <v>2248</v>
       </c>
       <c r="B2014" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2015" spans="1:2">
       <c r="A2015" s="2" t="s">
-        <v>2261</v>
+        <v>2249</v>
       </c>
       <c r="B2015" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2016" spans="1:2">
       <c r="A2016" s="2" t="s">
-        <v>2262</v>
+        <v>2250</v>
       </c>
       <c r="B2016" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2017" spans="1:2">
       <c r="A2017" s="2" t="s">
-        <v>2263</v>
+        <v>2251</v>
       </c>
       <c r="B2017" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2018" spans="1:2">
       <c r="A2018" s="2" t="s">
-        <v>2264</v>
+        <v>2252</v>
       </c>
       <c r="B2018" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2019" spans="1:2">
       <c r="A2019" t="s">
-        <v>2265</v>
+        <v>2253</v>
       </c>
       <c r="B2019" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2020" spans="1:2">
       <c r="A2020" s="2" t="s">
-        <v>2266</v>
+        <v>2254</v>
       </c>
       <c r="B2020" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2021" spans="1:2">
       <c r="A2021" s="2" t="s">
-        <v>2267</v>
+        <v>2255</v>
       </c>
       <c r="B2021" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2022" spans="1:2">
       <c r="A2022" s="2" t="s">
-        <v>2268</v>
+        <v>2256</v>
       </c>
       <c r="B2022" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2023" spans="1:2">
       <c r="A2023" s="2" t="s">
-        <v>2269</v>
+        <v>2257</v>
       </c>
       <c r="B2023" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2024" spans="1:2">
       <c r="A2024" s="2" t="s">
-        <v>2270</v>
+        <v>2258</v>
       </c>
       <c r="B2024" t="s">
-        <v>2246</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2025" spans="1:2">
       <c r="A2025" s="2" t="s">
-        <v>2271</v>
+        <v>2259</v>
       </c>
       <c r="B2025" t="s">
-        <v>2276</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2026" spans="1:2">
       <c r="A2026" s="2" t="s">
-        <v>2272</v>
+        <v>2260</v>
       </c>
       <c r="B2026" t="s">
-        <v>2276</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2027" spans="1:2">
       <c r="A2027" s="2" t="s">
-        <v>2273</v>
+        <v>2261</v>
       </c>
       <c r="B2027" t="s">
-        <v>2276</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2028" spans="1:2">
       <c r="A2028" s="2" t="s">
-        <v>2274</v>
+        <v>2262</v>
       </c>
       <c r="B2028" t="s">
-        <v>2276</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2029" spans="1:2">
       <c r="A2029" s="2" t="s">
-        <v>2275</v>
+        <v>2263</v>
       </c>
       <c r="B2029" t="s">
-        <v>2276</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2030" spans="1:2">
       <c r="A2030" s="2" t="s">
-        <v>2277</v>
+        <v>2265</v>
       </c>
       <c r="B2030" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2031" spans="1:2">
       <c r="A2031" s="2" t="s">
-        <v>2278</v>
+        <v>2266</v>
       </c>
       <c r="B2031" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2032" spans="1:2">
       <c r="A2032" s="2" t="s">
-        <v>2279</v>
+        <v>2267</v>
       </c>
       <c r="B2032" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2033" spans="1:2">
       <c r="A2033" s="2" t="s">
-        <v>2280</v>
+        <v>2268</v>
       </c>
       <c r="B2033" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2034" spans="1:2">
       <c r="A2034" s="2" t="s">
-        <v>2281</v>
+        <v>2269</v>
       </c>
       <c r="B2034" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2035" spans="1:2">
       <c r="A2035" t="s">
-        <v>2282</v>
+        <v>2270</v>
       </c>
       <c r="B2035" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2036" spans="1:2">
       <c r="A2036" s="2" t="s">
-        <v>2283</v>
+        <v>2271</v>
       </c>
       <c r="B2036" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2037" spans="1:2">
       <c r="A2037" s="2" t="s">
-        <v>2284</v>
+        <v>2272</v>
       </c>
       <c r="B2037" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2038" spans="1:2">
       <c r="A2038" s="2" t="s">
-        <v>2285</v>
+        <v>2273</v>
       </c>
       <c r="B2038" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2039" spans="1:2">
       <c r="A2039" s="2" t="s">
-        <v>2286</v>
+        <v>2274</v>
       </c>
       <c r="B2039" t="s">
-        <v>2287</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="2040" spans="1:2">
       <c r="A2040" s="2" t="s">
-        <v>2289</v>
+        <v>2277</v>
       </c>
       <c r="B2040" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2041" spans="1:2">
       <c r="A2041" s="2" t="s">
-        <v>2290</v>
+        <v>2278</v>
       </c>
       <c r="B2041" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2042" spans="1:2">
       <c r="A2042" s="2" t="s">
-        <v>2291</v>
+        <v>2279</v>
       </c>
       <c r="B2042" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2043" spans="1:2">
       <c r="A2043" s="2" t="s">
-        <v>2292</v>
+        <v>2280</v>
       </c>
       <c r="B2043" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2044" spans="1:2">
       <c r="A2044" s="2" t="s">
-        <v>2293</v>
+        <v>2281</v>
       </c>
       <c r="B2044" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2045" spans="1:2">
       <c r="A2045" s="2" t="s">
-        <v>2294</v>
+        <v>2282</v>
       </c>
       <c r="B2045" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="2046" spans="1:2">
       <c r="A2046" s="2" t="s">
-        <v>2295</v>
+        <v>2283</v>
       </c>
       <c r="B2046" t="s">
         <v>1688</v>
@@ -25486,7 +25339,7 @@
     </row>
     <row r="2047" spans="1:2">
       <c r="A2047" s="2" t="s">
-        <v>2296</v>
+        <v>2284</v>
       </c>
       <c r="B2047" t="s">
         <v>1688</v>

--- a/utils/駅名標.xlsx
+++ b/utils/駅名標.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keisu\my-discord-bot\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FEDA3F6-F126-42F6-AA1C-445C56654785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D973EB-B013-486E-BBC1-68873D6B38C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D59C1B8B-96E7-492C-A94A-67C6C45EEFA4}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="2301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4712" uniqueCount="2702">
   <si>
     <t>室蘭本線</t>
     <rPh sb="0" eb="4">
@@ -8076,17 +8075,7 @@
     <t>西武山口線</t>
   </si>
   <si>
-    <t>多摩湖</t>
-  </si>
-  <si>
     <t>西武園ゆうえんち</t>
-  </si>
-  <si>
-    <t>西武山口線、西武多摩湖線</t>
-    <rPh sb="6" eb="12">
-      <t>セイブタマコセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>西武新宿線</t>
@@ -8751,6 +8740,1677 @@
     <rPh sb="23" eb="27">
       <t>ウエノトウキョウジョウエツセンリョウモウセンショウナンシンジュクウエノトウキョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉県</t>
+    <rPh sb="0" eb="3">
+      <t>チバケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉</t>
+  </si>
+  <si>
+    <t>本千葉</t>
+  </si>
+  <si>
+    <t>蘇我</t>
+  </si>
+  <si>
+    <t>鎌取</t>
+  </si>
+  <si>
+    <t>誉田</t>
+  </si>
+  <si>
+    <t>土気</t>
+  </si>
+  <si>
+    <t>大網</t>
+  </si>
+  <si>
+    <t>永田（千葉）</t>
+  </si>
+  <si>
+    <t>本納</t>
+  </si>
+  <si>
+    <t>新茂原</t>
+  </si>
+  <si>
+    <t>茂原</t>
+  </si>
+  <si>
+    <t>八積</t>
+  </si>
+  <si>
+    <t>上総一ノ宮</t>
+  </si>
+  <si>
+    <t>東浪見</t>
+  </si>
+  <si>
+    <t>太東</t>
+  </si>
+  <si>
+    <t>長者町</t>
+  </si>
+  <si>
+    <t>三門</t>
+  </si>
+  <si>
+    <t>大原（千葉）</t>
+  </si>
+  <si>
+    <t>浪花</t>
+  </si>
+  <si>
+    <t>御宿</t>
+  </si>
+  <si>
+    <t>勝浦</t>
+  </si>
+  <si>
+    <t>鵜原</t>
+  </si>
+  <si>
+    <t>上総興津</t>
+  </si>
+  <si>
+    <t>行川アイランド</t>
+  </si>
+  <si>
+    <t>安房小湊</t>
+  </si>
+  <si>
+    <t>安房天津</t>
+  </si>
+  <si>
+    <t>安房鴨川</t>
+  </si>
+  <si>
+    <t>外房線</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、京葉線、内房線</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ケイヨウセン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、東金線</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>トウガネセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、いすみ鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、内房線</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、（内房線）</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木更津</t>
+  </si>
+  <si>
+    <t>祇園（千葉）</t>
+  </si>
+  <si>
+    <t>上総清川</t>
+  </si>
+  <si>
+    <t>東清川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>横田</t>
+  </si>
+  <si>
+    <t>東横田</t>
+  </si>
+  <si>
+    <t>馬来田</t>
+  </si>
+  <si>
+    <t>下郡</t>
+  </si>
+  <si>
+    <t>小櫃</t>
+  </si>
+  <si>
+    <t>俵田</t>
+  </si>
+  <si>
+    <t>久留里</t>
+  </si>
+  <si>
+    <t>平山</t>
+  </si>
+  <si>
+    <t>上総松丘</t>
+  </si>
+  <si>
+    <t>上総亀山</t>
+  </si>
+  <si>
+    <t>久留里線、内房線</t>
+    <rPh sb="0" eb="4">
+      <t>クルリセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>久留里線</t>
+    <rPh sb="0" eb="4">
+      <t>クルリセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>舞浜</t>
+  </si>
+  <si>
+    <t>新浦安</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市川塩浜</t>
+  </si>
+  <si>
+    <t>二俣新町</t>
+  </si>
+  <si>
+    <t>南船橋</t>
+  </si>
+  <si>
+    <t>新習志野</t>
+  </si>
+  <si>
+    <t>幕張豊砂</t>
+  </si>
+  <si>
+    <t>海浜幕張</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検見川浜</t>
+  </si>
+  <si>
+    <t>稲毛海岸</t>
+  </si>
+  <si>
+    <t>千葉みなと</t>
+  </si>
+  <si>
+    <t>京葉線</t>
+    <rPh sb="0" eb="3">
+      <t>ケイヨウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京葉線、武蔵野線</t>
+    <rPh sb="0" eb="3">
+      <t>ケイヨウセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ムサシノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京葉線、千葉都市モノレール</t>
+    <rPh sb="0" eb="3">
+      <t>ケイヨウセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>チバトシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香取</t>
+  </si>
+  <si>
+    <t>十二橋</t>
+  </si>
+  <si>
+    <t>鹿島線、成田線</t>
+    <rPh sb="4" eb="7">
+      <t>ナリタセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鹿島線</t>
+    <rPh sb="0" eb="3">
+      <t>カシマセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松戸</t>
+  </si>
+  <si>
+    <t>柏</t>
+  </si>
+  <si>
+    <t>我孫子</t>
+  </si>
+  <si>
+    <t>天王台</t>
+  </si>
+  <si>
+    <t>常磐線、常磐線各停、京成松戸線</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケイセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マツド</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、常磐線各停、東武アーバンパークライン</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>ジョウバンセンカクテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東我孫子</t>
+  </si>
+  <si>
+    <t>湖北</t>
+  </si>
+  <si>
+    <t>新木（千葉）</t>
+  </si>
+  <si>
+    <t>布佐</t>
+  </si>
+  <si>
+    <t>木下</t>
+  </si>
+  <si>
+    <t>小林（千葉）</t>
+  </si>
+  <si>
+    <t>安食</t>
+  </si>
+  <si>
+    <t>下総松崎</t>
+  </si>
+  <si>
+    <t>成田</t>
+  </si>
+  <si>
+    <t>成田線（我孫子支線）</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>アビコシセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐倉</t>
+  </si>
+  <si>
+    <t>酒々井</t>
+  </si>
+  <si>
+    <t>久住</t>
+  </si>
+  <si>
+    <t>滑河</t>
+  </si>
+  <si>
+    <t>下総神崎</t>
+  </si>
+  <si>
+    <t>大戸</t>
+  </si>
+  <si>
+    <t>水郷</t>
+  </si>
+  <si>
+    <t>小見川</t>
+  </si>
+  <si>
+    <t>笹川</t>
+  </si>
+  <si>
+    <t>下総橘</t>
+  </si>
+  <si>
+    <t>下総豊里</t>
+  </si>
+  <si>
+    <t>椎柴</t>
+  </si>
+  <si>
+    <t>松岸</t>
+  </si>
+  <si>
+    <t>銚子</t>
+  </si>
+  <si>
+    <t>成田線、成田線（空港支線）</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>クウコウシセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田線、成田線（我孫子支線）、成田線（空港支線）</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="8" eb="13">
+      <t>アビコシセン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>クウコウシセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田線</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田線、総武本線</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田線、総武本線、銚子電気鉄道</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <rPh sb="9" eb="15">
+      <t>チョウシデンキテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田空港（成田第１ターミナル）</t>
+  </si>
+  <si>
+    <t>成田線（空港支線）、京成本線、京成成田スカイアクセス線</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>クウコウシセン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ケイセイホンセン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ケイセイナリタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東千葉</t>
+  </si>
+  <si>
+    <t>都賀</t>
+  </si>
+  <si>
+    <t>四街道</t>
+  </si>
+  <si>
+    <t>物井</t>
+  </si>
+  <si>
+    <t>成田線、成田線（空港支線）、総武本線</t>
+    <rPh sb="0" eb="3">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>クウコウシセン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南酒々井</t>
+  </si>
+  <si>
+    <t>榎戸（千葉）</t>
+  </si>
+  <si>
+    <t>八街</t>
+  </si>
+  <si>
+    <t>日向</t>
+  </si>
+  <si>
+    <t>成東</t>
+  </si>
+  <si>
+    <t>松尾（千葉）</t>
+  </si>
+  <si>
+    <t>横芝</t>
+  </si>
+  <si>
+    <t>飯倉</t>
+  </si>
+  <si>
+    <t>八日市場</t>
+  </si>
+  <si>
+    <t>干潟</t>
+  </si>
+  <si>
+    <t>旭（千葉）</t>
+  </si>
+  <si>
+    <t>飯岡</t>
+  </si>
+  <si>
+    <t>倉橋</t>
+  </si>
+  <si>
+    <t>猿田</t>
+  </si>
+  <si>
+    <t>総武本線</t>
+    <rPh sb="0" eb="4">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総武本線、千葉都市モノレール</t>
+    <rPh sb="0" eb="4">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>チバトシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総武本線、東金線</t>
+    <rPh sb="0" eb="4">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>トウガネセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>求名</t>
+  </si>
+  <si>
+    <t>東金</t>
+  </si>
+  <si>
+    <t>福俵</t>
+  </si>
+  <si>
+    <t>東金線</t>
+    <rPh sb="0" eb="3">
+      <t>トウガネセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浜野</t>
+  </si>
+  <si>
+    <t>八幡宿</t>
+  </si>
+  <si>
+    <t>五井</t>
+  </si>
+  <si>
+    <t>姉ヶ崎</t>
+  </si>
+  <si>
+    <t>長浦（千葉）</t>
+  </si>
+  <si>
+    <t>袖ヶ浦</t>
+  </si>
+  <si>
+    <t>巌根</t>
+  </si>
+  <si>
+    <t>君津</t>
+  </si>
+  <si>
+    <t>青堀</t>
+  </si>
+  <si>
+    <t>大貫</t>
+  </si>
+  <si>
+    <t>佐貫町</t>
+  </si>
+  <si>
+    <t>上総湊</t>
+  </si>
+  <si>
+    <t>竹岡</t>
+  </si>
+  <si>
+    <t>浜金谷</t>
+  </si>
+  <si>
+    <t>保田（千葉）</t>
+  </si>
+  <si>
+    <t>安房勝山</t>
+  </si>
+  <si>
+    <t>岩井</t>
+  </si>
+  <si>
+    <t>富浦（千葉）</t>
+  </si>
+  <si>
+    <t>那古船形</t>
+  </si>
+  <si>
+    <t>館山</t>
+  </si>
+  <si>
+    <t>九重</t>
+  </si>
+  <si>
+    <t>千倉</t>
+  </si>
+  <si>
+    <t>千歳（千葉）</t>
+  </si>
+  <si>
+    <t>南三原</t>
+  </si>
+  <si>
+    <t>和田浦</t>
+  </si>
+  <si>
+    <t>江見</t>
+  </si>
+  <si>
+    <t>太海</t>
+  </si>
+  <si>
+    <t>内房線</t>
+    <rPh sb="0" eb="3">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南流山</t>
+  </si>
+  <si>
+    <t>新松戸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新八柱</t>
+  </si>
+  <si>
+    <t>東松戸</t>
+  </si>
+  <si>
+    <t>市川大野</t>
+  </si>
+  <si>
+    <t>船橋法典</t>
+  </si>
+  <si>
+    <t>西船橋</t>
+  </si>
+  <si>
+    <t>上総中野</t>
+  </si>
+  <si>
+    <t>西畑</t>
+  </si>
+  <si>
+    <t>総元</t>
+  </si>
+  <si>
+    <t>久我原（千葉）</t>
+  </si>
+  <si>
+    <t>東総元</t>
+  </si>
+  <si>
+    <t>小谷松</t>
+  </si>
+  <si>
+    <t>大多喜</t>
+  </si>
+  <si>
+    <t>城見ヶ丘</t>
+  </si>
+  <si>
+    <t>上総中川</t>
+  </si>
+  <si>
+    <t>国吉</t>
+  </si>
+  <si>
+    <t>新田野</t>
+  </si>
+  <si>
+    <t>上総東</t>
+  </si>
+  <si>
+    <t>西大原</t>
+  </si>
+  <si>
+    <t>いすみ鉄道</t>
+    <rPh sb="3" eb="5">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いすみ鉄道、小湊鐵道</t>
+    <rPh sb="3" eb="5">
+      <t>テツドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コミナト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成千原線</t>
+  </si>
+  <si>
+    <t>千葉中央</t>
+  </si>
+  <si>
+    <t>千葉寺</t>
+  </si>
+  <si>
+    <t>大森台</t>
+  </si>
+  <si>
+    <t>学園前（千葉）</t>
+  </si>
+  <si>
+    <t>おゆみ野</t>
+  </si>
+  <si>
+    <t>ちはら台</t>
+  </si>
+  <si>
+    <t>京成津田沼</t>
+  </si>
+  <si>
+    <t>京成幕張本郷</t>
+  </si>
+  <si>
+    <t>京成幕張</t>
+  </si>
+  <si>
+    <t>検見川</t>
+  </si>
+  <si>
+    <t>京成稲毛</t>
+  </si>
+  <si>
+    <t>みどり台</t>
+  </si>
+  <si>
+    <t>西登戸</t>
+  </si>
+  <si>
+    <t>新千葉</t>
+  </si>
+  <si>
+    <t>京成千葉</t>
+  </si>
+  <si>
+    <t>京成成田</t>
+  </si>
+  <si>
+    <t>東成田</t>
+  </si>
+  <si>
+    <t>京成千原線、京成千葉線</t>
+    <rPh sb="6" eb="11">
+      <t>ケイセイチバセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成千葉線</t>
+    <rPh sb="0" eb="5">
+      <t>ケイセイチバセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成千葉線、京成本線、京成松戸線</t>
+    <rPh sb="0" eb="5">
+      <t>ケイセイチバセン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ケイセイホンセン</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ケイセイマツドセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成東成田線、京成本線</t>
+    <rPh sb="0" eb="6">
+      <t>ケイセイヒガシナリタセン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ケイセイホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成東成田線、芝山鉄道</t>
+    <rPh sb="0" eb="6">
+      <t>ケイセイヒガシナリタセン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シバヤマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国府台</t>
+  </si>
+  <si>
+    <t>市川真間</t>
+  </si>
+  <si>
+    <t>菅野</t>
+  </si>
+  <si>
+    <t>京成八幡</t>
+  </si>
+  <si>
+    <t>鬼越</t>
+  </si>
+  <si>
+    <t>京成中山</t>
+  </si>
+  <si>
+    <t>東中山</t>
+  </si>
+  <si>
+    <t>京成西船</t>
+  </si>
+  <si>
+    <t>海神</t>
+  </si>
+  <si>
+    <t>京成船橋</t>
+  </si>
+  <si>
+    <t>大神宮下</t>
+  </si>
+  <si>
+    <t>船橋競馬場</t>
+  </si>
+  <si>
+    <t>谷津</t>
+  </si>
+  <si>
+    <t>京成大久保</t>
+  </si>
+  <si>
+    <t>実籾</t>
+  </si>
+  <si>
+    <t>八千代台</t>
+  </si>
+  <si>
+    <t>京成大和田</t>
+  </si>
+  <si>
+    <t>勝田台</t>
+  </si>
+  <si>
+    <t>志津（千葉）</t>
+  </si>
+  <si>
+    <t>ユーカリが丘</t>
+  </si>
+  <si>
+    <t>京成臼井</t>
+  </si>
+  <si>
+    <t>京成佐倉</t>
+  </si>
+  <si>
+    <t>大佐倉</t>
+  </si>
+  <si>
+    <t>京成酒々井</t>
+  </si>
+  <si>
+    <t>宗吾参道</t>
+  </si>
+  <si>
+    <t>公津の杜</t>
+  </si>
+  <si>
+    <t>京成本線</t>
+    <rPh sb="0" eb="4">
+      <t>ケイセイホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成本線、山万ユーカリが丘線</t>
+    <rPh sb="0" eb="4">
+      <t>ケイセイホンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山万ユーカリが丘線</t>
+  </si>
+  <si>
+    <t>地区センター</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>女子大</t>
+  </si>
+  <si>
+    <t>中学校</t>
+  </si>
+  <si>
+    <t>井野（千葉）</t>
+  </si>
+  <si>
+    <t>小湊鐵道</t>
+    <rPh sb="2" eb="3">
+      <t>テツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上総村上</t>
+  </si>
+  <si>
+    <t>海士有木</t>
+  </si>
+  <si>
+    <t>上総三又</t>
+  </si>
+  <si>
+    <t>上総山田</t>
+  </si>
+  <si>
+    <t>光風台（千葉）</t>
+  </si>
+  <si>
+    <t>馬立</t>
+  </si>
+  <si>
+    <t>上総牛久</t>
+  </si>
+  <si>
+    <t>上総川間</t>
+  </si>
+  <si>
+    <t>上総鶴舞</t>
+  </si>
+  <si>
+    <t>上総久保</t>
+  </si>
+  <si>
+    <t>高滝</t>
+  </si>
+  <si>
+    <t>里見</t>
+  </si>
+  <si>
+    <t>飯給</t>
+  </si>
+  <si>
+    <t>月崎</t>
+  </si>
+  <si>
+    <t>上総大久保</t>
+  </si>
+  <si>
+    <t>養老渓谷</t>
+  </si>
+  <si>
+    <t>武蔵野線、つくばエクスプレス</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武蔵野線、常磐線各停</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ジョウバンセンカクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武蔵野線、北総線、京成成田スカイアクセス線</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ホクソウセン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>ケイセイナリタ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成松戸線</t>
+  </si>
+  <si>
+    <t>上本郷</t>
+  </si>
+  <si>
+    <t>松戸新田</t>
+  </si>
+  <si>
+    <t>みのり台</t>
+  </si>
+  <si>
+    <t>八柱</t>
+  </si>
+  <si>
+    <t>常盤平</t>
+  </si>
+  <si>
+    <t>五香</t>
+  </si>
+  <si>
+    <t>元山（千葉）</t>
+  </si>
+  <si>
+    <t>くぬぎ山</t>
+  </si>
+  <si>
+    <t>北初富</t>
+  </si>
+  <si>
+    <t>新鎌ヶ谷</t>
+  </si>
+  <si>
+    <t>初富</t>
+  </si>
+  <si>
+    <t>鎌ヶ谷大仏</t>
+  </si>
+  <si>
+    <t>二和向台</t>
+  </si>
+  <si>
+    <t>三咲</t>
+  </si>
+  <si>
+    <t>滝不動</t>
+  </si>
+  <si>
+    <t>高根公団</t>
+  </si>
+  <si>
+    <t>高根木戸</t>
+  </si>
+  <si>
+    <t>北習志野</t>
+  </si>
+  <si>
+    <t>習志野</t>
+  </si>
+  <si>
+    <t>薬園台</t>
+  </si>
+  <si>
+    <t>前原</t>
+  </si>
+  <si>
+    <t>新津田沼</t>
+  </si>
+  <si>
+    <t>京成松戸線、北総線、京成成田スカイアクセス線、東武アーバンパークライン</t>
+    <rPh sb="6" eb="9">
+      <t>ホクソウセン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ケイセイナリタ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線、常磐線各停、成田線（我孫子支線）</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジョウバンセン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ナリタセン</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>アビコシセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉都市モノレール</t>
+    <rPh sb="0" eb="4">
+      <t>チバトシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市役所前（千葉）</t>
+  </si>
+  <si>
+    <t>栄町（千葉）</t>
+  </si>
+  <si>
+    <t>葭川公園</t>
+  </si>
+  <si>
+    <t>県庁前（千葉）</t>
+  </si>
+  <si>
+    <t>千葉公園</t>
+  </si>
+  <si>
+    <t>作草部</t>
+  </si>
+  <si>
+    <t>天台</t>
+  </si>
+  <si>
+    <t>穴川（千葉）</t>
+  </si>
+  <si>
+    <t>スポーツセンター</t>
+  </si>
+  <si>
+    <t>動物公園</t>
+  </si>
+  <si>
+    <t>みつわ台</t>
+  </si>
+  <si>
+    <t>桜木（千葉）</t>
+  </si>
+  <si>
+    <t>小倉台</t>
+  </si>
+  <si>
+    <t>千城台北</t>
+  </si>
+  <si>
+    <t>千城台</t>
+  </si>
+  <si>
+    <t>馬橋</t>
+  </si>
+  <si>
+    <t>幸谷</t>
+  </si>
+  <si>
+    <t>小金城趾</t>
+  </si>
+  <si>
+    <t>鰭ヶ崎</t>
+  </si>
+  <si>
+    <t>平和台（千葉）</t>
+  </si>
+  <si>
+    <t>流山</t>
+  </si>
+  <si>
+    <t>流鉄流山線</t>
+    <rPh sb="0" eb="5">
+      <t>リュウテツナガレヤマセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>流鉄流山線、常磐線各停</t>
+    <rPh sb="0" eb="5">
+      <t>リュウテツナガレヤマセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>ジョウバンセンカクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北松戸</t>
+  </si>
+  <si>
+    <t>北小金</t>
+  </si>
+  <si>
+    <t>南柏</t>
+  </si>
+  <si>
+    <t>北柏</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常磐線各停</t>
+    <rPh sb="0" eb="5">
+      <t>ジョウバンセンカクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仲ノ町</t>
+  </si>
+  <si>
+    <t>観音</t>
+  </si>
+  <si>
+    <t>本銚子</t>
+  </si>
+  <si>
+    <t>笠上黒生</t>
+  </si>
+  <si>
+    <t>西海鹿島</t>
+  </si>
+  <si>
+    <t>海鹿島</t>
+  </si>
+  <si>
+    <t>君ヶ浜</t>
+  </si>
+  <si>
+    <t>犬吠</t>
+  </si>
+  <si>
+    <t>外川</t>
+  </si>
+  <si>
+    <t>銚子電気鉄道</t>
+    <rPh sb="0" eb="6">
+      <t>チョウシデンキテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原木中山</t>
+  </si>
+  <si>
+    <t>妙典</t>
+  </si>
+  <si>
+    <t>行徳</t>
+  </si>
+  <si>
+    <t>南行徳</t>
+  </si>
+  <si>
+    <t>浦安（千葉）</t>
+  </si>
+  <si>
+    <t>東京メトロ東西線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本八幡</t>
+  </si>
+  <si>
+    <t>川間</t>
+  </si>
+  <si>
+    <t>七光台</t>
+  </si>
+  <si>
+    <t>清水公園</t>
+  </si>
+  <si>
+    <t>愛宕（千葉）</t>
+  </si>
+  <si>
+    <t>野田市</t>
+  </si>
+  <si>
+    <t>梅郷</t>
+  </si>
+  <si>
+    <t>運河</t>
+  </si>
+  <si>
+    <t>江戸川台</t>
+  </si>
+  <si>
+    <t>初石</t>
+  </si>
+  <si>
+    <t>流山おおたかの森</t>
+  </si>
+  <si>
+    <t>豊四季</t>
+  </si>
+  <si>
+    <t>新柏</t>
+  </si>
+  <si>
+    <t>増尾</t>
+  </si>
+  <si>
+    <t>逆井</t>
+  </si>
+  <si>
+    <t>高柳</t>
+  </si>
+  <si>
+    <t>六実</t>
+  </si>
+  <si>
+    <t>鎌ヶ谷</t>
+  </si>
+  <si>
+    <t>馬込沢</t>
+  </si>
+  <si>
+    <t>塚田</t>
+  </si>
+  <si>
+    <t>新船橋</t>
+  </si>
+  <si>
+    <t>船橋</t>
+  </si>
+  <si>
+    <t>西千葉</t>
+  </si>
+  <si>
+    <t>東武アーバンパークライン、つくばエクスプレス</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外房線、中央・総武線各停、総武線快速、総武本線、千葉都市モノレール、（内房線）</t>
+    <rPh sb="0" eb="3">
+      <t>ソトボウセン</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>ソウブセンカイソク</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ソウブホンセン</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>チバトシ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ウチボウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都営新宿線、中央・総武線各停</t>
+    <rPh sb="0" eb="5">
+      <t>トエイシンジュクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東武アーバンパークライン、総武線快速、中央・総武線各停</t>
+    <rPh sb="0" eb="2">
+      <t>トウブ</t>
+    </rPh>
+    <rPh sb="13" eb="18">
+      <t>ソウブセンカイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>稲毛</t>
+  </si>
+  <si>
+    <t>新検見川</t>
+  </si>
+  <si>
+    <t>幕張</t>
+  </si>
+  <si>
+    <t>幕張本郷</t>
+  </si>
+  <si>
+    <t>津田沼</t>
+  </si>
+  <si>
+    <t>東船橋</t>
+  </si>
+  <si>
+    <t>下総中山</t>
+  </si>
+  <si>
+    <t>市川</t>
+  </si>
+  <si>
+    <t>中央・総武線各停</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ソウブセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央・総武線各停、総武線快速</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ソウブセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="9" eb="14">
+      <t>ソウブセンカイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武蔵野線、東京メトロ東西線、東葉高速線、中央・総武線各停</t>
+    <rPh sb="0" eb="4">
+      <t>ムサシノセン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>トウザイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成松戸線、東葉高速線</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東葉勝田台</t>
+  </si>
+  <si>
+    <t>村上（千葉）</t>
+  </si>
+  <si>
+    <t>八千代中央</t>
+  </si>
+  <si>
+    <t>八千代緑が丘</t>
+  </si>
+  <si>
+    <t>船橋日大前</t>
+  </si>
+  <si>
+    <t>飯山満</t>
+  </si>
+  <si>
+    <t>東海神</t>
+  </si>
+  <si>
+    <t>東葉高速線</t>
+    <rPh sb="0" eb="5">
+      <t>トウヨウコウソクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成田湯川</t>
+  </si>
+  <si>
+    <t>印旛日本医大</t>
+  </si>
+  <si>
+    <t>千葉ニュータウン中央</t>
+  </si>
+  <si>
+    <t>京成成田スカイアクセス線</t>
+    <rPh sb="0" eb="4">
+      <t>ケイセイナリタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>京成成田スカイアクセス線、北総線</t>
+    <rPh sb="0" eb="4">
+      <t>ケイセイナリタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ホクソウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>印西牧の原</t>
+  </si>
+  <si>
+    <t>小室</t>
+  </si>
+  <si>
+    <t>白井</t>
+  </si>
+  <si>
+    <t>西白井</t>
+  </si>
+  <si>
+    <t>大町（千葉）</t>
+  </si>
+  <si>
+    <t>松飛台</t>
+  </si>
+  <si>
+    <t>秋山</t>
+  </si>
+  <si>
+    <t>北国分</t>
+  </si>
+  <si>
+    <t>矢切</t>
+  </si>
+  <si>
+    <t>北総線</t>
+    <rPh sb="0" eb="3">
+      <t>ホクソウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リゾートゲートウェイ</t>
+  </si>
+  <si>
+    <t>東京ディズニーランド</t>
+  </si>
+  <si>
+    <t>ベイサイド</t>
+  </si>
+  <si>
+    <t>東京ディズニーシー</t>
+  </si>
+  <si>
+    <t>ディズニーリゾートライン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空港第２ビル（成田第２・第３ターミナル）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>芝山千代田</t>
+  </si>
+  <si>
+    <t>芝山鉄道</t>
+    <rPh sb="0" eb="4">
+      <t>シバヤマテツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>流山セントラルパーク</t>
+  </si>
+  <si>
+    <t>柏の葉キャンパス</t>
+  </si>
+  <si>
+    <t>柏たなか</t>
+  </si>
+  <si>
+    <t>つくばエクスプレス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9155,7 +10815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1437605C-2F57-4CF5-BCCA-5114B2B10271}">
-  <dimension ref="A1:B2047"/>
+  <dimension ref="A1:B2384"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="64.33203125" customWidth="1"/>
@@ -20895,7 +22555,7 @@
         <v>1628</v>
       </c>
       <c r="B1484" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="1485" spans="1:2">
@@ -21364,7 +23024,7 @@
         <v>1695</v>
       </c>
       <c r="B1545" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1546" spans="1:2">
@@ -21444,7 +23104,7 @@
         <v>1708</v>
       </c>
       <c r="B1555" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="1556" spans="1:2">
@@ -21540,7 +23200,7 @@
         <v>1723</v>
       </c>
       <c r="B1567" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1568" spans="1:2">
@@ -21548,7 +23208,7 @@
         <v>1724</v>
       </c>
       <c r="B1568" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1569" spans="1:2">
@@ -21556,7 +23216,7 @@
         <v>1725</v>
       </c>
       <c r="B1569" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1570" spans="1:2">
@@ -21564,7 +23224,7 @@
         <v>1726</v>
       </c>
       <c r="B1570" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1571" spans="1:2">
@@ -21572,7 +23232,7 @@
         <v>1727</v>
       </c>
       <c r="B1571" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1572" spans="1:2">
@@ -21580,7 +23240,7 @@
         <v>1728</v>
       </c>
       <c r="B1572" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1573" spans="1:2">
@@ -22441,7 +24101,7 @@
         <v>1855</v>
       </c>
       <c r="B1682" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1683" spans="1:2">
@@ -22449,7 +24109,7 @@
         <v>1856</v>
       </c>
       <c r="B1683" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1684" spans="1:2">
@@ -22457,7 +24117,7 @@
         <v>1857</v>
       </c>
       <c r="B1684" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1685" spans="1:2">
@@ -22465,7 +24125,7 @@
         <v>1858</v>
       </c>
       <c r="B1685" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1686" spans="1:2">
@@ -22473,7 +24133,7 @@
         <v>1859</v>
       </c>
       <c r="B1686" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1687" spans="1:2">
@@ -22481,7 +24141,7 @@
         <v>1860</v>
       </c>
       <c r="B1687" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1688" spans="1:2">
@@ -22809,7 +24469,7 @@
         <v>1909</v>
       </c>
       <c r="B1728" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1729" spans="1:2">
@@ -23514,23 +25174,23 @@
       </c>
     </row>
     <row r="1819" spans="1:2">
-      <c r="A1819" s="2" t="s">
+      <c r="A1819" t="s">
         <v>2015</v>
       </c>
       <c r="B1819" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
-      <c r="A1820" s="2" t="s">
+      <c r="A1820" t="s">
         <v>2016</v>
       </c>
       <c r="B1820" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
-      <c r="A1821" s="2" t="s">
+      <c r="A1821" t="s">
         <v>2017</v>
       </c>
       <c r="B1821" t="s">
@@ -23538,7 +25198,7 @@
       </c>
     </row>
     <row r="1822" spans="1:2">
-      <c r="A1822" s="2" t="s">
+      <c r="A1822" t="s">
         <v>2018</v>
       </c>
       <c r="B1822" t="s">
@@ -23546,15 +25206,15 @@
       </c>
     </row>
     <row r="1823" spans="1:2">
-      <c r="A1823" s="2" t="s">
+      <c r="A1823" t="s">
         <v>2019</v>
       </c>
       <c r="B1823" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1824" spans="1:2">
-      <c r="A1824" s="2" t="s">
+      <c r="A1824" t="s">
         <v>2020</v>
       </c>
       <c r="B1824" t="s">
@@ -23562,7 +25222,7 @@
       </c>
     </row>
     <row r="1825" spans="1:2">
-      <c r="A1825" s="2" t="s">
+      <c r="A1825" t="s">
         <v>2021</v>
       </c>
       <c r="B1825" t="s">
@@ -23570,7 +25230,7 @@
       </c>
     </row>
     <row r="1826" spans="1:2">
-      <c r="A1826" s="2" t="s">
+      <c r="A1826" t="s">
         <v>2022</v>
       </c>
       <c r="B1826" t="s">
@@ -23578,7 +25238,7 @@
       </c>
     </row>
     <row r="1827" spans="1:2">
-      <c r="A1827" s="2" t="s">
+      <c r="A1827" t="s">
         <v>2023</v>
       </c>
       <c r="B1827" t="s">
@@ -23586,127 +25246,127 @@
       </c>
     </row>
     <row r="1828" spans="1:2">
-      <c r="A1828" s="2" t="s">
+      <c r="A1828" t="s">
         <v>2026</v>
       </c>
       <c r="B1828" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1829" spans="1:2">
-      <c r="A1829" s="2" t="s">
+      <c r="A1829" t="s">
         <v>2027</v>
       </c>
       <c r="B1829" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1830" spans="1:2">
-      <c r="A1830" s="2" t="s">
+      <c r="A1830" t="s">
         <v>2028</v>
       </c>
       <c r="B1830" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
-      <c r="A1831" s="2" t="s">
+      <c r="A1831" t="s">
         <v>2029</v>
       </c>
       <c r="B1831" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1832" spans="1:2">
-      <c r="A1832" s="2" t="s">
+      <c r="A1832" t="s">
         <v>2030</v>
       </c>
       <c r="B1832" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1833" spans="1:2">
-      <c r="A1833" s="2" t="s">
+      <c r="A1833" t="s">
         <v>2031</v>
       </c>
       <c r="B1833" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1834" spans="1:2">
-      <c r="A1834" s="2" t="s">
+      <c r="A1834" t="s">
         <v>2032</v>
       </c>
       <c r="B1834" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1835" spans="1:2">
-      <c r="A1835" s="2" t="s">
+      <c r="A1835" t="s">
         <v>2033</v>
       </c>
       <c r="B1835" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1836" spans="1:2">
-      <c r="A1836" s="2" t="s">
+      <c r="A1836" t="s">
         <v>2034</v>
       </c>
       <c r="B1836" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
-      <c r="A1837" s="2" t="s">
+      <c r="A1837" t="s">
         <v>2035</v>
       </c>
       <c r="B1837" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1838" spans="1:2">
-      <c r="A1838" s="2" t="s">
+      <c r="A1838" t="s">
         <v>2036</v>
       </c>
       <c r="B1838" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1839" spans="1:2">
-      <c r="A1839" s="2" t="s">
+      <c r="A1839" t="s">
         <v>2037</v>
       </c>
       <c r="B1839" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1840" spans="1:2">
-      <c r="A1840" s="2" t="s">
+      <c r="A1840" t="s">
         <v>2038</v>
       </c>
       <c r="B1840" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1841" spans="1:2">
-      <c r="A1841" s="2" t="s">
+      <c r="A1841" t="s">
         <v>2039</v>
       </c>
       <c r="B1841" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1842" spans="1:2">
-      <c r="A1842" s="2" t="s">
+      <c r="A1842" t="s">
         <v>2040</v>
       </c>
       <c r="B1842" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1843" spans="1:2">
-      <c r="A1843" s="2" t="s">
+      <c r="A1843" t="s">
         <v>2042</v>
       </c>
       <c r="B1843" t="s">
@@ -23714,7 +25374,7 @@
       </c>
     </row>
     <row r="1844" spans="1:2">
-      <c r="A1844" s="2" t="s">
+      <c r="A1844" t="s">
         <v>2043</v>
       </c>
       <c r="B1844" t="s">
@@ -23722,7 +25382,7 @@
       </c>
     </row>
     <row r="1845" spans="1:2">
-      <c r="A1845" s="2" t="s">
+      <c r="A1845" t="s">
         <v>2044</v>
       </c>
       <c r="B1845" t="s">
@@ -23730,7 +25390,7 @@
       </c>
     </row>
     <row r="1846" spans="1:2">
-      <c r="A1846" s="2" t="s">
+      <c r="A1846" t="s">
         <v>2045</v>
       </c>
       <c r="B1846" t="s">
@@ -23738,7 +25398,7 @@
       </c>
     </row>
     <row r="1847" spans="1:2">
-      <c r="A1847" s="2" t="s">
+      <c r="A1847" t="s">
         <v>2046</v>
       </c>
       <c r="B1847" t="s">
@@ -23746,7 +25406,7 @@
       </c>
     </row>
     <row r="1848" spans="1:2">
-      <c r="A1848" s="2" t="s">
+      <c r="A1848" t="s">
         <v>2047</v>
       </c>
       <c r="B1848" t="s">
@@ -23754,7 +25414,7 @@
       </c>
     </row>
     <row r="1849" spans="1:2">
-      <c r="A1849" s="2" t="s">
+      <c r="A1849" t="s">
         <v>2048</v>
       </c>
       <c r="B1849" t="s">
@@ -23762,7 +25422,7 @@
       </c>
     </row>
     <row r="1850" spans="1:2">
-      <c r="A1850" s="2" t="s">
+      <c r="A1850" t="s">
         <v>2049</v>
       </c>
       <c r="B1850" t="s">
@@ -23770,15 +25430,15 @@
       </c>
     </row>
     <row r="1851" spans="1:2">
-      <c r="A1851" s="2" t="s">
+      <c r="A1851" t="s">
         <v>2051</v>
       </c>
       <c r="B1851" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="1852" spans="1:2">
-      <c r="A1852" s="2" t="s">
+      <c r="A1852" t="s">
         <v>2053</v>
       </c>
       <c r="B1852" t="s">
@@ -23786,7 +25446,7 @@
       </c>
     </row>
     <row r="1853" spans="1:2">
-      <c r="A1853" s="2" t="s">
+      <c r="A1853" t="s">
         <v>2054</v>
       </c>
       <c r="B1853" t="s">
@@ -23794,7 +25454,7 @@
       </c>
     </row>
     <row r="1854" spans="1:2">
-      <c r="A1854" s="2" t="s">
+      <c r="A1854" t="s">
         <v>2055</v>
       </c>
       <c r="B1854" t="s">
@@ -23802,7 +25462,7 @@
       </c>
     </row>
     <row r="1855" spans="1:2">
-      <c r="A1855" s="2" t="s">
+      <c r="A1855" t="s">
         <v>2056</v>
       </c>
       <c r="B1855" t="s">
@@ -23810,7 +25470,7 @@
       </c>
     </row>
     <row r="1856" spans="1:2">
-      <c r="A1856" s="2" t="s">
+      <c r="A1856" t="s">
         <v>2057</v>
       </c>
       <c r="B1856" t="s">
@@ -23818,7 +25478,7 @@
       </c>
     </row>
     <row r="1857" spans="1:2">
-      <c r="A1857" s="2" t="s">
+      <c r="A1857" t="s">
         <v>2058</v>
       </c>
       <c r="B1857" t="s">
@@ -23826,7 +25486,7 @@
       </c>
     </row>
     <row r="1858" spans="1:2">
-      <c r="A1858" s="2" t="s">
+      <c r="A1858" t="s">
         <v>2059</v>
       </c>
       <c r="B1858" t="s">
@@ -23834,7 +25494,7 @@
       </c>
     </row>
     <row r="1859" spans="1:2">
-      <c r="A1859" s="2" t="s">
+      <c r="A1859" t="s">
         <v>2060</v>
       </c>
       <c r="B1859" t="s">
@@ -23842,7 +25502,7 @@
       </c>
     </row>
     <row r="1860" spans="1:2">
-      <c r="A1860" s="2" t="s">
+      <c r="A1860" t="s">
         <v>2061</v>
       </c>
       <c r="B1860" t="s">
@@ -23850,7 +25510,7 @@
       </c>
     </row>
     <row r="1861" spans="1:2">
-      <c r="A1861" s="2" t="s">
+      <c r="A1861" t="s">
         <v>2062</v>
       </c>
       <c r="B1861" t="s">
@@ -23858,15 +25518,15 @@
       </c>
     </row>
     <row r="1862" spans="1:2">
-      <c r="A1862" s="2" t="s">
+      <c r="A1862" t="s">
         <v>2065</v>
       </c>
       <c r="B1862" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1863" spans="1:2">
-      <c r="A1863" s="2" t="s">
+      <c r="A1863" t="s">
         <v>2066</v>
       </c>
       <c r="B1863" t="s">
@@ -23874,7 +25534,7 @@
       </c>
     </row>
     <row r="1864" spans="1:2">
-      <c r="A1864" s="2" t="s">
+      <c r="A1864" t="s">
         <v>2067</v>
       </c>
       <c r="B1864" t="s">
@@ -23882,7 +25542,7 @@
       </c>
     </row>
     <row r="1865" spans="1:2">
-      <c r="A1865" s="2" t="s">
+      <c r="A1865" t="s">
         <v>2068</v>
       </c>
       <c r="B1865" t="s">
@@ -23890,7 +25550,7 @@
       </c>
     </row>
     <row r="1866" spans="1:2">
-      <c r="A1866" s="2" t="s">
+      <c r="A1866" t="s">
         <v>2069</v>
       </c>
       <c r="B1866" t="s">
@@ -23898,7 +25558,7 @@
       </c>
     </row>
     <row r="1867" spans="1:2">
-      <c r="A1867" s="2" t="s">
+      <c r="A1867" t="s">
         <v>2070</v>
       </c>
       <c r="B1867" t="s">
@@ -23906,7 +25566,7 @@
       </c>
     </row>
     <row r="1868" spans="1:2">
-      <c r="A1868" s="2" t="s">
+      <c r="A1868" t="s">
         <v>2071</v>
       </c>
       <c r="B1868" t="s">
@@ -23914,7 +25574,7 @@
       </c>
     </row>
     <row r="1869" spans="1:2">
-      <c r="A1869" s="2" t="s">
+      <c r="A1869" t="s">
         <v>2072</v>
       </c>
       <c r="B1869" t="s">
@@ -23922,7 +25582,7 @@
       </c>
     </row>
     <row r="1870" spans="1:2">
-      <c r="A1870" s="2" t="s">
+      <c r="A1870" t="s">
         <v>2075</v>
       </c>
       <c r="B1870" t="s">
@@ -23930,7 +25590,7 @@
       </c>
     </row>
     <row r="1871" spans="1:2">
-      <c r="A1871" s="2" t="s">
+      <c r="A1871" t="s">
         <v>2076</v>
       </c>
       <c r="B1871" t="s">
@@ -23938,7 +25598,7 @@
       </c>
     </row>
     <row r="1872" spans="1:2">
-      <c r="A1872" s="2" t="s">
+      <c r="A1872" t="s">
         <v>2077</v>
       </c>
       <c r="B1872" t="s">
@@ -23946,7 +25606,7 @@
       </c>
     </row>
     <row r="1873" spans="1:2">
-      <c r="A1873" s="2" t="s">
+      <c r="A1873" t="s">
         <v>2078</v>
       </c>
       <c r="B1873" t="s">
@@ -23954,7 +25614,7 @@
       </c>
     </row>
     <row r="1874" spans="1:2">
-      <c r="A1874" s="2" t="s">
+      <c r="A1874" t="s">
         <v>2079</v>
       </c>
       <c r="B1874" t="s">
@@ -23962,7 +25622,7 @@
       </c>
     </row>
     <row r="1875" spans="1:2">
-      <c r="A1875" s="2" t="s">
+      <c r="A1875" t="s">
         <v>2080</v>
       </c>
       <c r="B1875" t="s">
@@ -23970,7 +25630,7 @@
       </c>
     </row>
     <row r="1876" spans="1:2">
-      <c r="A1876" s="2" t="s">
+      <c r="A1876" t="s">
         <v>2081</v>
       </c>
       <c r="B1876" t="s">
@@ -23978,7 +25638,7 @@
       </c>
     </row>
     <row r="1877" spans="1:2">
-      <c r="A1877" s="2" t="s">
+      <c r="A1877" t="s">
         <v>2082</v>
       </c>
       <c r="B1877" t="s">
@@ -23986,7 +25646,7 @@
       </c>
     </row>
     <row r="1878" spans="1:2">
-      <c r="A1878" s="2" t="s">
+      <c r="A1878" t="s">
         <v>2083</v>
       </c>
       <c r="B1878" t="s">
@@ -23994,7 +25654,7 @@
       </c>
     </row>
     <row r="1879" spans="1:2">
-      <c r="A1879" s="2" t="s">
+      <c r="A1879" t="s">
         <v>2084</v>
       </c>
       <c r="B1879" t="s">
@@ -24002,7 +25662,7 @@
       </c>
     </row>
     <row r="1880" spans="1:2">
-      <c r="A1880" s="2" t="s">
+      <c r="A1880" t="s">
         <v>2085</v>
       </c>
       <c r="B1880" t="s">
@@ -24010,7 +25670,7 @@
       </c>
     </row>
     <row r="1881" spans="1:2">
-      <c r="A1881" s="2" t="s">
+      <c r="A1881" t="s">
         <v>2086</v>
       </c>
       <c r="B1881" t="s">
@@ -24018,7 +25678,7 @@
       </c>
     </row>
     <row r="1882" spans="1:2">
-      <c r="A1882" s="2" t="s">
+      <c r="A1882" t="s">
         <v>2087</v>
       </c>
       <c r="B1882" t="s">
@@ -24026,7 +25686,7 @@
       </c>
     </row>
     <row r="1883" spans="1:2">
-      <c r="A1883" s="2" t="s">
+      <c r="A1883" t="s">
         <v>2093</v>
       </c>
       <c r="B1883" t="s">
@@ -24042,7 +25702,7 @@
       </c>
     </row>
     <row r="1885" spans="1:2">
-      <c r="A1885" s="2" t="s">
+      <c r="A1885" t="s">
         <v>2095</v>
       </c>
       <c r="B1885" t="s">
@@ -24050,7 +25710,7 @@
       </c>
     </row>
     <row r="1886" spans="1:2">
-      <c r="A1886" s="2" t="s">
+      <c r="A1886" t="s">
         <v>2096</v>
       </c>
       <c r="B1886" t="s">
@@ -24058,7 +25718,7 @@
       </c>
     </row>
     <row r="1887" spans="1:2">
-      <c r="A1887" s="2" t="s">
+      <c r="A1887" t="s">
         <v>2097</v>
       </c>
       <c r="B1887" t="s">
@@ -24066,7 +25726,7 @@
       </c>
     </row>
     <row r="1888" spans="1:2">
-      <c r="A1888" s="2" t="s">
+      <c r="A1888" t="s">
         <v>2098</v>
       </c>
       <c r="B1888" t="s">
@@ -24074,7 +25734,7 @@
       </c>
     </row>
     <row r="1889" spans="1:2">
-      <c r="A1889" s="2" t="s">
+      <c r="A1889" t="s">
         <v>2099</v>
       </c>
       <c r="B1889" t="s">
@@ -24082,7 +25742,7 @@
       </c>
     </row>
     <row r="1890" spans="1:2">
-      <c r="A1890" s="2" t="s">
+      <c r="A1890" t="s">
         <v>2100</v>
       </c>
       <c r="B1890" t="s">
@@ -24090,7 +25750,7 @@
       </c>
     </row>
     <row r="1891" spans="1:2">
-      <c r="A1891" s="2" t="s">
+      <c r="A1891" t="s">
         <v>2101</v>
       </c>
       <c r="B1891" t="s">
@@ -24098,7 +25758,7 @@
       </c>
     </row>
     <row r="1892" spans="1:2">
-      <c r="A1892" s="2" t="s">
+      <c r="A1892" t="s">
         <v>2102</v>
       </c>
       <c r="B1892" t="s">
@@ -24106,7 +25766,7 @@
       </c>
     </row>
     <row r="1893" spans="1:2">
-      <c r="A1893" s="2" t="s">
+      <c r="A1893" t="s">
         <v>2103</v>
       </c>
       <c r="B1893" t="s">
@@ -24114,7 +25774,7 @@
       </c>
     </row>
     <row r="1894" spans="1:2">
-      <c r="A1894" s="2" t="s">
+      <c r="A1894" t="s">
         <v>2104</v>
       </c>
       <c r="B1894" t="s">
@@ -24122,7 +25782,7 @@
       </c>
     </row>
     <row r="1895" spans="1:2">
-      <c r="A1895" s="2" t="s">
+      <c r="A1895" t="s">
         <v>2107</v>
       </c>
       <c r="B1895" t="s">
@@ -24130,7 +25790,7 @@
       </c>
     </row>
     <row r="1896" spans="1:2">
-      <c r="A1896" s="2" t="s">
+      <c r="A1896" t="s">
         <v>2108</v>
       </c>
       <c r="B1896" t="s">
@@ -24138,7 +25798,7 @@
       </c>
     </row>
     <row r="1897" spans="1:2">
-      <c r="A1897" s="2" t="s">
+      <c r="A1897" t="s">
         <v>2109</v>
       </c>
       <c r="B1897" t="s">
@@ -24146,7 +25806,7 @@
       </c>
     </row>
     <row r="1898" spans="1:2">
-      <c r="A1898" s="2" t="s">
+      <c r="A1898" t="s">
         <v>2110</v>
       </c>
       <c r="B1898" t="s">
@@ -24154,7 +25814,7 @@
       </c>
     </row>
     <row r="1899" spans="1:2">
-      <c r="A1899" s="2" t="s">
+      <c r="A1899" t="s">
         <v>2111</v>
       </c>
       <c r="B1899" t="s">
@@ -24162,7 +25822,7 @@
       </c>
     </row>
     <row r="1900" spans="1:2">
-      <c r="A1900" s="2" t="s">
+      <c r="A1900" t="s">
         <v>2112</v>
       </c>
       <c r="B1900" t="s">
@@ -24170,7 +25830,7 @@
       </c>
     </row>
     <row r="1901" spans="1:2">
-      <c r="A1901" s="2" t="s">
+      <c r="A1901" t="s">
         <v>2113</v>
       </c>
       <c r="B1901" t="s">
@@ -24178,7 +25838,7 @@
       </c>
     </row>
     <row r="1902" spans="1:2">
-      <c r="A1902" s="2" t="s">
+      <c r="A1902" t="s">
         <v>2114</v>
       </c>
       <c r="B1902" t="s">
@@ -24186,7 +25846,7 @@
       </c>
     </row>
     <row r="1903" spans="1:2">
-      <c r="A1903" s="2" t="s">
+      <c r="A1903" t="s">
         <v>2115</v>
       </c>
       <c r="B1903" t="s">
@@ -24194,7 +25854,7 @@
       </c>
     </row>
     <row r="1904" spans="1:2">
-      <c r="A1904" s="2" t="s">
+      <c r="A1904" t="s">
         <v>2116</v>
       </c>
       <c r="B1904" t="s">
@@ -24202,7 +25862,7 @@
       </c>
     </row>
     <row r="1905" spans="1:2">
-      <c r="A1905" s="2" t="s">
+      <c r="A1905" t="s">
         <v>2117</v>
       </c>
       <c r="B1905" t="s">
@@ -24210,7 +25870,7 @@
       </c>
     </row>
     <row r="1906" spans="1:2">
-      <c r="A1906" s="2" t="s">
+      <c r="A1906" t="s">
         <v>2118</v>
       </c>
       <c r="B1906" t="s">
@@ -24218,7 +25878,7 @@
       </c>
     </row>
     <row r="1907" spans="1:2">
-      <c r="A1907" s="2" t="s">
+      <c r="A1907" t="s">
         <v>2120</v>
       </c>
       <c r="B1907" t="s">
@@ -24226,7 +25886,7 @@
       </c>
     </row>
     <row r="1908" spans="1:2">
-      <c r="A1908" s="2" t="s">
+      <c r="A1908" t="s">
         <v>2121</v>
       </c>
       <c r="B1908" t="s">
@@ -24234,7 +25894,7 @@
       </c>
     </row>
     <row r="1909" spans="1:2">
-      <c r="A1909" s="2" t="s">
+      <c r="A1909" t="s">
         <v>2122</v>
       </c>
       <c r="B1909" t="s">
@@ -24242,1107 +25902,3784 @@
       </c>
     </row>
     <row r="1910" spans="1:2">
-      <c r="A1910" s="2" t="s">
+      <c r="A1910" t="s">
         <v>2126</v>
       </c>
       <c r="B1910" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:2">
+      <c r="A1911" t="s">
         <v>2128</v>
       </c>
-    </row>
-    <row r="1911" spans="1:2">
-      <c r="A1911" s="2" t="s">
+      <c r="B1911" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:2">
+      <c r="A1912" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1912" t="s">
         <v>2127</v>
       </c>
-      <c r="B1911" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="1912" spans="1:2">
-      <c r="A1912" s="2" t="s">
+    </row>
+    <row r="1913" spans="1:2">
+      <c r="A1913" t="s">
         <v>2130</v>
       </c>
-      <c r="B1912" t="s">
+      <c r="B1913" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:2">
+      <c r="A1914" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:2">
+      <c r="A1915" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:2">
+      <c r="A1916" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:2">
+      <c r="A1917" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:2">
+      <c r="A1918" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:2">
+      <c r="A1919" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:2">
+      <c r="A1920" t="s">
         <v>2138</v>
       </c>
-    </row>
-    <row r="1913" spans="1:2">
-      <c r="A1913" s="2" t="s">
-        <v>2131</v>
-      </c>
-      <c r="B1913" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1914" spans="1:2">
-      <c r="A1914" s="2" t="s">
-        <v>2132</v>
-      </c>
-      <c r="B1914" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1915" spans="1:2">
-      <c r="A1915" s="2" t="s">
-        <v>2133</v>
-      </c>
-      <c r="B1915" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1916" spans="1:2">
-      <c r="A1916" s="2" t="s">
-        <v>2134</v>
-      </c>
-      <c r="B1916" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1917" spans="1:2">
-      <c r="A1917" s="2" t="s">
-        <v>2135</v>
-      </c>
-      <c r="B1917" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1918" spans="1:2">
-      <c r="A1918" s="2" t="s">
-        <v>2136</v>
-      </c>
-      <c r="B1918" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1919" spans="1:2">
-      <c r="A1919" s="2" t="s">
-        <v>2137</v>
-      </c>
-      <c r="B1919" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="1920" spans="1:2">
-      <c r="A1920" s="2" t="s">
+      <c r="B1920" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:2">
+      <c r="A1921" t="s">
         <v>2139</v>
       </c>
-      <c r="B1920" t="s">
+      <c r="B1921" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:2">
+      <c r="A1922" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:2">
+      <c r="A1923" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:2">
+      <c r="A1924" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:2">
+      <c r="A1925" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:2">
+      <c r="A1926" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:2">
+      <c r="A1927" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1927" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1921" spans="1:2">
-      <c r="A1921" s="2" t="s">
-        <v>2140</v>
-      </c>
-      <c r="B1921" t="s">
+    <row r="1928" spans="1:2">
+      <c r="A1928" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1928" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1922" spans="1:2">
-      <c r="A1922" s="2" t="s">
-        <v>2141</v>
-      </c>
-      <c r="B1922" t="s">
+    <row r="1929" spans="1:2">
+      <c r="A1929" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1929" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1923" spans="1:2">
-      <c r="A1923" s="2" t="s">
-        <v>2142</v>
-      </c>
-      <c r="B1923" t="s">
+    <row r="1930" spans="1:2">
+      <c r="A1930" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1930" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1924" spans="1:2">
-      <c r="A1924" s="2" t="s">
-        <v>2143</v>
-      </c>
-      <c r="B1924" t="s">
+    <row r="1931" spans="1:2">
+      <c r="A1931" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1931" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1925" spans="1:2">
-      <c r="A1925" s="2" t="s">
-        <v>2144</v>
-      </c>
-      <c r="B1925" t="s">
+    <row r="1932" spans="1:2">
+      <c r="A1932" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1932" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="1926" spans="1:2">
-      <c r="A1926" s="2" t="s">
-        <v>2145</v>
-      </c>
-      <c r="B1926" t="s">
+    <row r="1933" spans="1:2">
+      <c r="A1933" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1933" t="s">
         <v>2147</v>
-      </c>
-    </row>
-    <row r="1927" spans="1:2">
-      <c r="A1927" s="2" t="s">
-        <v>2146</v>
-      </c>
-      <c r="B1927" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="1928" spans="1:2">
-      <c r="A1928" s="2" t="s">
-        <v>2150</v>
-      </c>
-      <c r="B1928" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1929" spans="1:2">
-      <c r="A1929" s="2" t="s">
-        <v>2151</v>
-      </c>
-      <c r="B1929" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1930" spans="1:2">
-      <c r="A1930" s="2" t="s">
-        <v>2152</v>
-      </c>
-      <c r="B1930" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1931" spans="1:2">
-      <c r="A1931" s="2" t="s">
-        <v>2153</v>
-      </c>
-      <c r="B1931" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1932" spans="1:2">
-      <c r="A1932" s="2" t="s">
-        <v>2154</v>
-      </c>
-      <c r="B1932" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1933" spans="1:2">
-      <c r="A1933" s="2" t="s">
-        <v>2155</v>
-      </c>
-      <c r="B1933" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="1934" spans="1:2">
       <c r="A1934" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:2">
+      <c r="A1935" t="s">
         <v>2156</v>
       </c>
-      <c r="B1934" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="1935" spans="1:2">
-      <c r="A1935" s="2" t="s">
+      <c r="B1935" t="s">
         <v>2157</v>
       </c>
-      <c r="B1935" t="s">
-        <v>2149</v>
-      </c>
     </row>
     <row r="1936" spans="1:2">
-      <c r="A1936" s="2" t="s">
+      <c r="A1936" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1936" t="s">
         <v>2158</v>
       </c>
-      <c r="B1936" t="s">
-        <v>2159</v>
-      </c>
     </row>
     <row r="1937" spans="1:2">
-      <c r="A1937" s="2" t="s">
+      <c r="A1937" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:2">
+      <c r="A1938" t="s">
         <v>2161</v>
       </c>
-      <c r="B1937" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="1938" spans="1:2">
-      <c r="A1938" s="2" t="s">
+      <c r="B1938" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:2">
+      <c r="A1939" t="s">
         <v>2162</v>
       </c>
-      <c r="B1938" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="1939" spans="1:2">
-      <c r="A1939" s="2" t="s">
-        <v>2163</v>
-      </c>
       <c r="B1939" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1940" spans="1:2">
       <c r="A1940" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:2">
+      <c r="A1941" t="s">
         <v>2164</v>
       </c>
-      <c r="B1940" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="1941" spans="1:2">
-      <c r="A1941" s="2" t="s">
-        <v>2165</v>
-      </c>
       <c r="B1941" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1942" spans="1:2">
       <c r="A1942" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1942" t="s">
         <v>2166</v>
       </c>
-      <c r="B1942" t="s">
-        <v>2160</v>
-      </c>
     </row>
     <row r="1943" spans="1:2">
-      <c r="A1943" s="2" t="s">
+      <c r="A1943" t="s">
         <v>2167</v>
       </c>
       <c r="B1943" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:2">
+      <c r="A1944" t="s">
         <v>2168</v>
       </c>
-    </row>
-    <row r="1944" spans="1:2">
-      <c r="A1944" s="2" t="s">
+      <c r="B1944" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:2">
+      <c r="A1945" t="s">
         <v>2169</v>
       </c>
-      <c r="B1944" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1945" spans="1:2">
-      <c r="A1945" s="2" t="s">
+      <c r="B1945" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:2">
+      <c r="A1946" t="s">
         <v>2170</v>
       </c>
-      <c r="B1945" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1946" spans="1:2">
-      <c r="A1946" s="2" t="s">
+      <c r="B1946" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:2">
+      <c r="A1947" t="s">
         <v>2171</v>
       </c>
-      <c r="B1946" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1947" spans="1:2">
-      <c r="A1947" s="2" t="s">
+      <c r="B1947" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:2">
+      <c r="A1948" t="s">
         <v>2172</v>
       </c>
-      <c r="B1947" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1948" spans="1:2">
-      <c r="A1948" s="2" t="s">
+      <c r="B1948" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:2">
+      <c r="A1949" t="s">
         <v>2173</v>
       </c>
-      <c r="B1948" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1949" spans="1:2">
-      <c r="A1949" s="2" t="s">
+      <c r="B1949" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:2">
+      <c r="A1950" t="s">
         <v>2174</v>
       </c>
-      <c r="B1949" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1950" spans="1:2">
-      <c r="A1950" s="2" t="s">
+      <c r="B1950" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:2">
+      <c r="A1951" t="s">
         <v>2175</v>
       </c>
-      <c r="B1950" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1951" spans="1:2">
-      <c r="A1951" s="2" t="s">
+      <c r="B1951" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:2">
+      <c r="A1952" t="s">
         <v>2176</v>
       </c>
-      <c r="B1951" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1952" spans="1:2">
-      <c r="A1952" s="2" t="s">
+      <c r="B1952" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:2">
+      <c r="A1953" t="s">
         <v>2177</v>
       </c>
-      <c r="B1952" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1953" spans="1:2">
-      <c r="A1953" s="2" t="s">
+      <c r="B1953" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:2">
+      <c r="A1954" t="s">
         <v>2178</v>
       </c>
-      <c r="B1953" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1954" spans="1:2">
-      <c r="A1954" s="2" t="s">
+      <c r="B1954" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:2">
+      <c r="A1955" t="s">
         <v>2179</v>
       </c>
-      <c r="B1954" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1955" spans="1:2">
-      <c r="A1955" s="2" t="s">
+      <c r="B1955" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:2">
+      <c r="A1956" t="s">
         <v>2180</v>
       </c>
-      <c r="B1955" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1956" spans="1:2">
-      <c r="A1956" s="2" t="s">
+      <c r="B1956" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:2">
+      <c r="A1957" t="s">
         <v>2181</v>
       </c>
-      <c r="B1956" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1957" spans="1:2">
-      <c r="A1957" s="2" t="s">
+      <c r="B1957" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:2">
+      <c r="A1958" t="s">
         <v>2182</v>
       </c>
-      <c r="B1957" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1958" spans="1:2">
-      <c r="A1958" s="2" t="s">
+      <c r="B1958" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:2">
+      <c r="A1959" t="s">
         <v>2183</v>
       </c>
-      <c r="B1958" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1959" spans="1:2">
-      <c r="A1959" s="2" t="s">
+      <c r="B1959" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:2">
+      <c r="A1960" t="s">
         <v>2184</v>
       </c>
-      <c r="B1959" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1960" spans="1:2">
-      <c r="A1960" s="2" t="s">
-        <v>2185</v>
-      </c>
       <c r="B1960" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="1961" spans="1:2">
       <c r="A1961" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:2">
+      <c r="A1962" t="s">
         <v>2186</v>
       </c>
-      <c r="B1961" t="s">
+      <c r="B1962" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:2">
+      <c r="A1963" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:2">
+      <c r="A1964" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:2">
+      <c r="A1965" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:2">
+      <c r="A1966" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:2">
+      <c r="A1967" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:2">
+      <c r="A1968" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:2">
+      <c r="A1969" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:2">
+      <c r="A1970" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:2">
+      <c r="A1971" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1971" t="s">
         <v>2197</v>
-      </c>
-    </row>
-    <row r="1962" spans="1:2">
-      <c r="A1962" s="2" t="s">
-        <v>2187</v>
-      </c>
-      <c r="B1962" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1963" spans="1:2">
-      <c r="A1963" s="2" t="s">
-        <v>2188</v>
-      </c>
-      <c r="B1963" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1964" spans="1:2">
-      <c r="A1964" s="2" t="s">
-        <v>2189</v>
-      </c>
-      <c r="B1964" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1965" spans="1:2">
-      <c r="A1965" s="2" t="s">
-        <v>2190</v>
-      </c>
-      <c r="B1965" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1966" spans="1:2">
-      <c r="A1966" s="2" t="s">
-        <v>2191</v>
-      </c>
-      <c r="B1966" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1967" spans="1:2">
-      <c r="A1967" s="2" t="s">
-        <v>2192</v>
-      </c>
-      <c r="B1967" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1968" spans="1:2">
-      <c r="A1968" s="2" t="s">
-        <v>2193</v>
-      </c>
-      <c r="B1968" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1969" spans="1:2">
-      <c r="A1969" s="2" t="s">
-        <v>2194</v>
-      </c>
-      <c r="B1969" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1970" spans="1:2">
-      <c r="A1970" s="2" t="s">
-        <v>2195</v>
-      </c>
-      <c r="B1970" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="1971" spans="1:2">
-      <c r="A1971" s="2" t="s">
-        <v>2196</v>
-      </c>
-      <c r="B1971" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="1972" spans="1:2">
       <c r="A1972" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:2">
+      <c r="A1973" t="s">
         <v>2200</v>
-      </c>
-      <c r="B1972" t="s">
-        <v>2199</v>
-      </c>
-    </row>
-    <row r="1973" spans="1:2">
-      <c r="A1973" s="2" t="s">
-        <v>2201</v>
       </c>
       <c r="B1973" t="s">
         <v>1775</v>
       </c>
     </row>
     <row r="1974" spans="1:2">
-      <c r="A1974" s="2" t="s">
-        <v>2202</v>
+      <c r="A1974" t="s">
+        <v>2201</v>
       </c>
       <c r="B1974" t="s">
         <v>1775</v>
       </c>
     </row>
     <row r="1975" spans="1:2">
-      <c r="A1975" s="2" t="s">
-        <v>2203</v>
+      <c r="A1975" t="s">
+        <v>2202</v>
       </c>
       <c r="B1975" t="s">
         <v>1775</v>
       </c>
     </row>
     <row r="1976" spans="1:2">
-      <c r="A1976" s="2" t="s">
-        <v>2204</v>
+      <c r="A1976" t="s">
+        <v>2203</v>
       </c>
       <c r="B1976" t="s">
         <v>1775</v>
       </c>
     </row>
     <row r="1977" spans="1:2">
-      <c r="A1977" s="2" t="s">
+      <c r="A1977" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1977" t="s">
         <v>2205</v>
       </c>
-      <c r="B1977" t="s">
-        <v>1775</v>
-      </c>
     </row>
     <row r="1978" spans="1:2">
-      <c r="A1978" s="2" t="s">
+      <c r="A1978" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1978" t="s">
         <v>2206</v>
       </c>
-      <c r="B1978" t="s">
-        <v>2207</v>
-      </c>
     </row>
     <row r="1979" spans="1:2">
-      <c r="A1979" s="2" t="s">
-        <v>2209</v>
+      <c r="A1979" t="s">
+        <v>2208</v>
       </c>
       <c r="B1979" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1980" spans="1:2">
       <c r="A1980" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:2">
+      <c r="A1981" t="s">
         <v>2210</v>
       </c>
-      <c r="B1980" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1981" spans="1:2">
-      <c r="A1981" s="2" t="s">
+      <c r="B1981" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:2">
+      <c r="A1982" t="s">
         <v>2211</v>
       </c>
-      <c r="B1981" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1982" spans="1:2">
-      <c r="A1982" s="2" t="s">
+      <c r="B1982" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:2">
+      <c r="A1983" t="s">
         <v>2212</v>
       </c>
-      <c r="B1982" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1983" spans="1:2">
-      <c r="A1983" s="2" t="s">
+      <c r="B1983" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:2">
+      <c r="A1984" t="s">
         <v>2213</v>
       </c>
-      <c r="B1983" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1984" spans="1:2">
-      <c r="A1984" s="2" t="s">
+      <c r="B1984" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:2">
+      <c r="A1985" t="s">
         <v>2214</v>
       </c>
-      <c r="B1984" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1985" spans="1:2">
-      <c r="A1985" s="2" t="s">
+      <c r="B1985" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:2">
+      <c r="A1986" t="s">
         <v>2215</v>
       </c>
-      <c r="B1985" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1986" spans="1:2">
-      <c r="A1986" s="2" t="s">
+      <c r="B1986" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:2">
+      <c r="A1987" t="s">
         <v>2216</v>
       </c>
-      <c r="B1986" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1987" spans="1:2">
-      <c r="A1987" s="2" t="s">
+      <c r="B1987" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:2">
+      <c r="A1988" t="s">
         <v>2217</v>
       </c>
-      <c r="B1987" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1988" spans="1:2">
-      <c r="A1988" s="2" t="s">
+      <c r="B1988" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:2">
+      <c r="A1989" t="s">
         <v>2218</v>
       </c>
-      <c r="B1988" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1989" spans="1:2">
-      <c r="A1989" s="2" t="s">
+      <c r="B1989" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:2">
+      <c r="A1990" t="s">
         <v>2219</v>
       </c>
-      <c r="B1989" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1990" spans="1:2">
-      <c r="A1990" s="2" t="s">
+      <c r="B1990" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:2">
+      <c r="A1991" t="s">
         <v>2220</v>
       </c>
-      <c r="B1990" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1991" spans="1:2">
-      <c r="A1991" s="2" t="s">
+      <c r="B1991" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:2">
+      <c r="A1992" t="s">
         <v>2221</v>
       </c>
-      <c r="B1991" t="s">
+      <c r="B1992" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:2">
+      <c r="A1993" t="s">
         <v>2224</v>
       </c>
-    </row>
-    <row r="1992" spans="1:2">
-      <c r="A1992" s="2" t="s">
-        <v>2222</v>
-      </c>
-      <c r="B1992" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1993" spans="1:2">
-      <c r="A1993" s="2" t="s">
+      <c r="B1993" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:2">
+      <c r="A1994" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1994" t="s">
         <v>2223</v>
       </c>
-      <c r="B1993" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="1994" spans="1:2">
-      <c r="A1994" s="2" t="s">
+    </row>
+    <row r="1995" spans="1:2">
+      <c r="A1995" t="s">
         <v>2226</v>
       </c>
-      <c r="B1994" t="s">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="1995" spans="1:2">
-      <c r="A1995" s="2" t="s">
+      <c r="B1995" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:2">
+      <c r="A1996" t="s">
         <v>2227</v>
       </c>
-      <c r="B1995" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="1996" spans="1:2">
-      <c r="A1996" s="2" t="s">
+      <c r="B1996" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:2">
+      <c r="A1997" t="s">
         <v>2228</v>
       </c>
-      <c r="B1996" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="1997" spans="1:2">
-      <c r="A1997" s="2" t="s">
-        <v>2229</v>
-      </c>
       <c r="B1997" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1998" spans="1:2">
       <c r="A1998" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:2">
+      <c r="A1999" t="s">
         <v>2230</v>
       </c>
-      <c r="B1998" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="1999" spans="1:2">
-      <c r="A1999" s="2" t="s">
-        <v>2231</v>
-      </c>
       <c r="B1999" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="2000" spans="1:2">
-      <c r="A2000" s="2" t="s">
+      <c r="A2000" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B2000" t="s">
         <v>2232</v>
       </c>
-      <c r="B2000" t="s">
-        <v>2225</v>
-      </c>
     </row>
     <row r="2001" spans="1:2">
-      <c r="A2001" s="2" t="s">
+      <c r="A2001" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:2">
+      <c r="A2002" t="s">
         <v>2235</v>
       </c>
-      <c r="B2001" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2002" spans="1:2">
-      <c r="A2002" s="2" t="s">
+      <c r="B2002" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:2">
+      <c r="A2003" t="s">
         <v>2236</v>
       </c>
-      <c r="B2002" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2003" spans="1:2">
-      <c r="A2003" s="2" t="s">
+      <c r="B2003" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:2">
+      <c r="A2004" t="s">
         <v>2237</v>
       </c>
-      <c r="B2003" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2004" spans="1:2">
-      <c r="A2004" s="2" t="s">
+      <c r="B2004" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:2">
+      <c r="A2005" t="s">
         <v>2238</v>
       </c>
-      <c r="B2004" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2005" spans="1:2">
-      <c r="A2005" s="2" t="s">
+      <c r="B2005" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:2">
+      <c r="A2006" t="s">
         <v>2239</v>
       </c>
-      <c r="B2005" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2006" spans="1:2">
-      <c r="A2006" s="2" t="s">
+      <c r="B2006" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:2">
+      <c r="A2007" t="s">
         <v>2240</v>
       </c>
-      <c r="B2006" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2007" spans="1:2">
-      <c r="A2007" s="2" t="s">
+      <c r="B2007" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:2">
+      <c r="A2008" t="s">
         <v>2241</v>
       </c>
-      <c r="B2007" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2008" spans="1:2">
-      <c r="A2008" s="2" t="s">
+      <c r="B2008" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:2">
+      <c r="A2009" t="s">
         <v>2242</v>
       </c>
-      <c r="B2008" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2009" spans="1:2">
-      <c r="A2009" s="2" t="s">
+      <c r="B2009" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:2">
+      <c r="A2010" t="s">
         <v>2243</v>
       </c>
-      <c r="B2009" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2010" spans="1:2">
-      <c r="A2010" s="2" t="s">
+      <c r="B2010" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:2">
+      <c r="A2011" t="s">
         <v>2244</v>
       </c>
-      <c r="B2010" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2011" spans="1:2">
-      <c r="A2011" s="2" t="s">
+      <c r="B2011" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:2">
+      <c r="A2012" t="s">
         <v>2245</v>
       </c>
-      <c r="B2011" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2012" spans="1:2">
-      <c r="A2012" s="2" t="s">
+      <c r="B2012" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:2">
+      <c r="A2013" t="s">
         <v>2246</v>
       </c>
-      <c r="B2012" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2013" spans="1:2">
-      <c r="A2013" s="2" t="s">
+      <c r="B2013" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:2">
+      <c r="A2014" t="s">
         <v>2247</v>
       </c>
-      <c r="B2013" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2014" spans="1:2">
-      <c r="A2014" s="2" t="s">
+      <c r="B2014" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:2">
+      <c r="A2015" t="s">
         <v>2248</v>
       </c>
-      <c r="B2014" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2015" spans="1:2">
-      <c r="A2015" s="2" t="s">
+      <c r="B2015" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:2">
+      <c r="A2016" t="s">
         <v>2249</v>
       </c>
-      <c r="B2015" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2016" spans="1:2">
-      <c r="A2016" s="2" t="s">
+      <c r="B2016" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:2">
+      <c r="A2017" t="s">
         <v>2250</v>
       </c>
-      <c r="B2016" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2017" spans="1:2">
-      <c r="A2017" s="2" t="s">
+      <c r="B2017" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:2">
+      <c r="A2018" t="s">
         <v>2251</v>
       </c>
-      <c r="B2017" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2018" spans="1:2">
-      <c r="A2018" s="2" t="s">
-        <v>2252</v>
-      </c>
       <c r="B2018" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="2019" spans="1:2">
       <c r="A2019" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:2">
+      <c r="A2020" t="s">
         <v>2253</v>
       </c>
-      <c r="B2019" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2020" spans="1:2">
-      <c r="A2020" s="2" t="s">
+      <c r="B2020" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:2">
+      <c r="A2021" t="s">
         <v>2254</v>
       </c>
-      <c r="B2020" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2021" spans="1:2">
-      <c r="A2021" s="2" t="s">
+      <c r="B2021" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:2">
+      <c r="A2022" t="s">
         <v>2255</v>
       </c>
-      <c r="B2021" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2022" spans="1:2">
-      <c r="A2022" s="2" t="s">
+      <c r="B2022" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:2">
+      <c r="A2023" t="s">
         <v>2256</v>
       </c>
-      <c r="B2022" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2023" spans="1:2">
-      <c r="A2023" s="2" t="s">
+      <c r="B2023" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:2">
+      <c r="A2024" t="s">
         <v>2257</v>
       </c>
-      <c r="B2023" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2024" spans="1:2">
-      <c r="A2024" s="2" t="s">
+      <c r="B2024" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:2">
+      <c r="A2025" t="s">
         <v>2258</v>
       </c>
-      <c r="B2024" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="2025" spans="1:2">
-      <c r="A2025" s="2" t="s">
+      <c r="B2025" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:2">
+      <c r="A2026" t="s">
         <v>2259</v>
       </c>
-      <c r="B2025" t="s">
+      <c r="B2026" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:2">
+      <c r="A2027" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:2">
+      <c r="A2028" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:2">
+      <c r="A2029" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:2">
+      <c r="A2030" t="s">
         <v>2264</v>
       </c>
-    </row>
-    <row r="2026" spans="1:2">
-      <c r="A2026" s="2" t="s">
-        <v>2260</v>
-      </c>
-      <c r="B2026" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="2027" spans="1:2">
-      <c r="A2027" s="2" t="s">
-        <v>2261</v>
-      </c>
-      <c r="B2027" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="2028" spans="1:2">
-      <c r="A2028" s="2" t="s">
-        <v>2262</v>
-      </c>
-      <c r="B2028" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="2029" spans="1:2">
-      <c r="A2029" s="2" t="s">
-        <v>2263</v>
-      </c>
-      <c r="B2029" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="2030" spans="1:2">
-      <c r="A2030" s="2" t="s">
+      <c r="B2030" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:2">
+      <c r="A2031" t="s">
         <v>2265</v>
       </c>
-      <c r="B2030" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2031" spans="1:2">
-      <c r="A2031" s="2" t="s">
+      <c r="B2031" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:2">
+      <c r="A2032" t="s">
         <v>2266</v>
       </c>
-      <c r="B2031" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2032" spans="1:2">
-      <c r="A2032" s="2" t="s">
+      <c r="B2032" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:2">
+      <c r="A2033" t="s">
         <v>2267</v>
       </c>
-      <c r="B2032" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2033" spans="1:2">
-      <c r="A2033" s="2" t="s">
+      <c r="B2033" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:2">
+      <c r="A2034" t="s">
         <v>2268</v>
       </c>
-      <c r="B2033" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2034" spans="1:2">
-      <c r="A2034" s="2" t="s">
-        <v>2269</v>
-      </c>
       <c r="B2034" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="2035" spans="1:2">
       <c r="A2035" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:2">
+      <c r="A2036" t="s">
         <v>2270</v>
       </c>
-      <c r="B2035" t="s">
+      <c r="B2036" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:2">
+      <c r="A2037" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:2">
+      <c r="A2038" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:2">
+      <c r="A2039" t="s">
         <v>2275</v>
       </c>
-    </row>
-    <row r="2036" spans="1:2">
-      <c r="A2036" s="2" t="s">
-        <v>2271</v>
-      </c>
-      <c r="B2036" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2037" spans="1:2">
-      <c r="A2037" s="2" t="s">
-        <v>2272</v>
-      </c>
-      <c r="B2037" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2038" spans="1:2">
-      <c r="A2038" s="2" t="s">
-        <v>2273</v>
-      </c>
-      <c r="B2038" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="2039" spans="1:2">
-      <c r="A2039" s="2" t="s">
+      <c r="B2039" t="s">
         <v>2274</v>
       </c>
-      <c r="B2039" t="s">
-        <v>2275</v>
-      </c>
     </row>
     <row r="2040" spans="1:2">
-      <c r="A2040" s="2" t="s">
+      <c r="A2040" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:2">
+      <c r="A2041" t="s">
         <v>2277</v>
       </c>
-      <c r="B2040" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2041" spans="1:2">
-      <c r="A2041" s="2" t="s">
+      <c r="B2041" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:2">
+      <c r="A2042" t="s">
         <v>2278</v>
       </c>
-      <c r="B2041" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2042" spans="1:2">
-      <c r="A2042" s="2" t="s">
+      <c r="B2042" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:2">
+      <c r="A2043" t="s">
         <v>2279</v>
       </c>
-      <c r="B2042" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2043" spans="1:2">
-      <c r="A2043" s="2" t="s">
+      <c r="B2043" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:2">
+      <c r="A2044" t="s">
         <v>2280</v>
       </c>
-      <c r="B2043" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2044" spans="1:2">
-      <c r="A2044" s="2" t="s">
+      <c r="B2044" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:2">
+      <c r="A2045" t="s">
         <v>2281</v>
       </c>
-      <c r="B2044" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2045" spans="1:2">
-      <c r="A2045" s="2" t="s">
+      <c r="B2045" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:2">
+      <c r="A2046" t="s">
         <v>2282</v>
-      </c>
-      <c r="B2045" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="2046" spans="1:2">
-      <c r="A2046" s="2" t="s">
-        <v>2283</v>
       </c>
       <c r="B2046" t="s">
         <v>1688</v>
       </c>
     </row>
-    <row r="2047" spans="1:2">
-      <c r="A2047" s="2" t="s">
-        <v>2284</v>
-      </c>
-      <c r="B2047" t="s">
-        <v>1688</v>
+    <row r="2049" spans="1:2">
+      <c r="A2049" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:2">
+      <c r="A2050" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:2">
+      <c r="A2051" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:2">
+      <c r="A2052" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:2">
+      <c r="A2053" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:2">
+      <c r="A2054" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:2">
+      <c r="A2055" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:2">
+      <c r="A2056" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:2">
+      <c r="A2057" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:2">
+      <c r="A2058" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:2">
+      <c r="A2059" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:2">
+      <c r="A2060" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:2">
+      <c r="A2061" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:2">
+      <c r="A2062" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:2">
+      <c r="A2063" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:2">
+      <c r="A2064" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:2">
+      <c r="A2065" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:2">
+      <c r="A2066" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:2">
+      <c r="A2067" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:2">
+      <c r="A2068" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:2">
+      <c r="A2069" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:2">
+      <c r="A2070" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:2">
+      <c r="A2071" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:2">
+      <c r="A2072" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:2">
+      <c r="A2073" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:2">
+      <c r="A2074" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:2">
+      <c r="A2075" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:2">
+      <c r="A2076" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:2">
+      <c r="A2077" s="2" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:2">
+      <c r="A2078" s="2" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:2">
+      <c r="A2079" s="2" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:2">
+      <c r="A2080" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:2">
+      <c r="A2081" s="2" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:2">
+      <c r="A2082" s="2" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:2">
+      <c r="A2083" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:2">
+      <c r="A2084" s="2" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:2">
+      <c r="A2085" s="2" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:2">
+      <c r="A2086" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:2">
+      <c r="A2087" s="2" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:2">
+      <c r="A2088" s="2" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:2">
+      <c r="A2089" s="2" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:2">
+      <c r="A2090" s="2" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:2">
+      <c r="A2091" s="2" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:2">
+      <c r="A2092" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:2">
+      <c r="A2093" s="2" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:2">
+      <c r="A2094" s="2" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:2">
+      <c r="A2095" s="2" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:2">
+      <c r="A2096" s="2" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:2">
+      <c r="A2097" s="2" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:2">
+      <c r="A2098" s="2" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:2">
+      <c r="A2099" s="2" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:2">
+      <c r="A2100" s="2" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:2">
+      <c r="A2101" s="2" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:2">
+      <c r="A2102" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:2">
+      <c r="A2103" s="2" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:2">
+      <c r="A2104" s="2" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:2">
+      <c r="A2105" s="2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:2">
+      <c r="A2106" s="2" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:2">
+      <c r="A2107" s="2" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:2">
+      <c r="A2108" s="2" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:2">
+      <c r="A2109" s="2" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:2">
+      <c r="A2110" s="2" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:2">
+      <c r="A2111" s="2" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:2">
+      <c r="A2112" s="2" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:2">
+      <c r="A2113" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:2">
+      <c r="A2114" s="2" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:2">
+      <c r="A2115" s="2" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:2">
+      <c r="A2116" s="2" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:2">
+      <c r="A2117" s="2" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:2">
+      <c r="A2118" s="2" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:2">
+      <c r="A2119" s="2" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:2">
+      <c r="A2120" s="2" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:2">
+      <c r="A2121" s="2" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:2">
+      <c r="A2122" s="2" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:2">
+      <c r="A2123" s="2" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:2">
+      <c r="A2124" s="2" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:2">
+      <c r="A2125" s="2" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:2">
+      <c r="A2126" s="2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:2">
+      <c r="A2127" s="2" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:2">
+      <c r="A2128" s="2" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:2">
+      <c r="A2129" s="2" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:2">
+      <c r="A2130" s="2" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:2">
+      <c r="A2131" s="2" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:2">
+      <c r="A2132" s="2" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:2">
+      <c r="A2133" s="2" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:2">
+      <c r="A2134" s="2" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:2">
+      <c r="A2135" s="2" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:2">
+      <c r="A2136" s="2" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:2">
+      <c r="A2137" s="2" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:2">
+      <c r="A2138" s="2" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:2">
+      <c r="A2139" s="2" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:2">
+      <c r="A2140" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:2">
+      <c r="A2141" s="2" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:2">
+      <c r="A2142" s="2" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:2">
+      <c r="A2143" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:2">
+      <c r="A2144" s="2" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:2">
+      <c r="A2145" s="2" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:2">
+      <c r="A2146" s="2" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:2">
+      <c r="A2147" s="2" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:2">
+      <c r="A2148" s="2" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:2">
+      <c r="A2149" s="2" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:2">
+      <c r="A2150" s="2" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:2">
+      <c r="A2151" s="2" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:2">
+      <c r="A2152" s="2" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:2">
+      <c r="A2153" s="2" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:2">
+      <c r="A2154" s="2" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:2">
+      <c r="A2155" s="2" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:2">
+      <c r="A2156" s="2" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:2">
+      <c r="A2157" s="2" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:2">
+      <c r="A2158" s="2" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:2">
+      <c r="A2159" s="2" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:2">
+      <c r="A2160" s="2" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:2">
+      <c r="A2161" s="2" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B2161" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:2">
+      <c r="A2162" s="2" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B2162" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:2">
+      <c r="A2163" s="2" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B2163" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:2">
+      <c r="A2164" s="2" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B2164" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:2">
+      <c r="A2165" s="2" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B2165" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:2">
+      <c r="A2166" s="2" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:2">
+      <c r="A2167" s="2" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B2167" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:2">
+      <c r="A2168" s="2" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B2168" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:2">
+      <c r="A2169" s="2" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B2169" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:2">
+      <c r="A2170" s="2" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B2170" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:2">
+      <c r="A2171" s="2" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B2171" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:2">
+      <c r="A2172" s="2" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B2172" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:2">
+      <c r="A2173" s="2" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:2">
+      <c r="A2174" s="2" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:2">
+      <c r="A2175" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:2">
+      <c r="A2176" s="2" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:2">
+      <c r="A2177" s="2" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:2">
+      <c r="A2178" s="2" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:2">
+      <c r="A2179" s="2" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:2">
+      <c r="A2180" s="2" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:2">
+      <c r="A2181" s="2" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:2">
+      <c r="A2182" s="2" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:2">
+      <c r="A2183" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:2">
+      <c r="A2184" s="2" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:2">
+      <c r="A2185" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:2">
+      <c r="A2186" s="2" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:2">
+      <c r="A2187" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:2">
+      <c r="A2188" s="2" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:2">
+      <c r="A2189" s="2" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:2">
+      <c r="A2190" s="2" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:2">
+      <c r="A2191" s="2" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:2">
+      <c r="A2192" s="2" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:2">
+      <c r="A2193" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:2">
+      <c r="A2194" s="2" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:2">
+      <c r="A2195" s="2" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:2">
+      <c r="A2196" s="2" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:2">
+      <c r="A2197" s="2" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:2">
+      <c r="A2198" s="2" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:2">
+      <c r="A2199" s="2" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:2">
+      <c r="A2200" s="2" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:2">
+      <c r="A2201" s="2" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:2">
+      <c r="A2202" s="2" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:2">
+      <c r="A2203" s="2" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:2">
+      <c r="A2204" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:2">
+      <c r="A2205" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:2">
+      <c r="A2206" s="2" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:2">
+      <c r="A2207" s="2" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:2">
+      <c r="A2208" s="2" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:2">
+      <c r="A2209" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:2">
+      <c r="A2210" s="2" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:2">
+      <c r="A2211" s="2" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:2">
+      <c r="A2212" s="2" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:2">
+      <c r="A2213" s="2" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:2">
+      <c r="A2214" s="2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:2">
+      <c r="A2215" s="2" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:2">
+      <c r="A2216" s="2" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:2">
+      <c r="A2217" s="2" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:2">
+      <c r="A2218" s="2" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:2">
+      <c r="A2219" s="2" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:2">
+      <c r="A2220" s="2" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:2">
+      <c r="A2221" s="2" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:2">
+      <c r="A2222" s="2" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:2">
+      <c r="A2223" s="2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:2">
+      <c r="A2224" s="2" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:2">
+      <c r="A2225" s="2" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:2">
+      <c r="A2226" s="2" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:2">
+      <c r="A2227" s="2" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:2">
+      <c r="A2228" s="2" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:2">
+      <c r="A2229" s="2" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:2">
+      <c r="A2230" s="2" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:2">
+      <c r="A2231" s="2" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:2">
+      <c r="A2232" s="2" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:2">
+      <c r="A2233" s="2" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:2">
+      <c r="A2234" s="2" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:2">
+      <c r="A2235" s="2" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:2">
+      <c r="A2236" s="2" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:2">
+      <c r="A2237" s="2" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:2">
+      <c r="A2238" s="2" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:2">
+      <c r="A2239" s="2" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:2">
+      <c r="A2240" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:2">
+      <c r="A2241" s="2" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:2">
+      <c r="A2242" s="2" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:2">
+      <c r="A2243" s="2" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:2">
+      <c r="A2244" s="2" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:2">
+      <c r="A2245" s="2" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:2">
+      <c r="A2246" s="2" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:2">
+      <c r="A2247" s="2" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:2">
+      <c r="A2248" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:2">
+      <c r="A2249" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:2">
+      <c r="A2250" s="2" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:2">
+      <c r="A2251" s="2" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:2">
+      <c r="A2252" s="2" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:2">
+      <c r="A2253" s="2" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:2">
+      <c r="A2254" s="2" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:2">
+      <c r="A2255" s="2" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:2">
+      <c r="A2256" s="2" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:2">
+      <c r="A2257" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:2">
+      <c r="A2258" s="2" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:2">
+      <c r="A2259" s="2" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:2">
+      <c r="A2260" s="2" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:2">
+      <c r="A2261" s="2" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:2">
+      <c r="A2262" s="2" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:2">
+      <c r="A2263" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:2">
+      <c r="A2264" s="2" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:2">
+      <c r="A2265" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:2">
+      <c r="A2266" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:2">
+      <c r="A2267" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:2">
+      <c r="A2268" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:2">
+      <c r="A2269" s="2" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:2">
+      <c r="A2270" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:2">
+      <c r="A2271" s="2" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:2">
+      <c r="A2272" s="2" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:2">
+      <c r="A2273" s="2" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:2">
+      <c r="A2274" s="2" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:2">
+      <c r="A2275" s="2" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:2">
+      <c r="A2276" s="2" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:2">
+      <c r="A2277" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:2">
+      <c r="A2278" s="2" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:2">
+      <c r="A2279" s="2" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:2">
+      <c r="A2280" s="2" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:2">
+      <c r="A2281" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:2">
+      <c r="A2282" s="2" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:2">
+      <c r="A2283" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:2">
+      <c r="A2284" s="2" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:2">
+      <c r="A2285" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:2">
+      <c r="A2286" s="2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:2">
+      <c r="A2287" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:2">
+      <c r="A2288" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:2">
+      <c r="A2289" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:2">
+      <c r="A2290" s="2" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:2">
+      <c r="A2291" s="2" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:2">
+      <c r="A2292" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:2">
+      <c r="A2293" s="2" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:2">
+      <c r="A2294" s="2" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:2">
+      <c r="A2295" s="2" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:2">
+      <c r="A2296" s="2" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:2">
+      <c r="A2297" s="2" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:2">
+      <c r="A2298" s="2" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:2">
+      <c r="A2299" s="2" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:2">
+      <c r="A2300" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:2">
+      <c r="A2301" s="2" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:2">
+      <c r="A2302" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:2">
+      <c r="A2303" s="2" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:2">
+      <c r="A2304" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:2">
+      <c r="A2305" s="2" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:2">
+      <c r="A2306" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:2">
+      <c r="A2307" s="2" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:2">
+      <c r="A2308" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:2">
+      <c r="A2309" s="2" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:2">
+      <c r="A2310" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:2">
+      <c r="A2311" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:2">
+      <c r="A2312" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:2">
+      <c r="A2313" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:2">
+      <c r="A2314" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:2">
+      <c r="A2315" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:2">
+      <c r="A2316" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:2">
+      <c r="A2317" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:2">
+      <c r="A2318" s="2" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:2">
+      <c r="A2319" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:2">
+      <c r="A2320" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:2">
+      <c r="A2321" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:2">
+      <c r="A2322" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:2">
+      <c r="A2323" s="2" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:2">
+      <c r="A2324" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:2">
+      <c r="A2325" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:2">
+      <c r="A2326" s="2" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:2">
+      <c r="A2327" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:2">
+      <c r="A2328" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:2">
+      <c r="A2329" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:2">
+      <c r="A2330" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:2">
+      <c r="A2331" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:2">
+      <c r="A2332" s="2" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:2">
+      <c r="A2333" s="2" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:2">
+      <c r="A2334" s="2" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:2">
+      <c r="A2335" s="2" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:2">
+      <c r="A2336" s="2" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:2">
+      <c r="A2337" s="2" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:2">
+      <c r="A2338" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:2">
+      <c r="A2339" s="2" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:2">
+      <c r="A2340" s="2" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:2">
+      <c r="A2341" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:2">
+      <c r="A2342" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:2">
+      <c r="A2343" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:2">
+      <c r="A2344" s="2" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:2">
+      <c r="A2345" s="2" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2345" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:2">
+      <c r="A2346" s="2" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:2">
+      <c r="A2347" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:2">
+      <c r="A2348" s="2" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:2">
+      <c r="A2349" s="2" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B2349" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:2">
+      <c r="A2350" s="2" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:2">
+      <c r="A2351" s="2" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:2">
+      <c r="A2352" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:2">
+      <c r="A2353" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B2353" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:2">
+      <c r="A2354" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:2">
+      <c r="A2355" s="2" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:2">
+      <c r="A2356" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:2">
+      <c r="A2357" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:2">
+      <c r="A2358" s="2" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:2">
+      <c r="A2359" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B2359" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:2">
+      <c r="A2360" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:2">
+      <c r="A2361" s="2" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B2361" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:2">
+      <c r="A2362" s="2" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:2">
+      <c r="A2363" s="2" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B2363" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:2">
+      <c r="A2364" s="2" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:2">
+      <c r="A2365" s="2" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B2365" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:2">
+      <c r="A2366" s="2" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:2">
+      <c r="A2367" s="2" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B2367" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:2">
+      <c r="A2368" s="2" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B2368" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:2">
+      <c r="A2369" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B2369" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:2">
+      <c r="A2370" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B2370" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:2">
+      <c r="A2371" s="2" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B2371" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:2">
+      <c r="A2372" s="2" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B2372" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:2">
+      <c r="A2373" s="2" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B2373" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:2">
+      <c r="A2374" s="2" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:2">
+      <c r="A2375" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:2">
+      <c r="A2376" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:2">
+      <c r="A2377" s="2" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B2377" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:2">
+      <c r="A2378" s="2" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B2378" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:2">
+      <c r="A2379" s="2" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2379" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:2">
+      <c r="A2380" s="2" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B2380" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:2">
+      <c r="A2381" s="2" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B2381" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:2">
+      <c r="A2382" s="2" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B2382" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:2">
+      <c r="A2383" s="2" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B2383" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:2">
+      <c r="A2384" s="2" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B2384" t="s">
+        <v>2701</v>
       </c>
     </row>
   </sheetData>
